--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -487,8 +487,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>需求 713594979；只读</t>
@@ -501,7 +499,6 @@
           <t>活动入口_001</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>2</v>
       </c>
@@ -510,8 +507,6 @@
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>只切 tab + 数活动卡，不改数据</t>
@@ -537,8 +532,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>先摆正起点</t>
@@ -551,7 +544,6 @@
           <t>搜索页_001</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>2</v>
       </c>
@@ -565,7 +557,6 @@
           <t>test</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>关键词只能字母/数字/下划线/点/连字符（adb 不支持中文输入）</t>
@@ -578,7 +569,6 @@
           <t>搜索页_001</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>3</v>
       </c>
@@ -592,7 +582,6 @@
           <t>wx-input.search-input</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>搜索页的真实输入框</t>
@@ -605,7 +594,6 @@
           <t>搜索页_001</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>4</v>
       </c>
@@ -614,8 +602,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>把手机交还给下一条用例</t>
@@ -641,8 +627,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>先摆正起点。注意：首页轮播里没有「答题」卡时，打开这一步会记成「跳过」</t>
@@ -655,7 +639,6 @@
           <t>答题页_001</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>2</v>
       </c>
@@ -664,8 +647,6 @@
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>只读：不选选项、不提交</t>
@@ -678,7 +659,6 @@
           <t>答题页_001</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>3</v>
       </c>
@@ -692,7 +672,6 @@
           <t>.activity-quiz-page</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>答题页根容器，只在答题页出现</t>
@@ -705,7 +684,6 @@
           <t>答题页_001</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>4</v>
       </c>
@@ -719,7 +697,6 @@
           <t>答对最多可赢积分</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>吸顶栏文案（需求 713594985）</t>
@@ -732,7 +709,6 @@
           <t>答题页_001</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>5</v>
       </c>
@@ -741,9 +717,97 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
+        <is>
+          <t>把手机交还给下一条用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>学习中心_001</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>学习中心能进到专栏列表</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>先摆正起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>学习中心_001</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>打开学习中心专栏</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>需求「小程序-学习中心重组」：压铸百科/课程/专栏合并到学习中心</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>学习中心_001</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>热门专栏</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>「热门专栏」是专栏列表页独有的标记（页面对象里实测出来的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>学习中心_001</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>把手机交还给下一条用例</t>
         </is>
@@ -797,8 +861,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>自导航到「有问必答」首页（幂等；当前在二级页时会自动点返回）。用例第一步建议都用它</t>
@@ -811,8 +873,6 @@
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>点底部 tab「我的」，进入用户中心</t>
@@ -825,8 +885,6 @@
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>进学习中心，并切到「专栏」列表</t>
@@ -844,7 +902,6 @@
           <t>关键词</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>点搜索栏进搜索页并输入关键词。注意：只能是字母/数字/下划线/点/连字符（adb 不支持中文输入）</t>
@@ -857,8 +914,6 @@
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
@@ -876,7 +931,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
@@ -889,8 +943,6 @@
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>点返回按钮退回上一页（会校验页面确实变了）</t>
@@ -908,7 +960,6 @@
           <t>毫秒</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
@@ -926,7 +977,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
@@ -944,7 +994,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>断言页面上看不见这段文字</t>
@@ -962,7 +1011,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>断言页面上找得到这个选择器，例如 .search-container</t>
@@ -997,8 +1045,6 @@
           <t>检查答题页符合需求</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于**一道题**的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
@@ -1011,8 +1057,6 @@
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
@@ -1043,9 +1087,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1116,9 +1157,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -1146,9 +1184,6 @@
           <t xml:space="preserve">   · 「打开答题活动」只打开页面，不选选项、不提交（选选项会消耗答题机会）。</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -30,13 +30,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <b val="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -184,6 +177,9 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -487,155 +483,156 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1048,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -1582,10 +1579,495 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>搜索消失_001</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>进搜索页后首页筛选 tab 消失</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>搜索消失_001</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>最新提问</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>搜索消失_001</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>打开搜索并输入</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>搜索消失_001</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>检查文字不显示</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>最新提问</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>搜索消失_001</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>框架自检：把表格能用的动作全跑一遍</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>这条是给框架做体检的，业务上没用，可随时删</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>打印页面文字</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>不知道检查什么文字时，先跑它看日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>切换筛选tab</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>切完会验证真的选中了</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>切换筛选tab</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>最新提问</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>检查元素不存在</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>.activity-quiz-page</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>首页上不该有答题页根容器</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>滑动</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>在首页上滑（首页有可滚动内容）；滑不动它会自己报错，不会假装成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>滑动</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>再滑回顶部 —— 不然搜索栏被顶出屏幕，下一步会点空</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>点选择器</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>.search-container</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>按选择器点进搜索页</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>9</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>打开搜索并输入</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>关键词只能字母/数字</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>10</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>检查输入框的值</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>wx-input.search-input</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>读出来再比较</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>11</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>返回上一页</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>12</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>13</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>打开学习中心专栏</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>14</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>切换学习中心顶部tab</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>压铸百科</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>15</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>切换学习中心顶部tab</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>专栏</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>点第一张专栏</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>进详情页</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>17</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>返回上一页</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>18</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>='动作清单'!$A$2:$A$15</formula1>
+      <formula1>='动作清单'!$A$2:$A$24</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -1601,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1611,232 +2093,391 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>动作</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>自导航到「有问必答」首页（幂等；当前在二级页时会自动点返回）。用例第一步建议都用它</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>点底部 tab「我的」，进入用户中心</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>进学习中心，并切到「专栏」列表</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>点搜索栏进搜索页并输入关键词。注意：只能是字母/数字/下划线/点/连字符（adb 不支持中文输入）</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>点文字</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>点返回按钮退回上一页（会校验页面确实变了）</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>等待</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>毫秒</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>检查文字不显示</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>断言页面上看不见这段文字</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>检查元素数量</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>期望数量</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>检查答题页符合需求</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于**一道题**的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>打印页面文字</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>点选择器</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>选择器</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>按选择器点第一处元素（比按文字点更准：文字有重名时用它），例如 .search-container</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>滑动</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>次数</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>向上滑动屏幕，默认 1 次、最多 10 次。列表要滑到底才看得到的东西用它</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>切换筛选tab</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>tab名</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>切换学习中心顶部tab</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>tab名</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>切学习中心顶部那排 tab（切完会验证真的选中了）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>点第一张专栏</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>在学习中心的专栏列表里点第一张卡，进它的详情页</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>检查输入框的值</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>选择器</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>期望值</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>检查文字出现次数</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>期望次数</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>检查元素不存在</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>选择器</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
         </is>
       </c>
     </row>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -2064,10 +2064,285 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>搜索空态_001</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>搜索零结果时出现 AI 引导（需求 713582841）</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>先摆正起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>搜索空态_001</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>打开搜索并输入</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>zzz9999</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>实测：这个词是零结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>搜索空态_001</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>执行搜索</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>不提交的话停在「搜索历史」面板，看不到空态</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>搜索空态_001</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>没有找到相关内容？让小铸手帮你答</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>需求原话，实机核对过逐字一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>搜索空态_001</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>问小铸手</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>引导按钮文案</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>搜索空态_001</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>把手机交还给下一条</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>搜索空态_002</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>有结果时不出现 AI 引导（需求 713582841 的反向）</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>先摆正起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>搜索空态_002</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>打开搜索并输入</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>qqqqq</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>实测：这个词有结果（所以不该出现引导）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>搜索空态_002</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>执行搜索</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>搜索空态_002</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>4</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>全部回答</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>先确认真到了结果页，再断言「没有引导」才有意义</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>搜索空态_002</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>5</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>检查文字不显示</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>问小铸手</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>需求：有结果搜索不出现引导模块</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>搜索空态_002</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>6</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>把手机交还给下一条</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>='动作清单'!$A$2:$A$24</formula1>
+      <formula1>='动作清单'!$A$2:$A$25</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -2083,7 +2358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2098,384 +2373,494 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>动作</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
         <is>
           <t>自导航到「有问必答」首页（幂等；当前在二级页时会自动点返回）。用例第一步建议都用它</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
         <is>
           <t>点底部 tab「我的」，进入用户中心</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
         <is>
           <t>进学习中心，并切到「专栏」列表</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
         <is>
           <t>点搜索栏进搜索页并输入关键词。注意：只能是字母/数字/下划线/点/连字符（adb 不支持中文输入）</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>执行搜索</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>在搜索页按回车把搜索跑起来（只读：只是查一次）。不执行的话停在「搜索历史」面板，看不到结果页/空态</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
         <is>
           <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>点文字</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
         <is>
           <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
         <is>
           <t>点返回按钮退回上一页（会校验页面确实变了）</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>等待</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>毫秒</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
         <is>
           <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
         <is>
           <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>检查文字不显示</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
         <is>
           <t>断言页面上看不见这段文字</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
         <is>
           <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>检查元素数量</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>期望数量</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>检查答题页符合需求</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
         <is>
           <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于**一道题**的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
         <is>
           <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
         <is>
           <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>点选择器</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
         <is>
           <t>按选择器点第一处元素（比按文字点更准：文字有重名时用它），例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>滑动</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>次数</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>向上滑动屏幕，默认 1 次、最多 10 次。列表要滑到底才看得到的东西用它</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>切换筛选tab</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
         <is>
           <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>切换学习中心顶部tab</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
         <is>
           <t>切学习中心顶部那排 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>点第一张专栏</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
         <is>
           <t>在学习中心的专栏列表里点第一张卡，进它的详情页</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>检查输入框的值</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>期望值</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>检查文字出现次数</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>期望次数</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>检查元素不存在</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
         <is>
           <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
         </is>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -2339,10 +2339,95 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>回到顶部_001</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>积分商城的回到顶部按钮符合需求（需求 713582097）</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>先摆正起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>回到顶部_001</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>打开积分商城</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>用户中心 -&gt; 积分商城（二级页，没有底部 tab 栏）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>回到顶部_001</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>检查回到顶部按钮</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>需求口径：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>回到顶部_001</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>把手机交还给下一条</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>='动作清单'!$A$2:$A$25</formula1>
+      <formula1>='动作清单'!$A$2:$A$27</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -2358,7 +2443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D197"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2436,431 +2521,565 @@
     <row r="62"/>
     <row r="63"/>
     <row r="64"/>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171">
+      <c r="A171" t="inlineStr">
         <is>
           <t>动作</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D171" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="172">
+      <c r="A172" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr">
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
         <is>
           <t>自导航到「有问必答」首页（幂等；当前在二级页时会自动点返回）。用例第一步建议都用它</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="173">
+      <c r="A173" t="inlineStr">
         <is>
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr">
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
         <is>
           <t>点底部 tab「我的」，进入用户中心</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>打开积分商城</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>从用户中心点「积分商城」进商城首页（已在则原地不动）。积分商城是二级页，没有底部 tab 栏</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
         <is>
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr">
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
         <is>
           <t>进学习中心，并切到「专栏」列表</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="176">
+      <c r="A176" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr">
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
         <is>
           <t>点搜索栏进搜索页并输入关键词。注意：只能是字母/数字/下划线/点/连字符（adb 不支持中文输入）</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="177">
+      <c r="A177" t="inlineStr">
         <is>
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr">
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
         <is>
           <t>在搜索页按回车把搜索跑起来（只读：只是查一次）。不执行的话停在「搜索历史」面板，看不到结果页/空态</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="178">
+      <c r="A178" t="inlineStr">
         <is>
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr">
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
         <is>
           <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="179">
+      <c r="A179" t="inlineStr">
         <is>
           <t>点文字</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr">
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
         <is>
           <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="180">
+      <c r="A180" t="inlineStr">
         <is>
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr">
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
         <is>
           <t>点返回按钮退回上一页（会校验页面确实变了）</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="181">
+      <c r="A181" t="inlineStr">
         <is>
           <t>等待</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>毫秒</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr">
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
         <is>
           <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="182">
+      <c r="A182" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr">
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
         <is>
           <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="183">
+      <c r="A183" t="inlineStr">
         <is>
           <t>检查文字不显示</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr">
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
         <is>
           <t>断言页面上看不见这段文字</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="184">
+      <c r="A184" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr">
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
         <is>
           <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="185">
+      <c r="A185" t="inlineStr">
         <is>
           <t>检查元素数量</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C185" t="inlineStr">
         <is>
           <t>期望数量</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D185" t="inlineStr">
         <is>
           <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="186">
+      <c r="A186" t="inlineStr">
         <is>
           <t>检查答题页符合需求</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr">
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
         <is>
           <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于**一道题**的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="187">
+      <c r="A187" t="inlineStr">
         <is>
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr">
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
         <is>
           <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>检查回到顶部按钮</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
         <is>
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr">
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
         <is>
           <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="190">
+      <c r="A190" t="inlineStr">
         <is>
           <t>点选择器</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr">
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
         <is>
           <t>按选择器点第一处元素（比按文字点更准：文字有重名时用它），例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="191">
+      <c r="A191" t="inlineStr">
         <is>
           <t>滑动</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B191" t="inlineStr">
         <is>
           <t>次数</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C191" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D191" t="inlineStr">
         <is>
           <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="192">
+      <c r="A192" t="inlineStr">
         <is>
           <t>切换筛选tab</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B192" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr">
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
         <is>
           <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="193">
+      <c r="A193" t="inlineStr">
         <is>
           <t>切换学习中心顶部tab</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr">
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
         <is>
           <t>切学习中心顶部那排 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="194">
+      <c r="A194" t="inlineStr">
         <is>
           <t>点第一张专栏</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr">
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
         <is>
           <t>在学习中心的专栏列表里点第一张卡，进它的详情页</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="195">
+      <c r="A195" t="inlineStr">
         <is>
           <t>检查输入框的值</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B195" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C195" t="inlineStr">
         <is>
           <t>期望值</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D195" t="inlineStr">
         <is>
           <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="196">
+      <c r="A196" t="inlineStr">
         <is>
           <t>检查文字出现次数</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B196" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C196" t="inlineStr">
         <is>
           <t>期望次数</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D196" t="inlineStr">
         <is>
           <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="197">
+      <c r="A197" t="inlineStr">
         <is>
           <t>检查元素不存在</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B197" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr">
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
         <is>
           <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
         </is>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -2424,10 +2424,191 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>搜索话题_001</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>热门话题有 5 条且点第一条能进话题结果页（需求 713129788）</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>先摆正起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>搜索话题_001</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>打开搜索页</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>只进搜索页、不输入关键词（输入的话热门话题会被建议列表顶掉）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>搜索话题_001</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>检查元素数量</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>.hot-topics .inline-flex</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>需求：热门话题显示管理后台的前 5 个（区块标题是图片，所以只能按结构数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>搜索话题_001</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>点第一个热门话题</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>按位置点，不按名字点（话题名会变）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>搜索话题_001</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="n">
+        <v>5</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>最新发布</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>话题结果页的排序 tab（实测：这个页面不是「全部回答」那套）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>搜索话题_001</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="n">
+        <v>6</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>最多点赞</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>同上，两个一起断言更稳</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>搜索话题_001</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="n">
+        <v>7</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>把手机交还给下一条。注：「结果是否真的按该话题筛过」要读页面标题才能验，留给以后的代码用例</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>='动作清单'!$A$2:$A$27</formula1>
+      <formula1>='动作清单'!$A$2:$A$29</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -2443,7 +2624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D197"/>
+  <dimension ref="A1:D226"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2458,628 +2639,449 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171">
-      <c r="A171" t="inlineStr">
+    <row r="198">
+      <c r="A198" t="inlineStr">
         <is>
           <t>动作</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B198" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="C198" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="D198" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
+    <row r="199">
+      <c r="A199" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr"/>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" t="inlineStr">
+      <c r="D199" t="inlineStr">
         <is>
           <t>自导航到「有问必答」首页（幂等；当前在二级页时会自动点返回）。用例第一步建议都用它</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
+    <row r="200">
+      <c r="A200" t="inlineStr">
         <is>
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr"/>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr">
+      <c r="D200" t="inlineStr">
         <is>
           <t>点底部 tab「我的」，进入用户中心</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
+    <row r="201">
+      <c r="A201" t="inlineStr">
         <is>
           <t>打开积分商城</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr"/>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr">
+      <c r="D201" t="inlineStr">
         <is>
           <t>从用户中心点「积分商城」进商城首页（已在则原地不动）。积分商城是二级页，没有底部 tab 栏</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
+    <row r="202">
+      <c r="A202" t="inlineStr">
         <is>
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr"/>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr">
+      <c r="D202" t="inlineStr">
         <is>
           <t>进学习中心，并切到「专栏」列表</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
+    <row r="203">
+      <c r="A203" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B203" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr">
+      <c r="D203" t="inlineStr">
         <is>
           <t>点搜索栏进搜索页并输入关键词。注意：只能是字母/数字/下划线/点/连字符（adb 不支持中文输入）</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>打开搜索页</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>只进搜索页、不输入关键词（搜索页上能看到「搜索历史」和「热门话题」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>点第一个热门话题</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>点搜索页「热门话题」里的第 1 条，跳转到该话题的搜索结果页（需求 713129788）</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
         <is>
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr"/>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr">
+      <c r="D206" t="inlineStr">
         <is>
           <t>在搜索页按回车把搜索跑起来（只读：只是查一次）。不执行的话停在「搜索历史」面板，看不到结果页/空态</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
+    <row r="207">
+      <c r="A207" t="inlineStr">
         <is>
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr"/>
-      <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr">
+      <c r="D207" t="inlineStr">
         <is>
           <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
+    <row r="208">
+      <c r="A208" t="inlineStr">
         <is>
           <t>点文字</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr"/>
-      <c r="D179" t="inlineStr">
+      <c r="D208" t="inlineStr">
         <is>
           <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
+    <row r="209">
+      <c r="A209" t="inlineStr">
         <is>
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr"/>
-      <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr">
+      <c r="D209" t="inlineStr">
         <is>
           <t>点返回按钮退回上一页（会校验页面确实变了）</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
+    <row r="210">
+      <c r="A210" t="inlineStr">
         <is>
           <t>等待</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>毫秒</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr"/>
-      <c r="D181" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
+    <row r="211">
+      <c r="A211" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B211" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr">
+      <c r="D211" t="inlineStr">
         <is>
           <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
+    <row r="212">
+      <c r="A212" t="inlineStr">
         <is>
           <t>检查文字不显示</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B212" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr">
+      <c r="D212" t="inlineStr">
         <is>
           <t>断言页面上看不见这段文字</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
+    <row r="213">
+      <c r="A213" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
+    <row r="214">
+      <c r="A214" t="inlineStr">
         <is>
           <t>检查元素数量</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
+      <c r="C214" t="inlineStr">
         <is>
           <t>期望数量</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="D214" t="inlineStr">
         <is>
           <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
+    <row r="215">
+      <c r="A215" t="inlineStr">
         <is>
           <t>检查答题页符合需求</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr"/>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr">
+      <c r="D215" t="inlineStr">
         <is>
           <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于**一道题**的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
+    <row r="216">
+      <c r="A216" t="inlineStr">
         <is>
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr"/>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr">
+      <c r="D216" t="inlineStr">
         <is>
           <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
+    <row r="217">
+      <c r="A217" t="inlineStr">
         <is>
           <t>检查回到顶部按钮</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr"/>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr">
+      <c r="D217" t="inlineStr">
         <is>
           <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
+    <row r="218">
+      <c r="A218" t="inlineStr">
         <is>
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr"/>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr">
+      <c r="D218" t="inlineStr">
         <is>
           <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
+    <row r="219">
+      <c r="A219" t="inlineStr">
         <is>
           <t>点选择器</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>按选择器点第一处元素（比按文字点更准：文字有重名时用它），例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
+    <row r="220">
+      <c r="A220" t="inlineStr">
         <is>
           <t>滑动</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B220" t="inlineStr">
         <is>
           <t>次数</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
+      <c r="C220" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
+    <row r="221">
+      <c r="A221" t="inlineStr">
         <is>
           <t>切换筛选tab</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B221" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
+    <row r="222">
+      <c r="A222" t="inlineStr">
         <is>
           <t>切换学习中心顶部tab</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B222" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr">
+      <c r="D222" t="inlineStr">
         <is>
           <t>切学习中心顶部那排 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
+    <row r="223">
+      <c r="A223" t="inlineStr">
         <is>
           <t>点第一张专栏</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>在学习中心的专栏列表里点第一张卡，进它的详情页</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
+    <row r="224">
+      <c r="A224" t="inlineStr">
         <is>
           <t>检查输入框的值</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B224" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="C224" t="inlineStr">
         <is>
           <t>期望值</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D224" t="inlineStr">
         <is>
           <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
+    <row r="225">
+      <c r="A225" t="inlineStr">
         <is>
           <t>检查文字出现次数</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="B225" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
+      <c r="C225" t="inlineStr">
         <is>
           <t>期望次数</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="D225" t="inlineStr">
         <is>
           <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
+    <row r="226">
+      <c r="A226" t="inlineStr">
         <is>
           <t>检查元素不存在</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
         </is>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -2443,8 +2443,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>先摆正起点</t>
@@ -2457,7 +2455,6 @@
           <t>搜索话题_001</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
         <v>2</v>
       </c>
@@ -2466,8 +2463,6 @@
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>只进搜索页、不输入关键词（输入的话热门话题会被建议列表顶掉）</t>
@@ -2480,7 +2475,6 @@
           <t>搜索话题_001</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
         <v>3</v>
       </c>
@@ -2511,7 +2505,6 @@
           <t>搜索话题_001</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
         <v>4</v>
       </c>
@@ -2520,8 +2513,6 @@
           <t>点第一个热门话题</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>按位置点，不按名字点（话题名会变）</t>
@@ -2534,7 +2525,6 @@
           <t>搜索话题_001</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
         <v>5</v>
       </c>
@@ -2548,7 +2538,6 @@
           <t>最新发布</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>话题结果页的排序 tab（实测：这个页面不是「全部回答」那套）</t>
@@ -2561,7 +2550,6 @@
           <t>搜索话题_001</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
         <v>6</v>
       </c>
@@ -2575,7 +2563,6 @@
           <t>最多点赞</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>同上，两个一起断言更稳</t>
@@ -2588,7 +2575,6 @@
           <t>搜索话题_001</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
         <v>7</v>
       </c>
@@ -2597,11 +2583,159 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>把手机交还给下一条。注：「结果是否真的按该话题筛过」要读页面标题才能验，留给以后的代码用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>帖子主页按钮_001</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>帖子详情页点「主页」按钮回到首页（需求 713256065）</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>先摆正起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>帖子主页按钮_001</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>打开第一个帖子</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>点首页信息流第一张帖子卡片进详情（只读）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>帖子主页按钮_001</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>点主页按钮</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>详情页导航栏上那个主页图标（.icon-base-home）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>帖子主页按钮_001</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="n">
+        <v>4</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>最新提问</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>回到首页信息流的判据（那排筛选 tab）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>帖子主页按钮_001</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="n">
+        <v>5</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>检查元素存在</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>.search-container</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>首页独有的搜索栏，双保险</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>帖子主页按钮_001</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="n">
+        <v>6</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>把手机交还给下一条</t>
         </is>
       </c>
     </row>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -2608,8 +2608,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>先摆正起点</t>
@@ -2622,7 +2620,6 @@
           <t>帖子主页按钮_001</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
         <v>2</v>
       </c>
@@ -2631,8 +2628,6 @@
           <t>打开第一个帖子</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>点首页信息流第一张帖子卡片进详情（只读）</t>
@@ -2645,7 +2640,6 @@
           <t>帖子主页按钮_001</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
         <v>3</v>
       </c>
@@ -2654,8 +2648,6 @@
           <t>点主页按钮</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>详情页导航栏上那个主页图标（.icon-base-home）</t>
@@ -2668,7 +2660,6 @@
           <t>帖子主页按钮_001</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
         <v>4</v>
       </c>
@@ -2682,7 +2673,6 @@
           <t>最新提问</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>回到首页信息流的判据（那排筛选 tab）</t>
@@ -2695,7 +2685,6 @@
           <t>帖子主页按钮_001</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
         <v>5</v>
       </c>
@@ -2709,7 +2698,6 @@
           <t>.search-container</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>首页独有的搜索栏，双保险</t>
@@ -2722,7 +2710,6 @@
           <t>帖子主页按钮_001</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
         <v>6</v>
       </c>
@@ -2731,9 +2718,80 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
+        <is>
+          <t>把手机交还给下一条</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>首页tab顺序_001</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>首页筛选 tab 顺序与默认选中符合需求（需求 713341876）</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>先摆正起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>首页tab顺序_001</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>检查首页tab顺序</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>需求：最新提问和推荐互换顺序 + 最新提问为默认展示（置顶帖那半句依赖数据，暂不覆盖）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>首页tab顺序_001</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="n">
+        <v>3</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
         <is>
           <t>把手机交还给下一条</t>
         </is>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -2743,8 +2743,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>先摆正起点</t>
@@ -2757,7 +2755,6 @@
           <t>首页tab顺序_001</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
         <v>2</v>
       </c>
@@ -2766,8 +2763,6 @@
           <t>检查首页tab顺序</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>需求：最新提问和推荐互换顺序 + 最新提问为默认展示（置顶帖那半句依赖数据，暂不覆盖）</t>
@@ -2780,7 +2775,6 @@
           <t>首页tab顺序_001</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
         <v>3</v>
       </c>
@@ -2789,8 +2783,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>把手机交还给下一条</t>
@@ -2800,7 +2792,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>='动作清单'!$A$2:$A$29</formula1>
+      <formula1>='动作清单'!$A$2:$A$36</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -2816,7 +2808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D226"/>
+  <dimension ref="A1:D262"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2831,451 +2823,824 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
     </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227">
+      <c r="A227" t="inlineStr">
         <is>
           <t>动作</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="B227" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
+      <c r="C227" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
+    <row r="228">
+      <c r="A228" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
         <is>
           <t>自导航到「有问必答」首页（幂等；当前在二级页时会自动点返回）。用例第一步建议都用它</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
+    <row r="229">
+      <c r="A229" t="inlineStr">
         <is>
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
         <is>
           <t>点底部 tab「我的」，进入用户中心</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
+    <row r="230">
+      <c r="A230" t="inlineStr">
         <is>
           <t>打开积分商城</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
         <is>
           <t>从用户中心点「积分商城」进商城首页（已在则原地不动）。积分商城是二级页，没有底部 tab 栏</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
+    <row r="231">
+      <c r="A231" t="inlineStr">
         <is>
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
         <is>
           <t>进学习中心，并切到「专栏」列表</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
+    <row r="232">
+      <c r="A232" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B232" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
         <is>
           <t>点搜索栏进搜索页并输入关键词。注意：只能是字母/数字/下划线/点/连字符（adb 不支持中文输入）</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
+    <row r="233">
+      <c r="A233" t="inlineStr">
         <is>
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
         <is>
           <t>只进搜索页、不输入关键词（搜索页上能看到「搜索历史」和「热门话题」）</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
+    <row r="234">
+      <c r="A234" t="inlineStr">
         <is>
           <t>点第一个热门话题</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="B234" t="inlineStr"/>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
         <is>
           <t>点搜索页「热门话题」里的第 1 条，跳转到该话题的搜索结果页（需求 713129788）</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>打开第一个帖子</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>在首页信息流点第一张帖子卡片，进帖子详情页（只读：不点赞、不评论）</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>点主页按钮</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>点二级页导航栏上的「主页」图标回到首页（需求 713256065 的返回首页那半句）</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
         <is>
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="B237" t="inlineStr"/>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
         <is>
           <t>在搜索页按回车把搜索跑起来（只读：只是查一次）。不执行的话停在「搜索历史」面板，看不到结果页/空态</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
+    <row r="238">
+      <c r="A238" t="inlineStr">
         <is>
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="B238" t="inlineStr"/>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
         <is>
           <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
+    <row r="239">
+      <c r="A239" t="inlineStr">
         <is>
           <t>点文字</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B239" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
         <is>
           <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
+    <row r="240">
+      <c r="A240" t="inlineStr">
         <is>
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
         <is>
           <t>点返回按钮退回上一页（会校验页面确实变了）</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
+    <row r="241">
+      <c r="A241" t="inlineStr">
         <is>
           <t>等待</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B241" t="inlineStr">
         <is>
           <t>毫秒</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
         <is>
           <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
+    <row r="242">
+      <c r="A242" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B242" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
         <is>
           <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
+    <row r="243">
+      <c r="A243" t="inlineStr">
         <is>
           <t>检查文字不显示</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B243" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
         <is>
           <t>断言页面上看不见这段文字</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
+    <row r="244">
+      <c r="A244" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B244" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
         <is>
           <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
+    <row r="245">
+      <c r="A245" t="inlineStr">
         <is>
           <t>检查元素数量</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B245" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
+      <c r="C245" t="inlineStr">
         <is>
           <t>期望数量</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="D245" t="inlineStr">
         <is>
           <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
+    <row r="246">
+      <c r="A246" t="inlineStr">
         <is>
           <t>检查答题页符合需求</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="B246" t="inlineStr"/>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
         <is>
           <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于**一道题**的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
+    <row r="247">
+      <c r="A247" t="inlineStr">
         <is>
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
         <is>
           <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>检查首页tab顺序</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
         <is>
           <t>检查回到顶部按钮</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="B249" t="inlineStr"/>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
         <is>
           <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
+    <row r="250">
+      <c r="A250" t="inlineStr">
         <is>
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="B250" t="inlineStr"/>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
         <is>
           <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
+    <row r="251">
+      <c r="A251" t="inlineStr">
         <is>
           <t>点选择器</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B251" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
         <is>
           <t>按选择器点第一处元素（比按文字点更准：文字有重名时用它），例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
+    <row r="252">
+      <c r="A252" t="inlineStr">
         <is>
           <t>滑动</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B252" t="inlineStr">
         <is>
           <t>次数</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
+      <c r="C252" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D252" t="inlineStr">
         <is>
           <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
+    <row r="253">
+      <c r="A253" t="inlineStr">
         <is>
           <t>切换筛选tab</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B253" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
         <is>
           <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
+    <row r="254">
+      <c r="A254" t="inlineStr">
         <is>
           <t>切换学习中心顶部tab</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B254" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
         <is>
           <t>切学习中心顶部那排 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
+    <row r="255">
+      <c r="A255" t="inlineStr">
         <is>
           <t>点第一张专栏</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="B255" t="inlineStr"/>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
         <is>
           <t>在学习中心的专栏列表里点第一张卡，进它的详情页</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
+    <row r="256">
+      <c r="A256" t="inlineStr">
         <is>
           <t>检查输入框的值</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B256" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
+      <c r="C256" t="inlineStr">
         <is>
           <t>期望值</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="D256" t="inlineStr">
         <is>
           <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
+    <row r="257">
+      <c r="A257" t="inlineStr">
         <is>
           <t>检查文字出现次数</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B257" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
+      <c r="C257" t="inlineStr">
         <is>
           <t>期望次数</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D257" t="inlineStr">
         <is>
           <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
+    <row r="258">
+      <c r="A258" t="inlineStr">
         <is>
           <t>检查元素不存在</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
         <is>
           <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>逐题作答</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr"/>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、**不写库**，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>提交答卷</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>点答题页的提交按钮 —— **会真的写数据**。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>复位答题记录</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>活动名</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：**默认只预览、不删**，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>检查答题记录数</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>活动名</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>期望条数</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>读数据库，断言这个活动的**提交记录**正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关</t>
         </is>
       </c>
     </row>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -2789,10 +2789,95 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>案例库_001</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>案例库列表页：介绍banner在分类上方 + 卡片右下角是复制图标和复制数（需求 713381608）</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>先摆正起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>案例库_001</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>入口 = 底部 tab「设计专区」（2026/10/12 找到的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>案例库_001</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>3</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>检查案例库列表符合需求</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>需求 713381608：分类上方有介绍 banner；卡片右下角由评论图标+评论数改成复制图标+复制数</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>案例库_001</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>4</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>把手机交还给下一条用例</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>='动作清单'!$A$2:$A$36</formula1>
+      <formula1>='动作清单'!$A$2:$A$38</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -2808,7 +2893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D262"/>
+  <dimension ref="A1:D300"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3048,599 +3133,663 @@
     <row r="224"/>
     <row r="225"/>
     <row r="226"/>
-    <row r="227">
-      <c r="A227" t="inlineStr">
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263">
+      <c r="A263" t="inlineStr">
         <is>
           <t>动作</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="C263" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D263" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
+    <row r="264">
+      <c r="A264" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr"/>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr">
+      <c r="B264" t="inlineStr"/>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
         <is>
           <t>自导航到「有问必答」首页（幂等；当前在二级页时会自动点返回）。用例第一步建议都用它</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
+    <row r="265">
+      <c r="A265" t="inlineStr">
         <is>
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr"/>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr">
+      <c r="B265" t="inlineStr"/>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
         <is>
           <t>点底部 tab「我的」，进入用户中心</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
+    <row r="266">
+      <c r="A266" t="inlineStr">
         <is>
           <t>打开积分商城</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr"/>
-      <c r="C230" t="inlineStr"/>
-      <c r="D230" t="inlineStr">
+      <c r="B266" t="inlineStr"/>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
         <is>
           <t>从用户中心点「积分商城」进商城首页（已在则原地不动）。积分商城是二级页，没有底部 tab 栏</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
+    <row r="267">
+      <c r="A267" t="inlineStr">
         <is>
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr"/>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr">
+      <c r="B267" t="inlineStr"/>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
         <is>
           <t>进学习中心，并切到「专栏」列表</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
+    <row r="268">
+      <c r="A268" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B268" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr"/>
-      <c r="D232" t="inlineStr">
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
         <is>
           <t>点搜索栏进搜索页并输入关键词。注意：只能是字母/数字/下划线/点/连字符（adb 不支持中文输入）</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
+    <row r="269">
+      <c r="A269" t="inlineStr">
         <is>
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr"/>
-      <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr">
+      <c r="B269" t="inlineStr"/>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
         <is>
           <t>只进搜索页、不输入关键词（搜索页上能看到「搜索历史」和「热门话题」）</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
+    <row r="270">
+      <c r="A270" t="inlineStr">
         <is>
           <t>点第一个热门话题</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr"/>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr">
+      <c r="B270" t="inlineStr"/>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
         <is>
           <t>点搜索页「热门话题」里的第 1 条，跳转到该话题的搜索结果页（需求 713129788）</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
+    <row r="271">
+      <c r="A271" t="inlineStr">
         <is>
           <t>打开第一个帖子</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr"/>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr">
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
         <is>
           <t>在首页信息流点第一张帖子卡片，进帖子详情页（只读：不点赞、不评论）</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
+    <row r="272">
+      <c r="A272" t="inlineStr">
         <is>
           <t>点主页按钮</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr"/>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr">
+      <c r="B272" t="inlineStr"/>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
         <is>
           <t>点二级页导航栏上的「主页」图标回到首页（需求 713256065 的返回首页那半句）</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
+    <row r="273">
+      <c r="A273" t="inlineStr">
         <is>
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr"/>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr">
+      <c r="B273" t="inlineStr"/>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
         <is>
           <t>在搜索页按回车把搜索跑起来（只读：只是查一次）。不执行的话停在「搜索历史」面板，看不到结果页/空态</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
+    <row r="274">
+      <c r="A274" t="inlineStr">
         <is>
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr"/>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr">
+      <c r="B274" t="inlineStr"/>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
         <is>
           <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
+    <row r="275">
+      <c r="A275" t="inlineStr">
         <is>
           <t>点文字</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B275" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr">
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
         <is>
           <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
+    <row r="276">
+      <c r="A276" t="inlineStr">
         <is>
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr"/>
-      <c r="C240" t="inlineStr"/>
-      <c r="D240" t="inlineStr">
+      <c r="B276" t="inlineStr"/>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
         <is>
           <t>点返回按钮退回上一页（会校验页面确实变了）</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
+    <row r="277">
+      <c r="A277" t="inlineStr">
         <is>
           <t>等待</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B277" t="inlineStr">
         <is>
           <t>毫秒</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr"/>
-      <c r="D241" t="inlineStr">
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
         <is>
           <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
+    <row r="278">
+      <c r="A278" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B278" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr"/>
-      <c r="D242" t="inlineStr">
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
         <is>
           <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
+    <row r="279">
+      <c r="A279" t="inlineStr">
         <is>
           <t>检查文字不显示</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="B279" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr"/>
-      <c r="D243" t="inlineStr">
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
         <is>
           <t>断言页面上看不见这段文字</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
+    <row r="280">
+      <c r="A280" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B280" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr"/>
-      <c r="D244" t="inlineStr">
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
         <is>
           <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
+    <row r="281">
+      <c r="A281" t="inlineStr">
         <is>
           <t>检查元素数量</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B281" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
+      <c r="C281" t="inlineStr">
         <is>
           <t>期望数量</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="D281" t="inlineStr">
         <is>
           <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
+    <row r="282">
+      <c r="A282" t="inlineStr">
         <is>
           <t>检查答题页符合需求</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr"/>
-      <c r="C246" t="inlineStr"/>
-      <c r="D246" t="inlineStr">
+      <c r="B282" t="inlineStr"/>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
         <is>
           <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于**一道题**的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
+    <row r="283">
+      <c r="A283" t="inlineStr">
         <is>
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr"/>
-      <c r="C247" t="inlineStr"/>
-      <c r="D247" t="inlineStr">
+      <c r="B283" t="inlineStr"/>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
         <is>
           <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
+    <row r="284">
+      <c r="A284" t="inlineStr">
         <is>
           <t>检查首页tab顺序</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr"/>
-      <c r="C248" t="inlineStr"/>
-      <c r="D248" t="inlineStr">
+      <c r="B284" t="inlineStr"/>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
         <is>
           <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
+    <row r="285">
+      <c r="A285" t="inlineStr">
         <is>
           <t>检查回到顶部按钮</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr"/>
-      <c r="C249" t="inlineStr"/>
-      <c r="D249" t="inlineStr">
+      <c r="B285" t="inlineStr"/>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
         <is>
           <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
+    <row r="286">
+      <c r="A286" t="inlineStr">
         <is>
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr"/>
-      <c r="C250" t="inlineStr"/>
-      <c r="D250" t="inlineStr">
+      <c r="B286" t="inlineStr"/>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
         <is>
           <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
+    <row r="287">
+      <c r="A287" t="inlineStr">
         <is>
           <t>点选择器</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B287" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr"/>
-      <c r="D251" t="inlineStr">
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
         <is>
           <t>按选择器点第一处元素（比按文字点更准：文字有重名时用它），例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
+    <row r="288">
+      <c r="A288" t="inlineStr">
         <is>
           <t>滑动</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B288" t="inlineStr">
         <is>
           <t>次数</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
+      <c r="C288" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="D288" t="inlineStr">
         <is>
           <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
+    <row r="289">
+      <c r="A289" t="inlineStr">
         <is>
           <t>切换筛选tab</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B289" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr"/>
-      <c r="D253" t="inlineStr">
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
         <is>
           <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
+    <row r="290">
+      <c r="A290" t="inlineStr">
         <is>
           <t>切换学习中心顶部tab</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B290" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr"/>
-      <c r="D254" t="inlineStr">
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
         <is>
           <t>切学习中心顶部那排 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
+    <row r="291">
+      <c r="A291" t="inlineStr">
         <is>
           <t>点第一张专栏</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr"/>
-      <c r="C255" t="inlineStr"/>
-      <c r="D255" t="inlineStr">
+      <c r="B291" t="inlineStr"/>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
         <is>
           <t>在学习中心的专栏列表里点第一张卡，进它的详情页</t>
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
+    <row r="292">
+      <c r="A292" t="inlineStr">
         <is>
           <t>检查输入框的值</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B292" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
+      <c r="C292" t="inlineStr">
         <is>
           <t>期望值</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
+      <c r="D292" t="inlineStr">
         <is>
           <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
+    <row r="293">
+      <c r="A293" t="inlineStr">
         <is>
           <t>检查文字出现次数</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B293" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
+      <c r="C293" t="inlineStr">
         <is>
           <t>期望次数</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
+      <c r="D293" t="inlineStr">
         <is>
           <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
+    <row r="294">
+      <c r="A294" t="inlineStr">
         <is>
           <t>检查元素不存在</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B294" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr">
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
         <is>
           <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
+    <row r="295">
+      <c r="A295" t="inlineStr">
         <is>
           <t>逐题作答</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr"/>
-      <c r="C259" t="inlineStr"/>
-      <c r="D259" t="inlineStr">
+      <c r="B295" t="inlineStr"/>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
         <is>
           <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、**不写库**，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
+    <row r="296">
+      <c r="A296" t="inlineStr">
         <is>
           <t>提交答卷</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr"/>
-      <c r="C260" t="inlineStr"/>
-      <c r="D260" t="inlineStr">
+      <c r="B296" t="inlineStr"/>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
         <is>
           <t>点答题页的提交按钮 —— **会真的写数据**。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
+    <row r="297">
+      <c r="A297" t="inlineStr">
         <is>
           <t>复位答题记录</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B297" t="inlineStr">
         <is>
           <t>活动名</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr"/>
-      <c r="D261" t="inlineStr">
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
         <is>
           <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：**默认只预览、不删**，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
+    <row r="298">
+      <c r="A298" t="inlineStr">
         <is>
           <t>检查答题记录数</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B298" t="inlineStr">
         <is>
           <t>活动名</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
+      <c r="C298" t="inlineStr">
         <is>
           <t>期望条数</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
+      <c r="D298" t="inlineStr">
         <is>
           <t>读数据库，断言这个活动的**提交记录**正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr"/>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>打开案例库列表（**底部 tab「设计专区」打开就是它**，这是 2026/10/12 才找到的入口；页面顶部还有一排 tab：仿真案例库 / 压铸护航服务）</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>检查案例库列表符合需求</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr"/>
+      <c r="C300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>按需求 713381608 校验案例库列表页：① 分类**上方**有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「**复制图标 + 复制数**」，且整页找不到评论图标。只读</t>
         </is>
       </c>
     </row>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>案例库列表页：介绍banner在分类上方 + 卡片右下角是复制图标和复制数（需求 713381608）</t>
+          <t>案例库：介绍banner在分类上方、点它进长图；列表显示复制数；详情页评论区是「全部评论」（需求 713381608）</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2808,6 +2808,8 @@
           <t>回到首页</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>先摆正起点</t>
@@ -2820,6 +2822,7 @@
           <t>案例库_001</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
         <v>2</v>
       </c>
@@ -2828,9 +2831,11 @@
           <t>打开案例库</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>入口 = 底部 tab「设计专区」（2026/10/12 找到的）</t>
+          <t>入口 = 底部 tab「设计专区」</t>
         </is>
       </c>
     </row>
@@ -2840,6 +2845,7 @@
           <t>案例库_001</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
         <v>3</v>
       </c>
@@ -2848,9 +2854,11 @@
           <t>检查案例库列表符合需求</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>需求 713381608：分类上方有介绍 banner；卡片右下角由评论图标+评论数改成复制图标+复制数</t>
+          <t>分类上方有介绍 banner；卡片右下角是复制图标 + 复制数</t>
         </is>
       </c>
     </row>
@@ -2860,15 +2868,133 @@
           <t>案例库_001</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
         <v>4</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>打开案例库介绍长图</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>点首页那张 banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>案例库_001</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="n">
+        <v>5</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>检查案例库介绍长图符合需求</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>需求要求这一页是单张长图</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>案例库_001</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="n">
+        <v>6</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>返回上一页</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>从长图退回列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>案例库_001</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="n">
+        <v>7</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>打开第一个案例</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>列表第一张卡片（只读）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>案例库_001</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="n">
+        <v>8</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>检查案例详情页符合需求</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>评论区标题「全部评论」；底部无复制数/评论数图标</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>案例库_001</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="n">
+        <v>9</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
         <is>
           <t>把手机交还给下一条用例</t>
         </is>
@@ -2908,267 +3034,6 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
@@ -3197,8 +3062,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr"/>
-      <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
           <t>自导航到「有问必答」首页（幂等；当前在二级页时会自动点返回）。用例第一步建议都用它</t>
@@ -3211,8 +3074,6 @@
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr"/>
-      <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
           <t>点底部 tab「我的」，进入用户中心</t>
@@ -3225,8 +3086,6 @@
           <t>打开积分商城</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr"/>
-      <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
           <t>从用户中心点「积分商城」进商城首页（已在则原地不动）。积分商城是二级页，没有底部 tab 栏</t>
@@ -3239,8 +3098,6 @@
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr"/>
-      <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
           <t>进学习中心，并切到「专栏」列表</t>
@@ -3258,7 +3115,6 @@
           <t>关键词</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
           <t>点搜索栏进搜索页并输入关键词。注意：只能是字母/数字/下划线/点/连字符（adb 不支持中文输入）</t>
@@ -3271,8 +3127,6 @@
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr"/>
-      <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
           <t>只进搜索页、不输入关键词（搜索页上能看到「搜索历史」和「热门话题」）</t>
@@ -3285,8 +3139,6 @@
           <t>点第一个热门话题</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr"/>
-      <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
           <t>点搜索页「热门话题」里的第 1 条，跳转到该话题的搜索结果页（需求 713129788）</t>
@@ -3299,8 +3151,6 @@
           <t>打开第一个帖子</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr"/>
-      <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
           <t>在首页信息流点第一张帖子卡片，进帖子详情页（只读：不点赞、不评论）</t>
@@ -3313,8 +3163,6 @@
           <t>点主页按钮</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr"/>
-      <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
           <t>点二级页导航栏上的「主页」图标回到首页（需求 713256065 的返回首页那半句）</t>
@@ -3327,8 +3175,6 @@
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr"/>
-      <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
           <t>在搜索页按回车把搜索跑起来（只读：只是查一次）。不执行的话停在「搜索历史」面板，看不到结果页/空态</t>
@@ -3341,8 +3187,6 @@
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr"/>
-      <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
           <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
@@ -3360,7 +3204,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
           <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
@@ -3373,8 +3216,6 @@
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr"/>
-      <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
           <t>点返回按钮退回上一页（会校验页面确实变了）</t>
@@ -3392,7 +3233,6 @@
           <t>毫秒</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
           <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
@@ -3410,7 +3250,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
           <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
@@ -3428,7 +3267,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
           <t>断言页面上看不见这段文字</t>
@@ -3446,7 +3284,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
           <t>断言页面上找得到这个选择器，例如 .search-container</t>
@@ -3481,8 +3318,6 @@
           <t>检查答题页符合需求</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr"/>
-      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
           <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于**一道题**的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
@@ -3495,8 +3330,6 @@
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr"/>
-      <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
           <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
@@ -3509,8 +3342,6 @@
           <t>检查首页tab顺序</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr"/>
-      <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
           <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
@@ -3523,8 +3354,6 @@
           <t>检查回到顶部按钮</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr"/>
-      <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
           <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
@@ -3537,8 +3366,6 @@
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr"/>
-      <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
           <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
@@ -3556,7 +3383,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
           <t>按选择器点第一处元素（比按文字点更准：文字有重名时用它），例如 .search-container</t>
@@ -3596,7 +3422,6 @@
           <t>tab名</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
           <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
@@ -3614,7 +3439,6 @@
           <t>tab名</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
           <t>切学习中心顶部那排 tab（切完会验证真的选中了）</t>
@@ -3627,8 +3451,6 @@
           <t>点第一张专栏</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr"/>
-      <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
           <t>在学习中心的专栏列表里点第一张卡，进它的详情页</t>
@@ -3690,7 +3512,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
           <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
@@ -3703,8 +3524,6 @@
           <t>逐题作答</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr"/>
-      <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
           <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、**不写库**，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
@@ -3717,8 +3536,6 @@
           <t>提交答卷</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr"/>
-      <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
           <t>点答题页的提交按钮 —— **会真的写数据**。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
@@ -3736,7 +3553,6 @@
           <t>活动名</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
           <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：**默认只预览、不删**，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行</t>
@@ -3771,8 +3587,6 @@
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr"/>
-      <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
           <t>打开案例库列表（**底部 tab「设计专区」打开就是它**，这是 2026/10/12 才找到的入口；页面顶部还有一排 tab：仿真案例库 / 压铸护航服务）</t>
@@ -3785,8 +3599,6 @@
           <t>检查案例库列表符合需求</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr"/>
-      <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
           <t>按需求 713381608 校验案例库列表页：① 分类**上方**有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「**复制图标 + 复制数**」，且整页找不到评论图标。只读</t>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -2808,8 +2808,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>先摆正起点</t>
@@ -2822,7 +2820,6 @@
           <t>案例库_001</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
         <v>2</v>
       </c>
@@ -2831,8 +2828,6 @@
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>入口 = 底部 tab「设计专区」</t>
@@ -2845,7 +2840,6 @@
           <t>案例库_001</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
         <v>3</v>
       </c>
@@ -2854,8 +2848,6 @@
           <t>检查案例库列表符合需求</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>分类上方有介绍 banner；卡片右下角是复制图标 + 复制数</t>
@@ -2868,7 +2860,6 @@
           <t>案例库_001</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
         <v>4</v>
       </c>
@@ -2877,8 +2868,6 @@
           <t>打开案例库介绍长图</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>点首页那张 banner</t>
@@ -2891,7 +2880,6 @@
           <t>案例库_001</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
         <v>5</v>
       </c>
@@ -2900,8 +2888,6 @@
           <t>检查案例库介绍长图符合需求</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>需求要求这一页是单张长图</t>
@@ -2914,7 +2900,6 @@
           <t>案例库_001</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
         <v>6</v>
       </c>
@@ -2923,8 +2908,6 @@
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>从长图退回列表</t>
@@ -2937,7 +2920,6 @@
           <t>案例库_001</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
         <v>7</v>
       </c>
@@ -2946,8 +2928,6 @@
           <t>打开第一个案例</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>列表第一张卡片（只读）</t>
@@ -2960,7 +2940,6 @@
           <t>案例库_001</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
         <v>8</v>
       </c>
@@ -2969,8 +2948,6 @@
           <t>检查案例详情页符合需求</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>评论区标题「全部评论」；底部无复制数/评论数图标</t>
@@ -2983,7 +2960,6 @@
           <t>案例库_001</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
         <v>9</v>
       </c>
@@ -2992,9 +2968,153 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
+        <is>
+          <t>把手机交还给下一条用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>案例库_002</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>案例复制：点复制后弹出「复制成功 / 使用手机号登录智铸超云」（会写数据，跑完自动复位）</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>先摆正起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>案例库_002</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>入口 = 底部 tab「设计专区」</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>案例库_002</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="n">
+        <v>3</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>打开第一个案例</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>复制按钮在详情页上</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>案例库_002</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="n">
+        <v>4</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>复制当前案例</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>一条龙：记水位→复制→断言提示→库里校验→自动复位。需要开关 UITEST_ALLOW_SUBMIT=1；没开关会记「跳过」</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>案例库_002</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="n">
+        <v>5</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>复制成功</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>把界面上真的出现了这句提示也写成表格里的断言</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>案例库_002</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="n">
+        <v>6</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
         <is>
           <t>把手机交还给下一条用例</t>
         </is>
@@ -3003,7 +3123,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>='动作清单'!$A$2:$A$38</formula1>
+      <formula1>='动作清单'!$A$2:$A$43</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -3019,7 +3139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D300"/>
+  <dimension ref="A1:D343"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3034,574 +3154,634 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
     </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
+    <row r="301">
+      <c r="A301" t="inlineStr">
         <is>
           <t>动作</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B301" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
+      <c r="C301" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="D301" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
+    <row r="302">
+      <c r="A302" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="D302" t="inlineStr">
         <is>
           <t>自导航到「有问必答」首页（幂等；当前在二级页时会自动点返回）。用例第一步建议都用它</t>
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
+    <row r="303">
+      <c r="A303" t="inlineStr">
         <is>
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
+      <c r="D303" t="inlineStr">
         <is>
           <t>点底部 tab「我的」，进入用户中心</t>
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
+    <row r="304">
+      <c r="A304" t="inlineStr">
         <is>
           <t>打开积分商城</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
+      <c r="D304" t="inlineStr">
         <is>
           <t>从用户中心点「积分商城」进商城首页（已在则原地不动）。积分商城是二级页，没有底部 tab 栏</t>
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
+    <row r="305">
+      <c r="A305" t="inlineStr">
         <is>
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr">
+      <c r="D305" t="inlineStr">
         <is>
           <t>进学习中心，并切到「专栏」列表</t>
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
+    <row r="306">
+      <c r="A306" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr">
+      <c r="D306" t="inlineStr">
         <is>
           <t>点搜索栏进搜索页并输入关键词。注意：只能是字母/数字/下划线/点/连字符（adb 不支持中文输入）</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
+    <row r="307">
+      <c r="A307" t="inlineStr">
         <is>
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
+      <c r="D307" t="inlineStr">
         <is>
           <t>只进搜索页、不输入关键词（搜索页上能看到「搜索历史」和「热门话题」）</t>
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
+    <row r="308">
+      <c r="A308" t="inlineStr">
         <is>
           <t>点第一个热门话题</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
+      <c r="D308" t="inlineStr">
         <is>
           <t>点搜索页「热门话题」里的第 1 条，跳转到该话题的搜索结果页（需求 713129788）</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
+    <row r="309">
+      <c r="A309" t="inlineStr">
         <is>
           <t>打开第一个帖子</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
+      <c r="D309" t="inlineStr">
         <is>
           <t>在首页信息流点第一张帖子卡片，进帖子详情页（只读：不点赞、不评论）</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
+    <row r="310">
+      <c r="A310" t="inlineStr">
         <is>
           <t>点主页按钮</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
+      <c r="D310" t="inlineStr">
         <is>
           <t>点二级页导航栏上的「主页」图标回到首页（需求 713256065 的返回首页那半句）</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
+    <row r="311">
+      <c r="A311" t="inlineStr">
         <is>
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr">
+      <c r="D311" t="inlineStr">
         <is>
           <t>在搜索页按回车把搜索跑起来（只读：只是查一次）。不执行的话停在「搜索历史」面板，看不到结果页/空态</t>
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
+    <row r="312">
+      <c r="A312" t="inlineStr">
         <is>
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr">
+      <c r="D312" t="inlineStr">
         <is>
           <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
+    <row r="313">
+      <c r="A313" t="inlineStr">
         <is>
           <t>点文字</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
+      <c r="B313" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr">
+      <c r="D313" t="inlineStr">
         <is>
           <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
+    <row r="314">
+      <c r="A314" t="inlineStr">
         <is>
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
+      <c r="D314" t="inlineStr">
         <is>
           <t>点返回按钮退回上一页（会校验页面确实变了）</t>
         </is>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
+    <row r="315">
+      <c r="A315" t="inlineStr">
         <is>
           <t>等待</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
+      <c r="B315" t="inlineStr">
         <is>
           <t>毫秒</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr">
+      <c r="D315" t="inlineStr">
         <is>
           <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
+    <row r="316">
+      <c r="A316" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
+      <c r="B316" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr">
+      <c r="D316" t="inlineStr">
         <is>
           <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
+    <row r="317">
+      <c r="A317" t="inlineStr">
         <is>
           <t>检查文字不显示</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
+      <c r="B317" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr">
+      <c r="D317" t="inlineStr">
         <is>
           <t>断言页面上看不见这段文字</t>
         </is>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
+    <row r="318">
+      <c r="A318" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
+      <c r="B318" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr">
+      <c r="D318" t="inlineStr">
         <is>
           <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
+    <row r="319">
+      <c r="A319" t="inlineStr">
         <is>
           <t>检查元素数量</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
+      <c r="B319" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
+      <c r="C319" t="inlineStr">
         <is>
           <t>期望数量</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
+      <c r="D319" t="inlineStr">
         <is>
           <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
+    <row r="320">
+      <c r="A320" t="inlineStr">
         <is>
           <t>检查答题页符合需求</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr">
+      <c r="D320" t="inlineStr">
         <is>
           <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于**一道题**的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
+    <row r="321">
+      <c r="A321" t="inlineStr">
         <is>
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr">
+      <c r="D321" t="inlineStr">
         <is>
           <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
+    <row r="322">
+      <c r="A322" t="inlineStr">
         <is>
           <t>检查首页tab顺序</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr">
+      <c r="D322" t="inlineStr">
         <is>
           <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
         </is>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
+    <row r="323">
+      <c r="A323" t="inlineStr">
         <is>
           <t>检查回到顶部按钮</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr">
+      <c r="D323" t="inlineStr">
         <is>
           <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
         </is>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
+    <row r="324">
+      <c r="A324" t="inlineStr">
         <is>
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr">
+      <c r="D324" t="inlineStr">
         <is>
           <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
         </is>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
+    <row r="325">
+      <c r="A325" t="inlineStr">
         <is>
           <t>点选择器</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
+      <c r="B325" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr">
+      <c r="D325" t="inlineStr">
         <is>
           <t>按选择器点第一处元素（比按文字点更准：文字有重名时用它），例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
+    <row r="326">
+      <c r="A326" t="inlineStr">
         <is>
           <t>滑动</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
+      <c r="B326" t="inlineStr">
         <is>
           <t>次数</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr">
+      <c r="C326" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr">
+      <c r="D326" t="inlineStr">
         <is>
           <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
         </is>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
+    <row r="327">
+      <c r="A327" t="inlineStr">
         <is>
           <t>切换筛选tab</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
+      <c r="B327" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr">
+      <c r="D327" t="inlineStr">
         <is>
           <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
+    <row r="328">
+      <c r="A328" t="inlineStr">
         <is>
           <t>切换学习中心顶部tab</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
+      <c r="B328" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr">
+      <c r="D328" t="inlineStr">
         <is>
           <t>切学习中心顶部那排 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
+    <row r="329">
+      <c r="A329" t="inlineStr">
         <is>
           <t>点第一张专栏</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr">
+      <c r="D329" t="inlineStr">
         <is>
           <t>在学习中心的专栏列表里点第一张卡，进它的详情页</t>
         </is>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
+    <row r="330">
+      <c r="A330" t="inlineStr">
         <is>
           <t>检查输入框的值</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
+      <c r="B330" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr">
+      <c r="C330" t="inlineStr">
         <is>
           <t>期望值</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr">
+      <c r="D330" t="inlineStr">
         <is>
           <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
     </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
+    <row r="331">
+      <c r="A331" t="inlineStr">
         <is>
           <t>检查文字出现次数</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
+      <c r="B331" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr">
+      <c r="C331" t="inlineStr">
         <is>
           <t>期望次数</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr">
+      <c r="D331" t="inlineStr">
         <is>
           <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
         </is>
       </c>
     </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
+    <row r="332">
+      <c r="A332" t="inlineStr">
         <is>
           <t>检查元素不存在</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
+      <c r="B332" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr">
+      <c r="D332" t="inlineStr">
         <is>
           <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
         </is>
       </c>
     </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
+    <row r="333">
+      <c r="A333" t="inlineStr">
         <is>
           <t>逐题作答</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr">
+      <c r="D333" t="inlineStr">
         <is>
           <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、**不写库**，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
         </is>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
+    <row r="334">
+      <c r="A334" t="inlineStr">
         <is>
           <t>提交答卷</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr">
+      <c r="D334" t="inlineStr">
         <is>
           <t>点答题页的提交按钮 —— **会真的写数据**。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
         </is>
       </c>
     </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
+    <row r="335">
+      <c r="A335" t="inlineStr">
         <is>
           <t>复位答题记录</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
+      <c r="B335" t="inlineStr">
         <is>
           <t>活动名</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr">
+      <c r="D335" t="inlineStr">
         <is>
           <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：**默认只预览、不删**，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行</t>
         </is>
       </c>
     </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
+    <row r="336">
+      <c r="A336" t="inlineStr">
         <is>
           <t>检查答题记录数</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
+      <c r="B336" t="inlineStr">
         <is>
           <t>活动名</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr">
+      <c r="C336" t="inlineStr">
         <is>
           <t>期望条数</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr">
+      <c r="D336" t="inlineStr">
         <is>
           <t>读数据库，断言这个活动的**提交记录**正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关</t>
         </is>
       </c>
     </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
+    <row r="337">
+      <c r="A337" t="inlineStr">
         <is>
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr">
+      <c r="D337" t="inlineStr">
         <is>
           <t>打开案例库列表（**底部 tab「设计专区」打开就是它**，这是 2026/10/12 才找到的入口；页面顶部还有一排 tab：仿真案例库 / 压铸护航服务）</t>
         </is>
       </c>
     </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
+    <row r="338">
+      <c r="A338" t="inlineStr">
         <is>
           <t>检查案例库列表符合需求</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr">
+      <c r="D338" t="inlineStr">
         <is>
           <t>按需求 713381608 校验案例库列表页：① 分类**上方**有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「**复制图标 + 复制数**」，且整页找不到评论图标。只读</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>打开第一个案例</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>在案例库列表点开第一张卡片，进案例详情页（只读：不点赞、不收藏、不复制、不评论）</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>检查案例详情页符合需求</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部**没有**复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>打开案例库介绍长图</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>点案例库首页那张介绍 banner（在分类上方），进「介绍长图详情页」。只读</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>检查案例库介绍长图符合需求</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>按需求 713381608 校验介绍长图页：整页是**单张图片**，而且是**长图**（图高远大于屏高）。只读</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>复制当前案例</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>在案例详情页点「复制案例」—— **一条龙**：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → **自动复位**（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
         </is>
       </c>
     </row>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -2993,8 +2993,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>先摆正起点</t>
@@ -3007,7 +3005,6 @@
           <t>案例库_002</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
         <v>2</v>
       </c>
@@ -3016,8 +3013,6 @@
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>入口 = 底部 tab「设计专区」</t>
@@ -3030,7 +3025,6 @@
           <t>案例库_002</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
         <v>3</v>
       </c>
@@ -3039,8 +3033,6 @@
           <t>打开第一个案例</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>复制按钮在详情页上</t>
@@ -3053,7 +3045,6 @@
           <t>案例库_002</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
         <v>4</v>
       </c>
@@ -3062,8 +3053,6 @@
           <t>复制当前案例</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>一条龙：记水位→复制→断言提示→库里校验→自动复位。需要开关 UITEST_ALLOW_SUBMIT=1；没开关会记「跳过」</t>
@@ -3076,7 +3065,6 @@
           <t>案例库_002</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
         <v>5</v>
       </c>
@@ -3090,7 +3078,6 @@
           <t>复制成功</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>把界面上真的出现了这句提示也写成表格里的断言</t>
@@ -3103,7 +3090,6 @@
           <t>案例库_002</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
         <v>6</v>
       </c>
@@ -3112,9 +3098,111 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
+        <is>
+          <t>把手机交还给下一条用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>课程详情_001</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>课程详情页：已购买未开始显示「课程介绍」+ 课程标题 + 第一课时封面视频（需求 713367615）</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>先摆正起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>课程详情_001</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>打开课程详情</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>我们账号对这门课是已购买 + 学习进度 0%（库里 user_course_relation 有、course_record 没有）</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>课程详情_001</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>检查课程详情页符合需求</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>课程介绍</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>需求原文：已购买用户-未开始学习 -&gt; 默认课程介绍，展示课程标题和第一课时封面/视频</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>课程详情_001</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="n">
+        <v>4</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
         <is>
           <t>把手机交还给下一条用例</t>
         </is>
@@ -3123,7 +3211,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>='动作清单'!$A$2:$A$43</formula1>
+      <formula1>='动作清单'!$A$2:$A$45</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -3139,7 +3227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D343"/>
+  <dimension ref="A1:D388"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3154,634 +3242,668 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
     </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
+    <row r="344">
+      <c r="A344" t="inlineStr">
         <is>
           <t>动作</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
+      <c r="B344" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
+      <c r="C344" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr">
+      <c r="D344" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
+    <row r="345">
+      <c r="A345" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr">
+      <c r="D345" t="inlineStr">
         <is>
           <t>自导航到「有问必答」首页（幂等；当前在二级页时会自动点返回）。用例第一步建议都用它</t>
         </is>
       </c>
     </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
+    <row r="346">
+      <c r="A346" t="inlineStr">
         <is>
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr">
+      <c r="D346" t="inlineStr">
         <is>
           <t>点底部 tab「我的」，进入用户中心</t>
         </is>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
+    <row r="347">
+      <c r="A347" t="inlineStr">
         <is>
           <t>打开积分商城</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr">
+      <c r="D347" t="inlineStr">
         <is>
           <t>从用户中心点「积分商城」进商城首页（已在则原地不动）。积分商城是二级页，没有底部 tab 栏</t>
         </is>
       </c>
     </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
+    <row r="348">
+      <c r="A348" t="inlineStr">
         <is>
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr">
+      <c r="D348" t="inlineStr">
         <is>
           <t>进学习中心，并切到「专栏」列表</t>
         </is>
       </c>
     </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
+    <row r="349">
+      <c r="A349" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
+      <c r="B349" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr">
+      <c r="D349" t="inlineStr">
         <is>
           <t>点搜索栏进搜索页并输入关键词。注意：只能是字母/数字/下划线/点/连字符（adb 不支持中文输入）</t>
         </is>
       </c>
     </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
+    <row r="350">
+      <c r="A350" t="inlineStr">
         <is>
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr">
+      <c r="D350" t="inlineStr">
         <is>
           <t>只进搜索页、不输入关键词（搜索页上能看到「搜索历史」和「热门话题」）</t>
         </is>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
+    <row r="351">
+      <c r="A351" t="inlineStr">
         <is>
           <t>点第一个热门话题</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr">
+      <c r="D351" t="inlineStr">
         <is>
           <t>点搜索页「热门话题」里的第 1 条，跳转到该话题的搜索结果页（需求 713129788）</t>
         </is>
       </c>
     </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
+    <row r="352">
+      <c r="A352" t="inlineStr">
         <is>
           <t>打开第一个帖子</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr">
+      <c r="D352" t="inlineStr">
         <is>
           <t>在首页信息流点第一张帖子卡片，进帖子详情页（只读：不点赞、不评论）</t>
         </is>
       </c>
     </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
+    <row r="353">
+      <c r="A353" t="inlineStr">
         <is>
           <t>点主页按钮</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr">
+      <c r="D353" t="inlineStr">
         <is>
           <t>点二级页导航栏上的「主页」图标回到首页（需求 713256065 的返回首页那半句）</t>
         </is>
       </c>
     </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
+    <row r="354">
+      <c r="A354" t="inlineStr">
         <is>
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr">
+      <c r="D354" t="inlineStr">
         <is>
           <t>在搜索页按回车把搜索跑起来（只读：只是查一次）。不执行的话停在「搜索历史」面板，看不到结果页/空态</t>
         </is>
       </c>
     </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
+    <row r="355">
+      <c r="A355" t="inlineStr">
         <is>
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr">
+      <c r="D355" t="inlineStr">
         <is>
           <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
     </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
+    <row r="356">
+      <c r="A356" t="inlineStr">
         <is>
           <t>点文字</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
+      <c r="B356" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr">
+      <c r="D356" t="inlineStr">
         <is>
           <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
         </is>
       </c>
     </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
+    <row r="357">
+      <c r="A357" t="inlineStr">
         <is>
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr">
+      <c r="D357" t="inlineStr">
         <is>
           <t>点返回按钮退回上一页（会校验页面确实变了）</t>
         </is>
       </c>
     </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
+    <row r="358">
+      <c r="A358" t="inlineStr">
         <is>
           <t>等待</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
+      <c r="B358" t="inlineStr">
         <is>
           <t>毫秒</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr">
+      <c r="D358" t="inlineStr">
         <is>
           <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
     </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
+    <row r="359">
+      <c r="A359" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
+      <c r="B359" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr">
+      <c r="D359" t="inlineStr">
         <is>
           <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
+    <row r="360">
+      <c r="A360" t="inlineStr">
         <is>
           <t>检查文字不显示</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
+      <c r="B360" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr">
+      <c r="D360" t="inlineStr">
         <is>
           <t>断言页面上看不见这段文字</t>
         </is>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
+    <row r="361">
+      <c r="A361" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
+      <c r="B361" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr">
+      <c r="D361" t="inlineStr">
         <is>
           <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
+    <row r="362">
+      <c r="A362" t="inlineStr">
         <is>
           <t>检查元素数量</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
+      <c r="B362" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr">
+      <c r="C362" t="inlineStr">
         <is>
           <t>期望数量</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr">
+      <c r="D362" t="inlineStr">
         <is>
           <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
     </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
+    <row r="363">
+      <c r="A363" t="inlineStr">
         <is>
           <t>检查答题页符合需求</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr">
+      <c r="D363" t="inlineStr">
         <is>
           <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于**一道题**的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
     </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
+    <row r="364">
+      <c r="A364" t="inlineStr">
         <is>
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr">
+      <c r="D364" t="inlineStr">
         <is>
           <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
+    <row r="365">
+      <c r="A365" t="inlineStr">
         <is>
           <t>检查首页tab顺序</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr">
+      <c r="D365" t="inlineStr">
         <is>
           <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
         </is>
       </c>
     </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
+    <row r="366">
+      <c r="A366" t="inlineStr">
         <is>
           <t>检查回到顶部按钮</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr">
+      <c r="D366" t="inlineStr">
         <is>
           <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
         </is>
       </c>
     </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
+    <row r="367">
+      <c r="A367" t="inlineStr">
         <is>
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr">
+      <c r="D367" t="inlineStr">
         <is>
           <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
         </is>
       </c>
     </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
+    <row r="368">
+      <c r="A368" t="inlineStr">
         <is>
           <t>点选择器</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
+      <c r="B368" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr">
+      <c r="D368" t="inlineStr">
         <is>
           <t>按选择器点第一处元素（比按文字点更准：文字有重名时用它），例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
+    <row r="369">
+      <c r="A369" t="inlineStr">
         <is>
           <t>滑动</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
+      <c r="B369" t="inlineStr">
         <is>
           <t>次数</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr">
+      <c r="C369" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr">
+      <c r="D369" t="inlineStr">
         <is>
           <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
         </is>
       </c>
     </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
+    <row r="370">
+      <c r="A370" t="inlineStr">
         <is>
           <t>切换筛选tab</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
+      <c r="B370" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr">
+      <c r="D370" t="inlineStr">
         <is>
           <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
+    <row r="371">
+      <c r="A371" t="inlineStr">
         <is>
           <t>切换学习中心顶部tab</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
+      <c r="B371" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr">
+      <c r="D371" t="inlineStr">
         <is>
           <t>切学习中心顶部那排 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
+    <row r="372">
+      <c r="A372" t="inlineStr">
         <is>
           <t>点第一张专栏</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr">
+      <c r="D372" t="inlineStr">
         <is>
           <t>在学习中心的专栏列表里点第一张卡，进它的详情页</t>
         </is>
       </c>
     </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
+    <row r="373">
+      <c r="A373" t="inlineStr">
         <is>
           <t>检查输入框的值</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr">
+      <c r="B373" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr">
+      <c r="C373" t="inlineStr">
         <is>
           <t>期望值</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr">
+      <c r="D373" t="inlineStr">
         <is>
           <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
     </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
+    <row r="374">
+      <c r="A374" t="inlineStr">
         <is>
           <t>检查文字出现次数</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
+      <c r="B374" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr">
+      <c r="C374" t="inlineStr">
         <is>
           <t>期望次数</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr">
+      <c r="D374" t="inlineStr">
         <is>
           <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
         </is>
       </c>
     </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
+    <row r="375">
+      <c r="A375" t="inlineStr">
         <is>
           <t>检查元素不存在</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
+      <c r="B375" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr">
+      <c r="D375" t="inlineStr">
         <is>
           <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
         </is>
       </c>
     </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
+    <row r="376">
+      <c r="A376" t="inlineStr">
         <is>
           <t>逐题作答</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr">
+      <c r="D376" t="inlineStr">
         <is>
           <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、**不写库**，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
         </is>
       </c>
     </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
+    <row r="377">
+      <c r="A377" t="inlineStr">
         <is>
           <t>提交答卷</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr">
+      <c r="D377" t="inlineStr">
         <is>
           <t>点答题页的提交按钮 —— **会真的写数据**。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
         </is>
       </c>
     </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
+    <row r="378">
+      <c r="A378" t="inlineStr">
         <is>
           <t>复位答题记录</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
+      <c r="B378" t="inlineStr">
         <is>
           <t>活动名</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr">
+      <c r="D378" t="inlineStr">
         <is>
           <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：**默认只预览、不删**，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行</t>
         </is>
       </c>
     </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
+    <row r="379">
+      <c r="A379" t="inlineStr">
         <is>
           <t>检查答题记录数</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
+      <c r="B379" t="inlineStr">
         <is>
           <t>活动名</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr">
+      <c r="C379" t="inlineStr">
         <is>
           <t>期望条数</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr">
+      <c r="D379" t="inlineStr">
         <is>
           <t>读数据库，断言这个活动的**提交记录**正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关</t>
         </is>
       </c>
     </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
+    <row r="380">
+      <c r="A380" t="inlineStr">
         <is>
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr">
+      <c r="D380" t="inlineStr">
         <is>
           <t>打开案例库列表（**底部 tab「设计专区」打开就是它**，这是 2026/10/12 才找到的入口；页面顶部还有一排 tab：仿真案例库 / 压铸护航服务）</t>
         </is>
       </c>
     </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
+    <row r="381">
+      <c r="A381" t="inlineStr">
         <is>
           <t>检查案例库列表符合需求</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr">
+      <c r="D381" t="inlineStr">
         <is>
           <t>按需求 713381608 校验案例库列表页：① 分类**上方**有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「**复制图标 + 复制数**」，且整页找不到评论图标。只读</t>
         </is>
       </c>
     </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
+    <row r="382">
+      <c r="A382" t="inlineStr">
         <is>
           <t>打开第一个案例</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr">
+      <c r="D382" t="inlineStr">
         <is>
           <t>在案例库列表点开第一张卡片，进案例详情页（只读：不点赞、不收藏、不复制、不评论）</t>
         </is>
       </c>
     </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
+    <row r="383">
+      <c r="A383" t="inlineStr">
         <is>
           <t>检查案例详情页符合需求</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr">
+      <c r="D383" t="inlineStr">
         <is>
           <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部**没有**复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
         </is>
       </c>
     </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
+    <row r="384">
+      <c r="A384" t="inlineStr">
         <is>
           <t>打开案例库介绍长图</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr">
+      <c r="D384" t="inlineStr">
         <is>
           <t>点案例库首页那张介绍 banner（在分类上方），进「介绍长图详情页」。只读</t>
         </is>
       </c>
     </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
+    <row r="385">
+      <c r="A385" t="inlineStr">
         <is>
           <t>检查案例库介绍长图符合需求</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr">
+      <c r="D385" t="inlineStr">
         <is>
           <t>按需求 713381608 校验介绍长图页：整页是**单张图片**，而且是**长图**（图高远大于屏高）。只读</t>
         </is>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
+    <row r="386">
+      <c r="A386" t="inlineStr">
         <is>
           <t>复制当前案例</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr">
+      <c r="D386" t="inlineStr">
         <is>
           <t>在案例详情页点「复制案例」—— **一条龙**：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → **自动复位**（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>打开课程详情</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>课程名</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>打开某门课的详情页（学习页）：自己走到 学习中心 → 课程 tab → 按名字点课程。只读：不播放视频、不购买。课程名要跟列表上一字不差，例如 717</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>检查课程详情页符合需求</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>期望默认选中的tab</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、**默认选中填的那个**（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
         </is>
       </c>
     </row>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -3123,8 +3123,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>先摆正起点</t>
@@ -3137,7 +3135,6 @@
           <t>课程详情_001</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
         <v>2</v>
       </c>
@@ -3151,7 +3148,6 @@
           <t>717</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>我们账号对这门课是已购买 + 学习进度 0%（库里 user_course_relation 有、course_record 没有）</t>
@@ -3164,7 +3160,6 @@
           <t>课程详情_001</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
         <v>3</v>
       </c>
@@ -3178,7 +3173,6 @@
           <t>课程介绍</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>需求原文：已购买用户-未开始学习 -&gt; 默认课程介绍，展示课程标题和第一课时封面/视频</t>
@@ -3191,7 +3185,6 @@
           <t>课程详情_001</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
         <v>4</v>
       </c>
@@ -3200,9 +3193,130 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
+        <is>
+          <t>把手机交还给下一条用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>课程列表_001</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>课程列表：课时数为0的课程不显示（需求 713367615 第 1 条，跟数据库对账）</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>先摆正起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>课程列表_001</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="n">
+        <v>2</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>打开学习中心专栏</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>先到学习中心（默认落在专栏 tab）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>课程列表_001</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="n">
+        <v>3</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>切换学习中心顶部tab</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>切到课程列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>课程列表_001</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="n">
+        <v>4</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>检查课时数为0的课程不显示</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>库里 28 门 0 课时的公开课程，一个都不该出现在列表里（会让列表滚到底再对账）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>课程列表_001</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="n">
+        <v>5</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
         <is>
           <t>把手机交还给下一条用例</t>
         </is>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -3218,8 +3218,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>先摆正起点</t>
@@ -3232,7 +3230,6 @@
           <t>课程列表_001</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
         <v>2</v>
       </c>
@@ -3241,8 +3238,6 @@
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>先到学习中心（默认落在专栏 tab）</t>
@@ -3255,7 +3250,6 @@
           <t>课程列表_001</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
         <v>3</v>
       </c>
@@ -3269,7 +3263,6 @@
           <t>课程</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
           <t>切到课程列表</t>
@@ -3282,7 +3275,6 @@
           <t>课程列表_001</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
         <v>4</v>
       </c>
@@ -3291,8 +3283,6 @@
           <t>检查课时数为0的课程不显示</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>库里 28 门 0 课时的公开课程，一个都不该出现在列表里（会让列表滚到底再对账）</t>
@@ -3305,7 +3295,6 @@
           <t>课程列表_001</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
         <v>5</v>
       </c>
@@ -3314,9 +3303,142 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
+        <is>
+          <t>把手机交还给下一条用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>案例库_003</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>付费案例复制：也弹同样的提示（会写数据 + 扣积分，跑完自动复位记录与复制数）</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>先摆正起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>案例库_003</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>入口 = 底部 tab「设计专区」</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>案例库_003</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>3</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>打开案例</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>填充任务1</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>付费样本（5 积分，全库最便宜的付费案例之一；案例名要跟列表上一字不差）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>案例库_003</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>4</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>复制当前案例</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>需求：免费和付费案例都提示。付费会扣积分（中台记账，不复位）；复制记录与复制数会自动复位</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>案例库_003</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>5</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>复制成功</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>把界面上真的出现了这句提示也写成表格里的断言</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>案例库_003</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>6</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
         <is>
           <t>把手机交还给下一条用例</t>
         </is>
@@ -3325,7 +3447,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>='动作清单'!$A$2:$A$45</formula1>
+      <formula1>='动作清单'!$A$2:$A$47</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -3341,7 +3463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D388"/>
+  <dimension ref="A1:D435"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3356,668 +3478,1152 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
     </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
+    <row r="340"/>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
+    <row r="350"/>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
+    <row r="378"/>
+    <row r="379"/>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389">
+      <c r="A389" t="inlineStr">
         <is>
           <t>动作</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
+      <c r="B389" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="C344" t="inlineStr">
+      <c r="C389" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr">
+      <c r="D389" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
+    <row r="390">
+      <c r="A390" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr">
+      <c r="B390" t="inlineStr"/>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
         <is>
           <t>自导航到「有问必答」首页（幂等；当前在二级页时会自动点返回）。用例第一步建议都用它</t>
         </is>
       </c>
     </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
+    <row r="391">
+      <c r="A391" t="inlineStr">
         <is>
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr">
+      <c r="B391" t="inlineStr"/>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
         <is>
           <t>点底部 tab「我的」，进入用户中心</t>
         </is>
       </c>
     </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
+    <row r="392">
+      <c r="A392" t="inlineStr">
         <is>
           <t>打开积分商城</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr">
+      <c r="B392" t="inlineStr"/>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
         <is>
           <t>从用户中心点「积分商城」进商城首页（已在则原地不动）。积分商城是二级页，没有底部 tab 栏</t>
         </is>
       </c>
     </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
+    <row r="393">
+      <c r="A393" t="inlineStr">
         <is>
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr">
+      <c r="B393" t="inlineStr"/>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
         <is>
           <t>进学习中心，并切到「专栏」列表</t>
         </is>
       </c>
     </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
+    <row r="394">
+      <c r="A394" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
+      <c r="B394" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr">
+      <c r="C394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
         <is>
           <t>点搜索栏进搜索页并输入关键词。注意：只能是字母/数字/下划线/点/连字符（adb 不支持中文输入）</t>
         </is>
       </c>
     </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
+    <row r="395">
+      <c r="A395" t="inlineStr">
         <is>
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr">
+      <c r="B395" t="inlineStr"/>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
         <is>
           <t>只进搜索页、不输入关键词（搜索页上能看到「搜索历史」和「热门话题」）</t>
         </is>
       </c>
     </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
+    <row r="396">
+      <c r="A396" t="inlineStr">
         <is>
           <t>点第一个热门话题</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr">
+      <c r="B396" t="inlineStr"/>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
         <is>
           <t>点搜索页「热门话题」里的第 1 条，跳转到该话题的搜索结果页（需求 713129788）</t>
         </is>
       </c>
     </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
+    <row r="397">
+      <c r="A397" t="inlineStr">
         <is>
           <t>打开第一个帖子</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr">
+      <c r="B397" t="inlineStr"/>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
         <is>
           <t>在首页信息流点第一张帖子卡片，进帖子详情页（只读：不点赞、不评论）</t>
         </is>
       </c>
     </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
+    <row r="398">
+      <c r="A398" t="inlineStr">
         <is>
           <t>点主页按钮</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr">
+      <c r="B398" t="inlineStr"/>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
         <is>
           <t>点二级页导航栏上的「主页」图标回到首页（需求 713256065 的返回首页那半句）</t>
         </is>
       </c>
     </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
+    <row r="399">
+      <c r="A399" t="inlineStr">
         <is>
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr">
+      <c r="B399" t="inlineStr"/>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
         <is>
           <t>在搜索页按回车把搜索跑起来（只读：只是查一次）。不执行的话停在「搜索历史」面板，看不到结果页/空态</t>
         </is>
       </c>
     </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
+    <row r="400">
+      <c r="A400" t="inlineStr">
         <is>
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr">
+      <c r="B400" t="inlineStr"/>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
         <is>
           <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
     </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
+    <row r="401">
+      <c r="A401" t="inlineStr">
         <is>
           <t>点文字</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr">
+      <c r="B401" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr">
+      <c r="C401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
         <is>
           <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
         </is>
       </c>
     </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
+    <row r="402">
+      <c r="A402" t="inlineStr">
         <is>
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr">
+      <c r="B402" t="inlineStr"/>
+      <c r="C402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
         <is>
           <t>点返回按钮退回上一页（会校验页面确实变了）</t>
         </is>
       </c>
     </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
+    <row r="403">
+      <c r="A403" t="inlineStr">
         <is>
           <t>等待</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr">
+      <c r="B403" t="inlineStr">
         <is>
           <t>毫秒</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr">
+      <c r="C403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
         <is>
           <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
     </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
+    <row r="404">
+      <c r="A404" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr">
+      <c r="B404" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr">
+      <c r="C404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
         <is>
           <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
     </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
+    <row r="405">
+      <c r="A405" t="inlineStr">
         <is>
           <t>检查文字不显示</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr">
+      <c r="B405" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr">
+      <c r="C405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
         <is>
           <t>断言页面上看不见这段文字</t>
         </is>
       </c>
     </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
+    <row r="406">
+      <c r="A406" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr">
+      <c r="B406" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr">
+      <c r="C406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
         <is>
           <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
+    <row r="407">
+      <c r="A407" t="inlineStr">
         <is>
           <t>检查元素数量</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr">
+      <c r="B407" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr">
+      <c r="C407" t="inlineStr">
         <is>
           <t>期望数量</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr">
+      <c r="D407" t="inlineStr">
         <is>
           <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
     </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
+    <row r="408">
+      <c r="A408" t="inlineStr">
         <is>
           <t>检查答题页符合需求</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr">
+      <c r="B408" t="inlineStr"/>
+      <c r="C408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
         <is>
           <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于**一道题**的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
     </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
+    <row r="409">
+      <c r="A409" t="inlineStr">
         <is>
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr">
+      <c r="B409" t="inlineStr"/>
+      <c r="C409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
         <is>
           <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
     </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
+    <row r="410">
+      <c r="A410" t="inlineStr">
         <is>
           <t>检查首页tab顺序</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr">
+      <c r="B410" t="inlineStr"/>
+      <c r="C410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
         <is>
           <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
         </is>
       </c>
     </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
+    <row r="411">
+      <c r="A411" t="inlineStr">
         <is>
           <t>检查回到顶部按钮</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr">
+      <c r="B411" t="inlineStr"/>
+      <c r="C411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
         <is>
           <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
         </is>
       </c>
     </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
+    <row r="412">
+      <c r="A412" t="inlineStr">
         <is>
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr">
+      <c r="B412" t="inlineStr"/>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
         <is>
           <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
         </is>
       </c>
     </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
+    <row r="413">
+      <c r="A413" t="inlineStr">
         <is>
           <t>点选择器</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr">
+      <c r="B413" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr">
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
         <is>
           <t>按选择器点第一处元素（比按文字点更准：文字有重名时用它），例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
+    <row r="414">
+      <c r="A414" t="inlineStr">
         <is>
           <t>滑动</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr">
+      <c r="B414" t="inlineStr">
         <is>
           <t>次数</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr">
+      <c r="C414" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr">
+      <c r="D414" t="inlineStr">
         <is>
           <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
         </is>
       </c>
     </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
+    <row r="415">
+      <c r="A415" t="inlineStr">
         <is>
           <t>切换筛选tab</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr">
+      <c r="B415" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr">
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
         <is>
           <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
+    <row r="416">
+      <c r="A416" t="inlineStr">
         <is>
           <t>切换学习中心顶部tab</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr">
+      <c r="B416" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr">
+      <c r="C416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
         <is>
           <t>切学习中心顶部那排 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
+    <row r="417">
+      <c r="A417" t="inlineStr">
         <is>
           <t>点第一张专栏</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr">
+      <c r="B417" t="inlineStr"/>
+      <c r="C417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
         <is>
           <t>在学习中心的专栏列表里点第一张卡，进它的详情页</t>
         </is>
       </c>
     </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
+    <row r="418">
+      <c r="A418" t="inlineStr">
         <is>
           <t>检查输入框的值</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr">
+      <c r="B418" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C373" t="inlineStr">
+      <c r="C418" t="inlineStr">
         <is>
           <t>期望值</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr">
+      <c r="D418" t="inlineStr">
         <is>
           <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
     </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
+    <row r="419">
+      <c r="A419" t="inlineStr">
         <is>
           <t>检查文字出现次数</t>
         </is>
       </c>
-      <c r="B374" t="inlineStr">
+      <c r="B419" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C374" t="inlineStr">
+      <c r="C419" t="inlineStr">
         <is>
           <t>期望次数</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr">
+      <c r="D419" t="inlineStr">
         <is>
           <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
         </is>
       </c>
     </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
+    <row r="420">
+      <c r="A420" t="inlineStr">
         <is>
           <t>检查元素不存在</t>
         </is>
       </c>
-      <c r="B375" t="inlineStr">
+      <c r="B420" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr">
+      <c r="C420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
         <is>
           <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
         </is>
       </c>
     </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
+    <row r="421">
+      <c r="A421" t="inlineStr">
         <is>
           <t>逐题作答</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr">
+      <c r="B421" t="inlineStr"/>
+      <c r="C421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
         <is>
           <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、**不写库**，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
         </is>
       </c>
     </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
+    <row r="422">
+      <c r="A422" t="inlineStr">
         <is>
           <t>提交答卷</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr">
+      <c r="B422" t="inlineStr"/>
+      <c r="C422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
         <is>
           <t>点答题页的提交按钮 —— **会真的写数据**。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
         </is>
       </c>
     </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
+    <row r="423">
+      <c r="A423" t="inlineStr">
         <is>
           <t>复位答题记录</t>
         </is>
       </c>
-      <c r="B378" t="inlineStr">
+      <c r="B423" t="inlineStr">
         <is>
           <t>活动名</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr">
+      <c r="C423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
         <is>
           <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：**默认只预览、不删**，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行</t>
         </is>
       </c>
     </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
+    <row r="424">
+      <c r="A424" t="inlineStr">
         <is>
           <t>检查答题记录数</t>
         </is>
       </c>
-      <c r="B379" t="inlineStr">
+      <c r="B424" t="inlineStr">
         <is>
           <t>活动名</t>
         </is>
       </c>
-      <c r="C379" t="inlineStr">
+      <c r="C424" t="inlineStr">
         <is>
           <t>期望条数</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr">
+      <c r="D424" t="inlineStr">
         <is>
           <t>读数据库，断言这个活动的**提交记录**正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关</t>
         </is>
       </c>
     </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
+    <row r="425">
+      <c r="A425" t="inlineStr">
         <is>
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr">
+      <c r="B425" t="inlineStr"/>
+      <c r="C425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
         <is>
           <t>打开案例库列表（**底部 tab「设计专区」打开就是它**，这是 2026/10/12 才找到的入口；页面顶部还有一排 tab：仿真案例库 / 压铸护航服务）</t>
         </is>
       </c>
     </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
+    <row r="426">
+      <c r="A426" t="inlineStr">
         <is>
           <t>检查案例库列表符合需求</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr">
+      <c r="B426" t="inlineStr"/>
+      <c r="C426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
         <is>
           <t>按需求 713381608 校验案例库列表页：① 分类**上方**有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「**复制图标 + 复制数**」，且整页找不到评论图标。只读</t>
         </is>
       </c>
     </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
+    <row r="427">
+      <c r="A427" t="inlineStr">
         <is>
           <t>打开第一个案例</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr">
+      <c r="B427" t="inlineStr"/>
+      <c r="C427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
         <is>
           <t>在案例库列表点开第一张卡片，进案例详情页（只读：不点赞、不收藏、不复制、不评论）</t>
         </is>
       </c>
     </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>打开案例</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>案例名</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>按名字点开指定案例（点不到会往下滚几屏再找）。给「付费案例复制」挑样本时用它，例如 填充任务1。只读：不点赞、不收藏、不复制</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
         <is>
           <t>检查案例详情页符合需求</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr">
+      <c r="B429" t="inlineStr"/>
+      <c r="C429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
         <is>
           <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部**没有**复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
         </is>
       </c>
     </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
+    <row r="430">
+      <c r="A430" t="inlineStr">
         <is>
           <t>打开案例库介绍长图</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr">
+      <c r="B430" t="inlineStr"/>
+      <c r="C430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
         <is>
           <t>点案例库首页那张介绍 banner（在分类上方），进「介绍长图详情页」。只读</t>
         </is>
       </c>
     </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
+    <row r="431">
+      <c r="A431" t="inlineStr">
         <is>
           <t>检查案例库介绍长图符合需求</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr">
+      <c r="B431" t="inlineStr"/>
+      <c r="C431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
         <is>
           <t>按需求 713381608 校验介绍长图页：整页是**单张图片**，而且是**长图**（图高远大于屏高）。只读</t>
         </is>
       </c>
     </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
+    <row r="432">
+      <c r="A432" t="inlineStr">
         <is>
           <t>复制当前案例</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr">
+      <c r="B432" t="inlineStr"/>
+      <c r="C432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
         <is>
           <t>在案例详情页点「复制案例」—— **一条龙**：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → **自动复位**（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
         </is>
       </c>
     </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
+    <row r="433">
+      <c r="A433" t="inlineStr">
         <is>
           <t>打开课程详情</t>
         </is>
       </c>
-      <c r="B387" t="inlineStr">
+      <c r="B433" t="inlineStr">
         <is>
           <t>课程名</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr">
+      <c r="C433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
         <is>
           <t>打开某门课的详情页（学习页）：自己走到 学习中心 → 课程 tab → 按名字点课程。只读：不播放视频、不购买。课程名要跟列表上一字不差，例如 717</t>
         </is>
       </c>
     </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
+    <row r="434">
+      <c r="A434" t="inlineStr">
         <is>
           <t>检查课程详情页符合需求</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr">
+      <c r="B434" t="inlineStr">
         <is>
           <t>期望默认选中的tab</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr">
+      <c r="C434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
         <is>
           <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、**默认选中填的那个**（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>检查课时数为0的课程不显示</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr"/>
+      <c r="C435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字**一个都没出现在**小程序的课程列表里（会自己滚到列表底部）。只读</t>
         </is>
       </c>
     </row>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -3444,10 +3444,105 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>课程详情_002</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>未购买课程点课时：封面和标题不变、始终显示课程名（需求 713367615 第 2 条）</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>先摆正起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>课程详情_002</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>2</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>打开课程详情</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>7.8课程new</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>我们账号只买过 717 一门课，所以这门是未购买（依据：user_course_relation 表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>课程详情_002</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>检查未购买点课时不改变封面标题</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>7.8课程new</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>需求原文：未购买用户点击课时不改变封面图和标题，始终显示课程名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>课程详情_002</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>4</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>把手机交还给下一条用例</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>='动作清单'!$A$2:$A$47</formula1>
+      <formula1>='动作清单'!$A$2:$A$48</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -3463,7 +3558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D435"/>
+  <dimension ref="A1:D483"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3865,765 +3960,830 @@
     <row r="386"/>
     <row r="387"/>
     <row r="388"/>
-    <row r="389">
-      <c r="A389" t="inlineStr">
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
+    <row r="414"/>
+    <row r="415"/>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435"/>
+    <row r="436">
+      <c r="A436" t="inlineStr">
         <is>
           <t>动作</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr">
+      <c r="B436" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr">
+      <c r="C436" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr">
+      <c r="D436" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
+    <row r="437">
+      <c r="A437" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr"/>
-      <c r="C390" t="inlineStr"/>
-      <c r="D390" t="inlineStr">
+      <c r="B437" t="inlineStr"/>
+      <c r="C437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
         <is>
           <t>自导航到「有问必答」首页（幂等；当前在二级页时会自动点返回）。用例第一步建议都用它</t>
         </is>
       </c>
     </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
+    <row r="438">
+      <c r="A438" t="inlineStr">
         <is>
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr"/>
-      <c r="C391" t="inlineStr"/>
-      <c r="D391" t="inlineStr">
+      <c r="B438" t="inlineStr"/>
+      <c r="C438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
         <is>
           <t>点底部 tab「我的」，进入用户中心</t>
         </is>
       </c>
     </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
+    <row r="439">
+      <c r="A439" t="inlineStr">
         <is>
           <t>打开积分商城</t>
         </is>
       </c>
-      <c r="B392" t="inlineStr"/>
-      <c r="C392" t="inlineStr"/>
-      <c r="D392" t="inlineStr">
+      <c r="B439" t="inlineStr"/>
+      <c r="C439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
         <is>
           <t>从用户中心点「积分商城」进商城首页（已在则原地不动）。积分商城是二级页，没有底部 tab 栏</t>
         </is>
       </c>
     </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
+    <row r="440">
+      <c r="A440" t="inlineStr">
         <is>
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="B393" t="inlineStr"/>
-      <c r="C393" t="inlineStr"/>
-      <c r="D393" t="inlineStr">
+      <c r="B440" t="inlineStr"/>
+      <c r="C440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
         <is>
           <t>进学习中心，并切到「专栏」列表</t>
         </is>
       </c>
     </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
+    <row r="441">
+      <c r="A441" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
+      <c r="B441" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="C394" t="inlineStr"/>
-      <c r="D394" t="inlineStr">
+      <c r="C441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
         <is>
           <t>点搜索栏进搜索页并输入关键词。注意：只能是字母/数字/下划线/点/连字符（adb 不支持中文输入）</t>
         </is>
       </c>
     </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
+    <row r="442">
+      <c r="A442" t="inlineStr">
         <is>
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr"/>
-      <c r="C395" t="inlineStr"/>
-      <c r="D395" t="inlineStr">
+      <c r="B442" t="inlineStr"/>
+      <c r="C442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
         <is>
           <t>只进搜索页、不输入关键词（搜索页上能看到「搜索历史」和「热门话题」）</t>
         </is>
       </c>
     </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
+    <row r="443">
+      <c r="A443" t="inlineStr">
         <is>
           <t>点第一个热门话题</t>
         </is>
       </c>
-      <c r="B396" t="inlineStr"/>
-      <c r="C396" t="inlineStr"/>
-      <c r="D396" t="inlineStr">
+      <c r="B443" t="inlineStr"/>
+      <c r="C443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
         <is>
           <t>点搜索页「热门话题」里的第 1 条，跳转到该话题的搜索结果页（需求 713129788）</t>
         </is>
       </c>
     </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
+    <row r="444">
+      <c r="A444" t="inlineStr">
         <is>
           <t>打开第一个帖子</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr"/>
-      <c r="C397" t="inlineStr"/>
-      <c r="D397" t="inlineStr">
+      <c r="B444" t="inlineStr"/>
+      <c r="C444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
         <is>
           <t>在首页信息流点第一张帖子卡片，进帖子详情页（只读：不点赞、不评论）</t>
         </is>
       </c>
     </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
+    <row r="445">
+      <c r="A445" t="inlineStr">
         <is>
           <t>点主页按钮</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr"/>
-      <c r="C398" t="inlineStr"/>
-      <c r="D398" t="inlineStr">
+      <c r="B445" t="inlineStr"/>
+      <c r="C445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
         <is>
           <t>点二级页导航栏上的「主页」图标回到首页（需求 713256065 的返回首页那半句）</t>
         </is>
       </c>
     </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
+    <row r="446">
+      <c r="A446" t="inlineStr">
         <is>
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr"/>
-      <c r="C399" t="inlineStr"/>
-      <c r="D399" t="inlineStr">
+      <c r="B446" t="inlineStr"/>
+      <c r="C446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
         <is>
           <t>在搜索页按回车把搜索跑起来（只读：只是查一次）。不执行的话停在「搜索历史」面板，看不到结果页/空态</t>
         </is>
       </c>
     </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
+    <row r="447">
+      <c r="A447" t="inlineStr">
         <is>
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr"/>
-      <c r="C400" t="inlineStr"/>
-      <c r="D400" t="inlineStr">
+      <c r="B447" t="inlineStr"/>
+      <c r="C447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
         <is>
           <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
     </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
+    <row r="448">
+      <c r="A448" t="inlineStr">
         <is>
           <t>点文字</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr">
+      <c r="B448" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C401" t="inlineStr"/>
-      <c r="D401" t="inlineStr">
+      <c r="C448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
         <is>
           <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
         </is>
       </c>
     </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
+    <row r="449">
+      <c r="A449" t="inlineStr">
         <is>
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr"/>
-      <c r="C402" t="inlineStr"/>
-      <c r="D402" t="inlineStr">
+      <c r="B449" t="inlineStr"/>
+      <c r="C449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
         <is>
           <t>点返回按钮退回上一页（会校验页面确实变了）</t>
         </is>
       </c>
     </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
+    <row r="450">
+      <c r="A450" t="inlineStr">
         <is>
           <t>等待</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr">
+      <c r="B450" t="inlineStr">
         <is>
           <t>毫秒</t>
         </is>
       </c>
-      <c r="C403" t="inlineStr"/>
-      <c r="D403" t="inlineStr">
+      <c r="C450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
         <is>
           <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
     </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
+    <row r="451">
+      <c r="A451" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr">
+      <c r="B451" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C404" t="inlineStr"/>
-      <c r="D404" t="inlineStr">
+      <c r="C451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
         <is>
           <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
     </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
+    <row r="452">
+      <c r="A452" t="inlineStr">
         <is>
           <t>检查文字不显示</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr">
+      <c r="B452" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr"/>
-      <c r="D405" t="inlineStr">
+      <c r="C452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
         <is>
           <t>断言页面上看不见这段文字</t>
         </is>
       </c>
     </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
+    <row r="453">
+      <c r="A453" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr">
+      <c r="B453" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C406" t="inlineStr"/>
-      <c r="D406" t="inlineStr">
+      <c r="C453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
         <is>
           <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
+    <row r="454">
+      <c r="A454" t="inlineStr">
         <is>
           <t>检查元素数量</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr">
+      <c r="B454" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C407" t="inlineStr">
+      <c r="C454" t="inlineStr">
         <is>
           <t>期望数量</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr">
+      <c r="D454" t="inlineStr">
         <is>
           <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
     </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
+    <row r="455">
+      <c r="A455" t="inlineStr">
         <is>
           <t>检查答题页符合需求</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr"/>
-      <c r="C408" t="inlineStr"/>
-      <c r="D408" t="inlineStr">
+      <c r="B455" t="inlineStr"/>
+      <c r="C455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
         <is>
           <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于**一道题**的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
     </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
+    <row r="456">
+      <c r="A456" t="inlineStr">
         <is>
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr"/>
-      <c r="C409" t="inlineStr"/>
-      <c r="D409" t="inlineStr">
+      <c r="B456" t="inlineStr"/>
+      <c r="C456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
         <is>
           <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
     </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
+    <row r="457">
+      <c r="A457" t="inlineStr">
         <is>
           <t>检查首页tab顺序</t>
         </is>
       </c>
-      <c r="B410" t="inlineStr"/>
-      <c r="C410" t="inlineStr"/>
-      <c r="D410" t="inlineStr">
+      <c r="B457" t="inlineStr"/>
+      <c r="C457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
         <is>
           <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
         </is>
       </c>
     </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
+    <row r="458">
+      <c r="A458" t="inlineStr">
         <is>
           <t>检查回到顶部按钮</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr"/>
-      <c r="C411" t="inlineStr"/>
-      <c r="D411" t="inlineStr">
+      <c r="B458" t="inlineStr"/>
+      <c r="C458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
         <is>
           <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
         </is>
       </c>
     </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
+    <row r="459">
+      <c r="A459" t="inlineStr">
         <is>
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="B412" t="inlineStr"/>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr">
+      <c r="B459" t="inlineStr"/>
+      <c r="C459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
         <is>
           <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
         </is>
       </c>
     </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
+    <row r="460">
+      <c r="A460" t="inlineStr">
         <is>
           <t>点选择器</t>
         </is>
       </c>
-      <c r="B413" t="inlineStr">
+      <c r="B460" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr">
+      <c r="C460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
         <is>
           <t>按选择器点第一处元素（比按文字点更准：文字有重名时用它），例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
+    <row r="461">
+      <c r="A461" t="inlineStr">
         <is>
           <t>滑动</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
+      <c r="B461" t="inlineStr">
         <is>
           <t>次数</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr">
+      <c r="C461" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr">
+      <c r="D461" t="inlineStr">
         <is>
           <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
         </is>
       </c>
     </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
+    <row r="462">
+      <c r="A462" t="inlineStr">
         <is>
           <t>切换筛选tab</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr">
+      <c r="B462" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr">
+      <c r="C462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
         <is>
           <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
+    <row r="463">
+      <c r="A463" t="inlineStr">
         <is>
           <t>切换学习中心顶部tab</t>
         </is>
       </c>
-      <c r="B416" t="inlineStr">
+      <c r="B463" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="C416" t="inlineStr"/>
-      <c r="D416" t="inlineStr">
+      <c r="C463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
         <is>
           <t>切学习中心顶部那排 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
+    <row r="464">
+      <c r="A464" t="inlineStr">
         <is>
           <t>点第一张专栏</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr"/>
-      <c r="C417" t="inlineStr"/>
-      <c r="D417" t="inlineStr">
+      <c r="B464" t="inlineStr"/>
+      <c r="C464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
         <is>
           <t>在学习中心的专栏列表里点第一张卡，进它的详情页</t>
         </is>
       </c>
     </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
+    <row r="465">
+      <c r="A465" t="inlineStr">
         <is>
           <t>检查输入框的值</t>
         </is>
       </c>
-      <c r="B418" t="inlineStr">
+      <c r="B465" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr">
+      <c r="C465" t="inlineStr">
         <is>
           <t>期望值</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr">
+      <c r="D465" t="inlineStr">
         <is>
           <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
     </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
+    <row r="466">
+      <c r="A466" t="inlineStr">
         <is>
           <t>检查文字出现次数</t>
         </is>
       </c>
-      <c r="B419" t="inlineStr">
+      <c r="B466" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C419" t="inlineStr">
+      <c r="C466" t="inlineStr">
         <is>
           <t>期望次数</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr">
+      <c r="D466" t="inlineStr">
         <is>
           <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
         </is>
       </c>
     </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
+    <row r="467">
+      <c r="A467" t="inlineStr">
         <is>
           <t>检查元素不存在</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr">
+      <c r="B467" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C420" t="inlineStr"/>
-      <c r="D420" t="inlineStr">
+      <c r="C467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
         <is>
           <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
         </is>
       </c>
     </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
+    <row r="468">
+      <c r="A468" t="inlineStr">
         <is>
           <t>逐题作答</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr"/>
-      <c r="C421" t="inlineStr"/>
-      <c r="D421" t="inlineStr">
+      <c r="B468" t="inlineStr"/>
+      <c r="C468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
         <is>
           <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、**不写库**，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
         </is>
       </c>
     </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
+    <row r="469">
+      <c r="A469" t="inlineStr">
         <is>
           <t>提交答卷</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr"/>
-      <c r="C422" t="inlineStr"/>
-      <c r="D422" t="inlineStr">
+      <c r="B469" t="inlineStr"/>
+      <c r="C469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
         <is>
           <t>点答题页的提交按钮 —— **会真的写数据**。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
         </is>
       </c>
     </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
+    <row r="470">
+      <c r="A470" t="inlineStr">
         <is>
           <t>复位答题记录</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr">
+      <c r="B470" t="inlineStr">
         <is>
           <t>活动名</t>
         </is>
       </c>
-      <c r="C423" t="inlineStr"/>
-      <c r="D423" t="inlineStr">
+      <c r="C470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
         <is>
           <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：**默认只预览、不删**，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行</t>
         </is>
       </c>
     </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
+    <row r="471">
+      <c r="A471" t="inlineStr">
         <is>
           <t>检查答题记录数</t>
         </is>
       </c>
-      <c r="B424" t="inlineStr">
+      <c r="B471" t="inlineStr">
         <is>
           <t>活动名</t>
         </is>
       </c>
-      <c r="C424" t="inlineStr">
+      <c r="C471" t="inlineStr">
         <is>
           <t>期望条数</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr">
+      <c r="D471" t="inlineStr">
         <is>
           <t>读数据库，断言这个活动的**提交记录**正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关</t>
         </is>
       </c>
     </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
+    <row r="472">
+      <c r="A472" t="inlineStr">
         <is>
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr"/>
-      <c r="C425" t="inlineStr"/>
-      <c r="D425" t="inlineStr">
+      <c r="B472" t="inlineStr"/>
+      <c r="C472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
         <is>
           <t>打开案例库列表（**底部 tab「设计专区」打开就是它**，这是 2026/10/12 才找到的入口；页面顶部还有一排 tab：仿真案例库 / 压铸护航服务）</t>
         </is>
       </c>
     </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
+    <row r="473">
+      <c r="A473" t="inlineStr">
         <is>
           <t>检查案例库列表符合需求</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr"/>
-      <c r="C426" t="inlineStr"/>
-      <c r="D426" t="inlineStr">
+      <c r="B473" t="inlineStr"/>
+      <c r="C473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
         <is>
           <t>按需求 713381608 校验案例库列表页：① 分类**上方**有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「**复制图标 + 复制数**」，且整页找不到评论图标。只读</t>
         </is>
       </c>
     </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
+    <row r="474">
+      <c r="A474" t="inlineStr">
         <is>
           <t>打开第一个案例</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr"/>
-      <c r="C427" t="inlineStr"/>
-      <c r="D427" t="inlineStr">
+      <c r="B474" t="inlineStr"/>
+      <c r="C474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
         <is>
           <t>在案例库列表点开第一张卡片，进案例详情页（只读：不点赞、不收藏、不复制、不评论）</t>
         </is>
       </c>
     </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
+    <row r="475">
+      <c r="A475" t="inlineStr">
         <is>
           <t>打开案例</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr">
+      <c r="B475" t="inlineStr">
         <is>
           <t>案例名</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr">
+      <c r="C475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
         <is>
           <t>按名字点开指定案例（点不到会往下滚几屏再找）。给「付费案例复制」挑样本时用它，例如 填充任务1。只读：不点赞、不收藏、不复制</t>
         </is>
       </c>
     </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
+    <row r="476">
+      <c r="A476" t="inlineStr">
         <is>
           <t>检查案例详情页符合需求</t>
         </is>
       </c>
-      <c r="B429" t="inlineStr"/>
-      <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr">
+      <c r="B476" t="inlineStr"/>
+      <c r="C476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
         <is>
           <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部**没有**复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
         </is>
       </c>
     </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
+    <row r="477">
+      <c r="A477" t="inlineStr">
         <is>
           <t>打开案例库介绍长图</t>
         </is>
       </c>
-      <c r="B430" t="inlineStr"/>
-      <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr">
+      <c r="B477" t="inlineStr"/>
+      <c r="C477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
         <is>
           <t>点案例库首页那张介绍 banner（在分类上方），进「介绍长图详情页」。只读</t>
         </is>
       </c>
     </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
+    <row r="478">
+      <c r="A478" t="inlineStr">
         <is>
           <t>检查案例库介绍长图符合需求</t>
         </is>
       </c>
-      <c r="B431" t="inlineStr"/>
-      <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr">
+      <c r="B478" t="inlineStr"/>
+      <c r="C478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
         <is>
           <t>按需求 713381608 校验介绍长图页：整页是**单张图片**，而且是**长图**（图高远大于屏高）。只读</t>
         </is>
       </c>
     </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
+    <row r="479">
+      <c r="A479" t="inlineStr">
         <is>
           <t>复制当前案例</t>
         </is>
       </c>
-      <c r="B432" t="inlineStr"/>
-      <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr">
+      <c r="B479" t="inlineStr"/>
+      <c r="C479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
         <is>
           <t>在案例详情页点「复制案例」—— **一条龙**：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → **自动复位**（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
         </is>
       </c>
     </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
+    <row r="480">
+      <c r="A480" t="inlineStr">
         <is>
           <t>打开课程详情</t>
         </is>
       </c>
-      <c r="B433" t="inlineStr">
+      <c r="B480" t="inlineStr">
         <is>
           <t>课程名</t>
         </is>
       </c>
-      <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr">
+      <c r="C480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
         <is>
           <t>打开某门课的详情页（学习页）：自己走到 学习中心 → 课程 tab → 按名字点课程。只读：不播放视频、不购买。课程名要跟列表上一字不差，例如 717</t>
         </is>
       </c>
     </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
+    <row r="481">
+      <c r="A481" t="inlineStr">
         <is>
           <t>检查课程详情页符合需求</t>
         </is>
       </c>
-      <c r="B434" t="inlineStr">
+      <c r="B481" t="inlineStr">
         <is>
           <t>期望默认选中的tab</t>
         </is>
       </c>
-      <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
+      <c r="C481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
         <is>
           <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、**默认选中填的那个**（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
         </is>
       </c>
     </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
+    <row r="482">
+      <c r="A482" t="inlineStr">
         <is>
           <t>检查课时数为0的课程不显示</t>
         </is>
       </c>
-      <c r="B435" t="inlineStr"/>
-      <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
+      <c r="B482" t="inlineStr"/>
+      <c r="C482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
         <is>
           <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字**一个都没出现在**小程序的课程列表里（会自己滚到列表底部）。只读</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>检查未购买点课时不改变封面标题</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>课程名</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>按需求 713367615 第 2 条校验：**未购买**的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号**没买过**的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
         </is>
       </c>
     </row>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1120,11 +1120,6 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>活动入口_001</t>
-        </is>
-      </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
@@ -1165,11 +1160,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>搜索页_001</t>
-        </is>
-      </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
@@ -1190,11 +1180,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>搜索页_001</t>
-        </is>
-      </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
@@ -1215,11 +1200,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>搜索页_001</t>
-        </is>
-      </c>
       <c r="C7" t="n">
         <v>4</v>
       </c>
@@ -1260,11 +1240,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>答题页_001</t>
-        </is>
-      </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
@@ -1280,11 +1255,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>答题页_001</t>
-        </is>
-      </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
@@ -1305,11 +1275,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>答题页_001</t>
-        </is>
-      </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
@@ -1330,11 +1295,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>答题页_001</t>
-        </is>
-      </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
@@ -1375,11 +1335,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>学习中心_001</t>
-        </is>
-      </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
@@ -1395,11 +1350,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>学习中心_001</t>
-        </is>
-      </c>
       <c r="C15" t="n">
         <v>3</v>
       </c>
@@ -1420,11 +1370,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>学习中心_001</t>
-        </is>
-      </c>
       <c r="C16" t="n">
         <v>4</v>
       </c>
@@ -1460,11 +1405,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>积分商城_001</t>
-        </is>
-      </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
@@ -1475,11 +1415,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>积分商城_001</t>
-        </is>
-      </c>
       <c r="C19" t="n">
         <v>3</v>
       </c>
@@ -1495,11 +1430,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>积分商城_001</t>
-        </is>
-      </c>
       <c r="C20" t="n">
         <v>4</v>
       </c>
@@ -1530,11 +1460,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>学习中心_002</t>
-        </is>
-      </c>
       <c r="C22" t="n">
         <v>2</v>
       </c>
@@ -1545,11 +1470,6 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>学习中心_002</t>
-        </is>
-      </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
@@ -1565,11 +1485,6 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>学习中心_002</t>
-        </is>
-      </c>
       <c r="C24" t="n">
         <v>4</v>
       </c>
@@ -1600,11 +1515,6 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>搜索消失_001</t>
-        </is>
-      </c>
       <c r="C26" t="n">
         <v>2</v>
       </c>
@@ -1620,11 +1530,6 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>搜索消失_001</t>
-        </is>
-      </c>
       <c r="C27" t="n">
         <v>3</v>
       </c>
@@ -1640,11 +1545,6 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>搜索消失_001</t>
-        </is>
-      </c>
       <c r="C28" t="n">
         <v>4</v>
       </c>
@@ -1660,11 +1560,6 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>搜索消失_001</t>
-        </is>
-      </c>
       <c r="C29" t="n">
         <v>5</v>
       </c>
@@ -1700,11 +1595,6 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
       <c r="C31" t="n">
         <v>2</v>
       </c>
@@ -1720,11 +1610,6 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
       <c r="C32" t="n">
         <v>3</v>
       </c>
@@ -1745,11 +1630,6 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
       <c r="C33" t="n">
         <v>4</v>
       </c>
@@ -1765,11 +1645,6 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
       <c r="C34" t="n">
         <v>5</v>
       </c>
@@ -1790,11 +1665,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
       <c r="C35" t="n">
         <v>6</v>
       </c>
@@ -1820,11 +1690,6 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
       <c r="C36" t="n">
         <v>7</v>
       </c>
@@ -1850,11 +1715,6 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
       <c r="C37" t="n">
         <v>8</v>
       </c>
@@ -1875,11 +1735,6 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
       <c r="C38" t="n">
         <v>9</v>
       </c>
@@ -1900,11 +1755,6 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
       <c r="C39" t="n">
         <v>10</v>
       </c>
@@ -1930,11 +1780,6 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
       <c r="C40" t="n">
         <v>11</v>
       </c>
@@ -1945,11 +1790,6 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
       <c r="C41" t="n">
         <v>12</v>
       </c>
@@ -1960,11 +1800,6 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
       <c r="C42" t="n">
         <v>13</v>
       </c>
@@ -1975,11 +1810,6 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
       <c r="C43" t="n">
         <v>14</v>
       </c>
@@ -1995,11 +1825,6 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
       <c r="C44" t="n">
         <v>15</v>
       </c>
@@ -2015,11 +1840,6 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
       <c r="C45" t="n">
         <v>16</v>
       </c>
@@ -2035,11 +1855,6 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
       <c r="C46" t="n">
         <v>17</v>
       </c>
@@ -2050,11 +1865,6 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
       <c r="C47" t="n">
         <v>18</v>
       </c>
@@ -2090,11 +1900,6 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>搜索空态_001</t>
-        </is>
-      </c>
       <c r="C49" t="n">
         <v>2</v>
       </c>
@@ -2115,11 +1920,6 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>搜索空态_001</t>
-        </is>
-      </c>
       <c r="C50" t="n">
         <v>3</v>
       </c>
@@ -2135,11 +1935,6 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>搜索空态_001</t>
-        </is>
-      </c>
       <c r="C51" t="n">
         <v>4</v>
       </c>
@@ -2160,11 +1955,6 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>搜索空态_001</t>
-        </is>
-      </c>
       <c r="C52" t="n">
         <v>5</v>
       </c>
@@ -2185,11 +1975,6 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>搜索空态_001</t>
-        </is>
-      </c>
       <c r="C53" t="n">
         <v>6</v>
       </c>
@@ -2230,11 +2015,6 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>搜索空态_002</t>
-        </is>
-      </c>
       <c r="C55" t="n">
         <v>2</v>
       </c>
@@ -2255,11 +2035,6 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>搜索空态_002</t>
-        </is>
-      </c>
       <c r="C56" t="n">
         <v>3</v>
       </c>
@@ -2270,11 +2045,6 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>搜索空态_002</t>
-        </is>
-      </c>
       <c r="C57" t="n">
         <v>4</v>
       </c>
@@ -2295,11 +2065,6 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>搜索空态_002</t>
-        </is>
-      </c>
       <c r="C58" t="n">
         <v>5</v>
       </c>
@@ -2320,11 +2085,6 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>搜索空态_002</t>
-        </is>
-      </c>
       <c r="C59" t="n">
         <v>6</v>
       </c>
@@ -2365,11 +2125,6 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>回到顶部_001</t>
-        </is>
-      </c>
       <c r="C61" t="n">
         <v>2</v>
       </c>
@@ -2385,11 +2140,6 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>回到顶部_001</t>
-        </is>
-      </c>
       <c r="C62" t="n">
         <v>3</v>
       </c>
@@ -2405,11 +2155,6 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>回到顶部_001</t>
-        </is>
-      </c>
       <c r="C63" t="n">
         <v>4</v>
       </c>
@@ -2450,11 +2195,6 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>搜索话题_001</t>
-        </is>
-      </c>
       <c r="C65" t="n">
         <v>2</v>
       </c>
@@ -2470,11 +2210,6 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>搜索话题_001</t>
-        </is>
-      </c>
       <c r="C66" t="n">
         <v>3</v>
       </c>
@@ -2500,11 +2235,6 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>搜索话题_001</t>
-        </is>
-      </c>
       <c r="C67" t="n">
         <v>4</v>
       </c>
@@ -2520,11 +2250,6 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>搜索话题_001</t>
-        </is>
-      </c>
       <c r="C68" t="n">
         <v>5</v>
       </c>
@@ -2545,11 +2270,6 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>搜索话题_001</t>
-        </is>
-      </c>
       <c r="C69" t="n">
         <v>6</v>
       </c>
@@ -2570,11 +2290,6 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>搜索话题_001</t>
-        </is>
-      </c>
       <c r="C70" t="n">
         <v>7</v>
       </c>
@@ -2615,11 +2330,6 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>帖子主页按钮_001</t>
-        </is>
-      </c>
       <c r="C72" t="n">
         <v>2</v>
       </c>
@@ -2635,11 +2345,6 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>帖子主页按钮_001</t>
-        </is>
-      </c>
       <c r="C73" t="n">
         <v>3</v>
       </c>
@@ -2655,11 +2360,6 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>帖子主页按钮_001</t>
-        </is>
-      </c>
       <c r="C74" t="n">
         <v>4</v>
       </c>
@@ -2680,11 +2380,6 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>帖子主页按钮_001</t>
-        </is>
-      </c>
       <c r="C75" t="n">
         <v>5</v>
       </c>
@@ -2705,11 +2400,6 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>帖子主页按钮_001</t>
-        </is>
-      </c>
       <c r="C76" t="n">
         <v>6</v>
       </c>
@@ -2750,11 +2440,6 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>首页tab顺序_001</t>
-        </is>
-      </c>
       <c r="C78" t="n">
         <v>2</v>
       </c>
@@ -2770,11 +2455,6 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>首页tab顺序_001</t>
-        </is>
-      </c>
       <c r="C79" t="n">
         <v>3</v>
       </c>
@@ -2815,11 +2495,6 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>案例库_001</t>
-        </is>
-      </c>
       <c r="C81" t="n">
         <v>2</v>
       </c>
@@ -2835,11 +2510,6 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>案例库_001</t>
-        </is>
-      </c>
       <c r="C82" t="n">
         <v>3</v>
       </c>
@@ -2855,11 +2525,6 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>案例库_001</t>
-        </is>
-      </c>
       <c r="C83" t="n">
         <v>4</v>
       </c>
@@ -2875,11 +2540,6 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>案例库_001</t>
-        </is>
-      </c>
       <c r="C84" t="n">
         <v>5</v>
       </c>
@@ -2895,11 +2555,6 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>案例库_001</t>
-        </is>
-      </c>
       <c r="C85" t="n">
         <v>6</v>
       </c>
@@ -2915,11 +2570,6 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>案例库_001</t>
-        </is>
-      </c>
       <c r="C86" t="n">
         <v>7</v>
       </c>
@@ -2935,11 +2585,6 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>案例库_001</t>
-        </is>
-      </c>
       <c r="C87" t="n">
         <v>8</v>
       </c>
@@ -2955,11 +2600,6 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>案例库_001</t>
-        </is>
-      </c>
       <c r="C88" t="n">
         <v>9</v>
       </c>
@@ -3000,11 +2640,6 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>案例库_002</t>
-        </is>
-      </c>
       <c r="C90" t="n">
         <v>2</v>
       </c>
@@ -3020,11 +2655,6 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>案例库_002</t>
-        </is>
-      </c>
       <c r="C91" t="n">
         <v>3</v>
       </c>
@@ -3040,11 +2670,6 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>案例库_002</t>
-        </is>
-      </c>
       <c r="C92" t="n">
         <v>4</v>
       </c>
@@ -3060,11 +2685,6 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>案例库_002</t>
-        </is>
-      </c>
       <c r="C93" t="n">
         <v>5</v>
       </c>
@@ -3085,11 +2705,6 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>案例库_002</t>
-        </is>
-      </c>
       <c r="C94" t="n">
         <v>6</v>
       </c>
@@ -3130,11 +2745,6 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>课程详情_001</t>
-        </is>
-      </c>
       <c r="C96" t="n">
         <v>2</v>
       </c>
@@ -3155,11 +2765,6 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>课程详情_001</t>
-        </is>
-      </c>
       <c r="C97" t="n">
         <v>3</v>
       </c>
@@ -3180,11 +2785,6 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>课程详情_001</t>
-        </is>
-      </c>
       <c r="C98" t="n">
         <v>4</v>
       </c>
@@ -3225,11 +2825,6 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>课程列表_001</t>
-        </is>
-      </c>
       <c r="C100" t="n">
         <v>2</v>
       </c>
@@ -3245,11 +2840,6 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>课程列表_001</t>
-        </is>
-      </c>
       <c r="C101" t="n">
         <v>3</v>
       </c>
@@ -3270,11 +2860,6 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>课程列表_001</t>
-        </is>
-      </c>
       <c r="C102" t="n">
         <v>4</v>
       </c>
@@ -3290,11 +2875,6 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>课程列表_001</t>
-        </is>
-      </c>
       <c r="C103" t="n">
         <v>5</v>
       </c>
@@ -3335,11 +2915,6 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>案例库_003</t>
-        </is>
-      </c>
       <c r="C105" t="n">
         <v>2</v>
       </c>
@@ -3355,11 +2930,6 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>案例库_003</t>
-        </is>
-      </c>
       <c r="C106" t="n">
         <v>3</v>
       </c>
@@ -3380,11 +2950,6 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>案例库_003</t>
-        </is>
-      </c>
       <c r="C107" t="n">
         <v>4</v>
       </c>
@@ -3400,11 +2965,6 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>案例库_003</t>
-        </is>
-      </c>
       <c r="C108" t="n">
         <v>5</v>
       </c>
@@ -3425,11 +2985,6 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>案例库_003</t>
-        </is>
-      </c>
       <c r="C109" t="n">
         <v>6</v>
       </c>
@@ -3470,11 +3025,6 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>课程详情_002</t>
-        </is>
-      </c>
       <c r="C111" t="n">
         <v>2</v>
       </c>
@@ -3495,11 +3045,6 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>课程详情_002</t>
-        </is>
-      </c>
       <c r="C112" t="n">
         <v>3</v>
       </c>
@@ -3520,11 +3065,6 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>课程详情_002</t>
-        </is>
-      </c>
       <c r="C113" t="n">
         <v>4</v>
       </c>
@@ -3540,6 +3080,48 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="40">
+    <mergeCell ref="A80:A88"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="B99:B103"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B71:B76"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="B30:B47"/>
+    <mergeCell ref="B64:B70"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A54:A59"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A95:A98"/>
+    <mergeCell ref="B80:B88"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="A89:A94"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="B60:B63"/>
+    <mergeCell ref="B25:B29"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="A64:A70"/>
+    <mergeCell ref="A104:A109"/>
+    <mergeCell ref="B95:B98"/>
+    <mergeCell ref="A30:A47"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B89:B94"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="A25:A29"/>
+    <mergeCell ref="A99:A103"/>
+    <mergeCell ref="B104:B109"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="B54:B59"/>
+  </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
       <formula1>='动作清单'!$A$2:$A$48</formula1>
@@ -3558,7 +3140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D483"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3568,1220 +3150,780 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="n"/>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436">
-      <c r="A436" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>动作</t>
         </is>
       </c>
-      <c r="B436" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="C436" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="B437" t="inlineStr"/>
-      <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr">
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t>自导航到「有问必答」首页（幂等；当前在二级页时会自动点返回）。用例第一步建议都用它</t>
         </is>
       </c>
     </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="B438" t="inlineStr"/>
-      <c r="C438" t="inlineStr"/>
-      <c r="D438" t="inlineStr">
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
         <is>
           <t>点底部 tab「我的」，进入用户中心</t>
         </is>
       </c>
     </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>打开积分商城</t>
         </is>
       </c>
-      <c r="B439" t="inlineStr"/>
-      <c r="C439" t="inlineStr"/>
-      <c r="D439" t="inlineStr">
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
         <is>
           <t>从用户中心点「积分商城」进商城首页（已在则原地不动）。积分商城是二级页，没有底部 tab 栏</t>
         </is>
       </c>
     </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="B440" t="inlineStr"/>
-      <c r="C440" t="inlineStr"/>
-      <c r="D440" t="inlineStr">
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
         <is>
           <t>进学习中心，并切到「专栏」列表</t>
         </is>
       </c>
     </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="B441" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="C441" t="inlineStr"/>
-      <c r="D441" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
         <is>
           <t>点搜索栏进搜索页并输入关键词。注意：只能是字母/数字/下划线/点/连字符（adb 不支持中文输入）</t>
         </is>
       </c>
     </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="B442" t="inlineStr"/>
-      <c r="C442" t="inlineStr"/>
-      <c r="D442" t="inlineStr">
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
         <is>
           <t>只进搜索页、不输入关键词（搜索页上能看到「搜索历史」和「热门话题」）</t>
         </is>
       </c>
     </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>点第一个热门话题</t>
         </is>
       </c>
-      <c r="B443" t="inlineStr"/>
-      <c r="C443" t="inlineStr"/>
-      <c r="D443" t="inlineStr">
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t>点搜索页「热门话题」里的第 1 条，跳转到该话题的搜索结果页（需求 713129788）</t>
         </is>
       </c>
     </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>打开第一个帖子</t>
         </is>
       </c>
-      <c r="B444" t="inlineStr"/>
-      <c r="C444" t="inlineStr"/>
-      <c r="D444" t="inlineStr">
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
         <is>
           <t>在首页信息流点第一张帖子卡片，进帖子详情页（只读：不点赞、不评论）</t>
         </is>
       </c>
     </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>点主页按钮</t>
         </is>
       </c>
-      <c r="B445" t="inlineStr"/>
-      <c r="C445" t="inlineStr"/>
-      <c r="D445" t="inlineStr">
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
         <is>
           <t>点二级页导航栏上的「主页」图标回到首页（需求 713256065 的返回首页那半句）</t>
         </is>
       </c>
     </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="B446" t="inlineStr"/>
-      <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr">
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t>在搜索页按回车把搜索跑起来（只读：只是查一次）。不执行的话停在「搜索历史」面板，看不到结果页/空态</t>
         </is>
       </c>
     </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="B447" t="inlineStr"/>
-      <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr">
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
     </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>点文字</t>
         </is>
       </c>
-      <c r="B448" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
         </is>
       </c>
     </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="B449" t="inlineStr"/>
-      <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr">
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>点返回按钮退回上一页（会校验页面确实变了）</t>
         </is>
       </c>
     </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>等待</t>
         </is>
       </c>
-      <c r="B450" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>毫秒</t>
         </is>
       </c>
-      <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
     </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="B451" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
     </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>检查文字不显示</t>
         </is>
       </c>
-      <c r="B452" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>断言页面上看不见这段文字</t>
         </is>
       </c>
     </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="B453" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>检查元素数量</t>
         </is>
       </c>
-      <c r="B454" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C454" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>期望数量</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
     </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>检查答题页符合需求</t>
         </is>
       </c>
-      <c r="B455" t="inlineStr"/>
-      <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr">
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于**一道题**的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
     </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="B456" t="inlineStr"/>
-      <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr">
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
     </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>检查首页tab顺序</t>
         </is>
       </c>
-      <c r="B457" t="inlineStr"/>
-      <c r="C457" t="inlineStr"/>
-      <c r="D457" t="inlineStr">
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
         </is>
       </c>
     </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>检查回到顶部按钮</t>
         </is>
       </c>
-      <c r="B458" t="inlineStr"/>
-      <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr">
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
         </is>
       </c>
     </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="B459" t="inlineStr"/>
-      <c r="C459" t="inlineStr"/>
-      <c r="D459" t="inlineStr">
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
         <is>
           <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
         </is>
       </c>
     </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>点选择器</t>
         </is>
       </c>
-      <c r="B460" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C460" t="inlineStr"/>
-      <c r="D460" t="inlineStr">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
         <is>
           <t>按选择器点第一处元素（比按文字点更准：文字有重名时用它），例如 .search-container</t>
         </is>
       </c>
     </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>滑动</t>
         </is>
       </c>
-      <c r="B461" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>次数</t>
         </is>
       </c>
-      <c r="C461" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
         </is>
       </c>
     </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>切换筛选tab</t>
         </is>
       </c>
-      <c r="B462" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="C462" t="inlineStr"/>
-      <c r="D462" t="inlineStr">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>切换学习中心顶部tab</t>
         </is>
       </c>
-      <c r="B463" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>tab名</t>
         </is>
       </c>
-      <c r="C463" t="inlineStr"/>
-      <c r="D463" t="inlineStr">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
         <is>
           <t>切学习中心顶部那排 tab（切完会验证真的选中了）</t>
         </is>
       </c>
     </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>点第一张专栏</t>
         </is>
       </c>
-      <c r="B464" t="inlineStr"/>
-      <c r="C464" t="inlineStr"/>
-      <c r="D464" t="inlineStr">
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t>在学习中心的专栏列表里点第一张卡，进它的详情页</t>
         </is>
       </c>
     </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>检查输入框的值</t>
         </is>
       </c>
-      <c r="B465" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C465" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>期望值</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
     </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>检查文字出现次数</t>
         </is>
       </c>
-      <c r="B466" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C466" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>期望次数</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
         </is>
       </c>
     </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>检查元素不存在</t>
         </is>
       </c>
-      <c r="B467" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C467" t="inlineStr"/>
-      <c r="D467" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
         <is>
           <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
         </is>
       </c>
     </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>逐题作答</t>
         </is>
       </c>
-      <c r="B468" t="inlineStr"/>
-      <c r="C468" t="inlineStr"/>
-      <c r="D468" t="inlineStr">
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
         <is>
           <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、**不写库**，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
         </is>
       </c>
     </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>提交答卷</t>
         </is>
       </c>
-      <c r="B469" t="inlineStr"/>
-      <c r="C469" t="inlineStr"/>
-      <c r="D469" t="inlineStr">
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
         <is>
           <t>点答题页的提交按钮 —— **会真的写数据**。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
         </is>
       </c>
     </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>复位答题记录</t>
         </is>
       </c>
-      <c r="B470" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>活动名</t>
         </is>
       </c>
-      <c r="C470" t="inlineStr"/>
-      <c r="D470" t="inlineStr">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
         <is>
           <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：**默认只预览、不删**，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行</t>
         </is>
       </c>
     </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>检查答题记录数</t>
         </is>
       </c>
-      <c r="B471" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>活动名</t>
         </is>
       </c>
-      <c r="C471" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>期望条数</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>读数据库，断言这个活动的**提交记录**正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关</t>
         </is>
       </c>
     </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="B472" t="inlineStr"/>
-      <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr">
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
         <is>
           <t>打开案例库列表（**底部 tab「设计专区」打开就是它**，这是 2026/10/12 才找到的入口；页面顶部还有一排 tab：仿真案例库 / 压铸护航服务）</t>
         </is>
       </c>
     </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>检查案例库列表符合需求</t>
         </is>
       </c>
-      <c r="B473" t="inlineStr"/>
-      <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr">
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
         <is>
           <t>按需求 713381608 校验案例库列表页：① 分类**上方**有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「**复制图标 + 复制数**」，且整页找不到评论图标。只读</t>
         </is>
       </c>
     </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>打开第一个案例</t>
         </is>
       </c>
-      <c r="B474" t="inlineStr"/>
-      <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr">
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
         <is>
           <t>在案例库列表点开第一张卡片，进案例详情页（只读：不点赞、不收藏、不复制、不评论）</t>
         </is>
       </c>
     </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>打开案例</t>
         </is>
       </c>
-      <c r="B475" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>案例名</t>
         </is>
       </c>
-      <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
         <is>
           <t>按名字点开指定案例（点不到会往下滚几屏再找）。给「付费案例复制」挑样本时用它，例如 填充任务1。只读：不点赞、不收藏、不复制</t>
         </is>
       </c>
     </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>检查案例详情页符合需求</t>
         </is>
       </c>
-      <c r="B476" t="inlineStr"/>
-      <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr">
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
         <is>
           <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部**没有**复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
         </is>
       </c>
     </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>打开案例库介绍长图</t>
         </is>
       </c>
-      <c r="B477" t="inlineStr"/>
-      <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr">
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
         <is>
           <t>点案例库首页那张介绍 banner（在分类上方），进「介绍长图详情页」。只读</t>
         </is>
       </c>
     </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>检查案例库介绍长图符合需求</t>
         </is>
       </c>
-      <c r="B478" t="inlineStr"/>
-      <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr">
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
         <is>
           <t>按需求 713381608 校验介绍长图页：整页是**单张图片**，而且是**长图**（图高远大于屏高）。只读</t>
         </is>
       </c>
     </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>复制当前案例</t>
         </is>
       </c>
-      <c r="B479" t="inlineStr"/>
-      <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr">
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
         <is>
           <t>在案例详情页点「复制案例」—— **一条龙**：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → **自动复位**（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
         </is>
       </c>
     </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>打开课程详情</t>
         </is>
       </c>
-      <c r="B480" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>课程名</t>
         </is>
       </c>
-      <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr">
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
         <is>
           <t>打开某门课的详情页（学习页）：自己走到 学习中心 → 课程 tab → 按名字点课程。只读：不播放视频、不购买。课程名要跟列表上一字不差，例如 717</t>
         </is>
       </c>
     </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>检查课程详情页符合需求</t>
         </is>
       </c>
-      <c r="B481" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>期望默认选中的tab</t>
         </is>
       </c>
-      <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr">
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
         <is>
           <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、**默认选中填的那个**（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
         </is>
       </c>
     </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>检查课时数为0的课程不显示</t>
         </is>
       </c>
-      <c r="B482" t="inlineStr"/>
-      <c r="C482" t="inlineStr"/>
-      <c r="D482" t="inlineStr">
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
         <is>
           <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字**一个都没出现在**小程序的课程列表里（会自己滚到列表底部）。只读</t>
         </is>
       </c>
     </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>检查未购买点课时不改变封面标题</t>
         </is>
       </c>
-      <c r="B483" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>课程名</t>
         </is>
       </c>
-      <c r="C483" t="inlineStr"/>
-      <c r="D483" t="inlineStr">
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
         <is>
           <t>按需求 713367615 第 2 条校验：**未购买**的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号**没买过**的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
         </is>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -3082,8 +3082,8 @@
   </sheetData>
   <mergeCells count="40">
     <mergeCell ref="A80:A88"/>
+    <mergeCell ref="A110:A113"/>
     <mergeCell ref="A48:A53"/>
-    <mergeCell ref="A110:A113"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="A60:A63"/>
     <mergeCell ref="B21:B24"/>
@@ -3101,25 +3101,25 @@
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="B80:B88"/>
     <mergeCell ref="A71:A76"/>
+    <mergeCell ref="B13:B16"/>
     <mergeCell ref="A89:A94"/>
-    <mergeCell ref="B13:B16"/>
     <mergeCell ref="B60:B63"/>
     <mergeCell ref="B25:B29"/>
     <mergeCell ref="A17:A20"/>
     <mergeCell ref="A64:A70"/>
     <mergeCell ref="A104:A109"/>
     <mergeCell ref="B95:B98"/>
+    <mergeCell ref="B110:B113"/>
     <mergeCell ref="A30:A47"/>
+    <mergeCell ref="A13:A16"/>
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A13:A16"/>
     <mergeCell ref="B89:B94"/>
     <mergeCell ref="B77:B79"/>
+    <mergeCell ref="A25:A29"/>
+    <mergeCell ref="B8:B12"/>
     <mergeCell ref="B4:B7"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="A25:A29"/>
     <mergeCell ref="A99:A103"/>
     <mergeCell ref="B104:B109"/>
-    <mergeCell ref="B110:B113"/>
     <mergeCell ref="B54:B59"/>
   </mergeCells>
   <dataValidations count="2">
@@ -3140,13 +3140,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="78" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="78" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3167,6 +3168,11 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>会不会改数据</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>说明</t>
         </is>
       </c>
@@ -3181,7 +3187,12 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>自导航到「有问必答」首页（幂等；当前在二级页时会自动点返回）。用例第一步建议都用它</t>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>自导航到「有问必答」首页信息流（幂等；在二级页/搜索页会先点返回退出），并把筛选 tab 归位到「最新提问」。用例第一步建议都用它</t>
         </is>
       </c>
     </row>
@@ -3195,6 +3206,11 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>点底部 tab「我的」，进入用户中心</t>
         </is>
       </c>
@@ -3209,6 +3225,11 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>从用户中心点「积分商城」进商城首页（已在则原地不动）。积分商城是二级页，没有底部 tab 栏</t>
         </is>
       </c>
@@ -3223,6 +3244,11 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>进学习中心，并切到「专栏」列表</t>
         </is>
       </c>
@@ -3240,6 +3266,11 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>点搜索栏进搜索页并输入关键词。注意：只能是字母/数字/下划线/点/连字符（adb 不支持中文输入）</t>
         </is>
@@ -3255,6 +3286,11 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>只进搜索页、不输入关键词（搜索页上能看到「搜索历史」和「热门话题」）</t>
         </is>
       </c>
@@ -3269,6 +3305,11 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>点搜索页「热门话题」里的第 1 条，跳转到该话题的搜索结果页（需求 713129788）</t>
         </is>
       </c>
@@ -3283,6 +3324,11 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>在首页信息流点第一张帖子卡片，进帖子详情页（只读：不点赞、不评论）</t>
         </is>
       </c>
@@ -3297,6 +3343,11 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>点二级页导航栏上的「主页」图标回到首页（需求 713256065 的返回首页那半句）</t>
         </is>
       </c>
@@ -3311,6 +3362,11 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>在搜索页按回车把搜索跑起来（只读：只是查一次）。不执行的话停在「搜索历史」面板，看不到结果页/空态</t>
         </is>
       </c>
@@ -3325,6 +3381,11 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
@@ -3342,6 +3403,11 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
+        <is>
+          <t>会（提交/兑换/支付类文字已被默认拦住）</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
         </is>
@@ -3357,6 +3423,11 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>点返回按钮退回上一页（会校验页面确实变了）</t>
         </is>
       </c>
@@ -3375,6 +3446,11 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
@@ -3393,6 +3469,11 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
@@ -3411,6 +3492,11 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>断言页面上看不见这段文字</t>
         </is>
       </c>
@@ -3429,6 +3515,11 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
@@ -3450,6 +3541,11 @@
         </is>
       </c>
       <c r="D19" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
@@ -3465,6 +3561,11 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于**一道题**的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
@@ -3479,6 +3580,11 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
@@ -3493,6 +3599,11 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
         </is>
       </c>
@@ -3507,6 +3618,11 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
         </is>
       </c>
@@ -3521,6 +3637,11 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
         </is>
       </c>
@@ -3539,6 +3660,11 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
+          <t>会（和「点文字」同一道安全阀）</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>按选择器点第一处元素（比按文字点更准：文字有重名时用它），例如 .search-container</t>
         </is>
       </c>
@@ -3561,6 +3687,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
         </is>
       </c>
@@ -3579,6 +3710,11 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
         </is>
       </c>
@@ -3596,6 +3732,11 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>切学习中心顶部那排 tab（切完会验证真的选中了）</t>
         </is>
@@ -3611,6 +3752,11 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>在学习中心的专栏列表里点第一张卡，进它的详情页</t>
         </is>
       </c>
@@ -3633,6 +3779,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
@@ -3655,6 +3806,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
         </is>
       </c>
@@ -3672,6 +3828,11 @@
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
         </is>
@@ -3687,6 +3848,11 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
+          <t>只改前端选中态（不写库、不需要开关）</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、**不写库**，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
         </is>
       </c>
@@ -3701,6 +3867,11 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
+          <t>**会写库**（必须开开关）</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>点答题页的提交按钮 —— **会真的写数据**。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
         </is>
       </c>
@@ -3719,6 +3890,11 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
+          <t>**会删库**（默认只预览；真删要开开关）</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：**默认只预览、不删**，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行</t>
         </is>
       </c>
@@ -3740,6 +3916,11 @@
         </is>
       </c>
       <c r="D36" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>读数据库，断言这个活动的**提交记录**正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关</t>
         </is>
@@ -3755,6 +3936,11 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>打开案例库列表（**底部 tab「设计专区」打开就是它**，这是 2026/10/12 才找到的入口；页面顶部还有一排 tab：仿真案例库 / 压铸护航服务）</t>
         </is>
       </c>
@@ -3769,6 +3955,11 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>按需求 713381608 校验案例库列表页：① 分类**上方**有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「**复制图标 + 复制数**」，且整页找不到评论图标。只读</t>
         </is>
       </c>
@@ -3783,6 +3974,11 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>在案例库列表点开第一张卡片，进案例详情页（只读：不点赞、不收藏、不复制、不评论）</t>
         </is>
       </c>
@@ -3800,6 +3996,11 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>按名字点开指定案例（点不到会往下滚几屏再找）。给「付费案例复制」挑样本时用它，例如 填充任务1。只读：不点赞、不收藏、不复制</t>
         </is>
@@ -3815,6 +4016,11 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部**没有**复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
         </is>
       </c>
@@ -3829,6 +4035,11 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>点案例库首页那张介绍 banner（在分类上方），进「介绍长图详情页」。只读</t>
         </is>
       </c>
@@ -3843,6 +4054,11 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>按需求 713381608 校验介绍长图页：整页是**单张图片**，而且是**长图**（图高远大于屏高）。只读</t>
         </is>
       </c>
@@ -3857,6 +4073,11 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
+          <t>**会写库**（要开开关；没开时记跳过）</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>在案例详情页点「复制案例」—— **一条龙**：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → **自动复位**（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
         </is>
       </c>
@@ -3875,6 +4096,11 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>打开某门课的详情页（学习页）：自己走到 学习中心 → 课程 tab → 按名字点课程。只读：不播放视频、不购买。课程名要跟列表上一字不差，例如 717</t>
         </is>
       </c>
@@ -3892,6 +4118,11 @@
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、**默认选中填的那个**（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
         </is>
@@ -3907,6 +4138,11 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字**一个都没出现在**小程序的课程列表里（会自己滚到列表底部）。只读</t>
         </is>
       </c>
@@ -3924,6 +4160,11 @@
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>按需求 713367615 第 2 条校验：**未购买**的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号**没买过**的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
         </is>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -9,6 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动作清单" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名称候选" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -3321,8 +3322,8 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="3"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="78" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
@@ -3464,7 +3465,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>tab名</t>
+          <t>顶部栏名称（只能填：课程 / 专栏 / 压铸百科）</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -3571,7 +3572,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>打开案例库列表（**底部 tab「设计专区」打开就是它**，这是 2026/10/12 才找到的入口；页面顶部还有一排 tab：仿真案例库 / 压铸护航服务）</t>
+          <t>打开案例库列表（底部 tab「设计专区」打开就是它，这是 2026/10/12 才找到的入口；页面顶部还有一排 tab：仿真案例库 / 压铸护航服务）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3599,7 +3600,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>打开某门课的详情页（学习页）：自己走到 学习中心 → 课程 tab → 按名字点课程。只读：不播放视频、不购买。课程名要跟列表上一字不差，例如 717</t>
+          <t>打开某门课的详情页（学习页）：自己走到 学习中心 → 课程 tab → 按名字点课程。只读：不播放视频、不购买。课程名要跟列表上一字不差，例如 717（「课程名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3799,7 +3800,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>按名字点开指定案例（点不到会往下滚几屏再找）。给「付费案例复制」挑样本时用它，例如 填充任务1。只读：不点赞、不收藏、不复制</t>
+          <t>按名字点开指定案例（点不到会往下滚几屏再找）。给「付费案例复制」挑样本时用它，例如 填充任务1。只读：不点赞、不收藏、不复制（「案例名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3872,12 +3873,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>次数</t>
+          <t>次数（只能填：1 / 2 / 3 / 4 / 5 / 6 / 7 / 8 / 9 / 10）</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>方向</t>
+          <t>方向（只能填：上 / 下）</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3904,7 +3905,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>tab名</t>
+          <t>筛选栏名称（只能填：最新提问 / 推荐 / 精选问答 / 我的关注）</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -4045,7 +4046,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>期望次数</t>
+          <t>期望次数（只能填：1 / 2 / 3 / 4 / 5）</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4271,7 +4272,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于**一道题**的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
+          <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于一道题的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4295,7 +4296,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验案例库列表页：① 分类**上方**有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「**复制图标 + 复制数**」，且整页找不到评论图标。只读</t>
+          <t>按需求 713381608 校验案例库列表页：① 分类上方有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「复制图标 + 复制数」，且整页找不到评论图标。只读</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4319,7 +4320,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部**没有**复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
+          <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部没有复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4343,7 +4344,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验介绍长图页：整页是**单张图片**，而且是**长图**（图高远大于屏高）。只读</t>
+          <t>按需求 713381608 校验介绍长图页：整页是单张图片，而且是长图（图高远大于屏高）。只读</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4360,7 +4361,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>期望默认选中的tab</t>
+          <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -4371,7 +4372,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、**默认选中填的那个**（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
+          <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、默认选中填的那个（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4395,7 +4396,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字**一个都没出现在**小程序的课程列表里（会自己滚到列表底部）。只读</t>
+          <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字一个都没出现在小程序的课程列表里（会自己滚到列表底部）。只读</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4423,7 +4424,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>按需求 713367615 第 2 条校验：**未购买**的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号**没买过**的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
+          <t>按需求 713367615 第 2 条校验：未购买的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号没买过的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4471,7 +4472,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、**不写库**，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
+          <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、不写库，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4490,12 +4491,12 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>**会写库**（必须开开关）</t>
+          <t>会写库（必须开开关）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>点答题页的提交按钮 —— **会真的写数据**。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
+          <t>点答题页的提交按钮 —— 会真的写数据。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4518,12 +4519,12 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>**会删库**（默认只预览；真删要开开关）</t>
+          <t>会删库（默认只预览；真删要开开关）</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：**默认只预览、不删**，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行</t>
+          <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：默认只预览、不删，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4555,7 +4556,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>读数据库，断言这个活动的**提交记录**正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关</t>
+          <t>读数据库，断言这个活动的提交记录正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4574,12 +4575,12 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>**会写库**（要开开关；没开时记跳过）</t>
+          <t>会写库（要开开关；没开时记跳过）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>在案例详情页点「复制案例」—— **一条龙**：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → **自动复位**（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
+          <t>在案例详情页点「复制案例」—— 一条龙：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → 自动复位（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4741,4 +4742,2405 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C154"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>名字</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>课程2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>课程3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>课程4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>课程4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>课程4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>012345678901234567890123456789</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>012345678901234567890123456789</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>模流仿真1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>设计提升1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>设计提升1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>免费课程</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>设计提升1-系列课程-付费</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>设计提升1-专项课程</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>设计提升1-专题课程</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>测试课程</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>无敌贵的课程</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>无敌贵的课程</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>无敌贵的课程</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>设计提升-专项-2分钟</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>免费课程</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>免费课程1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>免费课程1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>付费课程1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>付费课程2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>付费课程3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>付费课程4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>付费课程5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>付费课程7</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>付费课程8</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>付费课程9</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>付费课程10</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>付费课程11</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>付费课程12</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>付费课程13</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>免费课程-测ios1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>免费课程-测ios2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10-27</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>新增课题测试</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>12-8新增0元课程</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>付费课程1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>课程22222</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>设计提升1-专题课程-付费</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>测试验证课时bug</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>测试验证课时bug</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>测试封面图</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>测试封面图</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>测试封面图</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>测试封面图-修改</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>测试封面图-修改</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>测试封面图-修改</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>测试封面图-修改</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>测试封面图-修改</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>测试课程版本-v1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>测试课程版本-v1-v2</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>低洼瞧得起我</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>特别的名字</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>测试-11</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>4.16 创建课程</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5月18日课程</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>7.8课程new</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>买没买=是；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>test2</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>一二三四五六七八九十</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>id=352</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Z-题干图验证</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>id=349</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Z-导入床</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>id=348</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Z-B4-答题角标</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>id=347</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>答题</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>id=343</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>M1-六选项六图</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>id=340</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>L5-待开始14题</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>id=339</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>L4-排序3题</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>id=338</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>L3-导入床</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>id=337</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>L2-六选项多选</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>id=336</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>L1-规则200字</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>id=335</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>G1-三题型带答案</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>id=316</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>F4-1000分</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>id=315</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>F3-十分答题</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>id=314</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>F2-十分答题</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>id=313</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>F1-十分答题</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>id=312</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>id=311</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>id=310</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>积分上限</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>id=309</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>答题</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>id=304</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>B6-字段全覆盖</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>id=287</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>B5-导入床</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>id=269</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>B4-每日限开</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>id=268</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>B3-15题</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>id=267</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>B2-14题</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>id=266</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>B1-1题</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>id=265</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>A5-特殊字符</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>id=264</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>A4-不轮播</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>id=263</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>A1-答题</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>id=260</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>轮播-答题</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>id=255</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>方案一变形</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>仅凝固</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>仅充填2</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>充填凝固应力</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>充填凝固应力1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>7201744-孙</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>带组织性能结果</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>充填-排气</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1月 20250115</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>紫色1</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>内部数据6</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1QQ区qqqqq</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>重力铸造-重力砂型-0602-163625-仅充填仅浏览-重力铸造-重力砂型-0602-163625</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>重力铸造-重力砂型-0602-163625-充填凝固0602_165141-仅浏览</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>COPY3</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>3月26测试 私有材料分享(copy)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>内部数据-虚拟模具</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>内部数据</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>鹅鹅鹅</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>仅凝固+应力-选择点2</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>仅凝固1</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>循环凝固</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>131231</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>131231</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>循环凝固-热循环</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>6668</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>6668</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>填充任务1</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>0605测试</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>循环凝固+应力+选点1</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>料筒(copy)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>仅凝固</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>#713392277</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>？？？？</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>复制任务失败问题测试-分享</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>浇口充填-高级模式</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>热热热热</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>eeee</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>亲亲</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>3333 私有曲线</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>111111</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>测试二级页面案例111111111111111111111111111</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>分享高压 2</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>料筒充填</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>料筒充填1</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>料筒分享</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1WWWW</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>凝固应力</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>模拟汽车</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>模拟汽车减震</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>多浇口充填(粒子数量10)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>（说明）</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>课程那张表里的「我们账号买没买」按 user_id=1966910（config/env.yaml）判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>（说明）</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>注意：这些课程名在库里有多门同名，按名字打开只会命中第一门 —— 012345678901234567890123456789、付费课程1、免费课程、免费课程1、无敌贵的课程、测试封面图、测试封面图-修改、测试验证课时bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>（说明）</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>案例共 56 条，已全部列出</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1049,7 +1049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -3189,12 +3189,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>点文字</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>我的</t>
+          <t>回到首页</t>
         </is>
       </c>
     </row>
@@ -3204,12 +3199,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>点文字</t>
+          <t>打开搜索并输入</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>积分商城</t>
+          <t>zxz</t>
         </is>
       </c>
     </row>
@@ -3219,12 +3214,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>点文字</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>积分获取</t>
+          <t>执行搜索</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3224,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>点文字</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>积分明细</t>
+          <t>打印页面文字</t>
         </is>
       </c>
     </row>
@@ -3253,8 +3238,103 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>中文搜索_001</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>中文关键词能搜出东西（靠搜索历史点进去）</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>先摆正起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="C126" t="n">
+        <v>2</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>打开搜索页</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>搜索页上才有「搜索历史」面板</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="C127" t="n">
+        <v>3</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>点搜索历史里的词</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>压铸测试</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>中文搜索的关键一步：框架自己敲不了中文，靠点历史词条触发。这个词用工具造过：python tools/search_history_tool.py --user 1966910 --keyword 压铸测试 --add --yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="C128" t="n">
+        <v>4</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>压铸测试</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>结果页的搜索栏里应当是这个词（= 真的照它搜了）</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="C129" t="n">
+        <v>5</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>把手机交还给下一条用例</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="46">
     <mergeCell ref="A80:A88"/>
     <mergeCell ref="A110:A113"/>
     <mergeCell ref="A48:A53"/>
@@ -3264,6 +3344,7 @@
     <mergeCell ref="B21:B24"/>
     <mergeCell ref="B99:B103"/>
     <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A125:A129"/>
     <mergeCell ref="B71:B76"/>
     <mergeCell ref="B17:B20"/>
     <mergeCell ref="B48:B53"/>
@@ -3275,6 +3356,7 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="B80:B88"/>
+    <mergeCell ref="B125:B129"/>
     <mergeCell ref="A71:A76"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="A89:A94"/>
@@ -3302,7 +3384,7 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>='动作清单'!$A$2:$A$48</formula1>
+      <formula1>='动作清单'!$A$2:$A$49</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -3318,11 +3400,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="78" customWidth="1" min="5" max="5"/>
@@ -3664,10 +3746,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>打开第一个热门话题</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>点搜索历史里的词</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>词</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
@@ -3676,7 +3762,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>点搜索页「热门话题」里的第 1 条，跳转到该话题的搜索结果页（需求 713129788）</t>
+          <t>点「搜索历史」里的某个词，直接触发一次搜索。中文关键词搜索就靠它 —— 框架自己敲不了中文（adb 只支持 ASCII），但可以先往搜索历史里插一行中文（用 tools/search_history_tool.py），再点它。点了没搜起来会报错，不会静默放过。只读</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3688,7 +3774,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>打开第一个帖子</t>
+          <t>打开第一个热门话题</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -3700,7 +3786,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>在首页信息流点第一张帖子卡片，进帖子详情页（只读：不点赞、不评论）</t>
+          <t>点搜索页「热门话题」里的第 1 条，跳转到该话题的搜索结果页（需求 713129788）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3712,7 +3798,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>打开第一张专栏</t>
+          <t>打开第一个帖子</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -3724,7 +3810,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>在学习中心的专栏列表里点第一张卡，进它的详情页</t>
+          <t>在首页信息流点第一张帖子卡片，进帖子详情页（只读：不点赞、不评论）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3736,7 +3822,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>打开第一个案例</t>
+          <t>打开第一张专栏</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -3748,7 +3834,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>在案例库列表点开第一张卡片，进案例详情页（只读：不点赞、不收藏、不复制、不评论）</t>
+          <t>在学习中心的专栏列表里点第一张卡，进它的详情页</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3760,7 +3846,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>打开案例库介绍长图</t>
+          <t>打开第一个案例</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -3772,7 +3858,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>点案例库首页那张介绍 banner（在分类上方），进「介绍长图详情页」。只读</t>
+          <t>在案例库列表点开第一张卡片，进案例详情页（只读：不点赞、不收藏、不复制、不评论）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3784,14 +3870,10 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>打开案例</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>案例名</t>
-        </is>
-      </c>
+          <t>打开案例库介绍长图</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
@@ -3800,7 +3882,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>按名字点开指定案例（点不到会往下滚几屏再找）。给「付费案例复制」挑样本时用它，例如 填充任务1。只读：不点赞、不收藏、不复制（「案例名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+          <t>点案例库首页那张介绍 banner（在分类上方），进「介绍长图详情页」。只读</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3812,51 +3894,51 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>点文字</t>
+          <t>打开案例</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>文字</t>
+          <t>案例名</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>会（提交/兑换/支付类文字已被默认拦住）</t>
+          <t>不会</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
+          <t>按名字点开指定案例（点不到会往下滚几屏再找）。给「付费案例复制」挑样本时用它，例如 填充任务1。只读：不点赞、不收藏、不复制（「案例名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>③ 通用交互</t>
+          <t>② 搜索与内容（点进去看，只读）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>点选择器</t>
+          <t>点文字</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>选择器</t>
+          <t>文字</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>会（和「点文字」同一道安全阀）</t>
+          <t>会（提交/兑换/支付类文字已被默认拦住）</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>按选择器点第一处元素（比按文字点更准：文字有重名时用它），例如 .search-container</t>
+          <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3868,27 +3950,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>滑动</t>
+          <t>点选择器</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>次数（只能填：1 / 2 / 3 / 4 / 5 / 6 / 7 / 8 / 9 / 10）</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>方向（只能填：上 / 下）</t>
-        </is>
-      </c>
+          <t>选择器</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>不会</t>
+          <t>会（和「点文字」同一道安全阀）</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
+          <t>按选择器点第一处元素（比按文字点更准：文字有重名时用它），例如 .search-container</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3900,15 +3978,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>切换首页筛选栏</t>
+          <t>滑动</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>筛选栏名称（只能填：最新提问 / 推荐 / 精选问答 / 我的关注）</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>次数（只能填：1 / 2 / 3 / 4 / 5 / 6 / 7 / 8 / 9 / 10）</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>方向（只能填：上 / 下）</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>不会</t>
@@ -3916,7 +3998,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
+          <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3928,12 +4010,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>等待</t>
+          <t>切换首页筛选栏</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>毫秒</t>
+          <t>筛选栏名称（只能填：最新提问 / 推荐 / 精选问答 / 我的关注）</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -3944,7 +4026,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
+          <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3956,10 +4038,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>打印页面文字</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>等待</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>毫秒</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
@@ -3968,7 +4054,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
+          <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3980,14 +4066,10 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
+          <t>打印页面文字</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
@@ -3996,19 +4078,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
+          <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>④ 通用断言（检查「看得见没有」）</t>
+          <t>③ 通用交互</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>检查文字不显示</t>
+          <t>检查文字显示</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4024,7 +4106,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>断言页面上看不见这段文字</t>
+          <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4036,7 +4118,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>检查文字出现次数</t>
+          <t>检查文字不显示</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4044,11 +4126,7 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>期望次数（只能填：1 / 2 / 3 / 4 / 5）</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>不会</t>
@@ -4056,7 +4134,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
+          <t>断言页面上看不见这段文字</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4068,15 +4146,19 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>检查元素存在</t>
+          <t>检查文字出现次数</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>选择器</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>期望次数（只能填：1 / 2 / 3 / 4 / 5）</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>不会</t>
@@ -4084,7 +4166,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>断言页面上找得到这个选择器，例如 .search-container</t>
+          <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4096,7 +4178,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>检查元素不存在</t>
+          <t>检查元素存在</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4112,7 +4194,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
+          <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4124,7 +4206,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>检查元素数量</t>
+          <t>检查元素不存在</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4132,11 +4214,7 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>期望数量</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>不会</t>
@@ -4144,7 +4222,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
+          <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4156,7 +4234,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>检查输入框的值</t>
+          <t>检查元素数量</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4166,7 +4244,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>期望值</t>
+          <t>期望数量</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4176,7 +4254,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
+          <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4188,11 +4266,19 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>检查活动入口</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+          <t>检查输入框的值</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>选择器</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>期望值</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>不会</t>
@@ -4200,19 +4286,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
+          <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>⑤ 需求专项检查</t>
+          <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>检查首页筛选栏顺序</t>
+          <t>检查活动入口</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -4224,7 +4310,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
+          <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4236,7 +4322,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>检查回到顶部按钮</t>
+          <t>检查首页筛选栏顺序</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -4248,7 +4334,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
+          <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4260,7 +4346,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>检查答题页</t>
+          <t>检查回到顶部按钮</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -4272,7 +4358,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于一道题的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
+          <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4284,7 +4370,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>检查案例库列表</t>
+          <t>检查答题页</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -4296,7 +4382,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验案例库列表页：① 分类上方有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「复制图标 + 复制数」，且整页找不到评论图标。只读</t>
+          <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于一道题的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4308,7 +4394,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>检查案例详情页</t>
+          <t>检查案例库列表</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -4320,7 +4406,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部没有复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
+          <t>按需求 713381608 校验案例库列表页：① 分类上方有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「复制图标 + 复制数」，且整页找不到评论图标。只读</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4332,7 +4418,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>检查案例库介绍长图</t>
+          <t>检查案例详情页</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -4344,7 +4430,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验介绍长图页：整页是单张图片，而且是长图（图高远大于屏高）。只读</t>
+          <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部没有复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4356,14 +4442,10 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>检查课程详情页</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
-        </is>
-      </c>
+          <t>检查案例库介绍长图</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
@@ -4372,7 +4454,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、默认选中填的那个（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
+          <t>按需求 713381608 校验介绍长图页：整页是单张图片，而且是长图（图高远大于屏高）。只读</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4384,10 +4466,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>检查0课时课程不显示</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>检查课程详情页</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
@@ -4396,7 +4482,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字一个都没出现在小程序的课程列表里（会自己滚到列表底部）。只读</t>
+          <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、默认选中填的那个（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4408,14 +4494,10 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>检查未购买点课时</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>课程名</t>
-        </is>
-      </c>
+          <t>检查0课时课程不显示</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
@@ -4424,7 +4506,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>按需求 713367615 第 2 条校验：未购买的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号没买过的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
+          <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字一个都没出现在小程序的课程列表里（会自己滚到列表底部）。只读</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4436,10 +4518,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>打开答题活动</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>检查未购买点课时</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>课程名</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
@@ -4448,31 +4534,31 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
+          <t>按需求 713367615 第 2 条校验：未购买的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号没买过的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+          <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>逐题作答</t>
+          <t>打开答题活动</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>只改前端选中态（不写库、不需要开关）</t>
+          <t>不会</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、不写库，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
+          <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4484,19 +4570,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>提交答卷</t>
+          <t>逐题作答</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>会写库（必须开开关）</t>
+          <t>只改前端选中态（不写库、不需要开关）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>点答题页的提交按钮 —— 会真的写数据。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
+          <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、不写库，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4508,23 +4594,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>复位答题记录</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>活动名</t>
-        </is>
-      </c>
+          <t>提交答卷</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>会删库（默认只预览；真删要开开关）</t>
+          <t>会写库（必须开开关）</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：默认只预览、不删，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+          <t>点答题页的提交按钮 —— 会真的写数据。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4536,7 +4618,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>检查答题记录数</t>
+          <t>复位答题记录</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4544,19 +4626,15 @@
           <t>活动名</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>期望条数</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>不会</t>
+          <t>会删库（默认只预览；真删要开开关）</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>读数据库，断言这个活动的提交记录正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+          <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：默认只预览、不删，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4568,22 +4646,54 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>检查答题记录数</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>活动名</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>期望条数</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>读数据库，断言这个活动的提交记录正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>复制当前案例</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
         <is>
           <t>会写库（要开开关；没开时记跳过）</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>在案例详情页点「复制案例」—— 一条龙：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → 自动复位（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>
@@ -4751,7 +4861,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C154"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1049,7 +1049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -3333,8 +3333,103 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>中文搜索_002</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>中文关键词直接输入也能搜（框架自动切输入法）</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>先摆正起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="C131" t="n">
+        <v>2</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>打开搜索并输入</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>压铸</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>中文关键词：框架会自动临时切到 ADBKeyboard，用完切回你原来的输入法</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="C132" t="n">
+        <v>3</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>执行搜索</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>按回车把搜索跑起来</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="C133" t="n">
+        <v>4</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>压铸</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>结果页搜索栏里应当是这个词（= 真照它搜了）</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="C134" t="n">
+        <v>5</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>把手机交还给下一条用例</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="48">
     <mergeCell ref="A80:A88"/>
     <mergeCell ref="A110:A113"/>
     <mergeCell ref="A48:A53"/>
@@ -3353,18 +3448,20 @@
     <mergeCell ref="A77:A79"/>
     <mergeCell ref="A54:A59"/>
     <mergeCell ref="A21:A24"/>
+    <mergeCell ref="A130:A134"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="B80:B88"/>
     <mergeCell ref="B125:B129"/>
+    <mergeCell ref="A89:A94"/>
     <mergeCell ref="A71:A76"/>
     <mergeCell ref="B13:B16"/>
-    <mergeCell ref="A89:A94"/>
     <mergeCell ref="B60:B63"/>
     <mergeCell ref="B25:B29"/>
     <mergeCell ref="A17:A20"/>
     <mergeCell ref="A64:A70"/>
     <mergeCell ref="A104:A109"/>
+    <mergeCell ref="B130:B134"/>
     <mergeCell ref="B110:B113"/>
     <mergeCell ref="B95:B98"/>
     <mergeCell ref="A30:A47"/>
@@ -3710,7 +3807,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>点搜索栏进搜索页并输入关键词。注意：只能是字母/数字/下划线/点/连字符（adb 不支持中文输入）</t>
+          <t>点搜索栏进搜索页并输入关键词（输入后会读回来校验）。中文也能填：遇到中文/空格/符号时，框架会自动临时切到手机上的 ADBKeyboard 输入法把它送进去，用完自动切回你原来的输入法（这一步会多花 1~2 秒）。只读</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -3481,7 +3481,7 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>='动作清单'!$A$2:$A$49</formula1>
+      <formula1>='动作清单'!$A$2:$A$50</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -3497,7 +3497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4187,12 +4187,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>检查文字显示</t>
+          <t>打印页面结构</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>文字</t>
+          <t>范围（只能填：全量 / 只看有文字）</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -4203,19 +4203,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
+          <t>把当前页面的元素结构（标签 / class / id + 文字）打进日志：控制台只打前 300 行，完整内容写到 report/dump_&lt;月日_时分秒&gt;.txt（可以在编辑器里搜，适合挑「检查元素存在」的选择器）。参数1 填「只看有文字」时只输出看得见文字的分支（几十行，最省事）。调完把这一行删掉 —— 它是调试用的，不是断言。只读</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>④ 通用断言（检查「看得见没有」）</t>
+          <t>③ 通用交互</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>检查文字不显示</t>
+          <t>检查文字显示</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>断言页面上看不见这段文字</t>
+          <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4243,7 +4243,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>检查文字出现次数</t>
+          <t>检查文字不显示</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4251,11 +4251,7 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>期望次数（只能填：1 / 2 / 3 / 4 / 5）</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>不会</t>
@@ -4263,7 +4259,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
+          <t>断言页面上看不见这段文字</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4275,15 +4271,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>检查元素存在</t>
+          <t>检查文字出现次数</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>选择器</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>期望次数（只能填：1 / 2 / 3 / 4 / 5）</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>不会</t>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>断言页面上找得到这个选择器，例如 .search-container</t>
+          <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4303,7 +4303,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>检查元素不存在</t>
+          <t>检查元素存在</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
+          <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4331,7 +4331,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>检查元素数量</t>
+          <t>检查元素不存在</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4339,11 +4339,7 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>期望数量</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>不会</t>
@@ -4351,7 +4347,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
+          <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4363,7 +4359,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>检查输入框的值</t>
+          <t>检查元素数量</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4373,7 +4369,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>期望值</t>
+          <t>期望数量</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4383,7 +4379,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
+          <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4395,11 +4391,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>检查活动入口</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+          <t>检查输入框的值</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>选择器</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>期望值</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>不会</t>
@@ -4407,19 +4411,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
+          <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>⑤ 需求专项检查</t>
+          <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>检查首页筛选栏顺序</t>
+          <t>检查活动入口</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -4431,7 +4435,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
+          <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4443,7 +4447,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>检查回到顶部按钮</t>
+          <t>检查首页筛选栏顺序</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -4455,7 +4459,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
+          <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4467,7 +4471,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>检查答题页</t>
+          <t>检查回到顶部按钮</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -4479,7 +4483,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于一道题的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
+          <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4491,7 +4495,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>检查案例库列表</t>
+          <t>检查答题页</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -4503,7 +4507,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验案例库列表页：① 分类上方有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「复制图标 + 复制数」，且整页找不到评论图标。只读</t>
+          <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于一道题的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4515,7 +4519,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>检查案例详情页</t>
+          <t>检查案例库列表</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -4527,7 +4531,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部没有复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
+          <t>按需求 713381608 校验案例库列表页：① 分类上方有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「复制图标 + 复制数」，且整页找不到评论图标。只读</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4539,7 +4543,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>检查案例库介绍长图</t>
+          <t>检查案例详情页</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -4551,7 +4555,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验介绍长图页：整页是单张图片，而且是长图（图高远大于屏高）。只读</t>
+          <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部没有复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4563,14 +4567,10 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>检查课程详情页</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
-        </is>
-      </c>
+          <t>检查案例库介绍长图</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、默认选中填的那个（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
+          <t>按需求 713381608 校验介绍长图页：整页是单张图片，而且是长图（图高远大于屏高）。只读</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4591,10 +4591,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>检查0课时课程不显示</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>检查课程详情页</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
@@ -4603,7 +4607,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字一个都没出现在小程序的课程列表里（会自己滚到列表底部）。只读</t>
+          <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、默认选中填的那个（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4615,14 +4619,10 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>检查未购买点课时</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>课程名</t>
-        </is>
-      </c>
+          <t>检查0课时课程不显示</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>按需求 713367615 第 2 条校验：未购买的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号没买过的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
+          <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字一个都没出现在小程序的课程列表里（会自己滚到列表底部）。只读</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4643,10 +4643,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>打开答题活动</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>检查未购买点课时</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>课程名</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
@@ -4655,31 +4659,31 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
+          <t>按需求 713367615 第 2 条校验：未购买的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号没买过的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+          <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>逐题作答</t>
+          <t>打开答题活动</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>只改前端选中态（不写库、不需要开关）</t>
+          <t>不会</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、不写库，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
+          <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4691,19 +4695,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>提交答卷</t>
+          <t>逐题作答</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>会写库（必须开开关）</t>
+          <t>只改前端选中态（不写库、不需要开关）</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>点答题页的提交按钮 —— 会真的写数据。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
+          <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、不写库，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4715,23 +4719,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>复位答题记录</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>活动名</t>
-        </is>
-      </c>
+          <t>提交答卷</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>会删库（默认只预览；真删要开开关）</t>
+          <t>会写库（必须开开关）</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：默认只预览、不删，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+          <t>点答题页的提交按钮 —— 会真的写数据。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>检查答题记录数</t>
+          <t>复位答题记录</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4751,19 +4751,15 @@
           <t>活动名</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>期望条数</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>不会</t>
+          <t>会删库（默认只预览；真删要开开关）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>读数据库，断言这个活动的提交记录正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+          <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：默认只预览、不删，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4775,22 +4771,54 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>检查答题记录数</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>活动名</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>期望条数</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>读数据库，断言这个活动的提交记录正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>复制当前案例</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr">
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
         <is>
           <t>会写库（要开开关；没开时记跳过）</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>在案例详情页点「复制案例」—— 一条龙：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → 自动复位（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -3497,15 +3497,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="78" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="78" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3526,15 +3527,20 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>怎么填（示例）</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>会不会改数据</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>属于哪一类</t>
         </is>
@@ -3550,15 +3556,20 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>自导航到「有问必答」首页信息流（幂等；在二级页/搜索页会先点返回退出），并把筛选 tab 归位到「最新提问」。用例第一步建议都用它</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
@@ -3574,15 +3585,20 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>点底部 tab「我的」，进入用户中心</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
@@ -3598,15 +3614,20 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>从用户中心点「积分商城」进商城首页（已在则原地不动）。积分商城是二级页，没有底部 tab 栏</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
@@ -3622,15 +3643,20 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>进学习中心，并切到「专栏」列表</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
@@ -3650,15 +3676,20 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
+          <t>专栏</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>切学习中心顶部那排 tab（切完会验证真的选中了）</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
@@ -3674,15 +3705,20 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>点返回按钮退回上一页（会校验页面确实变了）</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
@@ -3698,15 +3734,20 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>点二级页导航栏上的「主页」图标回到首页（需求 713256065 的返回首页那半句）</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
@@ -3722,15 +3763,20 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>只进搜索页、不输入关键词（搜索页上能看到「搜索历史」和「热门话题」）</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
@@ -3746,15 +3792,20 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>打开案例库列表（底部 tab「设计专区」打开就是它，这是 2026/10/12 才找到的入口；页面顶部还有一排 tab：仿真案例库 / 压铸护航服务）</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
@@ -3774,15 +3825,20 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>打开某门课的详情页（学习页）：自己走到 学习中心 → 课程 tab → 按名字点课程。只读：不播放视频、不购买。课程名要跟列表上一字不差，例如 717（「课程名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
@@ -3802,15 +3858,20 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
+          <t>test（中文也行，例如 压铸）</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>点搜索栏进搜索页并输入关键词（输入后会读回来校验）。中文也能填：遇到中文/空格/符号时，框架会自动临时切到手机上的 ADBKeyboard 输入法把它送进去，用完自动切回你原来的输入法（这一步会多花 1~2 秒）。只读</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
@@ -3826,15 +3887,20 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>在搜索页按回车把搜索跑起来（只读：只是查一次）。不执行的话停在「搜索历史」面板，看不到结果页/空态</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
@@ -3854,15 +3920,20 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
+          <t>压铸测试</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>点「搜索历史」里的某个词，直接触发一次搜索。中文关键词搜索就靠它 —— 框架自己敲不了中文（adb 只支持 ASCII），但可以先往搜索历史里插一行中文（用 tools/search_history_tool.py），再点它。点了没搜起来会报错，不会静默放过。只读</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
@@ -3878,15 +3949,20 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>点搜索页「热门话题」里的第 1 条，跳转到该话题的搜索结果页（需求 713129788）</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
@@ -3902,15 +3978,20 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>在首页信息流点第一张帖子卡片，进帖子详情页（只读：不点赞、不评论）</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
@@ -3926,15 +4007,20 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>在学习中心的专栏列表里点第一张卡，进它的详情页</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
@@ -3950,15 +4036,20 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>在案例库列表点开第一张卡片，进案例详情页（只读：不点赞、不收藏、不复制、不评论）</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
@@ -3974,15 +4065,20 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>点案例库首页那张介绍 banner（在分类上方），进「介绍长图详情页」。只读</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
@@ -4002,15 +4098,20 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
+          <t>填充任务1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>按名字点开指定案例（点不到会往下滚几屏再找）。给「付费案例复制」挑样本时用它，例如 填充任务1。只读：不点赞、不收藏、不复制（「案例名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
@@ -4030,15 +4131,20 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
+          <t>我的</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>会（提交/兑换/支付类文字已被默认拦住）</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>③ 通用交互</t>
         </is>
@@ -4058,15 +4164,20 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
+          <t>.search-container</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>会（和「点文字」同一道安全阀）</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>按选择器点第一处元素（比按文字点更准：文字有重名时用它），例如 .search-container</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>③ 通用交互</t>
         </is>
@@ -4090,15 +4201,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>3 / 上</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>③ 通用交互</t>
         </is>
@@ -4118,15 +4234,20 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>③ 通用交互</t>
         </is>
@@ -4146,15 +4267,20 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2000（= 等 2 秒）</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>③ 通用交互</t>
         </is>
@@ -4170,15 +4296,20 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>③ 通用交互</t>
         </is>
@@ -4198,15 +4329,20 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
+          <t>只看有文字</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>把当前页面的元素结构（标签 / class / id + 文字）打进日志：控制台只打前 300 行，完整内容写到 report/dump_&lt;月日_时分秒&gt;.txt（可以在编辑器里搜，适合挑「检查元素存在」的选择器）。参数1 填「只看有文字」时只输出看得见文字的分支（几十行，最省事）。调完把这一行删掉 —— 它是调试用的，不是断言。只读</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>③ 通用交互</t>
         </is>
@@ -4226,15 +4362,20 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
+          <t>答对最多可赢积分</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
@@ -4254,15 +4395,20 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
+          <t>最新提问（搜索页上不该有）</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>断言页面上看不见这段文字</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
@@ -4286,15 +4432,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>收藏 / 1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
@@ -4314,15 +4465,20 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
+          <t>.search-container</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
@@ -4342,15 +4498,20 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
+          <t>.activity-quiz-page</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
@@ -4374,15 +4535,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>.hot-topics .inline-flex / 5</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
@@ -4406,15 +4572,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>wx-input.search-input / test</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
@@ -4430,15 +4601,20 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
@@ -4454,15 +4630,20 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
@@ -4478,15 +4659,20 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
@@ -4502,15 +4688,20 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于一道题的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
@@ -4526,15 +4717,20 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>按需求 713381608 校验案例库列表页：① 分类上方有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「复制图标 + 复制数」，且整页找不到评论图标。只读</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
@@ -4550,15 +4746,20 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部没有复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
@@ -4574,15 +4775,20 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>按需求 713381608 校验介绍长图页：整页是单张图片，而且是长图（图高远大于屏高）。只读</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
@@ -4602,15 +4808,20 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
+          <t>课程介绍</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、默认选中填的那个（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
@@ -4626,15 +4837,20 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字一个都没出现在小程序的课程列表里（会自己滚到列表底部）。只读</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
@@ -4654,15 +4870,20 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
+          <t>7.8课程new</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>按需求 713367615 第 2 条校验：未购买的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号没买过的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
@@ -4678,15 +4899,20 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>
@@ -4702,15 +4928,20 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>只改前端选中态（不写库、不需要开关）</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、不写库，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>
@@ -4726,15 +4957,20 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>会写库（必须开开关）</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>点答题页的提交按钮 —— 会真的写数据。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>
@@ -4754,15 +4990,20 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
+          <t>Z-B4-答题角标</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>会删库（默认只预览；真删要开开关）</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：默认只预览、不删，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>
@@ -4786,15 +5027,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>Z-B4-答题角标 / 1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>读数据库，断言这个活动的提交记录正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>
@@ -4810,15 +5056,20 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>会写库（要开开关；没开时记跳过）</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>在案例详情页点「复制案例」—— 一条龙：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → 自动复位（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -586,7 +586,7 @@
     <t>测试</t>
   </si>
   <si>
-    <t>.fs-28 text-blacks28 ml-2</t>
+    <t>.fs-28</t>
   </si>
   <si>
     <t>中文搜索_001</t>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -3446,8 +3446,8 @@
     <mergeCell ref="A64:A70"/>
     <mergeCell ref="A104:A109"/>
     <mergeCell ref="B130:B134"/>
+    <mergeCell ref="B95:B98"/>
     <mergeCell ref="B110:B113"/>
-    <mergeCell ref="B95:B98"/>
     <mergeCell ref="A30:A47"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="A4:A7"/>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -3462,14 +3462,15 @@
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="A60:A63"/>
     <mergeCell ref="B21:B24"/>
+    <mergeCell ref="B114:B119"/>
     <mergeCell ref="B99:B103"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="A125:A129"/>
     <mergeCell ref="B71:B76"/>
     <mergeCell ref="B17:B20"/>
     <mergeCell ref="B48:B53"/>
+    <mergeCell ref="B30:B47"/>
     <mergeCell ref="B130:B135"/>
-    <mergeCell ref="B30:B47"/>
     <mergeCell ref="B64:B70"/>
     <mergeCell ref="A77:A79"/>
     <mergeCell ref="A54:A59"/>
@@ -3498,15 +3499,14 @@
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="B4:B7"/>
     <mergeCell ref="A99:A103"/>
+    <mergeCell ref="B54:B59"/>
     <mergeCell ref="A130:A135"/>
     <mergeCell ref="B104:B109"/>
-    <mergeCell ref="B54:B59"/>
-    <mergeCell ref="B114:B119"/>
     <mergeCell ref="A120:A124"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>='动作清单'!$A$2:$A$51</formula1>
+      <formula1>='动作清单'!$A$2:$A$54</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -3522,7 +3522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4244,32 +4244,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>滑动</t>
+          <t>点id</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>次数（只能填：1 / 2 / 3 / 4 / 5 / 6 / 7 / 8 / 9 / 10）</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>方向（只能填：上 / 下）</t>
-        </is>
-      </c>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3 / 上</t>
+          <t>_AQ（首页搜索栏；也可以写 #_AQ）</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>不会</t>
+          <t>会（和「点文字」同一道安全阀）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
+          <t>按元素 id 点一下（从「打印页面结构」里抄，形如 _AQ；前面不用写 #）。id 比 class 更精确、也不怕重名，但只适合页面上部那些固定元素 —— 实测短 id（_AQ）隔天还在，而带 hash 前缀的（9d834775--_XFi）只在某一次出现过，别拿它当锚点。只读</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4281,18 +4277,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>切换首页筛选栏</t>
+          <t>滑动</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>筛选栏名称（只能填：最新提问 / 推荐 / 精选问答 / 我的关注）</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>次数（只能填：1 / 2 / 3 / 4 / 5 / 6 / 7 / 8 / 9 / 10）</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>方向（只能填：上 / 下）</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>推荐</t>
+          <t>3 / 上</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
+          <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4314,18 +4314,18 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>等待</t>
+          <t>切换首页筛选栏</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>毫秒</t>
+          <t>筛选栏名称（只能填：最新提问 / 推荐 / 精选问答 / 我的关注）</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2000（= 等 2 秒）</t>
+          <t>推荐</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
+          <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4347,14 +4347,18 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>打印页面文字</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>等待</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>毫秒</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>2000（= 等 2 秒）</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4364,7 +4368,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
+          <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4376,18 +4380,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>打印页面结构</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>范围（只能填：全量 / 只看有文字）</t>
-        </is>
-      </c>
+          <t>打印页面文字</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>只看有文字</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>把当前页面的元素结构（标签 / class / id + 文字）打进日志：控制台只打前 300 行，完整内容写到 report/dump_&lt;月日_时分秒&gt;.txt（可以在编辑器里搜，适合挑「检查元素存在」的选择器）。参数1 填「只看有文字」时只输出看得见文字的分支（几十行，最省事）。调完把这一行删掉 —— 它是调试用的，不是断言。只读</t>
+          <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4409,18 +4409,18 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>检查文字显示</t>
+          <t>打印页面结构</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>文字</t>
+          <t>范围（只能填：全量 / 只看有文字）</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>答对最多可赢积分</t>
+          <t>只看有文字</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4430,19 +4430,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
+          <t>把当前页面的元素结构（标签 / class / id + 文字）打进日志：控制台只打前 300 行，完整内容写到 report/dump_&lt;月日_时分秒&gt;.txt（可以在编辑器里搜，适合挑「检查元素存在」的选择器）。参数1 填「只看有文字」时只输出看得见文字的分支（几十行，最省事）。调完把这一行删掉 —— 它是调试用的，不是断言。只读</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>④ 通用断言（检查「看得见没有」）</t>
+          <t>③ 通用交互</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>检查文字不显示</t>
+          <t>检查文字显示</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4453,7 +4453,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>最新提问（搜索页上不该有）</t>
+          <t>答对最多可赢积分</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>断言页面上看不见这段文字</t>
+          <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4475,7 +4475,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>检查文字出现次数</t>
+          <t>检查文字不显示</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4483,14 +4483,10 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>期望次数（只能填：1 / 2 / 3 / 4 / 5）</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>收藏 / 1</t>
+          <t>最新提问（搜索页上不该有）</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4500,7 +4496,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
+          <t>断言页面上看不见这段文字</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4512,18 +4508,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>检查元素存在</t>
+          <t>检查文字出现次数</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>选择器</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>期望次数（只能填：1 / 2 / 3 / 4 / 5）</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>.search-container</t>
+          <t>收藏 / 1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>断言页面上找得到这个选择器，例如 .search-container</t>
+          <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4545,7 +4545,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>检查元素不存在</t>
+          <t>检查元素存在</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4556,7 +4556,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>.activity-quiz-page</t>
+          <t>.search-container</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
+          <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>检查元素数量</t>
+          <t>检查元素不存在</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4586,14 +4586,10 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>期望数量</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>.hot-topics .inline-flex / 5</t>
+          <t>.activity-quiz-page</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4603,7 +4599,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
+          <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4615,7 +4611,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>检查输入框的值</t>
+          <t>检查元素数量</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4625,12 +4621,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>期望值</t>
+          <t>期望数量</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>wx-input.search-input / test</t>
+          <t>.hot-topics .inline-flex / 5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4640,7 +4636,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
+          <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4652,14 +4648,18 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>检查活动入口</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>检查id存在</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>_AQ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4669,26 +4669,30 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
+          <t>断言页面上找得到这个 id 的元素（前面不用写 #，从「打印页面结构」里抄，形如 _AQ）。适合「没有文字可打、class 又不够特别」的固定元素；列表里的东西优先用文字/class（见「点id」的说明）。只读</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>⑤ 需求专项检查</t>
+          <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>检查首页筛选栏顺序</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>检查id不存在</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>_AQ（进了搜索页之后，首页那个搜索栏就不该在了）</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4698,26 +4702,34 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
+          <t>断言页面上没有这个 id 的元素（例如：进了搜索页之后，首页那个 _AQ 搜索栏就不该在）。只读</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>⑤ 需求专项检查</t>
+          <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>检查回到顶部按钮</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+          <t>检查输入框的值</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>选择器</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>期望值</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>wx-input.search-input / test</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4727,19 +4739,19 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
+          <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>⑤ 需求专项检查</t>
+          <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>检查答题页</t>
+          <t>检查活动入口</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -4756,7 +4768,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于一道题的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
+          <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4768,7 +4780,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>检查案例库列表</t>
+          <t>检查首页筛选栏顺序</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -4785,7 +4797,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验案例库列表页：① 分类上方有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「复制图标 + 复制数」，且整页找不到评论图标。只读</t>
+          <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4797,7 +4809,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>检查案例详情页</t>
+          <t>检查回到顶部按钮</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -4814,7 +4826,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部没有复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
+          <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4826,7 +4838,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>检查案例库介绍长图</t>
+          <t>检查答题页</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -4843,7 +4855,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验介绍长图页：整页是单张图片，而且是长图（图高远大于屏高）。只读</t>
+          <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于一道题的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4855,18 +4867,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>检查课程详情页</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
-        </is>
-      </c>
+          <t>检查案例库列表</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>课程介绍</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4876,7 +4884,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、默认选中填的那个（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
+          <t>按需求 713381608 校验案例库列表页：① 分类上方有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「复制图标 + 复制数」，且整页找不到评论图标。只读</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4888,7 +4896,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>检查0课时课程不显示</t>
+          <t>检查案例详情页</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -4905,7 +4913,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字一个都没出现在小程序的课程列表里（会自己滚到列表底部）。只读</t>
+          <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部没有复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4917,18 +4925,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>检查未购买点课时</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>课程名</t>
-        </is>
-      </c>
+          <t>检查案例库介绍长图</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7.8课程new</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4938,7 +4942,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>按需求 713367615 第 2 条校验：未购买的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号没买过的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
+          <t>按需求 713381608 校验介绍长图页：整页是单张图片，而且是长图（图高远大于屏高）。只读</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4950,14 +4954,18 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>打开答题活动</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>检查课程详情页</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>课程介绍</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4967,19 +4975,19 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
+          <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、默认选中填的那个（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+          <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>逐题作答</t>
+          <t>检查0课时课程不显示</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -4991,74 +4999,74 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>只改前端选中态（不写库、不需要开关）</t>
+          <t>不会</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、不写库，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
+          <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字一个都没出现在小程序的课程列表里（会自己滚到列表底部）。只读</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+          <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>提交答卷</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>检查未购买点课时</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>课程名</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>7.8课程new</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>会写库（必须开开关）</t>
+          <t>不会</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>点答题页的提交按钮 —— 会真的写数据。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
+          <t>按需求 713367615 第 2 条校验：未购买的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号没买过的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+          <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>复位答题记录</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>活动名</t>
-        </is>
-      </c>
+          <t>打开答题活动</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Z-B4-答题角标</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>会删库（默认只预览；真删要开开关）</t>
+          <t>不会</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：默认只预览、不删，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+          <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5070,32 +5078,24 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>检查答题记录数</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>活动名</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>期望条数</t>
-        </is>
-      </c>
+          <t>逐题作答</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Z-B4-答题角标 / 1</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>不会</t>
+          <t>只改前端选中态（不写库、不需要开关）</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>读数据库，断言这个活动的提交记录正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+          <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、不写库，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5107,7 +5107,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>复制当前案例</t>
+          <t>提交答卷</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -5119,15 +5119,114 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>会写库（必须开开关）</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>点答题页的提交按钮 —— 会真的写数据。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>复位答题记录</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>活动名</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Z-B4-答题角标</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>会删库（默认只预览；真删要开开关）</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：默认只预览、不删，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>检查答题记录数</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>活动名</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>期望条数</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Z-B4-答题角标 / 1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>读数据库，断言这个活动的提交记录正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>复制当前案例</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>会写库（要开开关；没开时记跳过）</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>在案例详情页点「复制案例」—— 一条龙：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → 自动复位（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>
@@ -5294,11 +5393,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C154"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -5322,2365 +5421,13 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>课程2</t>
-        </is>
-      </c>
+          <t>(没取到)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>课程3</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>课程4</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>课程4</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>课程4</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>012345678901234567890123456789</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>012345678901234567890123456789</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>模流仿真1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>设计提升1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=4</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>设计提升1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>免费课程</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>设计提升1-系列课程-付费</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=4</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>设计提升1-专项课程</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=4</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>设计提升1-专题课程</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>测试课程</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>无敌贵的课程</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>无敌贵的课程</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>无敌贵的课程</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>设计提升-专项-2分钟</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>免费课程</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>免费课程1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>免费课程1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>付费课程1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>付费课程2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>付费课程3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>付费课程4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>付费课程5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>付费课程7</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>付费课程8</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>付费课程9</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>付费课程10</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>付费课程11</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>付费课程12</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>付费课程13</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>免费课程-测ios1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>免费课程-测ios2</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=3</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>10-27</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>新增课题测试</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>12-8新增0元课程</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>付费课程1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>课程22222</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>设计提升1-专题课程-付费</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>测试验证课时bug</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>测试验证课时bug</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>测试封面图</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>测试封面图</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>测试封面图</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>测试封面图-修改</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>测试封面图-修改</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>测试封面图-修改</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>测试封面图-修改</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>测试封面图-修改</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>测试课程版本-v1</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>测试课程版本-v1-v2</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>低洼瞧得起我</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>特别的名字</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>测试-11</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=2</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>4.16 创建课程</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>5月18日课程</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=2</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>7.8课程new</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=2</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>买没买=是；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>test2</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>买没买=否；课时数=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>一二三四五六七八九十</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>id=352</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Z-题干图验证</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>id=349</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Z-导入床</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>id=348</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Z-B4-答题角标</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>id=347</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>答题</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>id=343</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>M1-六选项六图</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>id=340</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>L5-待开始14题</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>id=339</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>L4-排序3题</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>id=338</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>L3-导入床</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>id=337</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>L2-六选项多选</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>id=336</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>L1-规则200字</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>id=335</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>G1-三题型带答案</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>id=316</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>F4-1000分</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>id=315</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>F3-十分答题</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>id=314</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>F2-十分答题</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>id=313</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>F1-十分答题</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>id=312</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>id=311</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>000</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>id=310</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>积分上限</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>id=309</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>答题</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>id=304</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>B6-字段全覆盖</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>id=287</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>B5-导入床</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>id=269</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>B4-每日限开</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>id=268</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>B3-15题</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>id=267</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>B2-14题</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>id=266</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>B1-1题</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>id=265</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>A5-特殊字符</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>id=264</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>A4-不轮播</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>id=263</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>A1-答题</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>id=260</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>答题活动</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>轮播-答题</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>id=255</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>方案一变形</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>仅凝固</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>仅充填2</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>充填凝固应力</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>充填凝固应力1</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>7201744-孙</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>带组织性能结果</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>充填-排气</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1月 20250115</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>紫色1</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>内部数据6</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1QQ区qqqqq</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>重力铸造-重力砂型-0602-163625-仅充填仅浏览-重力铸造-重力砂型-0602-163625</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>重力铸造-重力砂型-0602-163625-充填凝固0602_165141-仅浏览</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>COPY3</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>3月26测试 私有材料分享(copy)</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>内部数据-虚拟模具</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>内部数据</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>鹅鹅鹅</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>仅凝固+应力-选择点2</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>仅凝固1</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>循环凝固</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>131231</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>131231</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>循环凝固-热循环</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>6668</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>6668</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>填充任务1</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>0605测试</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>循环凝固+应力+选点1</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>料筒(copy)</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>仅凝固</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>#713392277</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>？？？？</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>复制任务失败问题测试-分享</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>浇口充填-高级模式</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>热热热热</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>eeee</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>亲亲</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>3333 私有曲线</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>111111</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>测试二级页面案例111111111111111111111111111</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>分享高压 2</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>料筒充填</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>料筒充填1</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>料筒分享</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>1WWWW</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>凝固应力</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>模拟汽车</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>模拟汽车减震</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>多浇口充填(粒子数量10)</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>（说明）</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>课程那张表里的「我们账号买没买」按 user_id=1966910（config/env.yaml）判断</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>（说明）</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>注意：这些课程名在库里有多门同名，按名字打开只会命中第一门 —— 012345678901234567890123456789、付费课程1、免费课程、免费课程1、无敌贵的课程、测试封面图、测试封面图-修改、测试验证课时bug</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>（说明）</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr"/>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>案例共 56 条，已全部列出</t>
+          <t>读候选值时出错：连不上测试库：rm-8vbop0t5nc6heu4b09o.mysql.zhangbei.rds.aliyuncs.com:3306（库 eco_microapp_alpha）</t>
         </is>
       </c>
     </row>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -4265,7 +4265,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>按元素 id 点一下（从「打印页面结构」里抄，形如 _AQ；前面不用写 #）。id 比 class 更精确、也不怕重名，但只适合页面上部那些固定元素 —— 实测短 id（_AQ）隔天还在，而带 hash 前缀的（9d834775--_XFi）只在某一次出现过，别拿它当锚点。只读</t>
+          <t>按元素 id 点一下（从「打印页面结构」里抄，形如 _AQ；前面不用写 #）。id 比 class 更精确、也不怕重名 —— 但只适合临时调试：实测页面一直开着时 id 不变（首页搜索栏 _AQ 隔天还在），可只要重进一次页面，id 就全变（退出去再进搜索页：搜索框 _JN-&gt;_Kr，5 个热门话题的 id 全换）。长期用例请用文字或 class。只读</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>断言页面上找得到这个 id 的元素（前面不用写 #，从「打印页面结构」里抄，形如 _AQ）。适合「没有文字可打、class 又不够特别」的固定元素；列表里的东西优先用文字/class（见「点id」的说明）。只读</t>
+          <t>断言页面上找得到这个 id 的元素（前面不用写 #，从「打印页面结构」里抄，形如 _AQ）。适合临时确认「这个 id 现在在不在」；别写进长期用例 —— 重进一次页面 id 就会全变（见「点id」的说明）。只读</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -4186,10 +4186,14 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>第几个（可不填）</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>我的</t>
+          <t>我的（重名时参数2填 2 = 点第 2 个）</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4199,7 +4203,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>按页面上看得见的文字点一下。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
+          <t>按页面上看得见的文字点一下。参数2 可以填「第几个」（留空 = 第 1 个）——文字重名时用它挑，比写选择器省事。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4219,10 +4223,14 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>第几个（可不填）</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>.search-container</t>
+          <t>.search-container（重名时参数2填 2 = 点第 2 个，例如 .hot-topics .inline-flex 第 2 条）</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4232,7 +4240,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>按选择器点第一处元素（比按文字点更准：文字有重名时用它），例如 .search-container</t>
+          <t>按选择器点一处元素（比按文字点更准：文字有重名时用它），例如 .search-container。参数2 可以填「第几个」（留空 = 第 1 个）——class 重复时用它挑，例如热门话题 5 条标题 class 完全一样</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -5393,11 +5401,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C154"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -5421,13 +5429,2365 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>(没取到)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>课程2</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>读候选值时出错：连不上测试库：rm-8vbop0t5nc6heu4b09o.mysql.zhangbei.rds.aliyuncs.com:3306（库 eco_microapp_alpha）</t>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>课程3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>课程4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>课程4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>课程4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>012345678901234567890123456789</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>012345678901234567890123456789</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>模流仿真1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>设计提升1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>设计提升1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>免费课程</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>设计提升1-系列课程-付费</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>设计提升1-专项课程</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>设计提升1-专题课程</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>测试课程</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>无敌贵的课程</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>无敌贵的课程</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>无敌贵的课程</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>设计提升-专项-2分钟</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>免费课程</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>免费课程1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>免费课程1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>付费课程1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>付费课程2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>付费课程3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>付费课程4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>付费课程5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>付费课程7</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>付费课程8</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>付费课程9</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>付费课程10</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>付费课程11</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>付费课程12</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>付费课程13</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>免费课程-测ios1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>免费课程-测ios2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10-27</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>新增课题测试</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>12-8新增0元课程</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>付费课程1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>课程22222</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>设计提升1-专题课程-付费</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>测试验证课时bug</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>测试验证课时bug</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>测试封面图</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>测试封面图</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>测试封面图</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>测试封面图-修改</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>测试封面图-修改</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>测试封面图-修改</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>测试封面图-修改</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>测试封面图-修改</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>测试课程版本-v1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>测试课程版本-v1-v2</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>低洼瞧得起我</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>特别的名字</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>测试-11</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>4.16 创建课程</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5月18日课程</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>7.8课程new</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>买没买=是；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>test2</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>买没买=否；课时数=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>一二三四五六七八九十</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>id=352</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Z-题干图验证</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>id=349</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Z-导入床</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>id=348</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Z-B4-答题角标</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>id=347</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>答题</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>id=343</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>M1-六选项六图</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>id=340</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>L5-待开始14题</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>id=339</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>L4-排序3题</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>id=338</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>L3-导入床</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>id=337</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>L2-六选项多选</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>id=336</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>L1-规则200字</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>id=335</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>G1-三题型带答案</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>id=316</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>F4-1000分</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>id=315</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>F3-十分答题</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>id=314</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>F2-十分答题</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>id=313</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>F1-十分答题</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>id=312</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>id=311</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>id=310</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>积分上限</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>id=309</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>答题</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>id=304</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>B6-字段全覆盖</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>id=287</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>B5-导入床</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>id=269</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>B4-每日限开</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>id=268</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>B3-15题</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>id=267</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>B2-14题</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>id=266</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>B1-1题</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>id=265</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>A5-特殊字符</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>id=264</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>A4-不轮播</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>id=263</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>A1-答题</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>id=260</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>答题活动</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>轮播-答题</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>id=255</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>方案一变形</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>仅凝固</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>仅充填2</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>充填凝固应力</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>充填凝固应力1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>7201744-孙</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>带组织性能结果</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>充填-排气</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1月 20250115</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>紫色1</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>内部数据6</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1QQ区qqqqq</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>重力铸造-重力砂型-0602-163625-仅充填仅浏览-重力铸造-重力砂型-0602-163625</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>重力铸造-重力砂型-0602-163625-充填凝固0602_165141-仅浏览</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>COPY3</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>3月26测试 私有材料分享(copy)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>内部数据-虚拟模具</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>内部数据</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>鹅鹅鹅</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>仅凝固+应力-选择点2</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>仅凝固1</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>循环凝固</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>131231</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>131231</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>循环凝固-热循环</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>6668</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>6668</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>填充任务1</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>0605测试</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>循环凝固+应力+选点1</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>料筒(copy)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>仅凝固</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>#713392277</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>？？？？</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>复制任务失败问题测试-分享</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>浇口充填-高级模式</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>热热热热</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>eeee</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>亲亲</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>3333 私有曲线</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>111111</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>测试二级页面案例111111111111111111111111111</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>分享高压 2</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>料筒充填</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>料筒充填1</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>料筒分享</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1WWWW</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>凝固应力</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>模拟汽车</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>模拟汽车减震</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>案例</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>多浇口充填(粒子数量10)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>（说明）</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>课程那张表里的「我们账号买没买」按 user_id=1966910（config/env.yaml）判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>（说明）</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>注意：这些课程名在库里有多门同名，按名字打开只会命中第一门 —— 012345678901234567890123456789、付费课程1、免费课程、免费课程1、无敌贵的课程、测试封面图、测试封面图-修改、测试验证课时bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>（说明）</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>案例共 56 条，已全部列出</t>
         </is>
       </c>
     </row>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -182,7 +182,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -373,6 +373,11 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -630,13 +635,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1049,2466 +1061,2902 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="13.25" customWidth="1" min="1" max="1"/>
-    <col width="35.125" customWidth="1" min="2" max="2"/>
-    <col width="9.375" customWidth="1" min="3" max="3"/>
-    <col width="17.125" customWidth="1" min="4" max="4"/>
-    <col width="23.75" customWidth="1" min="5" max="5"/>
-    <col width="6.5" customWidth="1" min="6" max="6"/>
-    <col width="73.375" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>用例编号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>用例名称</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>用例标题</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>前置条件</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>步骤序号</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>动作</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>活动入口_001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>首页活动入口在各筛选 tab 下都显示</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>手机在小程序首页（不用登录）</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>需求 713594979；只读</t>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>第1步：需求 713594979；只读
+第2步：只切 tab + 数活动卡，不改数据</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="C3" t="n">
+      <c r="D3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>只切 tab + 数活动卡，不改数据</t>
-        </is>
-      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>搜索页_001</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>搜索页能打开并输入关键词</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>手机在小程序首页（不用登录）</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>先摆正起点</t>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>第1步：先摆正起点
+第2步：关键词只能字母/数字/下划线/点/连字符（adb 不支持中文输入）
+第3步：搜索页的真实输入框
+第4步：把手机交还给下一条用例</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="n">
+      <c r="D5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>关键词只能字母/数字/下划线/点/连字符（adb 不支持中文输入）</t>
-        </is>
-      </c>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="C6" t="n">
+      <c r="D6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>wx-input.search-input</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>搜索页的真实输入框</t>
-        </is>
-      </c>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="C7" t="n">
+      <c r="D7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>把手机交还给下一条用例</t>
-        </is>
-      </c>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>答题页_001</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>答题活动页能打开且吸顶文案齐全</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>首页轮播里有「答题」卡（没有时「打开答题活动」记「跳过」，不算失败）</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>先摆正起点。注意：首页轮播里没有「答题」卡时，打开这一步会记成「跳过」</t>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>第1步：先摆正起点。注意：首页轮播里没有「答题」卡时，打开这一步会记成「跳过」
+第2步：只读：不选选项、不提交
+第3步：答题页根容器，只在答题页出现
+第4步：吸顶栏文案（需求 713594985）
+第5步：把手机交还给下一条用例</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="C9" t="n">
+      <c r="D9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>只读：不选选项、不提交</t>
-        </is>
-      </c>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="C10" t="n">
+      <c r="D10" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>.activity-quiz-page</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>答题页根容器，只在答题页出现</t>
-        </is>
-      </c>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="C11" t="n">
+      <c r="D11" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>答对最多可赢积分</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>吸顶栏文案（需求 713594985）</t>
-        </is>
-      </c>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="C12" t="n">
+      <c r="D12" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>把手机交还给下一条用例</t>
-        </is>
-      </c>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>学习中心_001</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>学习中心能进到专栏列表</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>手机在小程序首页（不用登录）</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>先摆正起点</t>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>需求「小程序-学习中心重组」（713223483）。第3步原先是断言「热门专栏」这个小标题，
+2026/10/14 全量回归时它红了：真机整页只有「往期专栏」，没有「热门专栏」——
+（互动专栏过了活动期会落到「往期专栏」，所以这个小标题**会随运营数据变**，不能拿来做断言）。
+改盯稳定结构：专栏卡片 .column-card 存在。页面对象那边的「到达判据」也同步放宽成
+「热门专栏 / 往期专栏 任一 + 有卡片」（见 learn_center_page.js 的注释）。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="C14" t="n">
+      <c r="D14" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>需求「小程序-学习中心重组」：压铸百科/课程/专栏合并到学习中心</t>
-        </is>
-      </c>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="C15" t="n">
+      <c r="D15" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>检查元素存在</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>.column-card</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="D16" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>积分商城_001</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>用户中心能看到积分商城</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>测试环境自己的账号已登录；手机在小程序首页</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>切到用户中心</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="D19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>热门专栏</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>「热门专栏」是专栏列表页独有的标记（页面对象里实测出来的）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" t="n">
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>积分商城</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="D20" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>把手机交还给下一条用例</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>积分商城_001</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>用户中心能看到积分商城</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>学习中心_002</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>学习中心能看见压铸百科</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>手机在小程序首页（不用登录）</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="C18" t="n">
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="D22" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>打开学习中心专栏</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="D23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>压铸百科</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="D24" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>搜索消失_001</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>进搜索页后首页筛选 tab 消失</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>手机在小程序首页（不用登录）</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="D26" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>最新提问</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="D27" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>打开搜索并输入</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="D28" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>检查文字不显示</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>最新提问</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="D29" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>框架自检_001</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>框架自检：把表格能用的动作全跑一遍</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；首页有可滚动内容（滑不动会报错，不会假装成功）</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>第1步：这条是给框架做体检的，业务上没用，可随时删
+第2步：不知道检查什么文字时，先跑它看日志
+第3步：切完会验证真的选中了
+第5步：首页上不该有答题页根容器
+第6步：在首页上滑（首页有可滚动内容）；滑不动它会自己报错，不会假装成功
+第7步：再滑回顶部 —— 不然搜索栏被顶出屏幕，下一步会点空
+第8步：按选择器点进搜索页
+第9步：关键词只能字母/数字
+第10步：读出来再比较
+第16步：进详情页</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>打印页面文字</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="D32" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>切换首页筛选栏</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="D33" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>切换首页筛选栏</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>最新提问</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>检查元素不存在</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>.activity-quiz-page</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="D35" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>滑动</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="D36" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>滑动</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="D37" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>点选择器</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>.search-container</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="D38" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>打开搜索并输入</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="D39" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>检查输入框的值</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>wx-input.search-input</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="D40" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>返回上一页</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="D41" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="D42" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>打开学习中心专栏</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="D43" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>切换学习中心顶部栏</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>压铸百科</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="D44" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>切换学习中心顶部栏</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>专栏</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="D45" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>打开第一张专栏</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="D46" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>返回上一页</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="D47" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>搜索空态_001</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>搜索零结果时出现 AI 引导（需求 713582841）</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；关键词 zzz9999 仍然零结果</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>第1步：先摆正起点
+第2步：实测：这个词是零结果
+第3步：不提交的话停在「搜索历史」面板，看不到空态
+第4步：需求原话，实机核对过逐字一致
+第5步：引导按钮文案
+第6步：把手机交还给下一条</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="D49" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>打开搜索并输入</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>zzz9999</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="D50" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>执行搜索</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="D51" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>没有找到相关内容？让小铸手帮你答</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="D52" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>问小铸手</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="D53" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>搜索空态_002</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>有结果时不出现 AI 引导（需求 713582841 的反向）</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；关键词 qqqqq 仍然有结果</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>第1步：先摆正起点
+第2步：实测：这个词有结果（所以不该出现引导）
+第4步：先确认真到了结果页，再断言「没有引导」才有意义
+第5步：需求：有结果搜索不出现引导模块
+第6步：把手机交还给下一条</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="D55" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>打开搜索并输入</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>qqqqq</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="D56" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>执行搜索</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="D57" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>全部回答</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="D58" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>检查文字不显示</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>问小铸手</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="D59" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr"/>
+      <c r="G59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>回到顶部_001</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>积分商城的回到顶部按钮符合需求（需求 713582097）</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>测试环境自己的账号已登录；手机在小程序首页</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="5" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>第1步：先摆正起点
+第2步：用户中心 -&gt; 积分商城（二级页，没有底部 tab 栏）
+第3步：需求口径：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏
+第4步：把手机交还给下一条</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="D61" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>打开积分商城</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr"/>
+      <c r="G61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="D62" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>检查回到顶部按钮</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="D63" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr"/>
+      <c r="G63" s="5" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>搜索话题_001</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>热门话题有 5 条且点第一条能进话题结果页（需求 713129788）</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>管理后台的「热门话题」配了 ≥5 个；手机在小程序首页</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="5" t="inlineStr"/>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>第1步：先摆正起点
+第2步：只进搜索页、不输入关键词（输入的话热门话题会被建议列表顶掉）
+第3步：需求：热门话题显示管理后台的前 5 个（区块标题是图片，所以只能按结构数）
+第4步：按位置点，不按名字点（话题名会变）
+第5步：话题结果页的排序 tab（实测：这个页面不是「全部回答」那套）
+第6步：同上，两个一起断言更稳
+第7步：把手机交还给下一条。注：「结果是否真的按该话题筛过」要读页面标题才能验，留给以后的代码用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="D65" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>打开搜索页</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr"/>
+      <c r="G65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="D66" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>检查元素数量</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>.hot-topics .inline-flex</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="D67" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>打开第一个热门话题</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="D68" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>最新发布</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="D69" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>最多点赞</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="D70" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr"/>
+      <c r="G70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>帖子主页按钮_001</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>帖子详情页点「主页」按钮回到首页（需求 713256065）</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>首页信息流里至少有 1 张帖子卡片</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr"/>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>第1步：先摆正起点
+第2步：点首页信息流第一张帖子卡片进详情（只读）
+第3步：详情页导航栏上那个主页图标（.icon-base-home）
+第4步：回到首页信息流的判据（那排筛选 tab）
+第5步：首页独有的搜索栏，双保险
+第6步：把手机交还给下一条</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="D72" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>打开第一个帖子</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="D73" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>点主页按钮</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr"/>
+      <c r="G73" s="5" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="D74" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>最新提问</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="D75" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>检查元素存在</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>.search-container</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="D76" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr"/>
+      <c r="G76" s="5" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>首页tab顺序_001</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>首页筛选 tab 顺序与默认选中符合需求（需求 713341876）</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>手机在小程序首页（不用登录）</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr"/>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>第1步：先摆正起点
+第2步：需求：最新提问和推荐互换顺序 + 最新提问为默认展示（置顶帖那半句依赖数据，暂不覆盖）
+第3步：把手机交还给下一条</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="D78" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>检查首页筛选栏顺序</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr"/>
+      <c r="G78" s="5" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="D79" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr"/>
+      <c r="G79" s="5" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>案例库_001</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>案例库：介绍banner在分类上方、点它进长图；列表显示复制数；详情页评论区是「全部评论」（需求 713381608）</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；案例库列表里至少有 1 个案例</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>第1步：先摆正起点
+第2步：入口 = 底部 tab「设计专区」
+第3步：分类上方有介绍 banner；卡片右下角是复制图标 + 复制数
+第4步：点首页那张 banner
+第5步：需求要求这一页是单张长图
+第6步：从长图退回列表
+第7步：列表第一张卡片（只读）
+第8步：评论区标题「全部评论」；底部无复制数/评论数图标
+第9步：把手机交还给下一条用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="D81" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="D82" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>检查案例库列表</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr"/>
+      <c r="G82" s="5" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="D83" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>打开案例库介绍长图</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr"/>
+      <c r="G83" s="5" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="D84" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>检查案例库介绍长图</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr"/>
+      <c r="G84" s="5" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="D85" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>返回上一页</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr"/>
+      <c r="G85" s="5" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="D86" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>打开第一个案例</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr"/>
+      <c r="G86" s="5" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="D87" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>检查案例详情页</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr"/>
+      <c r="G87" s="5" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="D88" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr"/>
+      <c r="G88" s="5" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>案例库_002</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>案例复制：点复制后弹出「复制成功 / 使用手机号登录智铸超云」（会写数据，跑完自动复位）</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>需要开关 UITEST_ALLOW_SUBMIT=1（会写数据，跑完自动复位）；列表第 1 个案例可复制</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr"/>
+      <c r="G89" s="5" t="inlineStr"/>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>第1步：先摆正起点
+第2步：入口 = 底部 tab「设计专区」
+第3步：复制按钮在详情页上
+第4步：一条龙：记水位→复制→断言提示→库里校验→自动复位。需要开关 UITEST_ALLOW_SUBMIT=1；没开关会记「跳过」
+第5步：把界面上真的出现了这句提示也写成表格里的断言
+第6步：把手机交还给下一条用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="D90" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr"/>
+      <c r="G90" s="5" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="D91" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>打开第一个案例</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr"/>
+      <c r="G91" s="5" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="D92" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>复制当前案例</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="5" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="D93" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>复制成功</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="D94" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>课程详情_001</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>课程详情页：已购买未开始显示「课程介绍」+ 课程标题 + 第一课时封面视频（需求 713367615）</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>登录账号已购买课程 717 且学习进度 0%（库里 user_course_relation 有、course_record 没有）</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr"/>
+      <c r="G95" s="5" t="inlineStr"/>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>第1步：先摆正起点
+第2步：我们账号对这门课是已购买 + 学习进度 0%（库里 user_course_relation 有、course_record 没有）
+第3步：需求原文：已购买用户-未开始学习 -&gt; 默认课程介绍，展示课程标题和第一课时封面/视频
+第4步：把手机交还给下一条用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="D96" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>打开课程详情</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="D97" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>检查课程详情页</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>课程介绍</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="D98" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr"/>
+      <c r="G98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>课程列表_001</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>课程列表：课时数为0的课程不显示（需求 713367615 第 1 条，跟数据库对账）</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>能连上测试库（要跟 course 表对账）；手机在小程序首页</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr"/>
+      <c r="G99" s="5" t="inlineStr"/>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>第1步：先摆正起点
+第2步：先到学习中心（默认落在专栏 tab）
+第3步：切到课程列表
+第4步：库里 28 门 0 课时的公开课程，一个都不该出现在列表里（会让列表滚到底再对账）
+第5步：把手机交还给下一条用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="D100" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>打开学习中心专栏</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr"/>
+      <c r="G100" s="5" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="D101" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>切换学习中心顶部栏</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="D102" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>检查0课时课程不显示</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr"/>
+      <c r="G102" s="5" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="D103" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr"/>
+      <c r="G103" s="5" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>案例库_003</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>付费案例复制：也弹同样的提示（会写数据 + 扣积分，跑完自动复位记录与复制数）</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>需要开关 UITEST_ALLOW_SUBMIT=1（会写数据 + 扣积分，复制记录与复制数自动复位）；案例名「填充任务1」要与列表上一字不差</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr"/>
+      <c r="G104" s="5" t="inlineStr"/>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>第1步：先摆正起点
+第2步：入口 = 底部 tab「设计专区」
+第3步：付费样本（5 积分，全库最便宜的付费案例之一；案例名要跟列表上一字不差）
+第4步：需求：免费和付费案例都提示。付费会扣积分（中台记账，不复位）；复制记录与复制数会自动复位
+第5步：把界面上真的出现了这句提示也写成表格里的断言
+第6步：把手机交还给下一条用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="D105" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr"/>
+      <c r="G105" s="5" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="D106" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>打开案例</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>填充任务1</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="D107" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>复制当前案例</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr"/>
+      <c r="G107" s="5" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="D108" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>复制成功</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="D109" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr"/>
+      <c r="G109" s="5" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>课程详情_002</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>未购买课程点课时：封面和标题不变、始终显示课程名（需求 713367615 第 2 条）</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>登录账号未购买「7.8课程new」（依据 user_course_relation 表）</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr"/>
+      <c r="G110" s="5" t="inlineStr"/>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>第1步：先摆正起点
+第2步：我们账号只买过 717 一门课，所以这门是未购买（依据：user_course_relation 表）
+第3步：需求原文：未购买用户点击课时不改变封面图和标题，始终显示课程名称
+第4步：把手机交还给下一条用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="D111" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>打开课程详情</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>7.8课程new</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="D112" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>检查未购买点课时</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>7.8课程new</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="D113" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr"/>
+      <c r="G113" s="5" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>学习中心_003</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>学习中心顶部有三个 tab</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>手机在小程序首页（不用登录）</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr"/>
+      <c r="G114" s="5" t="inlineStr"/>
+      <c r="H114" s="6" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="D115" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>学习中心</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="D116" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>课程</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="D117" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>专栏</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="D118" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>压铸百科</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="D119" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr"/>
+      <c r="G119" s="5" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>手机在小程序首页</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr"/>
+      <c r="G120" s="5" t="inlineStr"/>
+      <c r="H120" s="6" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="D121" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>点选择器</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>.fs-28</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="D122" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>输入搜索关键词</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>吉宝</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="D123" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>执行搜索</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr"/>
+      <c r="G123" s="5" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="D124" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr"/>
+      <c r="G124" s="5" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>中文搜索_001</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>中文关键词能搜出东西（靠搜索历史点进去）</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>测试库里该账号的搜索历史里有「压铸测试」（用 tools/search_history_tool.py 造过）</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr"/>
+      <c r="G125" s="5" t="inlineStr"/>
+      <c r="H125" s="6" t="inlineStr">
+        <is>
+          <t>第1步：先摆正起点
+第2步：搜索页上才有「搜索历史」面板
+第3步：中文搜索的关键一步：框架自己敲不了中文，靠点历史词条触发。这个词用工具造过：python tools/search_history_tool.py --user 1966910 --keyword 压铸测试 --add --yes
+第4步：结果页的搜索栏里应当是这个词（= 真的照它搜了）
+第5步：把手机交还给下一条用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="D126" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>打开搜索页</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr"/>
+      <c r="G126" s="5" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="D127" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>点搜索历史里的词</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>压铸测试</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="D128" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>压铸测试</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="D129" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr"/>
+      <c r="G129" s="5" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>中文搜索_002</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>中文关键词直接输入也能搜（框架自动切输入法）</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；框架会自动临时切到 ADBKeyboard 输入中文</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr"/>
+      <c r="G130" s="5" t="inlineStr"/>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>第1步：先摆正起点
+第2步：中文关键词：框架会自动临时切到 ADBKeyboard，用完切回你原来的输入法
+第3步：按回车把搜索跑起来
+第4步：**关键断言**：回车后页面必须离开「搜索历史」面板 —— 否则就是没搜起来（原来这里写的是「压铸」，历史面板上也显示它，属于假绿）
+第5步：结果页的 tab 行（搜索历史面板上没有这几个字）
+第6步：把手机交还给下一条用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="D131" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>打开搜索并输入</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>压铸</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="D132" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>执行搜索</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr"/>
+      <c r="G132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="D133" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>检查文字不显示</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>搜索历史</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="D134" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>全部回答</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="D135" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr"/>
+      <c r="G135" s="5" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ZW_001</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>有问必答筛选栏第三个 tab 文案是「精选问答」</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>手机在小程序首页（不用登录）</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>缺陷 713070171（原文：有问必答中，精选回答tab应该为精选问答）；只读。
+第2步顺带验证四个 tab 的文案、顺序与默认选中（需求 713341876）—— 单独写"不显示"容易变成一句空断言。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="D137" t="n">
+        <v>2</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>检查首页筛选栏顺序</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="D138" t="n">
+        <v>3</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>精选问答</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="D139" t="n">
+        <v>4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>检查文字不显示</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>精选回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="D140" t="n">
+        <v>5</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ZW_002</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>普通用户在个人中心不显示身份标签</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>测试环境自己的账号已登录；手机在小程序首页</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>缺陷 713073541（原文：当用户为普通用户时，搜索结果、个人中心应该不显示普通用户的标签）+ 713295623（普通用户不显示身份标签）；只读。
+第3步是"证明个人中心真的到了"的前置断言 —— 少了它，页面没到也会绿（假绿）。
+没覆盖的半句：搜索结果里也不显示身份标签（关键词结果随线上数据变，容易假红，留给以后）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="D142" t="n">
+        <v>2</v>
+      </c>
+      <c r="E142" t="inlineStr">
         <is>
           <t>切到用户中心</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="C19" t="n">
+    <row r="143">
+      <c r="D143" t="n">
         <v>3</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>积分商城</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="C20" t="n">
+    <row r="144">
+      <c r="D144" t="n">
         <v>4</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>检查文字不显示</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>普通用户</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="D145" t="n">
+        <v>5</v>
+      </c>
+      <c r="E145" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>学习中心_002</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>学习中心能看见压铸百科</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ZW_003</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>帖子详情页点评论入口要弹出评论面板</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>首页信息流里至少有 1 张帖子卡片（首页自己要能加载出来）</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
         <v>1</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E146" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="n">
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>缺陷 713006028（原文：帖子详情页，评论按钮点击无响应）；只读，不发评论。
+第4步是核心断言：点了评论入口之后，面板上必须出现「发送」按钮。
+（点之前页面上没有「发送」—— 这条断言是当场在真机上正反两次验过的，见 probe_post_comment_entry.js）
+第5步点遮罩是收尾必须：面板 + 键盘会把整页盖住（overlay-mask），不关掉后面「回到首页」点不到任何东西。</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="D147" t="n">
         <v>2</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>打开学习中心专栏</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="n">
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>打开第一个帖子</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="D148" t="n">
         <v>3</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>留下你的回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="D149" t="n">
+        <v>4</v>
+      </c>
+      <c r="E149" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>压铸百科</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="n">
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>发送</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="D150" t="n">
+        <v>5</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>点选择器</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>.overlay-mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="D151" t="n">
+        <v>6</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ZW_004</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>话题详情页点筛选项不会把页面点坏</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；搜索页的「热门话题」至少有 1 条</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>缺陷 713335002（原文：话题详情页筛选项点击时报错）；只读。
+第4步点的是话题结果页的排序筛选项；第5步的断言不是"验证排序结果"，而是**页面还在** ——
+点一下筛选项就报错的话，那排 tab 会直接不见，这正是那个 bug 的样子。
+排序结果对不对要读数据，框架暂时验不了（记在《缺陷回归候选清单》里）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="D153" t="n">
+        <v>2</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>打开搜索页</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="D154" t="n">
+        <v>3</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>打开第一个热门话题</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="D155" t="n">
         <v>4</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>最新发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="D156" t="n">
+        <v>5</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>最多点赞</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="D157" t="n">
+        <v>6</v>
+      </c>
+      <c r="E157" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>搜索消失_001</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>进搜索页后首页筛选 tab 消失</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>最新提问</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>打开搜索并输入</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>hello</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" t="n">
-        <v>4</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>检查文字不显示</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>最新提问</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" t="n">
-        <v>5</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>框架自检_001</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>框架自检：把表格能用的动作全跑一遍</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>这条是给框架做体检的，业务上没用，可随时删</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>打印页面文字</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>不知道检查什么文字时，先跑它看日志</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="n">
-        <v>3</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>切换首页筛选栏</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>切完会验证真的选中了</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="n">
-        <v>4</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>切换首页筛选栏</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>最新提问</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="n">
-        <v>5</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>检查元素不存在</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>.activity-quiz-page</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>首页上不该有答题页根容器</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="n">
-        <v>6</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>滑动</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>上</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>在首页上滑（首页有可滚动内容）；滑不动它会自己报错，不会假装成功</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="n">
-        <v>7</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>滑动</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>下</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>再滑回顶部 —— 不然搜索栏被顶出屏幕，下一步会点空</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="n">
-        <v>8</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>点选择器</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>.search-container</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>按选择器点进搜索页</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>打开搜索并输入</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>hello</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>关键词只能字母/数字</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="n">
-        <v>10</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>检查输入框的值</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>wx-input.search-input</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>hello</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>读出来再比较</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="n">
-        <v>11</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>返回上一页</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="n">
-        <v>12</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="n">
-        <v>13</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>打开学习中心专栏</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="n">
-        <v>14</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>切换学习中心顶部栏</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>压铸百科</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="n">
-        <v>15</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>切换学习中心顶部栏</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>专栏</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="n">
-        <v>16</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>打开第一张专栏</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>进详情页</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="n">
-        <v>17</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>返回上一页</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="n">
-        <v>18</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>搜索空态_001</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>搜索零结果时出现 AI 引导（需求 713582841）</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>先摆正起点</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="n">
-        <v>2</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>打开搜索并输入</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>zzz9999</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>实测：这个词是零结果</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="n">
-        <v>3</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>执行搜索</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>不提交的话停在「搜索历史」面板，看不到空态</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="n">
-        <v>4</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>没有找到相关内容？让小铸手帮你答</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>需求原话，实机核对过逐字一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" t="n">
-        <v>5</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>问小铸手</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>引导按钮文案</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" t="n">
-        <v>6</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>把手机交还给下一条</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>搜索空态_002</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>有结果时不出现 AI 引导（需求 713582841 的反向）</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>先摆正起点</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="C55" t="n">
-        <v>2</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>打开搜索并输入</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>qqqqq</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>实测：这个词有结果（所以不该出现引导）</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="C56" t="n">
-        <v>3</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>执行搜索</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="C57" t="n">
-        <v>4</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>全部回答</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>先确认真到了结果页，再断言「没有引导」才有意义</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="C58" t="n">
-        <v>5</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>检查文字不显示</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>问小铸手</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>需求：有结果搜索不出现引导模块</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="C59" t="n">
-        <v>6</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>把手机交还给下一条</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>回到顶部_001</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>积分商城的回到顶部按钮符合需求（需求 713582097）</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>先摆正起点</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="C61" t="n">
-        <v>2</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>打开积分商城</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>用户中心 -&gt; 积分商城（二级页，没有底部 tab 栏）</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="C62" t="n">
-        <v>3</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>检查回到顶部按钮</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>需求口径：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="C63" t="n">
-        <v>4</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>把手机交还给下一条</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>搜索话题_001</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>热门话题有 5 条且点第一条能进话题结果页（需求 713129788）</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>先摆正起点</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="C65" t="n">
-        <v>2</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>打开搜索页</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>只进搜索页、不输入关键词（输入的话热门话题会被建议列表顶掉）</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="C66" t="n">
-        <v>3</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>检查元素数量</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>.hot-topics .inline-flex</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>需求：热门话题显示管理后台的前 5 个（区块标题是图片，所以只能按结构数）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="C67" t="n">
-        <v>4</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>打开第一个热门话题</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>按位置点，不按名字点（话题名会变）</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="C68" t="n">
-        <v>5</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>最新发布</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>话题结果页的排序 tab（实测：这个页面不是「全部回答」那套）</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="C69" t="n">
-        <v>6</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>最多点赞</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>同上，两个一起断言更稳</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="C70" t="n">
-        <v>7</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>把手机交还给下一条。注：「结果是否真的按该话题筛过」要读页面标题才能验，留给以后的代码用例</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>帖子主页按钮_001</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>帖子详情页点「主页」按钮回到首页（需求 713256065）</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>先摆正起点</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="C72" t="n">
-        <v>2</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>打开第一个帖子</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>点首页信息流第一张帖子卡片进详情（只读）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="C73" t="n">
-        <v>3</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>点主页按钮</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>详情页导航栏上那个主页图标（.icon-base-home）</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="C74" t="n">
-        <v>4</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>最新提问</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>回到首页信息流的判据（那排筛选 tab）</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="C75" t="n">
-        <v>5</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>检查元素存在</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>.search-container</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>首页独有的搜索栏，双保险</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="C76" t="n">
-        <v>6</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>把手机交还给下一条</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>首页tab顺序_001</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>首页筛选 tab 顺序与默认选中符合需求（需求 713341876）</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>先摆正起点</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="C78" t="n">
-        <v>2</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>检查首页筛选栏顺序</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>需求：最新提问和推荐互换顺序 + 最新提问为默认展示（置顶帖那半句依赖数据，暂不覆盖）</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="C79" t="n">
-        <v>3</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>把手机交还给下一条</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>案例库_001</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>案例库：介绍banner在分类上方、点它进长图；列表显示复制数；详情页评论区是「全部评论」（需求 713381608）</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>先摆正起点</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="C81" t="n">
-        <v>2</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>打开案例库</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>入口 = 底部 tab「设计专区」</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="C82" t="n">
-        <v>3</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>检查案例库列表</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>分类上方有介绍 banner；卡片右下角是复制图标 + 复制数</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="C83" t="n">
-        <v>4</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>打开案例库介绍长图</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>点首页那张 banner</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="C84" t="n">
-        <v>5</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>检查案例库介绍长图</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>需求要求这一页是单张长图</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="C85" t="n">
-        <v>6</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>返回上一页</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>从长图退回列表</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="C86" t="n">
-        <v>7</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>打开第一个案例</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>列表第一张卡片（只读）</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="C87" t="n">
-        <v>8</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>检查案例详情页</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>评论区标题「全部评论」；底部无复制数/评论数图标</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="C88" t="n">
-        <v>9</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>把手机交还给下一条用例</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>案例库_002</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>案例复制：点复制后弹出「复制成功 / 使用手机号登录智铸超云」（会写数据，跑完自动复位）</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>1</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>先摆正起点</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="C90" t="n">
-        <v>2</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>打开案例库</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>入口 = 底部 tab「设计专区」</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="C91" t="n">
-        <v>3</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>打开第一个案例</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>复制按钮在详情页上</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="C92" t="n">
-        <v>4</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>复制当前案例</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>一条龙：记水位→复制→断言提示→库里校验→自动复位。需要开关 UITEST_ALLOW_SUBMIT=1；没开关会记「跳过」</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="C93" t="n">
-        <v>5</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>复制成功</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>把界面上真的出现了这句提示也写成表格里的断言</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="C94" t="n">
-        <v>6</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>把手机交还给下一条用例</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>课程详情_001</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>课程详情页：已购买未开始显示「课程介绍」+ 课程标题 + 第一课时封面视频（需求 713367615）</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>先摆正起点</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="C96" t="n">
-        <v>2</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>打开课程详情</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>我们账号对这门课是已购买 + 学习进度 0%（库里 user_course_relation 有、course_record 没有）</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="C97" t="n">
-        <v>3</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>检查课程详情页</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>课程介绍</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>需求原文：已购买用户-未开始学习 -&gt; 默认课程介绍，展示课程标题和第一课时封面/视频</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="C98" t="n">
-        <v>4</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>把手机交还给下一条用例</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>课程列表_001</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>课程列表：课时数为0的课程不显示（需求 713367615 第 1 条，跟数据库对账）</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>1</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>先摆正起点</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="C100" t="n">
-        <v>2</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>打开学习中心专栏</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>先到学习中心（默认落在专栏 tab）</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="C101" t="n">
-        <v>3</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>切换学习中心顶部栏</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>切到课程列表</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="C102" t="n">
-        <v>4</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>检查0课时课程不显示</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>库里 28 门 0 课时的公开课程，一个都不该出现在列表里（会让列表滚到底再对账）</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="C103" t="n">
-        <v>5</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>把手机交还给下一条用例</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>案例库_003</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>付费案例复制：也弹同样的提示（会写数据 + 扣积分，跑完自动复位记录与复制数）</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>1</v>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>先摆正起点</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="C105" t="n">
-        <v>2</v>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>打开案例库</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>入口 = 底部 tab「设计专区」</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="C106" t="n">
-        <v>3</v>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>打开案例</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>填充任务1</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>付费样本（5 积分，全库最便宜的付费案例之一；案例名要跟列表上一字不差）</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="C107" t="n">
-        <v>4</v>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>复制当前案例</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>需求：免费和付费案例都提示。付费会扣积分（中台记账，不复位）；复制记录与复制数会自动复位</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="C108" t="n">
-        <v>5</v>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>复制成功</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>把界面上真的出现了这句提示也写成表格里的断言</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="C109" t="n">
-        <v>6</v>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>把手机交还给下一条用例</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>课程详情_002</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>未购买课程点课时：封面和标题不变、始终显示课程名（需求 713367615 第 2 条）</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>1</v>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>先摆正起点</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="C111" t="n">
-        <v>2</v>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>打开课程详情</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>7.8课程new</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>我们账号只买过 717 一门课，所以这门是未购买（依据：user_course_relation 表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="C112" t="n">
-        <v>3</v>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>检查未购买点课时</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>7.8课程new</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>需求原文：未购买用户点击课时不改变封面图和标题，始终显示课程名称</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="C113" t="n">
-        <v>4</v>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>把手机交还给下一条用例</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>学习中心_003</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>学习中心顶部有三个 tab</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>1</v>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="C115" t="n">
-        <v>2</v>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>点文字</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>学习中心</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="C116" t="n">
-        <v>3</v>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>课程</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="C117" t="n">
-        <v>4</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>专栏</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="C118" t="n">
-        <v>5</v>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>压铸百科</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="C119" t="n">
-        <v>6</v>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>测试</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>测试</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>1</v>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="C121" t="n">
-        <v>2</v>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>点选择器</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>.fs-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="C122" t="n">
-        <v>3</v>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>输入搜索关键词</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>吉宝</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="C123" t="n">
-        <v>4</v>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>执行搜索</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="C124" t="n">
-        <v>5</v>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>中文搜索_001</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>中文关键词能搜出东西（靠搜索历史点进去）</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>1</v>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>先摆正起点</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="C126" t="n">
-        <v>2</v>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>打开搜索页</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>搜索页上才有「搜索历史」面板</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="C127" t="n">
-        <v>3</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>点搜索历史里的词</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>压铸测试</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>中文搜索的关键一步：框架自己敲不了中文，靠点历史词条触发。这个词用工具造过：python tools/search_history_tool.py --user 1966910 --keyword 压铸测试 --add --yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="C128" t="n">
-        <v>4</v>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>压铸测试</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>结果页的搜索栏里应当是这个词（= 真的照它搜了）</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="C129" t="n">
-        <v>5</v>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>把手机交还给下一条用例</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>中文搜索_002</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>中文关键词直接输入也能搜（框架自动切输入法）</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>1</v>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>先摆正起点</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="C131" t="n">
-        <v>2</v>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>打开搜索并输入</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>压铸</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>中文关键词：框架会自动临时切到 ADBKeyboard，用完切回你原来的输入法</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="C132" t="n">
-        <v>3</v>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>执行搜索</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>按回车把搜索跑起来</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="C133" t="n">
-        <v>4</v>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>检查文字不显示</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>搜索历史</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>**关键断言**：回车后页面必须离开「搜索历史」面板 —— 否则就是没搜起来（原来这里写的是「压铸」，历史面板上也显示它，属于假绿）</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="C134" t="n">
-        <v>5</v>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>全部回答</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>结果页的 tab 行（搜索历史面板上没有这几个字）</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="C135" t="n">
-        <v>6</v>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>把手机交还给下一条用例</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="A80:A88"/>
-    <mergeCell ref="A110:A113"/>
+  <mergeCells count="112">
     <mergeCell ref="A48:A53"/>
     <mergeCell ref="A114:A119"/>
-    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="H99:H103"/>
+    <mergeCell ref="H130:H135"/>
+    <mergeCell ref="H141:H145"/>
+    <mergeCell ref="B130:B135"/>
+    <mergeCell ref="B30:B47"/>
+    <mergeCell ref="H17:H20"/>
+    <mergeCell ref="C125:C129"/>
+    <mergeCell ref="A54:A59"/>
+    <mergeCell ref="C54:C59"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H125:H129"/>
+    <mergeCell ref="H110:H113"/>
+    <mergeCell ref="B125:B129"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="H30:H47"/>
+    <mergeCell ref="C141:C145"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="C60:C63"/>
+    <mergeCell ref="C64:C70"/>
+    <mergeCell ref="B95:B98"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="H48:H53"/>
+    <mergeCell ref="H104:H109"/>
+    <mergeCell ref="A99:A103"/>
+    <mergeCell ref="H64:H70"/>
+    <mergeCell ref="A130:A135"/>
+    <mergeCell ref="B104:B109"/>
+    <mergeCell ref="B136:B140"/>
+    <mergeCell ref="A136:A140"/>
+    <mergeCell ref="H54:H59"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="B71:B76"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="H146:H151"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="C136:C140"/>
+    <mergeCell ref="C152:C157"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="A89:A94"/>
+    <mergeCell ref="H8:H12"/>
+    <mergeCell ref="B141:B145"/>
+    <mergeCell ref="B60:B63"/>
+    <mergeCell ref="B25:B29"/>
+    <mergeCell ref="A64:A70"/>
+    <mergeCell ref="H95:H98"/>
+    <mergeCell ref="C95:C98"/>
+    <mergeCell ref="A30:A47"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C48:C53"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="C120:C124"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="A141:A145"/>
     <mergeCell ref="A60:A63"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="B114:B119"/>
-    <mergeCell ref="B99:B103"/>
     <mergeCell ref="B2:B3"/>
+    <mergeCell ref="H152:H157"/>
+    <mergeCell ref="H77:H79"/>
     <mergeCell ref="A125:A129"/>
-    <mergeCell ref="B71:B76"/>
-    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="H120:H124"/>
+    <mergeCell ref="H114:H119"/>
+    <mergeCell ref="H89:H94"/>
+    <mergeCell ref="H80:H88"/>
     <mergeCell ref="B48:B53"/>
-    <mergeCell ref="B30:B47"/>
-    <mergeCell ref="B130:B135"/>
     <mergeCell ref="B64:B70"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="A54:A59"/>
-    <mergeCell ref="A21:A24"/>
-    <mergeCell ref="A2:A3"/>
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="B80:B88"/>
-    <mergeCell ref="B125:B129"/>
-    <mergeCell ref="A89:A94"/>
-    <mergeCell ref="A71:A76"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="B60:B63"/>
-    <mergeCell ref="B25:B29"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="A64:A70"/>
+    <mergeCell ref="H60:H63"/>
+    <mergeCell ref="C114:C119"/>
+    <mergeCell ref="C130:C135"/>
+    <mergeCell ref="C30:C47"/>
     <mergeCell ref="A104:A109"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="B95:B98"/>
-    <mergeCell ref="A30:A47"/>
-    <mergeCell ref="B120:B124"/>
+    <mergeCell ref="B146:B151"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="A4:A7"/>
+    <mergeCell ref="C13:C16"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="H25:H29"/>
+    <mergeCell ref="A152:A157"/>
+    <mergeCell ref="A120:A124"/>
+    <mergeCell ref="A80:A88"/>
+    <mergeCell ref="C80:C88"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="C8:C12"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="B99:B103"/>
+    <mergeCell ref="C89:C94"/>
+    <mergeCell ref="C104:C109"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="H136:H140"/>
+    <mergeCell ref="A146:A151"/>
+    <mergeCell ref="C146:C151"/>
+    <mergeCell ref="H21:H24"/>
+    <mergeCell ref="B152:B157"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="C71:C76"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="H13:H16"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="B120:B124"/>
     <mergeCell ref="B89:B94"/>
-    <mergeCell ref="B77:B79"/>
     <mergeCell ref="A25:A29"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="A99:A103"/>
+    <mergeCell ref="C25:C29"/>
+    <mergeCell ref="C99:C103"/>
+    <mergeCell ref="H71:H76"/>
     <mergeCell ref="B54:B59"/>
-    <mergeCell ref="A130:A135"/>
-    <mergeCell ref="B104:B109"/>
-    <mergeCell ref="A120:A124"/>
+    <mergeCell ref="B114:B119"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
       <formula1>='动作清单'!$A$2:$A$54</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
@@ -3577,8 +4025,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -3606,8 +4052,6 @@
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -3635,8 +4079,6 @@
           <t>打开积分商城</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -3664,8 +4106,6 @@
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -3698,7 +4138,6 @@
           <t>顶部栏名称（只能填：课程 / 专栏 / 压铸百科）</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>专栏</t>
@@ -3726,8 +4165,6 @@
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -3755,8 +4192,6 @@
           <t>点主页按钮</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -3784,8 +4219,6 @@
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -3813,8 +4246,6 @@
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -3847,7 +4278,6 @@
           <t>课程名</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>717</t>
@@ -3880,7 +4310,6 @@
           <t>关键词</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -3913,7 +4342,6 @@
           <t>关键词</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -3941,8 +4369,6 @@
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -3975,7 +4401,6 @@
           <t>词</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>压铸测试</t>
@@ -4003,8 +4428,6 @@
           <t>打开第一个热门话题</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4032,8 +4455,6 @@
           <t>打开第一个帖子</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4061,8 +4482,6 @@
           <t>打开第一张专栏</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4090,8 +4509,6 @@
           <t>打开第一个案例</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4119,8 +4536,6 @@
           <t>打开案例库介绍长图</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4153,7 +4568,6 @@
           <t>案例名</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>填充任务1</t>
@@ -4260,7 +4674,6 @@
           <t>id</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>_AQ（首页搜索栏；也可以写 #_AQ）</t>
@@ -4330,7 +4743,6 @@
           <t>筛选栏名称（只能填：最新提问 / 推荐 / 精选问答 / 我的关注）</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>推荐</t>
@@ -4363,7 +4775,6 @@
           <t>毫秒</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>2000（= 等 2 秒）</t>
@@ -4391,8 +4802,6 @@
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4425,7 +4834,6 @@
           <t>范围（只能填：全量 / 只看有文字）</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>只看有文字</t>
@@ -4458,7 +4866,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>答对最多可赢积分</t>
@@ -4491,7 +4898,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>最新提问（搜索页上不该有）</t>
@@ -4561,7 +4967,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>.search-container</t>
@@ -4594,7 +4999,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>.activity-quiz-page</t>
@@ -4664,7 +5068,6 @@
           <t>id</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>_AQ</t>
@@ -4697,7 +5100,6 @@
           <t>id</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>_AQ（进了搜索页之后，首页那个搜索栏就不该在了）</t>
@@ -4762,8 +5164,6 @@
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4791,8 +5191,6 @@
           <t>检查首页筛选栏顺序</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4820,8 +5218,6 @@
           <t>检查回到顶部按钮</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4849,8 +5245,6 @@
           <t>检查答题页</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4878,8 +5272,6 @@
           <t>检查案例库列表</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4907,8 +5299,6 @@
           <t>检查案例详情页</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4936,8 +5326,6 @@
           <t>检查案例库介绍长图</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4970,7 +5358,6 @@
           <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>课程介绍</t>
@@ -4998,8 +5385,6 @@
           <t>检查0课时课程不显示</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5032,7 +5417,6 @@
           <t>课程名</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>7.8课程new</t>
@@ -5060,8 +5444,6 @@
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5089,8 +5471,6 @@
           <t>逐题作答</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5118,8 +5498,6 @@
           <t>提交答卷</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5152,7 +5530,6 @@
           <t>活动名</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>Z-B4-答题角标</t>
@@ -5217,8 +5594,6 @@
           <t>复制当前案例</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5251,14 +5626,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>怎么用这张表（零基础版）</t>
         </is>
@@ -5267,126 +5642,364 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. 一行 = 一个步骤。同一个「用例编号」的若干行，按「步骤序号」顺序执行；它们一起算一条用例。</t>
+          <t>【表长什么样】8 列，分两种：</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. 必填三列：用例编号、步骤序号、动作。「用例名称」只在某条用例的第一行写一次就行。</t>
+          <t xml:space="preserve">  按用例的 4 列（表里并成一格，只有第一步那行有值）：</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3. 「动作」只能填「动作清单」工作表里列出的名字 —— 填别的会在导出时报错，不会静默跳过。</t>
+          <t xml:space="preserve">     用例编号 | 用例标题 | 前置条件 | 备注</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4. 「参数1 / 参数2」按动作需要填，不用就留空。填多了（该动作用不到）也会报错，防手滑。</t>
+          <t xml:space="preserve">  按步骤的 4 列（每一行都要填）：</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5. 「备注」随便写，只出现在日志和报告里，不影响执行。</t>
+          <t xml:space="preserve">     步骤序号 | 动作 | 参数1 | 参数2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6. 填完执行：python run.py      （它会先自动把本表导出成 json，再跑用例）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   只想跑表格里的某一条：python run.py -k 活动入口_001</t>
+          <t xml:space="preserve">  编号格式：ZW_001、ZW_002…（前缀 + 三位数字，唯一就行；填错的编号会让这条用例对不上号）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7. 每条用例开头都先用「回到首页」把起点摆正；会把手机停在二级页（搜索页/详情页/答题页）的用例，</t>
+          <t>1. 一行 = 一个步骤。同一个「用例编号」的若干行，按「步骤序号」顺序执行；它们一起算一条用例。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   最后再补一步「回到首页」把手机交还。原因：表里的用例共用同一部手机，</t>
+          <t>2. 一条用例怎么摆：第一行写「用例编号 + 用例标题 + 前置条件 + 备注」，</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   上一条停在二级页上，下一条可能报「找不到底部 tab」—— 开头摆正 + 结尾交还就不受影响。</t>
+          <t xml:space="preserve">   下面几行的这四列并成一格、空着就行 —— 表上看起来就是「一案一块」，</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   一眼数得出有几条用例、每条几步、每条要怎么准备。每行都要填的是「步骤序号」和「动作」。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>默认禁止（安全阀，避免手滑把真实数据改了）</t>
+          <t xml:space="preserve">   （按这个排版，导出时编号空着的行会自动并到上一条用例；但第一行数据必须写编号，否则整表报错。）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 「点文字」不能点这些字：提交、兑换、签到、下单、支付、购买、领取、抽奖、报名、删除、退出登录、退款、取消订单</t>
+          <t>2b.「前置条件」写「跑这条之前手机得在什么状态」（要不要先登录、首页得有什么卡），</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">     原因：这些操作会改真实数据/消耗真实积分。真要测它们，得单独写用例并显式打开开关，不能靠表格里写一行就触发。</t>
+          <t xml:space="preserve">   它不是动作、不会被自动执行 —— 是给人看的，也是「这条挂了先查什么」的线索。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 「打开答题活动」只打开页面，不选选项、不提交（选选项会消耗答题机会）。</t>
+          <t>2c.「备注」是整条用例的备注（也并成一格）。某一步自己的说明写在同一格里，</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   用「第2步：…」开头即可。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已知限制（诚实标注，别误读成框架不行）</t>
+          <t>3. 「动作」只能填「动作清单」工作表里列出的名字 —— 填别的会在导出时报错，不会静默跳过。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 搜索关键词只能是字母/数字/下划线/点/连字符：关键词是通过 adb 发过去的，adb 发中文不报错但不生效。</t>
+          <t>3b. 有几类参数要填数据里的名字（课程名 / 案例名 / 活动名），一字不差才行；</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 「点文字」点的是屏幕上看得见的文字；同名文字有多个时点第 1 个。</t>
+          <t xml:space="preserve">    候选值在「名称候选」工作表里，直接复制粘贴即可（刷新它：python tools/export_cases.py --dropdown）。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>4. 「参数1 / 参数2」按动作需要填，不用就留空。填多了（该动作用不到）也会报错，防手滑；</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   参数名后面写着「（可不填）」的，留空就走默认值（例如「第几个」留空 = 第 1 个）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>5. 「备注」随便写，只出现在日志和报告里，不影响执行（但它会显示在报告里，写清需求号很有用）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6. 填完执行：python run.py      （它会先自动把本表导出成 json，再跑用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   只想跑表格里的某一条：python run.py -k 活动入口_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7. 每条用例开头都先用「回到首页」把起点摆正；会把手机停在二级页（搜索页/详情页/答题页）的用例，</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   最后再补一步「回到首页」把手机交还。原因：表里的用例共用同一部手机，</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   上一条停在二级页上，下一条可能报「找不到底部 tab」—— 开头摆正 + 结尾交还就不受影响。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>8. 「动作」列是下拉框（点单元格右边的小箭头选），可选项来自「动作清单」工作表；</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   「步骤序号」列只接受 1、2、3… 这样的正整数。填错的动作名根本选不出来，省一轮报错。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8b. 自己新加的行不会自动并格。改完想让它并回去、顺便刷新下拉框，跑一次：</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    python tools/export_cases.py --dropdown    （只动排版，不动你填的内容；Excel 开着这份表时先关掉）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>9. 不知道「检查文字显示」该填哪段字？先加一行「打印页面文字」跑一次 ——</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   当前屏幕上看得见的文字会打进日志，照着抄就行（挑完把它删掉即可）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>默认禁止（安全阀，避免手滑把真实数据改了）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 「点文字」不能点这些字：提交、兑换、签到、下单、支付、购买、领取、抽奖、报名、删除、退出登录、退款、取消订单</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     原因：这些操作会改真实数据/消耗真实积分。真要测它们，得单独写用例并显式打开开关，不能靠表格里写一行就触发。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 「打开答题活动」只打开页面，不选选项、不提交（选选项会消耗答题机会）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>要测「会改数据」的操作？开着开关跑（owner 2026/10/12 同意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 开关就是一句环境变量：跑之前先执行  $env:UITEST_ALLOW_SUBMIT="1"  （PowerShell）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     不设这个开关时，下面这两个动作会直接报错，不会偷偷执行，也不会假装跳过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 「复位答题记录」（参数1=活动名）：删掉该活动在测试库里留下的答题记录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     默认只预览不删；开了开关才真删。跑完写数据的用例，务必用它把记录清干净。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 「提交答卷」：真的提交一次，用来测「提交后按钮变成已提交已参加」这条需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 「逐题作答」「检查答题记录数」不需要开关：前者只改前端选中态（不写库），后者是只读。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 写链路的标准写法（照抄即可）：回到首页 → 打开答题活动 → 复位答题记录(活动名) →</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     逐题作答 → 检查文字显示(已答) → 提交答卷 → 检查文字显示(已参加) →</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     检查答题记录数(活动名 / 1) → 复位答题记录(活动名) → 回到首页</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 现成模板：test_case/suprecast_app/test_quiz_submit.js（跑法：$env:UITEST_ALLOW_SUBMIT="1"; python run.py -k 答题写链路）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>已知限制（诚实标注，别误读成框架不行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 搜索关键词只能是字母/数字/下划线/点/连字符：关键词是通过 adb 发过去的，adb 发中文不报错但不生效。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 「点文字」点的是屏幕上看得见的文字；同名文字有多个时点第 1 个。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t xml:space="preserve">   · 断言的等待时间写死在框架里（文字类 8 秒、元素类 8 秒），表格里暂时改不了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 「复位答题记录」只能删答题相关的两张表；别的写操作（积分兑换、签到）还没做复位手段。</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7648,6 @@
           <t>方案一变形</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7048,7 +7660,6 @@
           <t>仅凝固</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7061,7 +7672,6 @@
           <t>仅充填2</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7074,7 +7684,6 @@
           <t>充填凝固应力</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7087,7 +7696,6 @@
           <t>充填凝固应力1</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7100,7 +7708,6 @@
           <t>7201744-孙</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7113,7 +7720,6 @@
           <t>带组织性能结果</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7126,7 +7732,6 @@
           <t>充填-排气</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7139,7 +7744,6 @@
           <t>1月 20250115</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7152,7 +7756,6 @@
           <t>紫色1</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7165,7 +7768,6 @@
           <t>内部数据6</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7178,7 +7780,6 @@
           <t>1QQ区qqqqq</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7191,7 +7792,6 @@
           <t>重力铸造-重力砂型-0602-163625-仅充填仅浏览-重力铸造-重力砂型-0602-163625</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7204,7 +7804,6 @@
           <t>重力铸造-重力砂型-0602-163625-充填凝固0602_165141-仅浏览</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7217,7 +7816,6 @@
           <t>COPY3</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7230,7 +7828,6 @@
           <t>3月26测试 私有材料分享(copy)</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7243,7 +7840,6 @@
           <t>内部数据-虚拟模具</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7256,7 +7852,6 @@
           <t>内部数据</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7269,7 +7864,6 @@
           <t>鹅鹅鹅</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7282,7 +7876,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7295,7 +7888,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7308,7 +7900,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7321,7 +7912,6 @@
           <t>仅凝固+应力-选择点2</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7334,7 +7924,6 @@
           <t>仅凝固1</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7347,7 +7936,6 @@
           <t>循环凝固</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7360,7 +7948,6 @@
           <t>131231</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7373,7 +7960,6 @@
           <t>131231</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7386,7 +7972,6 @@
           <t>循环凝固-热循环</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7399,7 +7984,6 @@
           <t>6668</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7412,7 +7996,6 @@
           <t>6668</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7425,7 +8008,6 @@
           <t>填充任务1</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7438,7 +8020,6 @@
           <t>0605测试</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7451,7 +8032,6 @@
           <t>循环凝固+应力+选点1</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7464,7 +8044,6 @@
           <t>料筒(copy)</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7477,7 +8056,6 @@
           <t>仅凝固</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7490,7 +8068,6 @@
           <t>#713392277</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7503,7 +8080,6 @@
           <t>？？？？</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7516,7 +8092,6 @@
           <t>复制任务失败问题测试-分享</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7529,7 +8104,6 @@
           <t>浇口充填-高级模式</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7542,7 +8116,6 @@
           <t>4.17</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7555,7 +8128,6 @@
           <t>热热热热</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7568,7 +8140,6 @@
           <t>eeee</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7581,7 +8152,6 @@
           <t>亲亲</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7594,7 +8164,6 @@
           <t>3333 私有曲线</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7607,7 +8176,6 @@
           <t>v2</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7620,7 +8188,6 @@
           <t>111111</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7633,7 +8200,6 @@
           <t>测试二级页面案例111111111111111111111111111</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7646,7 +8212,6 @@
           <t>分享高压 2</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7659,7 +8224,6 @@
           <t>料筒充填</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7672,7 +8236,6 @@
           <t>料筒充填1</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7685,7 +8248,6 @@
           <t>料筒分享</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7698,7 +8260,6 @@
           <t>1WWWW</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7711,7 +8272,6 @@
           <t>凝固应力</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7724,7 +8284,6 @@
           <t>模拟汽车</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7737,7 +8296,6 @@
           <t>模拟汽车减震</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7750,7 +8308,6 @@
           <t>多浇口充填(粒子数量10)</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7758,7 +8315,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
           <t>课程那张表里的「我们账号买没买」按 user_id=1966910（config/env.yaml）判断</t>
@@ -7771,7 +8327,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
           <t>注意：这些课程名在库里有多门同名，按名字打开只会命中第一门 —— 012345678901234567890123456789、付费课程1、免费课程、免费课程1、无敌贵的课程、测试封面图、测试封面图-修改、测试验证课时bug</t>
@@ -7784,7 +8339,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
           <t>案例共 56 条，已全部列出</t>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1119,7 +1119,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>活动入口_001</t>
+          <t>ZW_001</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>搜索页_001</t>
+          <t>ZW_002</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1243,7 +1243,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>答题页_001</t>
+          <t>ZW_003</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>学习中心_001</t>
+          <t>ZW_004</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -1411,7 +1411,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>积分商城_001</t>
+          <t>ZW_005</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1479,7 +1479,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>学习中心_002</t>
+          <t>ZW_006</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>搜索消失_001</t>
+          <t>ZW_007</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1635,7 +1635,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>框架自检_001</t>
+          <t>ZW_008</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1932,7 +1932,7 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>搜索空态_001</t>
+          <t>ZW_009</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -2041,7 +2041,7 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>搜索空态_002</t>
+          <t>ZW_010</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>回到顶部_001</t>
+          <t>ZW_011</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -2220,7 +2220,7 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>搜索话题_001</t>
+          <t>ZW_012</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -2346,7 +2346,7 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>帖子主页按钮_001</t>
+          <t>ZW_013</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>首页tab顺序_001</t>
+          <t>ZW_014</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -2509,7 +2509,7 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>案例库_001</t>
+          <t>ZW_015</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
@@ -2645,7 +2645,7 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>案例库_002</t>
+          <t>ZW_016</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>课程详情_001</t>
+          <t>ZW_017</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -2825,7 +2825,7 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>课程列表_001</t>
+          <t>ZW_018</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -2913,7 +2913,7 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>案例库_003</t>
+          <t>ZW_019</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
@@ -3018,7 +3018,7 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>课程详情_002</t>
+          <t>ZW_020</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
@@ -3097,7 +3097,7 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>学习中心_003</t>
+          <t>ZW_021</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
@@ -3201,7 +3201,7 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>测试</t>
+          <t>ZW_022</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
@@ -3285,7 +3285,7 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>中文搜索_001</t>
+          <t>ZW_023</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
@@ -3377,7 +3377,7 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>中文搜索_002</t>
+          <t>ZW_024</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
@@ -3486,7 +3486,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ZW_001</t>
+          <t>ZW_025</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
@@ -3567,7 +3567,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ZW_002</t>
+          <t>ZW_026</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
@@ -3649,7 +3649,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ZW_003</t>
+          <t>ZW_027</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
@@ -3747,7 +3747,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ZW_004</t>
+          <t>ZW_028</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例" sheetId="1" state="visible" r:id="rId1"/>
@@ -191,6 +191,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -375,11 +381,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -511,7 +512,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
@@ -535,16 +536,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
@@ -553,85 +554,85 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -639,16 +640,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1071,7 +1074,7 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="78.125" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1122,12 +1125,12 @@
           <t>ZW_001</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>首页活动入口在各筛选 tab 下都显示</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>手机在小程序首页（不用登录）</t>
         </is>
@@ -1142,7 +1145,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr"/>
       <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>第1步：需求 713594979；只读
 第2步：只切 tab + 数活动卡，不改数据</t>
@@ -1167,12 +1170,12 @@
           <t>ZW_002</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>搜索页能打开并输入关键词</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>手机在小程序首页（不用登录）</t>
         </is>
@@ -1187,7 +1190,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：关键词只能字母/数字/下划线/点/连字符（adb 不支持中文输入）
@@ -1212,7 +1215,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr"/>
     </row>
-    <row r="6">
+    <row r="6" ht="27" customHeight="1">
       <c r="D6" s="5" t="n">
         <v>3</v>
       </c>
@@ -1246,12 +1249,12 @@
           <t>ZW_003</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>答题活动页能打开且吸顶文案齐全</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>首页轮播里有「答题」卡（没有时「打开答题活动」记「跳过」，不算失败）</t>
         </is>
@@ -1266,7 +1269,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>第1步：先摆正起点。注意：首页轮播里没有「答题」卡时，打开这一步会记成「跳过」
 第2步：只读：不选选项、不提交
@@ -1338,12 +1341,12 @@
           <t>ZW_004</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>学习中心能进到专栏列表</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>手机在小程序首页（不用登录）</t>
         </is>
@@ -1358,7 +1361,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>需求「小程序-学习中心重组」（713223483）。第3步原先是断言「热门专栏」这个小标题，
 2026/10/14 全量回归时它红了：真机整页只有「往期专栏」，没有「热门专栏」——
@@ -1414,12 +1417,12 @@
           <t>ZW_005</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>用户中心能看到积分商城</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>测试环境自己的账号已登录；手机在小程序首页</t>
         </is>
@@ -1434,7 +1437,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr"/>
       <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="6" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="D18" s="5" t="n">
@@ -1482,12 +1485,12 @@
           <t>ZW_006</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>学习中心能看见压铸百科</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>手机在小程序首页（不用登录）</t>
         </is>
@@ -1502,7 +1505,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr"/>
       <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="D22" s="5" t="n">
@@ -1550,12 +1553,12 @@
           <t>ZW_007</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>进搜索页后首页筛选 tab 消失</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>手机在小程序首页（不用登录）</t>
         </is>
@@ -1570,7 +1573,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr"/>
       <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="D26" s="5" t="n">
@@ -1638,12 +1641,12 @@
           <t>ZW_008</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>框架自检：把表格能用的动作全跑一遍</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>手机在小程序首页；首页有可滚动内容（滑不动会报错，不会假装成功）</t>
         </is>
@@ -1658,7 +1661,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="6" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>第1步：这条是给框架做体检的，业务上没用，可随时删
 第2步：不知道检查什么文字时，先跑它看日志
@@ -1805,7 +1808,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr"/>
     </row>
-    <row r="39">
+    <row r="39" ht="27" customHeight="1">
       <c r="D39" s="5" t="n">
         <v>10</v>
       </c>
@@ -1935,12 +1938,12 @@
           <t>ZW_009</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>搜索零结果时出现 AI 引导（需求 713582841）</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>手机在小程序首页；关键词 zzz9999 仍然零结果</t>
         </is>
@@ -1955,7 +1958,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="6" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：实测：这个词是零结果
@@ -1994,7 +1997,7 @@
       <c r="F50" s="5" t="inlineStr"/>
       <c r="G50" s="5" t="inlineStr"/>
     </row>
-    <row r="51">
+    <row r="51" ht="27" customHeight="1">
       <c r="D51" s="5" t="n">
         <v>4</v>
       </c>
@@ -2044,12 +2047,12 @@
           <t>ZW_010</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>有结果时不出现 AI 引导（需求 713582841 的反向）</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>手机在小程序首页；关键词 qqqqq 仍然有结果</t>
         </is>
@@ -2064,7 +2067,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr"/>
       <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：实测：这个词有结果（所以不该出现引导）
@@ -2152,12 +2155,12 @@
           <t>ZW_011</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>积分商城的回到顶部按钮符合需求（需求 713582097）</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>测试环境自己的账号已登录；手机在小程序首页</t>
         </is>
@@ -2172,7 +2175,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="5" t="inlineStr"/>
-      <c r="H60" s="6" t="inlineStr">
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：用户中心 -&gt; 积分商城（二级页，没有底部 tab 栏）
@@ -2223,12 +2226,12 @@
           <t>ZW_012</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>热门话题有 5 条且点第一条能进话题结果页（需求 713129788）</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>管理后台的「热门话题」配了 ≥5 个；手机在小程序首页</t>
         </is>
@@ -2243,7 +2246,7 @@
       </c>
       <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="5" t="inlineStr"/>
-      <c r="H64" s="6" t="inlineStr">
+      <c r="H64" s="5" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：只进搜索页、不输入关键词（输入的话热门话题会被建议列表顶掉）
@@ -2267,7 +2270,7 @@
       <c r="F65" s="5" t="inlineStr"/>
       <c r="G65" s="5" t="inlineStr"/>
     </row>
-    <row r="66">
+    <row r="66" ht="27" customHeight="1">
       <c r="D66" s="5" t="n">
         <v>3</v>
       </c>
@@ -2349,12 +2352,12 @@
           <t>ZW_013</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>帖子详情页点「主页」按钮回到首页（需求 713256065）</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>首页信息流里至少有 1 张帖子卡片</t>
         </is>
@@ -2369,7 +2372,7 @@
       </c>
       <c r="F71" s="5" t="inlineStr"/>
       <c r="G71" s="5" t="inlineStr"/>
-      <c r="H71" s="6" t="inlineStr">
+      <c r="H71" s="5" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：点首页信息流第一张帖子卡片进详情（只读）
@@ -2454,12 +2457,12 @@
           <t>ZW_014</t>
         </is>
       </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>首页筛选 tab 顺序与默认选中符合需求（需求 713341876）</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>手机在小程序首页（不用登录）</t>
         </is>
@@ -2474,7 +2477,7 @@
       </c>
       <c r="F77" s="5" t="inlineStr"/>
       <c r="G77" s="5" t="inlineStr"/>
-      <c r="H77" s="6" t="inlineStr">
+      <c r="H77" s="5" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：需求：最新提问和推荐互换顺序 + 最新提问为默认展示（置顶帖那半句依赖数据，暂不覆盖）
@@ -2512,12 +2515,12 @@
           <t>ZW_015</t>
         </is>
       </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>案例库：介绍banner在分类上方、点它进长图；列表显示复制数；详情页评论区是「全部评论」（需求 713381608）</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>手机在小程序首页；案例库列表里至少有 1 个案例</t>
         </is>
@@ -2532,7 +2535,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr"/>
       <c r="G80" s="5" t="inlineStr"/>
-      <c r="H80" s="6" t="inlineStr">
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：入口 = 底部 tab「设计专区」
@@ -2648,12 +2651,12 @@
           <t>ZW_016</t>
         </is>
       </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>案例复制：点复制后弹出「复制成功 / 使用手机号登录智铸超云」（会写数据，跑完自动复位）</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>需要开关 UITEST_ALLOW_SUBMIT=1（会写数据，跑完自动复位）；列表第 1 个案例可复制</t>
         </is>
@@ -2668,7 +2671,7 @@
       </c>
       <c r="F89" s="5" t="inlineStr"/>
       <c r="G89" s="5" t="inlineStr"/>
-      <c r="H89" s="6" t="inlineStr">
+      <c r="H89" s="5" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：入口 = 底部 tab「设计专区」
@@ -2749,12 +2752,12 @@
           <t>ZW_017</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>课程详情页：已购买未开始显示「课程介绍」+ 课程标题 + 第一课时封面视频（需求 713367615）</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>登录账号已购买课程 717 且学习进度 0%（库里 user_course_relation 有、course_record 没有）</t>
         </is>
@@ -2769,7 +2772,7 @@
       </c>
       <c r="F95" s="5" t="inlineStr"/>
       <c r="G95" s="5" t="inlineStr"/>
-      <c r="H95" s="6" t="inlineStr">
+      <c r="H95" s="5" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：我们账号对这门课是已购买 + 学习进度 0%（库里 user_course_relation 有、course_record 没有）
@@ -2828,12 +2831,12 @@
           <t>ZW_018</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>课程列表：课时数为0的课程不显示（需求 713367615 第 1 条，跟数据库对账）</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>能连上测试库（要跟 course 表对账）；手机在小程序首页</t>
         </is>
@@ -2848,7 +2851,7 @@
       </c>
       <c r="F99" s="5" t="inlineStr"/>
       <c r="G99" s="5" t="inlineStr"/>
-      <c r="H99" s="6" t="inlineStr">
+      <c r="H99" s="5" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：先到学习中心（默认落在专栏 tab）
@@ -2916,12 +2919,12 @@
           <t>ZW_019</t>
         </is>
       </c>
-      <c r="B104" s="6" t="inlineStr">
+      <c r="B104" s="5" t="inlineStr">
         <is>
           <t>付费案例复制：也弹同样的提示（会写数据 + 扣积分，跑完自动复位记录与复制数）</t>
         </is>
       </c>
-      <c r="C104" s="6" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
         <is>
           <t>需要开关 UITEST_ALLOW_SUBMIT=1（会写数据 + 扣积分，复制记录与复制数自动复位）；案例名「填充任务1」要与列表上一字不差</t>
         </is>
@@ -2936,7 +2939,7 @@
       </c>
       <c r="F104" s="5" t="inlineStr"/>
       <c r="G104" s="5" t="inlineStr"/>
-      <c r="H104" s="6" t="inlineStr">
+      <c r="H104" s="5" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：入口 = 底部 tab「设计专区」
@@ -3021,12 +3024,12 @@
           <t>ZW_020</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B110" s="5" t="inlineStr">
         <is>
           <t>未购买课程点课时：封面和标题不变、始终显示课程名（需求 713367615 第 2 条）</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr">
+      <c r="C110" s="5" t="inlineStr">
         <is>
           <t>登录账号未购买「7.8课程new」（依据 user_course_relation 表）</t>
         </is>
@@ -3041,7 +3044,7 @@
       </c>
       <c r="F110" s="5" t="inlineStr"/>
       <c r="G110" s="5" t="inlineStr"/>
-      <c r="H110" s="6" t="inlineStr">
+      <c r="H110" s="5" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：我们账号只买过 717 一门课，所以这门是未购买（依据：user_course_relation 表）
@@ -3100,12 +3103,12 @@
           <t>ZW_021</t>
         </is>
       </c>
-      <c r="B114" s="6" t="inlineStr">
+      <c r="B114" s="5" t="inlineStr">
         <is>
           <t>学习中心顶部有三个 tab</t>
         </is>
       </c>
-      <c r="C114" s="6" t="inlineStr">
+      <c r="C114" s="5" t="inlineStr">
         <is>
           <t>手机在小程序首页（不用登录）</t>
         </is>
@@ -3120,7 +3123,7 @@
       </c>
       <c r="F114" s="5" t="inlineStr"/>
       <c r="G114" s="5" t="inlineStr"/>
-      <c r="H114" s="6" t="inlineStr"/>
+      <c r="H114" s="5" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="D115" s="5" t="n">
@@ -3204,12 +3207,12 @@
           <t>ZW_022</t>
         </is>
       </c>
-      <c r="B120" s="6" t="inlineStr">
+      <c r="B120" s="5" t="inlineStr">
         <is>
           <t>测试</t>
         </is>
       </c>
-      <c r="C120" s="6" t="inlineStr">
+      <c r="C120" s="5" t="inlineStr">
         <is>
           <t>手机在小程序首页</t>
         </is>
@@ -3224,7 +3227,7 @@
       </c>
       <c r="F120" s="5" t="inlineStr"/>
       <c r="G120" s="5" t="inlineStr"/>
-      <c r="H120" s="6" t="inlineStr"/>
+      <c r="H120" s="5" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="D121" s="5" t="n">
@@ -3288,12 +3291,12 @@
           <t>ZW_023</t>
         </is>
       </c>
-      <c r="B125" s="6" t="inlineStr">
+      <c r="B125" s="5" t="inlineStr">
         <is>
           <t>中文关键词能搜出东西（靠搜索历史点进去）</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
+      <c r="C125" s="5" t="inlineStr">
         <is>
           <t>测试库里该账号的搜索历史里有「压铸测试」（用 tools/search_history_tool.py 造过）</t>
         </is>
@@ -3308,7 +3311,7 @@
       </c>
       <c r="F125" s="5" t="inlineStr"/>
       <c r="G125" s="5" t="inlineStr"/>
-      <c r="H125" s="6" t="inlineStr">
+      <c r="H125" s="5" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：搜索页上才有「搜索历史」面板
@@ -3380,12 +3383,12 @@
           <t>ZW_024</t>
         </is>
       </c>
-      <c r="B130" s="6" t="inlineStr">
+      <c r="B130" s="5" t="inlineStr">
         <is>
           <t>中文关键词直接输入也能搜（框架自动切输入法）</t>
         </is>
       </c>
-      <c r="C130" s="6" t="inlineStr">
+      <c r="C130" s="5" t="inlineStr">
         <is>
           <t>手机在小程序首页；框架会自动临时切到 ADBKeyboard 输入中文</t>
         </is>
@@ -3400,7 +3403,7 @@
       </c>
       <c r="F130" s="5" t="inlineStr"/>
       <c r="G130" s="5" t="inlineStr"/>
-      <c r="H130" s="6" t="inlineStr">
+      <c r="H130" s="5" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：中文关键词：框架会自动临时切到 ADBKeyboard，用完切回你原来的输入法
@@ -3484,29 +3487,31 @@
       <c r="G135" s="5" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>ZW_025</t>
         </is>
       </c>
-      <c r="B136" s="6" t="inlineStr">
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>有问必答筛选栏第三个 tab 文案是「精选问答」</t>
         </is>
       </c>
-      <c r="C136" s="6" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
         <is>
           <t>手机在小程序首页（不用登录）</t>
         </is>
       </c>
-      <c r="D136" t="n">
+      <c r="D136" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
+      <c r="F136" s="2" t="n"/>
+      <c r="G136" s="2" t="n"/>
       <c r="H136" s="5" t="inlineStr">
         <is>
           <t>缺陷 713070171（原文：有问必答中，精选回答tab应该为精选问答）；只读。
@@ -3515,79 +3520,87 @@
       </c>
     </row>
     <row r="137">
-      <c r="D137" t="n">
+      <c r="D137" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>检查首页筛选栏顺序</t>
         </is>
       </c>
+      <c r="F137" s="2" t="n"/>
+      <c r="G137" s="2" t="n"/>
     </row>
     <row r="138">
-      <c r="D138" t="n">
+      <c r="D138" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>精选问答</t>
         </is>
       </c>
+      <c r="G138" s="2" t="n"/>
     </row>
     <row r="139">
-      <c r="D139" t="n">
+      <c r="D139" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>检查文字不显示</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>精选回答</t>
         </is>
       </c>
+      <c r="G139" s="2" t="n"/>
     </row>
     <row r="140">
-      <c r="D140" t="n">
+      <c r="D140" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
+      <c r="F140" s="2" t="n"/>
+      <c r="G140" s="2" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>ZW_026</t>
         </is>
       </c>
-      <c r="B141" s="6" t="inlineStr">
+      <c r="B141" s="5" t="inlineStr">
         <is>
           <t>普通用户在个人中心不显示身份标签</t>
         </is>
       </c>
-      <c r="C141" s="6" t="inlineStr">
+      <c r="C141" s="5" t="inlineStr">
         <is>
           <t>测试环境自己的账号已登录；手机在小程序首页</t>
         </is>
       </c>
-      <c r="D141" t="n">
+      <c r="D141" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
+      <c r="F141" s="2" t="n"/>
+      <c r="G141" s="2" t="n"/>
       <c r="H141" s="5" t="inlineStr">
         <is>
           <t>缺陷 713073541（原文：当用户为普通用户时，搜索结果、个人中心应该不显示普通用户的标签）+ 713295623（普通用户不显示身份标签）；只读。
@@ -3597,79 +3610,87 @@
       </c>
     </row>
     <row r="142">
-      <c r="D142" t="n">
+      <c r="D142" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>切到用户中心</t>
         </is>
       </c>
+      <c r="F142" s="2" t="n"/>
+      <c r="G142" s="2" t="n"/>
     </row>
     <row r="143">
-      <c r="D143" t="n">
+      <c r="D143" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>积分商城</t>
         </is>
       </c>
+      <c r="G143" s="2" t="n"/>
     </row>
     <row r="144">
-      <c r="D144" t="n">
+      <c r="D144" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>检查文字不显示</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>普通用户</t>
         </is>
       </c>
+      <c r="G144" s="2" t="n"/>
     </row>
     <row r="145">
-      <c r="D145" t="n">
+      <c r="D145" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
+      <c r="F145" s="2" t="n"/>
+      <c r="G145" s="2" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>ZW_027</t>
         </is>
       </c>
-      <c r="B146" s="6" t="inlineStr">
+      <c r="B146" s="5" t="inlineStr">
         <is>
           <t>帖子详情页点评论入口要弹出评论面板</t>
         </is>
       </c>
-      <c r="C146" s="6" t="inlineStr">
+      <c r="C146" s="5" t="inlineStr">
         <is>
           <t>首页信息流里至少有 1 张帖子卡片（首页自己要能加载出来）</t>
         </is>
       </c>
-      <c r="D146" t="n">
+      <c r="D146" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
+      <c r="F146" s="2" t="n"/>
+      <c r="G146" s="2" t="n"/>
       <c r="H146" s="5" t="inlineStr">
         <is>
           <t>缺陷 713006028（原文：帖子详情页，评论按钮点击无响应）；只读，不发评论。
@@ -3680,94 +3701,103 @@
       </c>
     </row>
     <row r="147">
-      <c r="D147" t="n">
+      <c r="D147" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>打开第一个帖子</t>
         </is>
       </c>
+      <c r="F147" s="2" t="n"/>
+      <c r="G147" s="2" t="n"/>
     </row>
     <row r="148">
-      <c r="D148" t="n">
+      <c r="D148" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>点文字</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>留下你的回答</t>
         </is>
       </c>
+      <c r="G148" s="2" t="n"/>
     </row>
     <row r="149">
-      <c r="D149" t="n">
+      <c r="D149" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>发送</t>
         </is>
       </c>
+      <c r="G149" s="2" t="n"/>
     </row>
     <row r="150">
-      <c r="D150" t="n">
+      <c r="D150" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>点选择器</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>.overlay-mask</t>
         </is>
       </c>
+      <c r="G150" s="2" t="n"/>
     </row>
     <row r="151">
-      <c r="D151" t="n">
+      <c r="D151" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
+      <c r="F151" s="2" t="n"/>
+      <c r="G151" s="2" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>ZW_028</t>
         </is>
       </c>
-      <c r="B152" s="6" t="inlineStr">
+      <c r="B152" s="5" t="inlineStr">
         <is>
           <t>话题详情页点筛选项不会把页面点坏</t>
         </is>
       </c>
-      <c r="C152" s="6" t="inlineStr">
+      <c r="C152" s="5" t="inlineStr">
         <is>
           <t>手机在小程序首页；搜索页的「热门话题」至少有 1 条</t>
         </is>
       </c>
-      <c r="D152" t="n">
+      <c r="D152" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
+      <c r="F152" s="2" t="n"/>
+      <c r="G152" s="2" t="n"/>
       <c r="H152" s="5" t="inlineStr">
         <is>
           <t>缺陷 713335002（原文：话题详情页筛选项点击时报错）；只读。
@@ -3778,64 +3808,72 @@
       </c>
     </row>
     <row r="153">
-      <c r="D153" t="n">
+      <c r="D153" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>打开搜索页</t>
         </is>
       </c>
+      <c r="F153" s="2" t="n"/>
+      <c r="G153" s="2" t="n"/>
     </row>
     <row r="154">
-      <c r="D154" t="n">
+      <c r="D154" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>打开第一个热门话题</t>
         </is>
       </c>
+      <c r="F154" s="2" t="n"/>
+      <c r="G154" s="2" t="n"/>
     </row>
     <row r="155">
-      <c r="D155" t="n">
+      <c r="D155" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>点文字</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>最新发布</t>
         </is>
       </c>
+      <c r="G155" s="2" t="n"/>
     </row>
     <row r="156">
-      <c r="D156" t="n">
+      <c r="D156" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>最多点赞</t>
         </is>
       </c>
+      <c r="G156" s="2" t="n"/>
     </row>
     <row r="157">
-      <c r="D157" t="n">
+      <c r="D157" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
+      <c r="F157" s="2" t="n"/>
+      <c r="G157" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="112">
@@ -3863,13 +3901,13 @@
     <mergeCell ref="C64:C70"/>
     <mergeCell ref="B95:B98"/>
     <mergeCell ref="B8:B12"/>
+    <mergeCell ref="H104:H109"/>
     <mergeCell ref="H48:H53"/>
-    <mergeCell ref="H104:H109"/>
     <mergeCell ref="A99:A103"/>
     <mergeCell ref="H64:H70"/>
+    <mergeCell ref="B136:B140"/>
     <mergeCell ref="A130:A135"/>
     <mergeCell ref="B104:B109"/>
-    <mergeCell ref="B136:B140"/>
     <mergeCell ref="A136:A140"/>
     <mergeCell ref="H54:H59"/>
     <mergeCell ref="H2:H3"/>
@@ -3891,15 +3929,15 @@
     <mergeCell ref="C95:C98"/>
     <mergeCell ref="A30:A47"/>
     <mergeCell ref="B4:B7"/>
+    <mergeCell ref="B110:B113"/>
     <mergeCell ref="C48:C53"/>
-    <mergeCell ref="B110:B113"/>
     <mergeCell ref="C120:C124"/>
     <mergeCell ref="H4:H7"/>
     <mergeCell ref="A110:A113"/>
     <mergeCell ref="A141:A145"/>
     <mergeCell ref="A60:A63"/>
+    <mergeCell ref="H152:H157"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="H152:H157"/>
     <mergeCell ref="H77:H79"/>
     <mergeCell ref="A125:A129"/>
     <mergeCell ref="H120:H124"/>
@@ -3954,7 +3992,7 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>='动作清单'!$A$2:$A$54</formula1>
+      <formula1>='动作清单'!$A$2:$A$51</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -3970,7 +4008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3983,48 +4021,50 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>动作</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>怎么填（示例）</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>会不会改数据</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>属于哪一类</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="27" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4052,6 +4092,8 @@
           <t>切到用户中心</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4073,12 +4115,14 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="27" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>打开积分商城</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4106,6 +4150,8 @@
           <t>打开学习中心专栏</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4127,7 +4173,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="27" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>切换学习中心顶部栏</t>
@@ -4138,6 +4184,7 @@
           <t>顶部栏名称（只能填：课程 / 专栏 / 压铸百科）</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>专栏</t>
@@ -4165,6 +4212,8 @@
           <t>返回上一页</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4192,6 +4241,8 @@
           <t>点主页按钮</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4219,6 +4270,8 @@
           <t>打开搜索页</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4240,12 +4293,14 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="27" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
           <t>打开案例库</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4267,7 +4322,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="40.5" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>打开课程详情</t>
@@ -4278,6 +4333,7 @@
           <t>课程名</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>717</t>
@@ -4299,7 +4355,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="54" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
           <t>输入搜索关键词</t>
@@ -4310,6 +4366,7 @@
           <t>关键词</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -4331,7 +4388,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="40.5" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
@@ -4342,6 +4399,7 @@
           <t>关键词</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -4363,12 +4421,14 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="40.5" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>执行搜索</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4390,7 +4450,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="40.5" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
           <t>点搜索历史里的词</t>
@@ -4401,6 +4461,7 @@
           <t>词</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>压铸测试</t>
@@ -4422,12 +4483,14 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="27" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>打开第一个热门话题</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4449,12 +4512,14 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="27" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
           <t>打开第一个帖子</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4476,12 +4541,14 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="27" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
           <t>打开第一张专栏</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4503,12 +4570,14 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="27" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
           <t>打开第一个案例</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4530,12 +4599,14 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="27" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
           <t>打开案例库介绍长图</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4557,7 +4628,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="40.5" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
           <t>打开案例</t>
@@ -4568,6 +4639,7 @@
           <t>案例名</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>填充任务1</t>
@@ -4589,7 +4661,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="40.5" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>点文字</t>
@@ -4626,7 +4698,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="40.5" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>点选择器</t>
@@ -4663,30 +4735,35 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="54" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>点id</t>
+          <t>滑动</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>次数（只能填：1 / 2 / 3 / 4 / 5 / 6 / 7 / 8 / 9 / 10）</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>方向（只能填：上 / 下）</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>_AQ（首页搜索栏；也可以写 #_AQ）</t>
+          <t>3 / 上</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>会（和「点文字」同一道安全阀）</t>
+          <t>不会</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>按元素 id 点一下（从「打印页面结构」里抄，形如 _AQ；前面不用写 #）。id 比 class 更精确、也不怕重名 —— 但只适合临时调试：实测页面一直开着时 id 不变（首页搜索栏 _AQ 隔天还在），可只要重进一次页面，id 就全变（退出去再进搜索页：搜索框 _JN-&gt;_Kr，5 个热门话题的 id 全换）。长期用例请用文字或 class。只读</t>
+          <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4695,25 +4772,21 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="40.5" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>滑动</t>
+          <t>切换首页筛选栏</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>次数（只能填：1 / 2 / 3 / 4 / 5 / 6 / 7 / 8 / 9 / 10）</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>方向（只能填：上 / 下）</t>
-        </is>
-      </c>
+          <t>筛选栏名称（只能填：最新提问 / 推荐 / 精选问答 / 我的关注）</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3 / 上</t>
+          <t>推荐</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4723,7 +4796,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
+          <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4732,20 +4805,21 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="40.5" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>切换首页筛选栏</t>
+          <t>等待</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>筛选栏名称（只能填：最新提问 / 推荐 / 精选问答 / 我的关注）</t>
-        </is>
-      </c>
+          <t>毫秒</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>推荐</t>
+          <t>2000（= 等 2 秒）</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4755,7 +4829,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
+          <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4767,17 +4841,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>等待</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>毫秒</t>
-        </is>
-      </c>
+          <t>打印页面文字</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2000（= 等 2 秒）</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4787,7 +4858,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
+          <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4796,825 +4867,769 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="27" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>打印页面文字</t>
-        </is>
-      </c>
+          <t>打印页面结构</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>范围（只能填：全量 / 只看有文字）</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
+          <t>只看有文字</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>把当前页面的元素结构（标签 / class / id + 文字）打进日志：控制台只打前 300 行，完整内容写到 report/dump_&lt;月日_时分秒&gt;.txt（可以在编辑器里搜，适合挑「检查元素存在」的选择器）。参数1 填「只看有文字」时只输出看得见文字的分支（几十行，最省事）。调完把这一行删掉 —— 它是调试用的，不是断言。只读</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>③ 通用交互</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>答对最多可赢积分</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>④ 通用断言（检查「看得见没有」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="27" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>检查文字不显示</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>最新提问（搜索页上不该有）</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>断言页面上看不见这段文字</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>④ 通用断言（检查「看得见没有」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="27" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>检查文字出现次数</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>期望次数（只能填：1 / 2 / 3 / 4 / 5）</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>收藏 / 1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>④ 通用断言（检查「看得见没有」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40.5" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>检查元素存在</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>选择器</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>.search-container</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>断言页面上找得到这个选择器，例如 .search-container</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>④ 通用断言（检查「看得见没有」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="27" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>检查元素不存在</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>选择器</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>.activity-quiz-page</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>④ 通用断言（检查「看得见没有」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="27" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>检查元素数量</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>选择器</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>期望数量</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>.hot-topics .inline-flex / 5</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>④ 通用断言（检查「看得见没有」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="27" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>检查输入框的值</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>选择器</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>期望值</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>wx-input.search-input / test</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>④ 通用断言（检查「看得见没有」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="40.5" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>检查活动入口</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>③ 通用交互</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>打印页面结构</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>范围（只能填：全量 / 只看有文字）</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>只看有文字</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>⑤ 需求专项检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="27" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>检查首页筛选栏顺序</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>把当前页面的元素结构（标签 / class / id + 文字）打进日志：控制台只打前 300 行，完整内容写到 report/dump_&lt;月日_时分秒&gt;.txt（可以在编辑器里搜，适合挑「检查元素存在」的选择器）。参数1 填「只看有文字」时只输出看得见文字的分支（几十行，最省事）。调完把这一行删掉 —— 它是调试用的，不是断言。只读</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>③ 通用交互</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>答对最多可赢积分</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>⑤ 需求专项检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="27" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>检查回到顶部按钮</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>④ 通用断言（检查「看得见没有」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>检查文字不显示</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>最新提问（搜索页上不该有）</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>⑤ 需求专项检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="27" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>检查答题页</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>断言页面上看不见这段文字</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>④ 通用断言（检查「看得见没有」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>检查文字出现次数</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>期望次数（只能填：1 / 2 / 3 / 4 / 5）</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>收藏 / 1</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于一道题的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>⑤ 需求专项检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="27" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>检查案例库列表</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>④ 通用断言（检查「看得见没有」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>检查元素存在</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>选择器</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>.search-container</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>按需求 713381608 校验案例库列表页：① 分类上方有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「复制图标 + 复制数」，且整页找不到评论图标。只读</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>⑤ 需求专项检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="27" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>检查案例详情页</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>断言页面上找得到这个选择器，例如 .search-container</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>④ 通用断言（检查「看得见没有」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>检查元素不存在</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>选择器</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>.activity-quiz-page</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部没有复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>⑤ 需求专项检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40.5" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>检查案例库介绍长图</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>④ 通用断言（检查「看得见没有」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>检查元素数量</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>选择器</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>期望数量</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>.hot-topics .inline-flex / 5</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>按需求 713381608 校验介绍长图页：整页是单张图片，而且是长图（图高远大于屏高）。只读</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>⑤ 需求专项检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="27" customHeight="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>检查课程详情页</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>课程介绍</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>④ 通用断言（检查「看得见没有」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>检查id存在</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>_AQ</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、默认选中填的那个（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>⑤ 需求专项检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="27" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>检查0课时课程不显示</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>断言页面上找得到这个 id 的元素（前面不用写 #，从「打印页面结构」里抄，形如 _AQ）。适合临时确认「这个 id 现在在不在」；别写进长期用例 —— 重进一次页面 id 就会全变（见「点id」的说明）。只读</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>④ 通用断言（检查「看得见没有」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>检查id不存在</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>_AQ（进了搜索页之后，首页那个搜索栏就不该在了）</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字一个都没出现在小程序的课程列表里（会自己滚到列表底部）。只读</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>⑤ 需求专项检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="27" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>检查未购买点课时</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>课程名</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>7.8课程new</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>断言页面上没有这个 id 的元素（例如：进了搜索页之后，首页那个 _AQ 搜索栏就不该在）。只读</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>④ 通用断言（检查「看得见没有」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>检查输入框的值</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>选择器</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>期望值</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>wx-input.search-input / test</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>按需求 713367615 第 2 条校验：未购买的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号没买过的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>⑤ 需求专项检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40.5" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>打开答题活动</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>④ 通用断言（检查「看得见没有」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>检查活动入口</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="27" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>逐题作答</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>只改前端选中态（不写库、不需要开关）</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、不写库，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40.5" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>提交答卷</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>（不用填参数）</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>会写库（必须开开关）</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>点答题页的提交按钮 —— 会真的写数据。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="27" customHeight="1">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>复位答题记录</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>活动名</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Z-B4-答题角标</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>会删库（默认只预览；真删要开开关）</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：默认只预览、不删，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="40.5" customHeight="1">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>检查答题记录数</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>活动名</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>期望条数</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Z-B4-答题角标 / 1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>⑤ 需求专项检查</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>检查首页筛选栏顺序</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>读数据库，断言这个活动的提交记录正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="27" customHeight="1">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>复制当前案例</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>不会</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>⑤ 需求专项检查</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>检查回到顶部按钮</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>（不用填参数）</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>不会</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>⑤ 需求专项检查</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>检查答题页</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>（不用填参数）</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>不会</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于一道题的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>⑤ 需求专项检查</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>检查案例库列表</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>（不用填参数）</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>不会</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>按需求 713381608 校验案例库列表页：① 分类上方有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「复制图标 + 复制数」，且整页找不到评论图标。只读</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>⑤ 需求专项检查</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>检查案例详情页</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>（不用填参数）</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>不会</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部没有复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>⑤ 需求专项检查</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>检查案例库介绍长图</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>（不用填参数）</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>不会</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>按需求 713381608 校验介绍长图页：整页是单张图片，而且是长图（图高远大于屏高）。只读</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>⑤ 需求专项检查</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>检查课程详情页</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>课程介绍</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>不会</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、默认选中填的那个（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>⑤ 需求专项检查</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>检查0课时课程不显示</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>（不用填参数）</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>不会</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字一个都没出现在小程序的课程列表里（会自己滚到列表底部）。只读</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>⑤ 需求专项检查</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>检查未购买点课时</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>课程名</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>7.8课程new</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>不会</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>按需求 713367615 第 2 条校验：未购买的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号没买过的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>⑤ 需求专项检查</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>打开答题活动</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>（不用填参数）</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>不会</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>会写库（要开开关；没开时记跳过）</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>在案例详情页点「复制案例」—— 一条龙：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → 自动复位（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>逐题作答</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>（不用填参数）</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>只改前端选中态（不写库、不需要开关）</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、不写库，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>提交答卷</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>（不用填参数）</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>会写库（必须开开关）</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>点答题页的提交按钮 —— 会真的写数据。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>复位答题记录</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>活动名</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Z-B4-答题角标</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>会删库（默认只预览；真删要开开关）</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：默认只预览、不删，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>检查答题记录数</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>活动名</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>期望条数</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Z-B4-答题角标 / 1</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>不会</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>读数据库，断言这个活动的提交记录正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>复制当前案例</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>（不用填参数）</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>会写库（要开开关；没开时记跳过）</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>在案例详情页点「复制案例」—— 一条龙：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → 自动复位（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
-        </is>
-      </c>
-    </row>
+    <row r="52" ht="54" customHeight="1"/>
+    <row r="53" ht="40.5" customHeight="1"/>
+    <row r="54" ht="67.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5629,7 +5644,8 @@
   <dimension ref="A1:A58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="99.875" customWidth="1" style="2" min="1" max="1"/>
+    <col width="9" customWidth="1" style="2" min="2" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5640,364 +5656,364 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>【表长什么样】8 列，分两种：</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  按用例的 4 列（表里并成一格，只有第一步那行有值）：</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">     用例编号 | 用例标题 | 前置条件 | 备注</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  按步骤的 4 列（每一行都要填）：</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">     步骤序号 | 动作 | 参数1 | 参数2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  编号格式：ZW_001、ZW_002…（前缀 + 三位数字，唯一就行；填错的编号会让这条用例对不上号）</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>1. 一行 = 一个步骤。同一个「用例编号」的若干行，按「步骤序号」顺序执行；它们一起算一条用例。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2. 一条用例怎么摆：第一行写「用例编号 + 用例标题 + 前置条件 + 备注」，</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   下面几行的这四列并成一格、空着就行 —— 表上看起来就是「一案一块」，</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   一眼数得出有几条用例、每条几步、每条要怎么准备。每行都要填的是「步骤序号」和「动作」。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   （按这个排版，导出时编号空着的行会自动并到上一条用例；但第一行数据必须写编号，否则整表报错。）</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2b.「前置条件」写「跑这条之前手机得在什么状态」（要不要先登录、首页得有什么卡），</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   它不是动作、不会被自动执行 —— 是给人看的，也是「这条挂了先查什么」的线索。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>2c.「备注」是整条用例的备注（也并成一格）。某一步自己的说明写在同一格里，</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   用「第2步：…」开头即可。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>3. 「动作」只能填「动作清单」工作表里列出的名字 —— 填别的会在导出时报错，不会静默跳过。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>3b. 有几类参数要填数据里的名字（课程名 / 案例名 / 活动名），一字不差才行；</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">    候选值在「名称候选」工作表里，直接复制粘贴即可（刷新它：python tools/export_cases.py --dropdown）。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>4. 「参数1 / 参数2」按动作需要填，不用就留空。填多了（该动作用不到）也会报错，防手滑；</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   参数名后面写着「（可不填）」的，留空就走默认值（例如「第几个」留空 = 第 1 个）。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>5. 「备注」随便写，只出现在日志和报告里，不影响执行（但它会显示在报告里，写清需求号很有用）。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>6. 填完执行：python run.py      （它会先自动把本表导出成 json，再跑用例）</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   只想跑表格里的某一条：python run.py -k 活动入口_001</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>7. 每条用例开头都先用「回到首页」把起点摆正；会把手机停在二级页（搜索页/详情页/答题页）的用例，</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   最后再补一步「回到首页」把手机交还。原因：表里的用例共用同一部手机，</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   上一条停在二级页上，下一条可能报「找不到底部 tab」—— 开头摆正 + 结尾交还就不受影响。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>8. 「动作」列是下拉框（点单元格右边的小箭头选），可选项来自「动作清单」工作表；</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   「步骤序号」列只接受 1、2、3… 这样的正整数。填错的动作名根本选不出来，省一轮报错。</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>8b. 自己新加的行不会自动并格。改完想让它并回去、顺便刷新下拉框，跑一次：</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">    python tools/export_cases.py --dropdown    （只动排版，不动你填的内容；Excel 开着这份表时先关掉）</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>9. 不知道「检查文字显示」该填哪段字？先加一行「打印页面文字」跑一次 ——</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   当前屏幕上看得见的文字会打进日志，照着抄就行（挑完把它删掉即可）。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>默认禁止（安全阀，避免手滑把真实数据改了）</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="38" ht="27" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 「点文字」不能点这些字：提交、兑换、签到、下单、支付、购买、领取、抽奖、报名、删除、退出登录、退款、取消订单</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="39" ht="27" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">     原因：这些操作会改真实数据/消耗真实积分。真要测它们，得单独写用例并显式打开开关，不能靠表格里写一行就触发。</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 「打开答题活动」只打开页面，不选选项、不提交（选选项会消耗答题机会）。</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>要测「会改数据」的操作？开着开关跑（owner 2026/10/12 同意）</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 开关就是一句环境变量：跑之前先执行  $env:UITEST_ALLOW_SUBMIT="1"  （PowerShell）</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">     不设这个开关时，下面这两个动作会直接报错，不会偷偷执行，也不会假装跳过。</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 「复位答题记录」（参数1=活动名）：删掉该活动在测试库里留下的答题记录。</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">     默认只预览不删；开了开关才真删。跑完写数据的用例，务必用它把记录清干净。</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 「提交答卷」：真的提交一次，用来测「提交后按钮变成已提交已参加」这条需求。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 「逐题作答」「检查答题记录数」不需要开关：前者只改前端选中态（不写库），后者是只读。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 写链路的标准写法（照抄即可）：回到首页 → 打开答题活动 → 复位答题记录(活动名) →</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">     逐题作答 → 检查文字显示(已答) → 提交答卷 → 检查文字显示(已参加) →</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">     检查答题记录数(活动名 / 1) → 复位答题记录(活动名) → 回到首页</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="52" ht="27" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 现成模板：test_case/suprecast_app/test_quiz_submit.js（跑法：$env:UITEST_ALLOW_SUBMIT="1"; python run.py -k 答题写链路）</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>已知限制（诚实标注，别误读成框架不行）</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 搜索关键词只能是字母/数字/下划线/点/连字符：关键词是通过 adb 发过去的，adb 发中文不报错但不生效。</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 「点文字」点的是屏幕上看得见的文字；同名文字有多个时点第 1 个。</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 断言的等待时间写死在框架里（文字类 8 秒、元素类 8 秒），表格里暂时改不了。</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 「复位答题记录」只能删答题相关的两张表；别的写操作（积分兑换、签到）还没做复位手段。</t>
         </is>
@@ -6023,17 +6039,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>名字</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -7648,6 +7664,7 @@
           <t>方案一变形</t>
         </is>
       </c>
+      <c r="C96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7660,6 +7677,7 @@
           <t>仅凝固</t>
         </is>
       </c>
+      <c r="C97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7672,6 +7690,7 @@
           <t>仅充填2</t>
         </is>
       </c>
+      <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7684,6 +7703,7 @@
           <t>充填凝固应力</t>
         </is>
       </c>
+      <c r="C99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7696,6 +7716,7 @@
           <t>充填凝固应力1</t>
         </is>
       </c>
+      <c r="C100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7708,6 +7729,7 @@
           <t>7201744-孙</t>
         </is>
       </c>
+      <c r="C101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7720,6 +7742,7 @@
           <t>带组织性能结果</t>
         </is>
       </c>
+      <c r="C102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7732,6 +7755,7 @@
           <t>充填-排气</t>
         </is>
       </c>
+      <c r="C103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7744,6 +7768,7 @@
           <t>1月 20250115</t>
         </is>
       </c>
+      <c r="C104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7756,6 +7781,7 @@
           <t>紫色1</t>
         </is>
       </c>
+      <c r="C105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7768,6 +7794,7 @@
           <t>内部数据6</t>
         </is>
       </c>
+      <c r="C106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7780,6 +7807,7 @@
           <t>1QQ区qqqqq</t>
         </is>
       </c>
+      <c r="C107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7792,6 +7820,7 @@
           <t>重力铸造-重力砂型-0602-163625-仅充填仅浏览-重力铸造-重力砂型-0602-163625</t>
         </is>
       </c>
+      <c r="C108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7804,6 +7833,7 @@
           <t>重力铸造-重力砂型-0602-163625-充填凝固0602_165141-仅浏览</t>
         </is>
       </c>
+      <c r="C109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7816,6 +7846,7 @@
           <t>COPY3</t>
         </is>
       </c>
+      <c r="C110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7828,6 +7859,7 @@
           <t>3月26测试 私有材料分享(copy)</t>
         </is>
       </c>
+      <c r="C111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7840,6 +7872,7 @@
           <t>内部数据-虚拟模具</t>
         </is>
       </c>
+      <c r="C112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7852,6 +7885,7 @@
           <t>内部数据</t>
         </is>
       </c>
+      <c r="C113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7864,6 +7898,7 @@
           <t>鹅鹅鹅</t>
         </is>
       </c>
+      <c r="C114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7876,6 +7911,7 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7888,6 +7924,7 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7900,6 +7937,7 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7912,6 +7950,7 @@
           <t>仅凝固+应力-选择点2</t>
         </is>
       </c>
+      <c r="C118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7924,6 +7963,7 @@
           <t>仅凝固1</t>
         </is>
       </c>
+      <c r="C119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7936,6 +7976,7 @@
           <t>循环凝固</t>
         </is>
       </c>
+      <c r="C120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7948,6 +7989,7 @@
           <t>131231</t>
         </is>
       </c>
+      <c r="C121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7960,6 +8002,7 @@
           <t>131231</t>
         </is>
       </c>
+      <c r="C122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7972,6 +8015,7 @@
           <t>循环凝固-热循环</t>
         </is>
       </c>
+      <c r="C123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7984,6 +8028,7 @@
           <t>6668</t>
         </is>
       </c>
+      <c r="C124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7996,6 +8041,7 @@
           <t>6668</t>
         </is>
       </c>
+      <c r="C125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8008,6 +8054,7 @@
           <t>填充任务1</t>
         </is>
       </c>
+      <c r="C126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8020,6 +8067,7 @@
           <t>0605测试</t>
         </is>
       </c>
+      <c r="C127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8032,6 +8080,7 @@
           <t>循环凝固+应力+选点1</t>
         </is>
       </c>
+      <c r="C128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8044,6 +8093,7 @@
           <t>料筒(copy)</t>
         </is>
       </c>
+      <c r="C129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8056,6 +8106,7 @@
           <t>仅凝固</t>
         </is>
       </c>
+      <c r="C130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8068,6 +8119,7 @@
           <t>#713392277</t>
         </is>
       </c>
+      <c r="C131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8080,6 +8132,7 @@
           <t>？？？？</t>
         </is>
       </c>
+      <c r="C132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8092,6 +8145,7 @@
           <t>复制任务失败问题测试-分享</t>
         </is>
       </c>
+      <c r="C133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8104,6 +8158,7 @@
           <t>浇口充填-高级模式</t>
         </is>
       </c>
+      <c r="C134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8116,6 +8171,7 @@
           <t>4.17</t>
         </is>
       </c>
+      <c r="C135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8128,6 +8184,7 @@
           <t>热热热热</t>
         </is>
       </c>
+      <c r="C136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8140,6 +8197,7 @@
           <t>eeee</t>
         </is>
       </c>
+      <c r="C137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8152,6 +8210,7 @@
           <t>亲亲</t>
         </is>
       </c>
+      <c r="C138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8164,6 +8223,7 @@
           <t>3333 私有曲线</t>
         </is>
       </c>
+      <c r="C139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8176,6 +8236,7 @@
           <t>v2</t>
         </is>
       </c>
+      <c r="C140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8188,6 +8249,7 @@
           <t>111111</t>
         </is>
       </c>
+      <c r="C141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8200,6 +8262,7 @@
           <t>测试二级页面案例111111111111111111111111111</t>
         </is>
       </c>
+      <c r="C142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8212,6 +8275,7 @@
           <t>分享高压 2</t>
         </is>
       </c>
+      <c r="C143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8224,6 +8288,7 @@
           <t>料筒充填</t>
         </is>
       </c>
+      <c r="C144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8236,6 +8301,7 @@
           <t>料筒充填1</t>
         </is>
       </c>
+      <c r="C145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8248,6 +8314,7 @@
           <t>料筒分享</t>
         </is>
       </c>
+      <c r="C146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8260,6 +8327,7 @@
           <t>1WWWW</t>
         </is>
       </c>
+      <c r="C147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8272,6 +8340,7 @@
           <t>凝固应力</t>
         </is>
       </c>
+      <c r="C148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8284,6 +8353,7 @@
           <t>模拟汽车</t>
         </is>
       </c>
+      <c r="C149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8296,6 +8366,7 @@
           <t>模拟汽车减震</t>
         </is>
       </c>
+      <c r="C150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8308,6 +8379,7 @@
           <t>多浇口充填(粒子数量10)</t>
         </is>
       </c>
+      <c r="C151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8315,6 +8387,7 @@
           <t>（说明）</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
           <t>课程那张表里的「我们账号买没买」按 user_id=1966910（config/env.yaml）判断</t>
@@ -8327,6 +8400,7 @@
           <t>（说明）</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
           <t>注意：这些课程名在库里有多门同名，按名字打开只会命中第一门 —— 012345678901234567890123456789、付费课程1、免费课程、免费课程1、无敌贵的课程、测试封面图、测试封面图-修改、测试验证课时bug</t>
@@ -8339,6 +8413,7 @@
           <t>（说明）</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
           <t>案例共 56 条，已全部列出</t>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例" sheetId="1" state="visible" r:id="rId1"/>
@@ -636,7 +636,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -645,11 +645,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1064,7 +1073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1078,74 +1087,74 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>用例编号</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>用例标题</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>前置条件</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>步骤序号</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>动作</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>ZW_001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>首页活动入口在各筛选 tab 下都显示</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>手机在小程序首页（不用登录）</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr"/>
+      <c r="G2" s="7" t="inlineStr"/>
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>第1步：需求 713594979；只读
 第2步：只切 tab + 数活动卡，不改数据</t>
@@ -1153,44 +1162,44 @@
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
+      <c r="F3" s="7" t="inlineStr"/>
+      <c r="G3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>ZW_002</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>搜索页能打开并输入关键词</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>手机在小程序首页（不用登录）</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：关键词只能字母/数字/下划线/点/连字符（adb 不支持中文输入）
@@ -1200,76 +1209,76 @@
       </c>
     </row>
     <row r="5">
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>wx-input.search-input</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>ZW_003</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>答题活动页能打开且吸顶文案齐全</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>首页轮播里有「答题」卡（没有时「打开答题活动」记「跳过」，不算失败）</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>第1步：先摆正起点。注意：首页轮播里没有「答题」卡时，打开这一步会记成「跳过」
 第2步：只读：不选选项、不提交
@@ -1280,88 +1289,88 @@
       </c>
     </row>
     <row r="9">
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>.activity-quiz-page</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>答对最多可赢积分</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>ZW_004</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>学习中心能进到专栏列表</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>手机在小程序首页（不用登录）</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>需求「小程序-学习中心重组」（713223483）。第3步原先是断言「热门专栏」这个小标题，
 2026/10/14 全量回归时它红了：真机整页只有「往期专栏」，没有「热门专栏」——
@@ -1372,303 +1381,303 @@
       </c>
     </row>
     <row r="14">
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr"/>
-      <c r="G14" s="5" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>.column-card</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>ZW_005</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>用户中心能看到积分商城</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>测试环境自己的账号已登录；手机在小程序首页</t>
         </is>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>积分商城</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="D20" s="5" t="n">
+      <c r="D20" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr"/>
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>ZW_006</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>学习中心能看见压铸百科</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>手机在小程序首页（不用登录）</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="D22" s="5" t="n">
+      <c r="D22" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="D23" s="5" t="n">
+      <c r="D23" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>压铸百科</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="D24" s="5" t="n">
+      <c r="D24" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>ZW_007</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>进搜索页后首页筛选 tab 消失</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>手机在小程序首页（不用登录）</t>
         </is>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D25" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr"/>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="D26" s="5" t="n">
+      <c r="D26" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>最新提问</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="D27" s="5" t="n">
+      <c r="D27" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="D28" s="5" t="n">
+      <c r="D28" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>检查文字不显示</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>最新提问</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="D29" s="5" t="n">
+      <c r="D29" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>ZW_008</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>框架自检：把表格能用的动作全跑一遍</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>手机在小程序首页；首页有可滚动内容（滑不动会报错，不会假装成功）</t>
         </is>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="D30" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>第1步：这条是给框架做体检的，业务上没用，可随时删
 第2步：不知道检查什么文字时，先跑它看日志
 第3步：切完会验证真的选中了
 第5步：首页上不该有答题页根容器
-第6步：在首页上滑（首页有可滚动内容）；滑不动它会自己报错，不会假装成功
-第7步：再滑回顶部 —— 不然搜索栏被顶出屏幕，下一步会点空
+第6步：向上滑到不动为止（最多 2 次，免得首页无限加载拖太久）—— 这就是「滑到底」的用法
+第7步：向下一直滑回顶部（滑到页面不再移动就停）—— 不然搜索栏被顶出屏幕，下一步会点空
 第8步：按选择器点进搜索页
 第9步：关键词只能字母/数字
 第10步：读出来再比较
@@ -1677,288 +1686,284 @@
       </c>
     </row>
     <row r="31">
-      <c r="D31" s="5" t="n">
+      <c r="D31" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr"/>
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="D32" s="5" t="n">
+      <c r="D32" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>切换首页筛选栏</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>推荐</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="D33" s="5" t="n">
+      <c r="D33" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>切换首页筛选栏</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>最新提问</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="D34" s="5" t="n">
+      <c r="D34" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>检查元素不存在</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>.activity-quiz-page</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="D35" s="5" t="n">
+      <c r="D35" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>滑动</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>上</t>
         </is>
       </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="D36" s="5" t="n">
+      <c r="D36" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>滑动</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>下</t>
         </is>
       </c>
+      <c r="G36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="D37" s="5" t="n">
+      <c r="D37" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>点选择器</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>.search-container</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="D38" s="5" t="n">
+      <c r="D38" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr"/>
     </row>
     <row r="39" ht="27" customHeight="1">
-      <c r="D39" s="5" t="n">
+      <c r="D39" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>检查输入框的值</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>wx-input.search-input</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="D40" s="5" t="n">
+      <c r="D40" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr"/>
+      <c r="F40" s="7" t="inlineStr"/>
+      <c r="G40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="D41" s="5" t="n">
+      <c r="D41" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr"/>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="D42" s="5" t="n">
+      <c r="D42" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr"/>
+      <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="D43" s="5" t="n">
+      <c r="D43" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>切换学习中心顶部栏</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>压铸百科</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr"/>
+      <c r="G43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="D44" s="5" t="n">
+      <c r="D44" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>切换学习中心顶部栏</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>专栏</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr"/>
+      <c r="G44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="D45" s="5" t="n">
+      <c r="D45" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>打开第一张专栏</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr"/>
-      <c r="G45" s="5" t="inlineStr"/>
+      <c r="F45" s="7" t="inlineStr"/>
+      <c r="G45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="D46" s="5" t="n">
+      <c r="D46" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="5" t="inlineStr"/>
+      <c r="F46" s="7" t="inlineStr"/>
+      <c r="G46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="D47" s="5" t="n">
+      <c r="D47" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="5" t="inlineStr"/>
+      <c r="F47" s="7" t="inlineStr"/>
+      <c r="G47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>ZW_009</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>搜索零结果时出现 AI 引导（需求 713582841）</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>手机在小程序首页；关键词 zzz9999 仍然零结果</t>
         </is>
       </c>
-      <c r="D48" s="5" t="n">
+      <c r="D48" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr"/>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr"/>
+      <c r="G48" s="7" t="inlineStr"/>
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：实测：这个词是零结果
@@ -1970,104 +1975,104 @@
       </c>
     </row>
     <row r="49">
-      <c r="D49" s="5" t="n">
+      <c r="D49" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>zzz9999</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr"/>
+      <c r="G49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="D50" s="5" t="n">
+      <c r="D50" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr"/>
-      <c r="G50" s="5" t="inlineStr"/>
+      <c r="F50" s="7" t="inlineStr"/>
+      <c r="G50" s="7" t="inlineStr"/>
     </row>
     <row r="51" ht="27" customHeight="1">
-      <c r="D51" s="5" t="n">
+      <c r="D51" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>没有找到相关内容？让小铸手帮你答</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr"/>
+      <c r="G51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="D52" s="5" t="n">
+      <c r="D52" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>问小铸手</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr"/>
+      <c r="G52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="D53" s="5" t="n">
+      <c r="D53" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr"/>
-      <c r="G53" s="5" t="inlineStr"/>
+      <c r="F53" s="7" t="inlineStr"/>
+      <c r="G53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>ZW_010</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>有结果时不出现 AI 引导（需求 713582841 的反向）</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>手机在小程序首页；关键词 qqqqq 仍然有结果</t>
         </is>
       </c>
-      <c r="D54" s="5" t="n">
+      <c r="D54" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr"/>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr"/>
+      <c r="G54" s="7" t="inlineStr"/>
+      <c r="H54" s="7" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：实测：这个词有结果（所以不该出现引导）
@@ -2078,104 +2083,104 @@
       </c>
     </row>
     <row r="55">
-      <c r="D55" s="5" t="n">
+      <c r="D55" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>qqqqq</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr"/>
+      <c r="G55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="D56" s="5" t="n">
+      <c r="D56" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr"/>
-      <c r="G56" s="5" t="inlineStr"/>
+      <c r="F56" s="7" t="inlineStr"/>
+      <c r="G56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="D57" s="5" t="n">
+      <c r="D57" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>全部回答</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr"/>
+      <c r="G57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="D58" s="5" t="n">
+      <c r="D58" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>检查文字不显示</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>问小铸手</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr"/>
+      <c r="G58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="D59" s="5" t="n">
+      <c r="D59" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr"/>
-      <c r="G59" s="5" t="inlineStr"/>
+      <c r="F59" s="7" t="inlineStr"/>
+      <c r="G59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>ZW_011</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>积分商城的回到顶部按钮符合需求（需求 713582097）</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>测试环境自己的账号已登录；手机在小程序首页</t>
         </is>
       </c>
-      <c r="D60" s="5" t="n">
+      <c r="D60" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr"/>
-      <c r="G60" s="5" t="inlineStr"/>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：用户中心 -&gt; 积分商城（二级页，没有底部 tab 栏）
@@ -2185,68 +2190,68 @@
       </c>
     </row>
     <row r="61">
-      <c r="D61" s="5" t="n">
+      <c r="D61" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>打开积分商城</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr"/>
-      <c r="G61" s="5" t="inlineStr"/>
+      <c r="F61" s="7" t="inlineStr"/>
+      <c r="G61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="D62" s="5" t="n">
+      <c r="D62" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>检查回到顶部按钮</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr"/>
-      <c r="G62" s="5" t="inlineStr"/>
+      <c r="F62" s="7" t="inlineStr"/>
+      <c r="G62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="D63" s="5" t="n">
+      <c r="D63" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr"/>
-      <c r="G63" s="5" t="inlineStr"/>
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="7" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>ZW_012</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>热门话题有 5 条且点第一条能进话题结果页（需求 713129788）</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>管理后台的「热门话题」配了 ≥5 个；手机在小程序首页</t>
         </is>
       </c>
-      <c r="D64" s="5" t="n">
+      <c r="D64" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr"/>
-      <c r="G64" s="5" t="inlineStr"/>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr"/>
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：只进搜索页、不输入关键词（输入的话热门话题会被建议列表顶掉）
@@ -2259,120 +2264,120 @@
       </c>
     </row>
     <row r="65">
-      <c r="D65" s="5" t="n">
+      <c r="D65" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr"/>
-      <c r="G65" s="5" t="inlineStr"/>
+      <c r="F65" s="7" t="inlineStr"/>
+      <c r="G65" s="7" t="inlineStr"/>
     </row>
     <row r="66" ht="27" customHeight="1">
-      <c r="D66" s="5" t="n">
+      <c r="D66" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>检查元素数量</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="F66" s="7" t="inlineStr">
         <is>
           <t>.hot-topics .inline-flex</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G66" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="D67" s="5" t="n">
+      <c r="D67" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>打开第一个热门话题</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr"/>
-      <c r="G67" s="5" t="inlineStr"/>
+      <c r="F67" s="7" t="inlineStr"/>
+      <c r="G67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="D68" s="5" t="n">
+      <c r="D68" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="F68" s="7" t="inlineStr">
         <is>
           <t>最新发布</t>
         </is>
       </c>
-      <c r="G68" s="5" t="inlineStr"/>
+      <c r="G68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="D69" s="5" t="n">
+      <c r="D69" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>最多点赞</t>
         </is>
       </c>
-      <c r="G69" s="5" t="inlineStr"/>
+      <c r="G69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="D70" s="5" t="n">
+      <c r="D70" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr"/>
-      <c r="G70" s="5" t="inlineStr"/>
+      <c r="F70" s="7" t="inlineStr"/>
+      <c r="G70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>ZW_013</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>帖子详情页点「主页」按钮回到首页（需求 713256065）</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>首页信息流里至少有 1 张帖子卡片</t>
         </is>
       </c>
-      <c r="D71" s="5" t="n">
+      <c r="D71" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr"/>
-      <c r="G71" s="5" t="inlineStr"/>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="F71" s="7" t="inlineStr"/>
+      <c r="G71" s="7" t="inlineStr"/>
+      <c r="H71" s="7" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：点首页信息流第一张帖子卡片进详情（只读）
@@ -2384,100 +2389,100 @@
       </c>
     </row>
     <row r="72">
-      <c r="D72" s="5" t="n">
+      <c r="D72" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>打开第一个帖子</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr"/>
-      <c r="G72" s="5" t="inlineStr"/>
+      <c r="F72" s="7" t="inlineStr"/>
+      <c r="G72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="D73" s="5" t="n">
+      <c r="D73" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>点主页按钮</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr"/>
-      <c r="G73" s="5" t="inlineStr"/>
+      <c r="F73" s="7" t="inlineStr"/>
+      <c r="G73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="D74" s="5" t="n">
+      <c r="D74" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="F74" s="7" t="inlineStr">
         <is>
           <t>最新提问</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr"/>
+      <c r="G74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="D75" s="5" t="n">
+      <c r="D75" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>.search-container</t>
         </is>
       </c>
-      <c r="G75" s="5" t="inlineStr"/>
+      <c r="G75" s="7" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="D76" s="5" t="n">
+      <c r="D76" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E76" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr"/>
-      <c r="G76" s="5" t="inlineStr"/>
+      <c r="F76" s="7" t="inlineStr"/>
+      <c r="G76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>ZW_014</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>首页筛选 tab 顺序与默认选中符合需求（需求 713341876）</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>手机在小程序首页（不用登录）</t>
         </is>
       </c>
-      <c r="D77" s="5" t="n">
+      <c r="D77" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr"/>
-      <c r="G77" s="5" t="inlineStr"/>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="F77" s="7" t="inlineStr"/>
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="7" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：需求：最新提问和推荐互换顺序 + 最新提问为默认展示（置顶帖那半句依赖数据，暂不覆盖）
@@ -2486,56 +2491,56 @@
       </c>
     </row>
     <row r="78">
-      <c r="D78" s="5" t="n">
+      <c r="D78" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E78" s="7" t="inlineStr">
         <is>
           <t>检查首页筛选栏顺序</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr"/>
-      <c r="G78" s="5" t="inlineStr"/>
+      <c r="F78" s="7" t="inlineStr"/>
+      <c r="G78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="D79" s="5" t="n">
+      <c r="D79" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr"/>
-      <c r="G79" s="5" t="inlineStr"/>
+      <c r="F79" s="7" t="inlineStr"/>
+      <c r="G79" s="7" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>ZW_015</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>案例库：介绍banner在分类上方、点它进长图；列表显示复制数；详情页评论区是「全部评论」（需求 713381608）</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>手机在小程序首页；案例库列表里至少有 1 个案例</t>
         </is>
       </c>
-      <c r="D80" s="5" t="n">
+      <c r="D80" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr"/>
-      <c r="G80" s="5" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="F80" s="7" t="inlineStr"/>
+      <c r="G80" s="7" t="inlineStr"/>
+      <c r="H80" s="7" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：入口 = 底部 tab「设计专区」
@@ -2550,128 +2555,128 @@
       </c>
     </row>
     <row r="81">
-      <c r="D81" s="5" t="n">
+      <c r="D81" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E81" s="5" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr"/>
-      <c r="G81" s="5" t="inlineStr"/>
+      <c r="F81" s="7" t="inlineStr"/>
+      <c r="G81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="D82" s="5" t="n">
+      <c r="D82" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="E82" s="7" t="inlineStr">
         <is>
           <t>检查案例库列表</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr"/>
-      <c r="G82" s="5" t="inlineStr"/>
+      <c r="F82" s="7" t="inlineStr"/>
+      <c r="G82" s="7" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="D83" s="5" t="n">
+      <c r="D83" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t>打开案例库介绍长图</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr"/>
-      <c r="G83" s="5" t="inlineStr"/>
+      <c r="F83" s="7" t="inlineStr"/>
+      <c r="G83" s="7" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="D84" s="5" t="n">
+      <c r="D84" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E84" s="5" t="inlineStr">
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t>检查案例库介绍长图</t>
         </is>
       </c>
-      <c r="F84" s="5" t="inlineStr"/>
-      <c r="G84" s="5" t="inlineStr"/>
+      <c r="F84" s="7" t="inlineStr"/>
+      <c r="G84" s="7" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="D85" s="5" t="n">
+      <c r="D85" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E85" s="5" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr"/>
-      <c r="G85" s="5" t="inlineStr"/>
+      <c r="F85" s="7" t="inlineStr"/>
+      <c r="G85" s="7" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="D86" s="5" t="n">
+      <c r="D86" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>打开第一个案例</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr"/>
-      <c r="G86" s="5" t="inlineStr"/>
+      <c r="F86" s="7" t="inlineStr"/>
+      <c r="G86" s="7" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="D87" s="5" t="n">
+      <c r="D87" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>检查案例详情页</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr"/>
-      <c r="G87" s="5" t="inlineStr"/>
+      <c r="F87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="D88" s="5" t="n">
+      <c r="D88" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="E88" s="5" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr"/>
-      <c r="G88" s="5" t="inlineStr"/>
+      <c r="F88" s="7" t="inlineStr"/>
+      <c r="G88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>ZW_016</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>案例复制：点复制后弹出「复制成功 / 使用手机号登录智铸超云」（会写数据，跑完自动复位）</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>需要开关 UITEST_ALLOW_SUBMIT=1（会写数据，跑完自动复位）；列表第 1 个案例可复制</t>
         </is>
       </c>
-      <c r="D89" s="5" t="n">
+      <c r="D89" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr"/>
-      <c r="G89" s="5" t="inlineStr"/>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="F89" s="7" t="inlineStr"/>
+      <c r="G89" s="7" t="inlineStr"/>
+      <c r="H89" s="7" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：入口 = 底部 tab「设计专区」
@@ -2683,96 +2688,96 @@
       </c>
     </row>
     <row r="90">
-      <c r="D90" s="5" t="n">
+      <c r="D90" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E90" s="5" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr"/>
-      <c r="G90" s="5" t="inlineStr"/>
+      <c r="F90" s="7" t="inlineStr"/>
+      <c r="G90" s="7" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="D91" s="5" t="n">
+      <c r="D91" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>打开第一个案例</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr"/>
-      <c r="G91" s="5" t="inlineStr"/>
+      <c r="F91" s="7" t="inlineStr"/>
+      <c r="G91" s="7" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="D92" s="5" t="n">
+      <c r="D92" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E92" s="7" t="inlineStr">
         <is>
           <t>复制当前案例</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr"/>
-      <c r="G92" s="5" t="inlineStr"/>
+      <c r="F92" s="7" t="inlineStr"/>
+      <c r="G92" s="7" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="D93" s="5" t="n">
+      <c r="D93" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
+      <c r="F93" s="7" t="inlineStr">
         <is>
           <t>复制成功</t>
         </is>
       </c>
-      <c r="G93" s="5" t="inlineStr"/>
+      <c r="G93" s="7" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="D94" s="5" t="n">
+      <c r="D94" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr"/>
-      <c r="G94" s="5" t="inlineStr"/>
+      <c r="F94" s="7" t="inlineStr"/>
+      <c r="G94" s="7" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>ZW_017</t>
         </is>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>课程详情页：已购买未开始显示「课程介绍」+ 课程标题 + 第一课时封面视频（需求 713367615）</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>登录账号已购买课程 717 且学习进度 0%（库里 user_course_relation 有、course_record 没有）</t>
         </is>
       </c>
-      <c r="D95" s="5" t="n">
+      <c r="D95" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr"/>
-      <c r="G95" s="5" t="inlineStr"/>
-      <c r="H95" s="5" t="inlineStr">
+      <c r="F95" s="7" t="inlineStr"/>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：我们账号对这门课是已购买 + 学习进度 0%（库里 user_course_relation 有、course_record 没有）
@@ -2782,76 +2787,76 @@
       </c>
     </row>
     <row r="96">
-      <c r="D96" s="5" t="n">
+      <c r="D96" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>打开课程详情</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>717</t>
         </is>
       </c>
-      <c r="G96" s="5" t="inlineStr"/>
+      <c r="G96" s="7" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="D97" s="5" t="n">
+      <c r="D97" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>检查课程详情页</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
+      <c r="F97" s="7" t="inlineStr">
         <is>
           <t>课程介绍</t>
         </is>
       </c>
-      <c r="G97" s="5" t="inlineStr"/>
+      <c r="G97" s="7" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="D98" s="5" t="n">
+      <c r="D98" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E98" s="5" t="inlineStr">
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr"/>
-      <c r="G98" s="5" t="inlineStr"/>
+      <c r="F98" s="7" t="inlineStr"/>
+      <c r="G98" s="7" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
+      <c r="A99" s="7" t="inlineStr">
         <is>
           <t>ZW_018</t>
         </is>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>课程列表：课时数为0的课程不显示（需求 713367615 第 1 条，跟数据库对账）</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>能连上测试库（要跟 course 表对账）；手机在小程序首页</t>
         </is>
       </c>
-      <c r="D99" s="5" t="n">
+      <c r="D99" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr"/>
-      <c r="G99" s="5" t="inlineStr"/>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="F99" s="7" t="inlineStr"/>
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="7" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：先到学习中心（默认落在专栏 tab）
@@ -2862,84 +2867,84 @@
       </c>
     </row>
     <row r="100">
-      <c r="D100" s="5" t="n">
+      <c r="D100" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E100" s="5" t="inlineStr">
+      <c r="E100" s="7" t="inlineStr">
         <is>
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr"/>
-      <c r="G100" s="5" t="inlineStr"/>
+      <c r="F100" s="7" t="inlineStr"/>
+      <c r="G100" s="7" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="D101" s="5" t="n">
+      <c r="D101" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E101" s="5" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>切换学习中心顶部栏</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>课程</t>
         </is>
       </c>
-      <c r="G101" s="5" t="inlineStr"/>
+      <c r="G101" s="7" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="D102" s="5" t="n">
+      <c r="D102" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E102" s="5" t="inlineStr">
+      <c r="E102" s="7" t="inlineStr">
         <is>
           <t>检查0课时课程不显示</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr"/>
-      <c r="G102" s="5" t="inlineStr"/>
+      <c r="F102" s="7" t="inlineStr"/>
+      <c r="G102" s="7" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="D103" s="5" t="n">
+      <c r="D103" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E103" s="5" t="inlineStr">
+      <c r="E103" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F103" s="5" t="inlineStr"/>
-      <c r="G103" s="5" t="inlineStr"/>
+      <c r="F103" s="7" t="inlineStr"/>
+      <c r="G103" s="7" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="inlineStr">
+      <c r="A104" s="7" t="inlineStr">
         <is>
           <t>ZW_019</t>
         </is>
       </c>
-      <c r="B104" s="5" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>付费案例复制：也弹同样的提示（会写数据 + 扣积分，跑完自动复位记录与复制数）</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
         <is>
           <t>需要开关 UITEST_ALLOW_SUBMIT=1（会写数据 + 扣积分，复制记录与复制数自动复位）；案例名「填充任务1」要与列表上一字不差</t>
         </is>
       </c>
-      <c r="D104" s="5" t="n">
+      <c r="D104" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E104" s="5" t="inlineStr">
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F104" s="5" t="inlineStr"/>
-      <c r="G104" s="5" t="inlineStr"/>
-      <c r="H104" s="5" t="inlineStr">
+      <c r="F104" s="7" t="inlineStr"/>
+      <c r="G104" s="7" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：入口 = 底部 tab「设计专区」
@@ -2951,100 +2956,100 @@
       </c>
     </row>
     <row r="105">
-      <c r="D105" s="5" t="n">
+      <c r="D105" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E105" s="5" t="inlineStr">
+      <c r="E105" s="7" t="inlineStr">
         <is>
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="F105" s="5" t="inlineStr"/>
-      <c r="G105" s="5" t="inlineStr"/>
+      <c r="F105" s="7" t="inlineStr"/>
+      <c r="G105" s="7" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="D106" s="5" t="n">
+      <c r="D106" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E106" s="5" t="inlineStr">
+      <c r="E106" s="7" t="inlineStr">
         <is>
           <t>打开案例</t>
         </is>
       </c>
-      <c r="F106" s="5" t="inlineStr">
+      <c r="F106" s="7" t="inlineStr">
         <is>
           <t>填充任务1</t>
         </is>
       </c>
-      <c r="G106" s="5" t="inlineStr"/>
+      <c r="G106" s="7" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="D107" s="5" t="n">
+      <c r="D107" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E107" s="5" t="inlineStr">
+      <c r="E107" s="7" t="inlineStr">
         <is>
           <t>复制当前案例</t>
         </is>
       </c>
-      <c r="F107" s="5" t="inlineStr"/>
-      <c r="G107" s="5" t="inlineStr"/>
+      <c r="F107" s="7" t="inlineStr"/>
+      <c r="G107" s="7" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="D108" s="5" t="n">
+      <c r="D108" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E108" s="5" t="inlineStr">
+      <c r="E108" s="7" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F108" s="5" t="inlineStr">
+      <c r="F108" s="7" t="inlineStr">
         <is>
           <t>复制成功</t>
         </is>
       </c>
-      <c r="G108" s="5" t="inlineStr"/>
+      <c r="G108" s="7" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="D109" s="5" t="n">
+      <c r="D109" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E109" s="5" t="inlineStr">
+      <c r="E109" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F109" s="5" t="inlineStr"/>
-      <c r="G109" s="5" t="inlineStr"/>
+      <c r="F109" s="7" t="inlineStr"/>
+      <c r="G109" s="7" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="inlineStr">
+      <c r="A110" s="7" t="inlineStr">
         <is>
           <t>ZW_020</t>
         </is>
       </c>
-      <c r="B110" s="5" t="inlineStr">
+      <c r="B110" s="7" t="inlineStr">
         <is>
           <t>未购买课程点课时：封面和标题不变、始终显示课程名（需求 713367615 第 2 条）</t>
         </is>
       </c>
-      <c r="C110" s="5" t="inlineStr">
+      <c r="C110" s="7" t="inlineStr">
         <is>
           <t>登录账号未购买「7.8课程new」（依据 user_course_relation 表）</t>
         </is>
       </c>
-      <c r="D110" s="5" t="n">
+      <c r="D110" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E110" s="5" t="inlineStr">
+      <c r="E110" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F110" s="5" t="inlineStr"/>
-      <c r="G110" s="5" t="inlineStr"/>
-      <c r="H110" s="5" t="inlineStr">
+      <c r="F110" s="7" t="inlineStr"/>
+      <c r="G110" s="7" t="inlineStr"/>
+      <c r="H110" s="7" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：我们账号只买过 717 一门课，所以这门是未购买（依据：user_course_relation 表）
@@ -3054,264 +3059,180 @@
       </c>
     </row>
     <row r="111">
-      <c r="D111" s="5" t="n">
+      <c r="D111" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E111" s="5" t="inlineStr">
+      <c r="E111" s="7" t="inlineStr">
         <is>
           <t>打开课程详情</t>
         </is>
       </c>
-      <c r="F111" s="5" t="inlineStr">
+      <c r="F111" s="7" t="inlineStr">
         <is>
           <t>7.8课程new</t>
         </is>
       </c>
-      <c r="G111" s="5" t="inlineStr"/>
+      <c r="G111" s="7" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="D112" s="5" t="n">
+      <c r="D112" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E112" s="5" t="inlineStr">
+      <c r="E112" s="7" t="inlineStr">
         <is>
           <t>检查未购买点课时</t>
         </is>
       </c>
-      <c r="F112" s="5" t="inlineStr">
+      <c r="F112" s="7" t="inlineStr">
         <is>
           <t>7.8课程new</t>
         </is>
       </c>
-      <c r="G112" s="5" t="inlineStr"/>
+      <c r="G112" s="7" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="D113" s="5" t="n">
+      <c r="D113" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E113" s="5" t="inlineStr">
+      <c r="E113" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F113" s="5" t="inlineStr"/>
-      <c r="G113" s="5" t="inlineStr"/>
+      <c r="F113" s="7" t="inlineStr"/>
+      <c r="G113" s="7" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="inlineStr">
+      <c r="A114" s="7" t="inlineStr">
         <is>
           <t>ZW_021</t>
         </is>
       </c>
-      <c r="B114" s="5" t="inlineStr">
+      <c r="B114" s="7" t="inlineStr">
         <is>
           <t>学习中心顶部有三个 tab</t>
         </is>
       </c>
-      <c r="C114" s="5" t="inlineStr">
+      <c r="C114" s="7" t="inlineStr">
         <is>
           <t>手机在小程序首页（不用登录）</t>
         </is>
       </c>
-      <c r="D114" s="5" t="n">
+      <c r="D114" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E114" s="5" t="inlineStr">
+      <c r="E114" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F114" s="5" t="inlineStr"/>
-      <c r="G114" s="5" t="inlineStr"/>
-      <c r="H114" s="5" t="inlineStr"/>
+      <c r="F114" s="7" t="inlineStr"/>
+      <c r="G114" s="7" t="inlineStr"/>
+      <c r="H114" s="7" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="D115" s="5" t="n">
+      <c r="D115" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E115" s="5" t="inlineStr">
+      <c r="E115" s="7" t="inlineStr">
         <is>
           <t>点文字</t>
         </is>
       </c>
-      <c r="F115" s="5" t="inlineStr">
+      <c r="F115" s="7" t="inlineStr">
         <is>
           <t>学习中心</t>
         </is>
       </c>
-      <c r="G115" s="5" t="inlineStr"/>
+      <c r="G115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="D116" s="5" t="n">
+      <c r="D116" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E116" s="5" t="inlineStr">
+      <c r="E116" s="7" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F116" s="5" t="inlineStr">
+      <c r="F116" s="7" t="inlineStr">
         <is>
           <t>课程</t>
         </is>
       </c>
-      <c r="G116" s="5" t="inlineStr"/>
+      <c r="G116" s="7" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="D117" s="5" t="n">
+      <c r="D117" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E117" s="5" t="inlineStr">
+      <c r="E117" s="7" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F117" s="5" t="inlineStr">
+      <c r="F117" s="7" t="inlineStr">
         <is>
           <t>专栏</t>
         </is>
       </c>
-      <c r="G117" s="5" t="inlineStr"/>
+      <c r="G117" s="7" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="D118" s="5" t="n">
+      <c r="D118" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E118" s="5" t="inlineStr">
+      <c r="E118" s="7" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F118" s="5" t="inlineStr">
+      <c r="F118" s="7" t="inlineStr">
         <is>
           <t>压铸百科</t>
         </is>
       </c>
-      <c r="G118" s="5" t="inlineStr"/>
+      <c r="G118" s="7" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="D119" s="5" t="n">
+      <c r="D119" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E119" s="5" t="inlineStr">
+      <c r="E119" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F119" s="5" t="inlineStr"/>
-      <c r="G119" s="5" t="inlineStr"/>
+      <c r="F119" s="7" t="inlineStr"/>
+      <c r="G119" s="7" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>ZW_022</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>测试</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>手机在小程序首页</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="n">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>ZW_023</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>中文关键词能搜出东西（靠搜索历史点进去）</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>测试库里该账号的搜索历史里有「压铸测试」（用 tools/search_history_tool.py 造过）</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E120" s="5" t="inlineStr">
+      <c r="E120" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F120" s="5" t="inlineStr"/>
-      <c r="G120" s="5" t="inlineStr"/>
-      <c r="H120" s="5" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="D121" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>点选择器</t>
-        </is>
-      </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>.fs-28</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="D122" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E122" s="5" t="inlineStr">
-        <is>
-          <t>输入搜索关键词</t>
-        </is>
-      </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>吉宝</t>
-        </is>
-      </c>
-      <c r="G122" s="5" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="D123" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>执行搜索</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="inlineStr"/>
-      <c r="G123" s="5" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="D124" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="F124" s="5" t="inlineStr"/>
-      <c r="G124" s="5" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>ZW_023</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>中文关键词能搜出东西（靠搜索历史点进去）</t>
-        </is>
-      </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>测试库里该账号的搜索历史里有「压铸测试」（用 tools/search_history_tool.py 造过）</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="F125" s="5" t="inlineStr"/>
-      <c r="G125" s="5" t="inlineStr"/>
-      <c r="H125" s="5" t="inlineStr">
+      <c r="F120" s="7" t="inlineStr"/>
+      <c r="G120" s="7" t="inlineStr"/>
+      <c r="H120" s="7" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：搜索页上才有「搜索历史」面板
@@ -3321,89 +3242,89 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="D126" s="5" t="n">
+    <row r="121">
+      <c r="D121" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E126" s="5" t="inlineStr">
+      <c r="E121" s="7" t="inlineStr">
         <is>
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="F126" s="5" t="inlineStr"/>
-      <c r="G126" s="5" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="D127" s="5" t="n">
+      <c r="F121" s="7" t="inlineStr"/>
+      <c r="G121" s="7" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="D122" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E127" s="5" t="inlineStr">
+      <c r="E122" s="7" t="inlineStr">
         <is>
           <t>点搜索历史里的词</t>
         </is>
       </c>
-      <c r="F127" s="5" t="inlineStr">
+      <c r="F122" s="7" t="inlineStr">
         <is>
           <t>压铸测试</t>
         </is>
       </c>
-      <c r="G127" s="5" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="D128" s="5" t="n">
+      <c r="G122" s="7" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="D123" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E128" s="5" t="inlineStr">
+      <c r="E123" s="7" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F128" s="5" t="inlineStr">
+      <c r="F123" s="7" t="inlineStr">
         <is>
           <t>压铸测试</t>
         </is>
       </c>
-      <c r="G128" s="5" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="D129" s="5" t="n">
+      <c r="G123" s="7" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="D124" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E129" s="5" t="inlineStr">
+      <c r="E124" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F129" s="5" t="inlineStr"/>
-      <c r="G129" s="5" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="5" t="inlineStr">
+      <c r="F124" s="7" t="inlineStr"/>
+      <c r="G124" s="7" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
         <is>
           <t>ZW_024</t>
         </is>
       </c>
-      <c r="B130" s="5" t="inlineStr">
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>中文关键词直接输入也能搜（框架自动切输入法）</t>
         </is>
       </c>
-      <c r="C130" s="5" t="inlineStr">
+      <c r="C125" s="7" t="inlineStr">
         <is>
           <t>手机在小程序首页；框架会自动临时切到 ADBKeyboard 输入中文</t>
         </is>
       </c>
-      <c r="D130" s="5" t="n">
+      <c r="D125" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E130" s="5" t="inlineStr">
+      <c r="E125" s="7" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F130" s="5" t="inlineStr"/>
-      <c r="G130" s="5" t="inlineStr"/>
-      <c r="H130" s="5" t="inlineStr">
+      <c r="F125" s="7" t="inlineStr"/>
+      <c r="G125" s="7" t="inlineStr"/>
+      <c r="H125" s="7" t="inlineStr">
         <is>
           <t>第1步：先摆正起点
 第2步：中文关键词：框架会自动临时切到 ADBKeyboard，用完切回你原来的输入法
@@ -3414,194 +3335,194 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="D126" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>打开搜索并输入</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>压铸</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="D127" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>执行搜索</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr"/>
+      <c r="G127" s="7" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="D128" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>检查文字不显示</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>搜索历史</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="D129" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>全部回答</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="D130" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr"/>
+      <c r="G130" s="7" t="inlineStr"/>
+    </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ZW_025</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>有问必答筛选栏第三个 tab 文案是「精选问答」</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>手机在小程序首页（不用登录）</t>
+        </is>
+      </c>
       <c r="D131" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>打开搜索并输入</t>
-        </is>
-      </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>压铸</t>
-        </is>
-      </c>
-      <c r="G131" s="5" t="inlineStr"/>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="n"/>
+      <c r="G131" s="5" t="n"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>缺陷 713070171（原文：有问必答中，精选回答tab应该为精选问答）；只读。
+第2步顺带验证四个 tab 的文案、顺序与默认选中（需求 713341876）—— 单独写"不显示"容易变成一句空断言。</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="D132" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>执行搜索</t>
-        </is>
-      </c>
-      <c r="F132" s="5" t="inlineStr"/>
-      <c r="G132" s="5" t="inlineStr"/>
+          <t>检查首页筛选栏顺序</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="n"/>
+      <c r="G132" s="5" t="n"/>
     </row>
     <row r="133">
       <c r="D133" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>检查文字不显示</t>
+          <t>检查文字显示</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>搜索历史</t>
-        </is>
-      </c>
-      <c r="G133" s="5" t="inlineStr"/>
+          <t>精选问答</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="n"/>
     </row>
     <row r="134">
       <c r="D134" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>检查文字显示</t>
+          <t>检查文字不显示</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>全部回答</t>
-        </is>
-      </c>
-      <c r="G134" s="5" t="inlineStr"/>
+          <t>精选回答</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="n"/>
     </row>
     <row r="135">
       <c r="D135" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F135" s="5" t="inlineStr"/>
-      <c r="G135" s="5" t="inlineStr"/>
+      <c r="F135" s="5" t="n"/>
+      <c r="G135" s="5" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>ZW_025</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>有问必答筛选栏第三个 tab 文案是「精选问答」</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>手机在小程序首页（不用登录）</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="n">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>ZW_026</t>
+        </is>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>普通用户在个人中心不显示身份标签</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>测试环境自己的账号已登录；手机在小程序首页</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E136" s="5" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F136" s="2" t="n"/>
-      <c r="G136" s="2" t="n"/>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>缺陷 713070171（原文：有问必答中，精选回答tab应该为精选问答）；只读。
-第2步顺带验证四个 tab 的文案、顺序与默认选中（需求 713341876）—— 单独写"不显示"容易变成一句空断言。</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="D137" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>检查首页筛选栏顺序</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="n"/>
-      <c r="G137" s="2" t="n"/>
-    </row>
-    <row r="138">
-      <c r="D138" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>精选问答</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="n"/>
-    </row>
-    <row r="139">
-      <c r="D139" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>检查文字不显示</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>精选回答</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="n"/>
-    </row>
-    <row r="140">
-      <c r="D140" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="n"/>
-      <c r="G140" s="2" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>ZW_026</t>
-        </is>
-      </c>
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>普通用户在个人中心不显示身份标签</t>
-        </is>
-      </c>
-      <c r="C141" s="5" t="inlineStr">
-        <is>
-          <t>测试环境自己的账号已登录；手机在小程序首页</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="n"/>
-      <c r="G141" s="2" t="n"/>
-      <c r="H141" s="5" t="inlineStr">
+      <c r="F136" s="5" t="n"/>
+      <c r="G136" s="5" t="n"/>
+      <c r="H136" s="7" t="inlineStr">
         <is>
           <t>缺陷 713073541（原文：当用户为普通用户时，搜索结果、个人中心应该不显示普通用户的标签）+ 713295623（普通用户不显示身份标签）；只读。
 第3步是"证明个人中心真的到了"的前置断言 —— 少了它，页面没到也会绿（假绿）。
@@ -3609,89 +3530,89 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="D142" s="2" t="n">
+    <row r="137">
+      <c r="D137" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E137" s="5" t="inlineStr">
         <is>
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="F142" s="2" t="n"/>
-      <c r="G142" s="2" t="n"/>
-    </row>
-    <row r="143">
-      <c r="D143" s="2" t="n">
+      <c r="F137" s="5" t="n"/>
+      <c r="G137" s="5" t="n"/>
+    </row>
+    <row r="138">
+      <c r="D138" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E138" s="5" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F138" s="5" t="inlineStr">
         <is>
           <t>积分商城</t>
         </is>
       </c>
-      <c r="G143" s="2" t="n"/>
-    </row>
-    <row r="144">
-      <c r="D144" s="2" t="n">
+      <c r="G138" s="5" t="n"/>
+    </row>
+    <row r="139">
+      <c r="D139" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E139" s="5" t="inlineStr">
         <is>
           <t>检查文字不显示</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F139" s="5" t="inlineStr">
         <is>
           <t>普通用户</t>
         </is>
       </c>
-      <c r="G144" s="2" t="n"/>
-    </row>
-    <row r="145">
-      <c r="D145" s="2" t="n">
+      <c r="G139" s="5" t="n"/>
+    </row>
+    <row r="140">
+      <c r="D140" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E140" s="5" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F145" s="2" t="n"/>
-      <c r="G145" s="2" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="F140" s="5" t="n"/>
+      <c r="G140" s="5" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
         <is>
           <t>ZW_027</t>
         </is>
       </c>
-      <c r="B146" s="5" t="inlineStr">
+      <c r="B141" s="7" t="inlineStr">
         <is>
           <t>帖子详情页点评论入口要弹出评论面板</t>
         </is>
       </c>
-      <c r="C146" s="5" t="inlineStr">
+      <c r="C141" s="7" t="inlineStr">
         <is>
           <t>首页信息流里至少有 1 张帖子卡片（首页自己要能加载出来）</t>
         </is>
       </c>
-      <c r="D146" s="2" t="n">
+      <c r="D141" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E141" s="5" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F146" s="2" t="n"/>
-      <c r="G146" s="2" t="n"/>
-      <c r="H146" s="5" t="inlineStr">
+      <c r="F141" s="5" t="n"/>
+      <c r="G141" s="5" t="n"/>
+      <c r="H141" s="7" t="inlineStr">
         <is>
           <t>缺陷 713006028（原文：帖子详情页，评论按钮点击无响应）；只读，不发评论。
 第4步是核心断言：点了评论入口之后，面板上必须出现「发送」按钮。
@@ -3700,105 +3621,105 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="D142" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>打开第一个帖子</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="n"/>
+      <c r="G142" s="5" t="n"/>
+    </row>
+    <row r="143">
+      <c r="D143" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>留下你的回答</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="n"/>
+    </row>
+    <row r="144">
+      <c r="D144" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>发送</t>
+        </is>
+      </c>
+      <c r="G144" s="5" t="n"/>
+    </row>
+    <row r="145">
+      <c r="D145" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>点选择器</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>.overlay-mask</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="n"/>
+    </row>
+    <row r="146">
+      <c r="D146" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="n"/>
+      <c r="G146" s="5" t="n"/>
+    </row>
     <row r="147">
-      <c r="D147" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>打开第一个帖子</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="n"/>
-      <c r="G147" s="2" t="n"/>
-    </row>
-    <row r="148">
-      <c r="D148" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>点文字</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>留下你的回答</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="n"/>
-    </row>
-    <row r="149">
-      <c r="D149" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>检查文字显示</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>发送</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="n"/>
-    </row>
-    <row r="150">
-      <c r="D150" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>点选择器</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>.overlay-mask</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="n"/>
-    </row>
-    <row r="151">
-      <c r="D151" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ZW_028</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>话题详情页点筛选项不会把页面点坏</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；搜索页的「热门话题」至少有 1 条</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F151" s="2" t="n"/>
-      <c r="G151" s="2" t="n"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>ZW_028</t>
-        </is>
-      </c>
-      <c r="B152" s="5" t="inlineStr">
-        <is>
-          <t>话题详情页点筛选项不会把页面点坏</t>
-        </is>
-      </c>
-      <c r="C152" s="5" t="inlineStr">
-        <is>
-          <t>手机在小程序首页；搜索页的「热门话题」至少有 1 条</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>回到首页</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="n"/>
-      <c r="G152" s="2" t="n"/>
-      <c r="H152" s="5" t="inlineStr">
+      <c r="F147" s="5" t="n"/>
+      <c r="G147" s="5" t="n"/>
+      <c r="H147" t="inlineStr">
         <is>
           <t>缺陷 713335002（原文：话题详情页筛选项点击时报错）；只读。
 第4步点的是话题结果页的排序筛选项；第5步的断言不是"验证排序结果"，而是**页面还在** ——
@@ -3807,98 +3728,94 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="D153" s="2" t="n">
+    <row r="148">
+      <c r="D148" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E148" s="5" t="inlineStr">
         <is>
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="F153" s="2" t="n"/>
-      <c r="G153" s="2" t="n"/>
-    </row>
-    <row r="154">
-      <c r="D154" s="2" t="n">
+      <c r="F148" s="5" t="n"/>
+      <c r="G148" s="5" t="n"/>
+    </row>
+    <row r="149">
+      <c r="D149" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E149" s="5" t="inlineStr">
         <is>
           <t>打开第一个热门话题</t>
         </is>
       </c>
-      <c r="F154" s="2" t="n"/>
-      <c r="G154" s="2" t="n"/>
-    </row>
-    <row r="155">
-      <c r="D155" s="2" t="n">
+      <c r="F149" s="5" t="n"/>
+      <c r="G149" s="5" t="n"/>
+    </row>
+    <row r="150">
+      <c r="D150" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E150" s="5" t="inlineStr">
         <is>
           <t>点文字</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F150" s="5" t="inlineStr">
         <is>
           <t>最新发布</t>
         </is>
       </c>
-      <c r="G155" s="2" t="n"/>
-    </row>
-    <row r="156">
-      <c r="D156" s="2" t="n">
+      <c r="G150" s="5" t="n"/>
+    </row>
+    <row r="151">
+      <c r="D151" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E151" s="5" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F151" s="5" t="inlineStr">
         <is>
           <t>最多点赞</t>
         </is>
       </c>
-      <c r="G156" s="2" t="n"/>
-    </row>
-    <row r="157">
-      <c r="D157" s="2" t="n">
+      <c r="G151" s="5" t="n"/>
+    </row>
+    <row r="152">
+      <c r="D152" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E152" s="5" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="F157" s="2" t="n"/>
-      <c r="G157" s="2" t="n"/>
+      <c r="F152" s="5" t="n"/>
+      <c r="G152" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="112">
+  <mergeCells count="108">
     <mergeCell ref="A48:A53"/>
     <mergeCell ref="A114:A119"/>
     <mergeCell ref="H99:H103"/>
-    <mergeCell ref="H130:H135"/>
-    <mergeCell ref="H141:H145"/>
-    <mergeCell ref="B130:B135"/>
+    <mergeCell ref="A131:A135"/>
+    <mergeCell ref="C131:C135"/>
     <mergeCell ref="B30:B47"/>
     <mergeCell ref="H17:H20"/>
-    <mergeCell ref="C125:C129"/>
     <mergeCell ref="A54:A59"/>
     <mergeCell ref="C54:C59"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="H125:H129"/>
     <mergeCell ref="H110:H113"/>
-    <mergeCell ref="B125:B129"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="H30:H47"/>
-    <mergeCell ref="C141:C145"/>
     <mergeCell ref="A17:A20"/>
     <mergeCell ref="C60:C63"/>
     <mergeCell ref="C64:C70"/>
+    <mergeCell ref="A147:A152"/>
     <mergeCell ref="B95:B98"/>
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="H104:H109"/>
@@ -3906,22 +3823,20 @@
     <mergeCell ref="A99:A103"/>
     <mergeCell ref="H64:H70"/>
     <mergeCell ref="B136:B140"/>
-    <mergeCell ref="A130:A135"/>
     <mergeCell ref="B104:B109"/>
     <mergeCell ref="A136:A140"/>
+    <mergeCell ref="H131:H135"/>
+    <mergeCell ref="H147:H152"/>
     <mergeCell ref="H54:H59"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="B71:B76"/>
     <mergeCell ref="C4:C7"/>
-    <mergeCell ref="H146:H151"/>
     <mergeCell ref="B17:B20"/>
     <mergeCell ref="C136:C140"/>
-    <mergeCell ref="C152:C157"/>
     <mergeCell ref="A21:A24"/>
     <mergeCell ref="C21:C24"/>
     <mergeCell ref="A89:A94"/>
     <mergeCell ref="H8:H12"/>
-    <mergeCell ref="B141:B145"/>
     <mergeCell ref="B60:B63"/>
     <mergeCell ref="B25:B29"/>
     <mergeCell ref="A64:A70"/>
@@ -3932,14 +3847,14 @@
     <mergeCell ref="B110:B113"/>
     <mergeCell ref="C48:C53"/>
     <mergeCell ref="C120:C124"/>
+    <mergeCell ref="B141:B146"/>
     <mergeCell ref="H4:H7"/>
     <mergeCell ref="A110:A113"/>
-    <mergeCell ref="A141:A145"/>
     <mergeCell ref="A60:A63"/>
-    <mergeCell ref="H152:H157"/>
+    <mergeCell ref="B125:B130"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="H77:H79"/>
-    <mergeCell ref="A125:A129"/>
+    <mergeCell ref="C141:C146"/>
     <mergeCell ref="H120:H124"/>
     <mergeCell ref="H114:H119"/>
     <mergeCell ref="H89:H94"/>
@@ -3948,33 +3863,33 @@
     <mergeCell ref="B64:B70"/>
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="B80:B88"/>
+    <mergeCell ref="B131:B135"/>
     <mergeCell ref="H60:H63"/>
     <mergeCell ref="C114:C119"/>
-    <mergeCell ref="C130:C135"/>
+    <mergeCell ref="B147:B152"/>
     <mergeCell ref="C30:C47"/>
     <mergeCell ref="A104:A109"/>
-    <mergeCell ref="B146:B151"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C13:C16"/>
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="H25:H29"/>
-    <mergeCell ref="A152:A157"/>
+    <mergeCell ref="C125:C130"/>
     <mergeCell ref="A120:A124"/>
+    <mergeCell ref="H141:H146"/>
     <mergeCell ref="A80:A88"/>
     <mergeCell ref="C80:C88"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="B21:B24"/>
+    <mergeCell ref="H125:H130"/>
     <mergeCell ref="B99:B103"/>
+    <mergeCell ref="C147:C152"/>
+    <mergeCell ref="C104:C109"/>
     <mergeCell ref="C89:C94"/>
-    <mergeCell ref="C104:C109"/>
     <mergeCell ref="C77:C79"/>
     <mergeCell ref="H136:H140"/>
-    <mergeCell ref="A146:A151"/>
-    <mergeCell ref="C146:C151"/>
     <mergeCell ref="H21:H24"/>
-    <mergeCell ref="B152:B157"/>
     <mergeCell ref="A77:A79"/>
     <mergeCell ref="A71:A76"/>
     <mergeCell ref="C71:C76"/>
@@ -3982,15 +3897,35 @@
     <mergeCell ref="H13:H16"/>
     <mergeCell ref="C110:C113"/>
     <mergeCell ref="B120:B124"/>
+    <mergeCell ref="A141:A146"/>
     <mergeCell ref="B89:B94"/>
     <mergeCell ref="A25:A29"/>
     <mergeCell ref="C25:C29"/>
+    <mergeCell ref="A125:A130"/>
     <mergeCell ref="C99:C103"/>
     <mergeCell ref="H71:H76"/>
     <mergeCell ref="B54:B59"/>
     <mergeCell ref="B114:B119"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="8">
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
+      <formula1>='动作清单'!$A$2:$A$51</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
+      <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
+      <formula1>='动作清单'!$A$2:$A$51</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
+      <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
+      <formula1>='动作清单'!$A$2:$A$51</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
+      <formula1>1</formula1>
+    </dataValidation>
     <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
       <formula1>='动作清单'!$A$2:$A$51</formula1>
     </dataValidation>
@@ -4021,37 +3956,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>动作</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>怎么填（示例）</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>会不会改数据</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>属于哪一类</t>
         </is>
@@ -4063,8 +3998,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4092,8 +4025,6 @@
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4121,8 +4052,6 @@
           <t>打开积分商城</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4150,8 +4079,6 @@
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4184,7 +4111,6 @@
           <t>顶部栏名称（只能填：课程 / 专栏 / 压铸百科）</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>专栏</t>
@@ -4212,8 +4138,6 @@
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4241,8 +4165,6 @@
           <t>点主页按钮</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4270,8 +4192,6 @@
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4299,8 +4219,6 @@
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4333,7 +4251,6 @@
           <t>课程名</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>717</t>
@@ -4366,7 +4283,6 @@
           <t>关键词</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -4399,7 +4315,6 @@
           <t>关键词</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -4427,8 +4342,6 @@
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4461,7 +4374,6 @@
           <t>词</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>压铸测试</t>
@@ -4489,8 +4401,6 @@
           <t>打开第一个热门话题</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4518,8 +4428,6 @@
           <t>打开第一个帖子</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4547,8 +4455,6 @@
           <t>打开第一张专栏</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4576,8 +4482,6 @@
           <t>打开第一个案例</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4605,8 +4509,6 @@
           <t>打开案例库介绍长图</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4639,7 +4541,6 @@
           <t>案例名</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>填充任务1</t>
@@ -4748,12 +4649,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>方向（只能填：上 / 下）</t>
+          <t>方向（上 / 下；要自己定每次滑多少就带幅度，例如「上 30%」= 每次滑屏高的 30%，不带就是半屏）</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3 / 上</t>
+          <t>3 / 上（每次半屏；想自己定就写「上 30%」= 每次滑屏高的 30%）</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4763,7 +4664,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」</t>
+          <t>滑动屏幕，次数 1~10、方向填 上 或 下。列表要滑到底才看得到的东西用「上」；滑完想滚回顶部用「下」。每次滑多少可以自己定：方向后面带百分比即可，例如「上 30%」= 每次只滑屏高的 30%（范围 5%~95%；不带数字就是默认的半屏）</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4783,7 +4684,6 @@
           <t>筛选栏名称（只能填：最新提问 / 推荐 / 精选问答 / 我的关注）</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>推荐</t>
@@ -4816,7 +4716,6 @@
           <t>毫秒</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>2000（= 等 2 秒）</t>
@@ -4838,14 +4737,12 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="27" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4878,7 +4775,6 @@
           <t>范围（只能填：全量 / 只看有文字）</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>只看有文字</t>
@@ -4911,7 +4807,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>答对最多可赢积分</t>
@@ -4944,7 +4839,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>最新提问（搜索页上不该有）</t>
@@ -5014,7 +4908,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>.search-container</t>
@@ -5047,7 +4940,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>.activity-quiz-page</t>
@@ -5149,8 +5041,6 @@
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5178,8 +5068,6 @@
           <t>检查首页筛选栏顺序</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5207,8 +5095,6 @@
           <t>检查回到顶部按钮</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5236,8 +5122,6 @@
           <t>检查答题页</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5265,8 +5149,6 @@
           <t>检查案例库列表</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5294,8 +5176,6 @@
           <t>检查案例详情页</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5323,8 +5203,6 @@
           <t>检查案例库介绍长图</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5357,7 +5235,6 @@
           <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>课程介绍</t>
@@ -5385,8 +5262,6 @@
           <t>检查0课时课程不显示</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5419,7 +5294,6 @@
           <t>课程名</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>7.8课程new</t>
@@ -5447,8 +5321,6 @@
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5476,8 +5348,6 @@
           <t>逐题作答</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5505,8 +5375,6 @@
           <t>提交答卷</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5539,7 +5407,6 @@
           <t>活动名</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>Z-B4-答题角标</t>
@@ -5604,8 +5471,6 @@
           <t>复制当前案例</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5644,376 +5509,376 @@
   <dimension ref="A1:A58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="99.875" customWidth="1" style="2" min="1" max="1"/>
-    <col width="9" customWidth="1" style="2" min="2" max="16384"/>
+    <col width="99.875" customWidth="1" style="5" min="1" max="1"/>
+    <col width="9" customWidth="1" style="5" min="2" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>怎么用这张表（零基础版）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>【表长什么样】8 列，分两种：</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  按用例的 4 列（表里并成一格，只有第一步那行有值）：</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">     用例编号 | 用例标题 | 前置条件 | 备注</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  按步骤的 4 列（每一行都要填）：</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">     步骤序号 | 动作 | 参数1 | 参数2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  编号格式：ZW_001、ZW_002…（前缀 + 三位数字，唯一就行；填错的编号会让这条用例对不上号）</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>1. 一行 = 一个步骤。同一个「用例编号」的若干行，按「步骤序号」顺序执行；它们一起算一条用例。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>2. 一条用例怎么摆：第一行写「用例编号 + 用例标题 + 前置条件 + 备注」，</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   下面几行的这四列并成一格、空着就行 —— 表上看起来就是「一案一块」，</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   一眼数得出有几条用例、每条几步、每条要怎么准备。每行都要填的是「步骤序号」和「动作」。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   （按这个排版，导出时编号空着的行会自动并到上一条用例；但第一行数据必须写编号，否则整表报错。）</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>2b.「前置条件」写「跑这条之前手机得在什么状态」（要不要先登录、首页得有什么卡），</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   它不是动作、不会被自动执行 —— 是给人看的，也是「这条挂了先查什么」的线索。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>2c.「备注」是整条用例的备注（也并成一格）。某一步自己的说明写在同一格里，</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   用「第2步：…」开头即可。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>3. 「动作」只能填「动作清单」工作表里列出的名字 —— 填别的会在导出时报错，不会静默跳过。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>3b. 有几类参数要填数据里的名字（课程名 / 案例名 / 活动名），一字不差才行；</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    候选值在「名称候选」工作表里，直接复制粘贴即可（刷新它：python tools/export_cases.py --dropdown）。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>4. 「参数1 / 参数2」按动作需要填，不用就留空。填多了（该动作用不到）也会报错，防手滑；</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   参数名后面写着「（可不填）」的，留空就走默认值（例如「第几个」留空 = 第 1 个）。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>5. 「备注」随便写，只出现在日志和报告里，不影响执行（但它会显示在报告里，写清需求号很有用）。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>6. 填完执行：python run.py      （它会先自动把本表导出成 json，再跑用例）</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   只想跑表格里的某一条：python run.py -k 活动入口_001</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>7. 每条用例开头都先用「回到首页」把起点摆正；会把手机停在二级页（搜索页/详情页/答题页）的用例，</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   最后再补一步「回到首页」把手机交还。原因：表里的用例共用同一部手机，</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   上一条停在二级页上，下一条可能报「找不到底部 tab」—— 开头摆正 + 结尾交还就不受影响。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>8. 「动作」列是下拉框（点单元格右边的小箭头选），可选项来自「动作清单」工作表；</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   「步骤序号」列只接受 1、2、3… 这样的正整数。填错的动作名根本选不出来，省一轮报错。</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>8b. 自己新加的行不会自动并格。改完想让它并回去、顺便刷新下拉框，跑一次：</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    python tools/export_cases.py --dropdown    （只动排版，不动你填的内容；Excel 开着这份表时先关掉）</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>9. 不知道「检查文字显示」该填哪段字？先加一行「打印页面文字」跑一次 ——</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   当前屏幕上看得见的文字会打进日志，照着抄就行（挑完把它删掉即可）。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>默认禁止（安全阀，避免手滑把真实数据改了）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="27" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 「点文字」不能点这些字：提交、兑换、签到、下单、支付、购买、领取、抽奖、报名、删除、退出登录、退款、取消订单</t>
         </is>
       </c>
     </row>
     <row r="39" ht="27" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">     原因：这些操作会改真实数据/消耗真实积分。真要测它们，得单独写用例并显式打开开关，不能靠表格里写一行就触发。</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 「打开答题活动」只打开页面，不选选项、不提交（选选项会消耗答题机会）。</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>要测「会改数据」的操作？开着开关跑（owner 2026/10/12 同意）</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 开关就是一句环境变量：跑之前先执行  $env:UITEST_ALLOW_SUBMIT="1"  （PowerShell）</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">     不设这个开关时，下面这两个动作会直接报错，不会偷偷执行，也不会假装跳过。</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 「复位答题记录」（参数1=活动名）：删掉该活动在测试库里留下的答题记录。</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">     默认只预览不删；开了开关才真删。跑完写数据的用例，务必用它把记录清干净。</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 「提交答卷」：真的提交一次，用来测「提交后按钮变成已提交已参加」这条需求。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 「逐题作答」「检查答题记录数」不需要开关：前者只改前端选中态（不写库），后者是只读。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 写链路的标准写法（照抄即可）：回到首页 → 打开答题活动 → 复位答题记录(活动名) →</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">     逐题作答 → 检查文字显示(已答) → 提交答卷 → 检查文字显示(已参加) →</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">     检查答题记录数(活动名 / 1) → 复位答题记录(活动名) → 回到首页</t>
         </is>
       </c>
     </row>
     <row r="52" ht="27" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 现成模板：test_case/suprecast_app/test_quiz_submit.js（跑法：$env:UITEST_ALLOW_SUBMIT="1"; python run.py -k 答题写链路）</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>已知限制（诚实标注，别误读成框架不行）</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 搜索关键词只能是字母/数字/下划线/点/连字符：关键词是通过 adb 发过去的，adb 发中文不报错但不生效。</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 「点文字」点的是屏幕上看得见的文字；同名文字有多个时点第 1 个。</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 断言的等待时间写死在框架里（文字类 8 秒、元素类 8 秒），表格里暂时改不了。</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 「复位答题记录」只能删答题相关的两张表；别的写操作（积分兑换、签到）还没做复位手段。</t>
         </is>
@@ -6039,17 +5904,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>名字</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -7664,7 +7529,6 @@
           <t>方案一变形</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7677,7 +7541,6 @@
           <t>仅凝固</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7690,7 +7553,6 @@
           <t>仅充填2</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7703,7 +7565,6 @@
           <t>充填凝固应力</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7716,7 +7577,6 @@
           <t>充填凝固应力1</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7729,7 +7589,6 @@
           <t>7201744-孙</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7742,7 +7601,6 @@
           <t>带组织性能结果</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7755,7 +7613,6 @@
           <t>充填-排气</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7768,7 +7625,6 @@
           <t>1月 20250115</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7781,7 +7637,6 @@
           <t>紫色1</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7794,7 +7649,6 @@
           <t>内部数据6</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7807,7 +7661,6 @@
           <t>1QQ区qqqqq</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7820,7 +7673,6 @@
           <t>重力铸造-重力砂型-0602-163625-仅充填仅浏览-重力铸造-重力砂型-0602-163625</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7833,7 +7685,6 @@
           <t>重力铸造-重力砂型-0602-163625-充填凝固0602_165141-仅浏览</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7846,7 +7697,6 @@
           <t>COPY3</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7859,7 +7709,6 @@
           <t>3月26测试 私有材料分享(copy)</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7872,7 +7721,6 @@
           <t>内部数据-虚拟模具</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7885,7 +7733,6 @@
           <t>内部数据</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7898,7 +7745,6 @@
           <t>鹅鹅鹅</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7911,7 +7757,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7924,7 +7769,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7937,7 +7781,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7950,7 +7793,6 @@
           <t>仅凝固+应力-选择点2</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7963,7 +7805,6 @@
           <t>仅凝固1</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7976,7 +7817,6 @@
           <t>循环凝固</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7989,7 +7829,6 @@
           <t>131231</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8002,7 +7841,6 @@
           <t>131231</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8015,7 +7853,6 @@
           <t>循环凝固-热循环</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8028,7 +7865,6 @@
           <t>6668</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8041,7 +7877,6 @@
           <t>6668</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8054,7 +7889,6 @@
           <t>填充任务1</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8067,7 +7901,6 @@
           <t>0605测试</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8080,7 +7913,6 @@
           <t>循环凝固+应力+选点1</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8093,7 +7925,6 @@
           <t>料筒(copy)</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8106,7 +7937,6 @@
           <t>仅凝固</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8119,7 +7949,6 @@
           <t>#713392277</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8132,7 +7961,6 @@
           <t>？？？？</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8145,7 +7973,6 @@
           <t>复制任务失败问题测试-分享</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8158,7 +7985,6 @@
           <t>浇口充填-高级模式</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8171,7 +7997,6 @@
           <t>4.17</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8184,7 +8009,6 @@
           <t>热热热热</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8197,7 +8021,6 @@
           <t>eeee</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8210,7 +8033,6 @@
           <t>亲亲</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8223,7 +8045,6 @@
           <t>3333 私有曲线</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8236,7 +8057,6 @@
           <t>v2</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8249,7 +8069,6 @@
           <t>111111</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8262,7 +8081,6 @@
           <t>测试二级页面案例111111111111111111111111111</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8275,7 +8093,6 @@
           <t>分享高压 2</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8288,7 +8105,6 @@
           <t>料筒充填</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8301,7 +8117,6 @@
           <t>料筒充填1</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8314,7 +8129,6 @@
           <t>料筒分享</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8327,7 +8141,6 @@
           <t>1WWWW</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8340,7 +8153,6 @@
           <t>凝固应力</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8353,7 +8165,6 @@
           <t>模拟汽车</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8366,7 +8177,6 @@
           <t>模拟汽车减震</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8379,7 +8189,6 @@
           <t>多浇口充填(粒子数量10)</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8387,7 +8196,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
           <t>课程那张表里的「我们账号买没买」按 user_id=1966910（config/env.yaml）判断</t>
@@ -8400,7 +8208,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
           <t>注意：这些课程名在库里有多门同名，按名字打开只会命中第一门 —— 012345678901234567890123456789、付费课程1、免费课程、免费课程1、无敌贵的课程、测试封面图、测试封面图-修改、测试验证课时bug</t>
@@ -8413,7 +8220,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
           <t>案例共 56 条，已全部列出</t>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="动作清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="填写说明" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="名称候选" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动作清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名称候选" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -177,6 +177,9 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="34">
@@ -633,7 +636,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -657,6 +660,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1069,7 +1073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4015,8 +4019,151 @@
         </is>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ZW_032</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>文字重名时用「范围内点文字」精确点中筛选栏</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；不用登录、不改数据</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>为什么有这条：实测（2026/10/16）首页「推荐」整页命中 2 处 —— 筛选 tab 一处、信息流某张卡片的标题一处。只按文字点（点文字）是按 DOM 顺序数第几个，点对是运气；圈定范围之后只剩 1 处。
+第 2 步：动作「范围内点文字」—— 参数1 = 范围 .eco-tab-bar-container、参数2 = 文字 推荐。
+第 3-4 步：断言「推荐」真的成了选中项（源码里选中态是多一个 class：eco-tab-item-active；:has-text 用来确定选中的是哪一个）。
+第 5-6 步：反向走一遍，回到「最新提问」。第 7 步收尾归位。</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="D167" t="n">
+        <v>2</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>范围内点文字</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>.eco-tab-bar-container</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>推荐</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="D168" t="n">
+        <v>3</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>检查元素数量</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>.eco-tab-item-active</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="D169" t="n">
+        <v>4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>检查元素数量</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>.eco-tab-item-active:has-text("推荐")</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="D170" t="n">
+        <v>5</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>范围内点文字</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>.eco-tab-bar-container</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>最新提问</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="D171" t="n">
+        <v>6</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>检查元素数量</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>.eco-tab-item-active:has-text("最新提问")</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="D172" t="n">
+        <v>7</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="116">
+  <mergeCells count="120">
     <mergeCell ref="A48:A53"/>
     <mergeCell ref="A114:A119"/>
     <mergeCell ref="H99:H103"/>
@@ -4029,8 +4176,8 @@
     <mergeCell ref="C54:C59"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A159:A165"/>
+    <mergeCell ref="C159:C165"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C159:C165"/>
     <mergeCell ref="H110:H113"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="H30:H47"/>
@@ -4040,12 +4187,13 @@
     <mergeCell ref="A147:A152"/>
     <mergeCell ref="B95:B98"/>
     <mergeCell ref="B8:B12"/>
+    <mergeCell ref="H104:H109"/>
     <mergeCell ref="H48:H53"/>
-    <mergeCell ref="H104:H109"/>
     <mergeCell ref="A99:A103"/>
     <mergeCell ref="H64:H70"/>
+    <mergeCell ref="B136:B140"/>
     <mergeCell ref="B104:B109"/>
-    <mergeCell ref="B136:B140"/>
+    <mergeCell ref="B166:B172"/>
     <mergeCell ref="A136:A140"/>
     <mergeCell ref="B153:B158"/>
     <mergeCell ref="H131:H135"/>
@@ -4065,11 +4213,11 @@
     <mergeCell ref="A64:A70"/>
     <mergeCell ref="C153:C158"/>
     <mergeCell ref="H95:H98"/>
+    <mergeCell ref="C95:C98"/>
     <mergeCell ref="A30:A47"/>
-    <mergeCell ref="C95:C98"/>
     <mergeCell ref="B4:B7"/>
+    <mergeCell ref="B110:B113"/>
     <mergeCell ref="C48:C53"/>
-    <mergeCell ref="B110:B113"/>
     <mergeCell ref="C120:C124"/>
     <mergeCell ref="B141:B146"/>
     <mergeCell ref="H4:H7"/>
@@ -4082,8 +4230,8 @@
     <mergeCell ref="C141:C146"/>
     <mergeCell ref="H120:H124"/>
     <mergeCell ref="H114:H119"/>
+    <mergeCell ref="H89:H94"/>
     <mergeCell ref="H80:H88"/>
-    <mergeCell ref="H89:H94"/>
     <mergeCell ref="B48:B53"/>
     <mergeCell ref="B64:B70"/>
     <mergeCell ref="A95:A98"/>
@@ -4095,30 +4243,33 @@
     <mergeCell ref="C30:C47"/>
     <mergeCell ref="A104:A109"/>
     <mergeCell ref="B159:B165"/>
+    <mergeCell ref="A166:A172"/>
+    <mergeCell ref="C13:C16"/>
+    <mergeCell ref="A13:A16"/>
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="C13:C16"/>
     <mergeCell ref="B77:B79"/>
+    <mergeCell ref="C166:C172"/>
     <mergeCell ref="H25:H29"/>
     <mergeCell ref="C125:C130"/>
     <mergeCell ref="A120:A124"/>
+    <mergeCell ref="H141:H146"/>
     <mergeCell ref="A80:A88"/>
-    <mergeCell ref="H141:H146"/>
     <mergeCell ref="C80:C88"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="B21:B24"/>
+    <mergeCell ref="H125:H130"/>
     <mergeCell ref="B99:B103"/>
-    <mergeCell ref="H125:H130"/>
+    <mergeCell ref="C147:C152"/>
+    <mergeCell ref="C104:C109"/>
     <mergeCell ref="C89:C94"/>
-    <mergeCell ref="C104:C109"/>
-    <mergeCell ref="C147:C152"/>
     <mergeCell ref="C77:C79"/>
     <mergeCell ref="H136:H140"/>
     <mergeCell ref="H21:H24"/>
     <mergeCell ref="A77:A79"/>
     <mergeCell ref="A71:A76"/>
     <mergeCell ref="C71:C76"/>
+    <mergeCell ref="H166:H172"/>
     <mergeCell ref="C17:C20"/>
     <mergeCell ref="H13:H16"/>
     <mergeCell ref="H153:H158"/>
@@ -4135,11 +4286,11 @@
     <mergeCell ref="B114:B119"/>
   </mergeCells>
   <dataValidations count="2">
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
+      <formula1>='动作清单'!$A$2:$A$58</formula1>
+    </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>动作清单!$A$2:$A$53</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4152,1692 +4303,1856 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="18.5" customWidth="1" min="1" max="1"/>
-    <col width="23.625" customWidth="1" min="2" max="2"/>
-    <col width="17.5" customWidth="1" min="3" max="3"/>
-    <col width="29.875" customWidth="1" min="4" max="4"/>
-    <col width="25.125" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="78" customWidth="1" min="6" max="6"/>
-    <col width="23.375" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>动作</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>怎么填（示例）</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>会不会改数据</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>属于哪一类</t>
         </is>
       </c>
     </row>
     <row r="2" ht="27" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>回到首页</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr"/>
-      <c r="C2" s="5" t="inlineStr"/>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>自导航到「有问必答」首页信息流（幂等；在二级页/搜索页会先点返回退出），并把筛选 tab 归位到「最新提问」。用例第一步建议都用它</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr"/>
-      <c r="C3" s="5" t="inlineStr"/>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>点底部 tab「我的」，进入用户中心</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
       </c>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>打开积分商城</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>从用户中心点「积分商城」进商城首页（已在则原地不动）。积分商城是二级页，没有底部 tab 栏</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>进学习中心，并切到「专栏」列表</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
       </c>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>切换学习中心顶部栏</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>顶部栏名称（只能填：课程 / 专栏 / 压铸百科）</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
         <is>
           <t>专栏</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>切学习中心顶部那排 tab（切完会验证真的选中了）</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>点返回按钮退回上一页（会校验页面确实变了）</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>点主页按钮</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>点二级页导航栏上的「主页」图标回到首页（需求 713256065 的返回首页那半句）</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>只进搜索页、不输入关键词（搜索页上能看到「搜索历史」和「热门话题」）</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
       </c>
     </row>
     <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>打开案例库列表（底部 tab「设计专区」打开就是它，这是 2026/10/12 才找到的入口；页面顶部还有一排 tab：仿真案例库 / 压铸护航服务）</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40.5" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>打开课程详情</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>课程名</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t>717</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>打开某门课的详情页（学习页）：自己走到 学习中心 → 课程 tab → 按名字点课程。只读：不播放视频、不购买。课程名要跟列表上一字不差，例如 717（「课程名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>① 到达 / 导航</t>
         </is>
       </c>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>输入搜索关键词</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>在当前（搜索页的）搜索框里输入关键词，输入后会读回来校验。要自己在别的页面起步、或者想先把搜索页看清楚再输入时用它 —— 「打开搜索页 → 输入搜索关键词 → 执行搜索」三行，比一条龙更好看懂、也好定位问题。中文也能填（框架遇到中文会临时切到 ADBKeyboard，用完切回你原来的输入法）。只读</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40.5" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>打开搜索并输入</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>点搜索栏进搜索页并输入关键词（输入后会读回来校验）。中文也能填：遇到中文/空格/符号时，框架会自动临时切到手机上的 ADBKeyboard 输入法把它送进去，用完自动切回你原来的输入法（这一步会多花 1~2 秒）。只读</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40.5" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>把已经输入的关键词搜出来（回车；只读：只是查一次）。会验证真的搜起来了：回车后必须看到页面离开「搜索历史」面板，否则报错（先补一下输入框焦点再重试一次）。不执行这一步的话，页面停在「搜索历史」面板，看不到结果页/空态</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40.5" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>点搜索历史里的词</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>词</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t>压铸测试</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>点「搜索历史」里的某个词，直接触发一次搜索。中文关键词搜索就靠它 —— 框架自己敲不了中文（adb 只支持 ASCII），但可以先往搜索历史里插一行中文（用 tools/search_history_tool.py），再点它。点了没搜起来会报错，不会静默放过。只读</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>打开第一个热门话题</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>点搜索页「热门话题」里的第 1 条，跳转到该话题的搜索结果页（需求 713129788）</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>打开第一个帖子</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>在首页信息流点第一张帖子卡片，进帖子详情页（只读：不点赞、不评论）</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>打开第一张专栏</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>在学习中心的专栏列表里点第一张卡，进它的详情页</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>打开第一个案例</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>在案例库列表点开第一张卡片，进案例详情页（只读：不点赞、不收藏、不复制、不评论）</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>打开案例库介绍长图</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="inlineStr"/>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>点案例库首页那张介绍 banner（在分类上方），进「介绍长图详情页」。只读</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40.5" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>打开案例</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>案例名</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>填充任务1</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>按名字点开指定案例（点不到会往下滚几屏再找）。给「付费案例复制」挑样本时用它，例如 填充任务1。只读：不点赞、不收藏、不复制（「案例名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>② 搜索与内容（点进去看，只读）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40.5" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>点文字</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>第几个（可不填）</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>我的（重名时参数2填 2 = 点第 2 个）</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>会（提交/兑换/支付类文字已被默认拦住）</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>按页面上看得见的文字点一下。参数2 可以填「第几个」（留空 = 第 1 个）——文字重名时用它挑，比写选择器省事。提交/兑换/支付这类会改数据的文字被默认禁止（见「填写说明」）</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>③ 通用交互</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40.5" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>范围内点文字</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>范围（选择器）</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>.eco-tab-bar-container / 推荐</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>会（和「点文字」同一道安全阀）</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>在指定的容器里按文字点一下：参数1 = 范围（容器选择器，例如 .eco-tab-bar-container）、参数2 = 要点的文字（例如 推荐）。什么时候用它：同一个词在页面上出现好几处时，用「点文字」只能数「第几个」、容易点错；圈定范围之后就只剩一处。真机实测：首页「推荐」整页命中 2 处（筛选 tab 一处、信息流某张卡片的标题一处），圈到 .eco-tab-bar-container 里只剩 1 处。范围选择器从哪来：python tools/scan_anchors.py --find &lt;关键词&gt;，或 knowledge/前端源码与选择器对照.md。安全阀同「点文字」</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>③ 通用交互</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40.5" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>点选择器</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>第几个（可不填）</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>.search-container（重名时参数2填 2 = 点第 2 个，例如 .hot-topics .inline-flex 第 2 条）</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>会（和「点文字」同一道安全阀）</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>按选择器点一处元素（比按文字点更准：文字有重名时用它），例如 .search-container。参数2 可以填「第几个」（留空 = 第 1 个）——class 重复时用它挑，例如热门话题 5 条标题 class 完全一样</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>③ 通用交互</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="40.5" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="25" ht="40.5" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>滑动</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>方向（可不填）（只能填：上 / 下）</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>最多滑几次（可不填）</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>上（不用填别的；想限制最多滑几次就把数字填到参数2，比如 5）</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>一直滑到页面不动为止（滑到底 / 滚回顶部），不用自己算次数。参数1 = 方向：上（往下翻到底）/ 下（滚回顶部），留空 = 上；参数2 = 最多滑几次（安全上限），留空 = 10 —— 首页那种无限加载的列表滑不到头，靠它兜着</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>③ 通用交互</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="40.5" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>切换首页筛选栏</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>筛选栏名称（只能填：最新提问 / 推荐 / 精选问答 / 我的关注）</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t>推荐</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>切首页信息流那排筛选 tab（切完会验证真的选中了）</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>③ 通用交互</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>等待</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>毫秒</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr"/>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t>2000（= 等 2 秒）</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>③ 通用交互</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="27" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr"/>
-      <c r="C27" s="5" t="inlineStr"/>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>③ 通用交互</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="54" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="29" ht="27" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>打印页面结构</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>范围（只能填：全量 / 只看有文字）</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t>只看有文字</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>把当前页面的元素结构（标签 / class / id + 文字）打进日志：控制台只打前 300 行，完整内容写到 report/dump_&lt;月日_时分秒&gt;.txt（可以在编辑器里搜，适合挑「检查元素存在」的选择器）。参数1 填「只看有文字」时只输出看得见文字的分支（几十行，最省事）。调完把这一行删掉 —— 它是调试用的，不是断言。只读</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>③ 通用交互</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="27" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="30" ht="27" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>检查文字显示</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
         <is>
           <t>答对最多可赢积分</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="27" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="31" ht="40.5" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>检查文字不显示</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t>最新提问（搜索页上不该有）</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>断言页面上看不见这段文字</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="40.5" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="32" ht="27" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>检查文字出现次数</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>期望次数（只能填：1 / 2 / 3 / 4 / 5）</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>收藏 / 1</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="27" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="33" ht="27" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>检查元素存在</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr"/>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
         <is>
           <t>.search-container</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="27" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="34" ht="27" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>检查元素不存在</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr"/>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
         <is>
           <t>.activity-quiz-page</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="27" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="35" ht="27" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>检查元素在视口里</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>选择器</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>.flow-item</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>断言这个元素完整显示在屏幕里（上下左右都在视口内、且有尺寸）。「检查元素存在」只能说明「在 DOM 里」——滚出屏幕的元素依然存在，所以「切了 tab 有没有回到顶部」这类问题只能靠它</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>④ 通用断言（检查「看得见没有」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="27" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>检查元素不在视口里</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>选择器</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>.flow-item</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>断言这个元素已经被滚出屏幕（或只露一角）。和上一条配对用：先证明「确实滚下去了」，再证明「切完 tab 回到顶部了」</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>④ 通用断言（检查「看得见没有」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="27" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>检查元素数量</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>期望数量</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>.hot-topics .inline-flex / 5</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="27" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="38" ht="27" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>检查输入框的值</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>选择器</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>期望值</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>wx-input.search-input / test</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="27" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="39" ht="40.5" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>记住积分余额</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>（不用填参数；之后配一步「检查积分增加」）</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>记住用户现在看到的积分余额（自己先回首页再进积分商城、强制重新取数，读页面上的「当前积分」）。和「检查积分增加」配成一对用：写数据前后各来一次，就能验证「发多少到账多少」。⚠️ 读的是页面上的数（用户看到的），不是库里那个 user.points —— 两者会差一批「还没从中台同步进来的流水」（见 docs/踩坑记录.md 坑 42）。只读</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>④ 通用断言（检查「看得见没有」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="27" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>检查积分增加</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>期望增加（分）</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1021（配合上一步「记住积分余额」；少发/多发/没发都会红）</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>不会</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>读一次当前积分余额，断言它比上一步「记住积分余额」记下的多正好这么多分。例：提交答卷后写 1021 —— 少发、多发、没发都能抓出来。只读（但要先有「记住积分余额」）</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>④ 通用断言（检查「看得见没有」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="27" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr"/>
-      <c r="C36" s="5" t="inlineStr"/>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="27" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="42" ht="27" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>检查首页筛选栏顺序</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr"/>
-      <c r="C37" s="5" t="inlineStr"/>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="27" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="43" ht="40.5" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>检查回到顶部按钮</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr"/>
-      <c r="C38" s="5" t="inlineStr"/>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="40.5" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="44" ht="27" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>检查答题页</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr"/>
-      <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于一道题的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="27" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="45" ht="40.5" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>检查案例库列表</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr"/>
-      <c r="C40" s="5" t="inlineStr"/>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>按需求 713381608 校验案例库列表页：① 分类上方有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「复制图标 + 复制数」，且整页找不到评论图标。只读</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="27" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="46" ht="27" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>检查案例详情页</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr"/>
-      <c r="C41" s="5" t="inlineStr"/>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部没有复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="27" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="47" ht="40.5" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>检查案例库介绍长图</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr"/>
-      <c r="C42" s="5" t="inlineStr"/>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>按需求 713381608 校验介绍长图页：整页是单张图片，而且是长图（图高远大于屏高）。只读</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="40.5" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="48" ht="27" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>检查课程详情页</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr"/>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
         <is>
           <t>课程介绍</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、默认选中填的那个（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="27" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="49" ht="54" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>检查0课时课程不显示</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr"/>
-      <c r="C44" s="5" t="inlineStr"/>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字一个都没出现在小程序的课程列表里（会自己滚到列表底部）。只读</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="40.5" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="50" ht="40.5" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>检查未购买点课时</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>课程名</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr"/>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
         <is>
           <t>7.8课程new</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>按需求 713367615 第 2 条校验：未购买的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号没买过的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="27" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="51" ht="67.5" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr"/>
-      <c r="C46" s="5" t="inlineStr"/>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="40.5" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="52" ht="54" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>逐题作答</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr"/>
-      <c r="C47" s="5" t="inlineStr"/>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>只改前端选中态（不写库、不需要开关）</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、不写库，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="27" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="53" ht="27" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>提交答卷</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="5" t="inlineStr"/>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>会写库（必须开开关）</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>点答题页的提交按钮 —— 会真的写数据。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="54" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="54" ht="67.5" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>复位答题记录</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>活动名</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr"/>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
         <is>
           <t>Z-B4-答题角标</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>会删库（默认只预览；真删要开开关）</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：默认只预览、不删，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="40.5" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>检查答题记录数</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>活动名</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>期望条数</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Z-B4-答题角标 / 1</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>不会</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>读数据库，断言这个活动的提交记录正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="67.5" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>复制当前案例</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr"/>
-      <c r="C51" s="5" t="inlineStr"/>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>会写库（要开开关；没开时记跳过）</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>在案例详情页点「复制案例」—— 一条龙：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → 自动复位（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="54" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>屏蔽礼品分类</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>分类名</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr"/>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
         <is>
           <t>实物商品（跟后台一字不差；跑完记得用「还原礼品分类」改回去）</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>会写库（要开开关）</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>把某个礼品分类改成未启用/屏蔽（只改 gift_category.status），造出「屏蔽分类后礼品不该显示」这个夹具。分类名要跟后台一字不差（重名会被拒绝，那时改用工具 --id）。⚠️ 会写测试库：必须开开关 UITEST_ALLOW_SUBMIT=1；这条用例末尾必须跟一步「还原礼品分类」（owner 2026/10/14：数据改完记得还原）</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="27" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>还原礼品分类</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>分类名</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr"/>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
         <is>
           <t>实物商品（跟「屏蔽礼品分类」里填的那个名字一样）</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>会写库（要开开关）</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>把「屏蔽礼品分类」改回去（status 还原成启用）—— 写链路的收尾步，跟着屏蔽那步成对使用</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="67.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6247,17 +6562,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>名字</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1073,7 +1073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H172"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4162,8 +4162,76 @@
         </is>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ZW_033</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>下拉刷新能重新取数（刷新口径的回归）</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；不用登录（只读：不改任何数据）</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>为什么有这条：owner 2026/10/15 定「需要刷新就刷新」，并让验证下拉刷新到底有没有用。
+实测（2026/10/16）：后台置顶一条帖子 → 只靠一次「下拉刷新」→ 第一条立刻变「置顶 兄弟」（约 1 秒）；取消置顶后再下拉一次 → 立刻摘掉。
+对照（不刷新就是看不到）：置顶之后**不做任何刷新**去读，列表还是旧的 —— 所以这条测试是灵敏的。
+第 2 步的动作自己会验证刷新真的发生了（转圈的点出现又停、容器位置回原位），没触发会重试两次并报错，不会假装成功。</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="D174" t="n">
+        <v>2</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>下拉刷新</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="D175" t="n">
+        <v>3</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>检查元素存在</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>.flow-item</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="D176" t="n">
+        <v>4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="120">
+  <mergeCells count="124">
     <mergeCell ref="A48:A53"/>
     <mergeCell ref="A114:A119"/>
     <mergeCell ref="H99:H103"/>
@@ -4182,6 +4250,7 @@
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="H30:H47"/>
     <mergeCell ref="A17:A20"/>
+    <mergeCell ref="C173:C176"/>
     <mergeCell ref="C60:C63"/>
     <mergeCell ref="C64:C70"/>
     <mergeCell ref="A147:A152"/>
@@ -4205,6 +4274,7 @@
     <mergeCell ref="B17:B20"/>
     <mergeCell ref="C136:C140"/>
     <mergeCell ref="A21:A24"/>
+    <mergeCell ref="H173:H176"/>
     <mergeCell ref="C21:C24"/>
     <mergeCell ref="A89:A94"/>
     <mergeCell ref="H8:H12"/>
@@ -4223,6 +4293,7 @@
     <mergeCell ref="H4:H7"/>
     <mergeCell ref="A110:A113"/>
     <mergeCell ref="H159:H165"/>
+    <mergeCell ref="A173:A176"/>
     <mergeCell ref="A60:A63"/>
     <mergeCell ref="B125:B130"/>
     <mergeCell ref="B2:B3"/>
@@ -4250,6 +4321,7 @@
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="C166:C172"/>
     <mergeCell ref="H25:H29"/>
+    <mergeCell ref="B173:B176"/>
     <mergeCell ref="C125:C130"/>
     <mergeCell ref="A120:A124"/>
     <mergeCell ref="H141:H146"/>
@@ -4287,7 +4359,7 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>='动作清单'!$A$2:$A$58</formula1>
+      <formula1>='动作清单'!$A$2:$A$59</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -4303,7 +4375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5140,18 +5212,14 @@
     <row r="27" ht="27" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>等待</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>毫秒</t>
-        </is>
-      </c>
+          <t>下拉刷新</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2000（= 等 2 秒）</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -5161,7 +5229,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
+          <t>把当前这一页下拉刷新一次（真的重新取数，已真机验证）。什么时候用它：后台改了数据（置顶、开关活动、屏蔽分类…）之后，想让小程序立刻看到 ——改成「等一会儿」没用，要真的重新取数。实测：后台置顶一条帖子 → 一次下拉 → 第一条立刻变「置顶」。它会自己验证刷新真的发生了（转圈出现又停、容器回原位），没触发会重试并报错，不会假装成功。注意：搜索页/帖子详情这类二级页没有下拉刷新（源码里开了的只有 12 个列表页，首页信息流/案例库/学习中心/我的/安全百科等）；这种页面要刷新就返回上一页重进</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -5173,14 +5241,18 @@
     <row r="28" ht="54" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>打印页面文字</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>等待</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>毫秒</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>2000（= 等 2 秒）</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -5190,7 +5262,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
+          <t>纯等待，例如 2000 = 等 2 秒。能不用就不用：先试试用「检查…」类动作替代</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -5202,18 +5274,14 @@
     <row r="29" ht="27" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>打印页面结构</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>范围（只能填：全量 / 只看有文字）</t>
-        </is>
-      </c>
+          <t>打印页面文字</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>只看有文字</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5223,7 +5291,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>把当前页面的元素结构（标签 / class / id + 文字）打进日志：控制台只打前 300 行，完整内容写到 report/dump_&lt;月日_时分秒&gt;.txt（可以在编辑器里搜，适合挑「检查元素存在」的选择器）。参数1 填「只看有文字」时只输出看得见文字的分支（几十行，最省事）。调完把这一行删掉 —— 它是调试用的，不是断言。只读</t>
+          <t>把当前屏幕上看得见的文字打进日志（长文截断）。挑「检查文字显示」该填什么时，先用它看一眼</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -5235,18 +5303,18 @@
     <row r="30" ht="27" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>检查文字显示</t>
+          <t>打印页面结构</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>文字</t>
+          <t>范围（只能填：全量 / 只看有文字）</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>答对最多可赢积分</t>
+          <t>只看有文字</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -5256,19 +5324,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
+          <t>把当前页面的元素结构（标签 / class / id + 文字）打进日志：控制台只打前 300 行，完整内容写到 report/dump_&lt;月日_时分秒&gt;.txt（可以在编辑器里搜，适合挑「检查元素存在」的选择器）。参数1 填「只看有文字」时只输出看得见文字的分支（几十行，最省事）。调完把这一行删掉 —— 它是调试用的，不是断言。只读</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>④ 通用断言（检查「看得见没有」）</t>
+          <t>③ 通用交互</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40.5" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>检查文字不显示</t>
+          <t>检查文字显示</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5279,7 +5347,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>最新提问（搜索页上不该有）</t>
+          <t>答对最多可赢积分</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -5289,7 +5357,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>断言页面上看不见这段文字</t>
+          <t>断言页面上看得见这段文字（会反复重试，默认最多等 8 秒）</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -5301,7 +5369,7 @@
     <row r="32" ht="27" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>检查文字出现次数</t>
+          <t>检查文字不显示</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5309,14 +5377,10 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>期望次数（只能填：1 / 2 / 3 / 4 / 5）</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>收藏 / 1</t>
+          <t>最新提问（搜索页上不该有）</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5326,7 +5390,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
+          <t>断言页面上看不见这段文字</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -5338,18 +5402,22 @@
     <row r="33" ht="27" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>检查元素存在</t>
+          <t>检查文字出现次数</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>选择器</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>期望次数（只能填：1 / 2 / 3 / 4 / 5）</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>.search-container</t>
+          <t>收藏 / 1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5359,7 +5427,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>断言页面上找得到这个选择器，例如 .search-container</t>
+          <t>整页里这段文字被命中几次。注意外层包裹元素也会被算一次，所以数字常比肉眼看到的多</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -5371,7 +5439,7 @@
     <row r="34" ht="27" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>检查元素不存在</t>
+          <t>检查元素存在</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5382,7 +5450,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>.activity-quiz-page</t>
+          <t>.search-container</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -5392,7 +5460,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
+          <t>断言页面上找得到这个选择器，例如 .search-container</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5404,7 +5472,7 @@
     <row r="35" ht="27" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>检查元素在视口里</t>
+          <t>检查元素不存在</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5415,7 +5483,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>.flow-item</t>
+          <t>.activity-quiz-page</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -5425,7 +5493,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>断言这个元素完整显示在屏幕里（上下左右都在视口内、且有尺寸）。「检查元素存在」只能说明「在 DOM 里」——滚出屏幕的元素依然存在，所以「切了 tab 有没有回到顶部」这类问题只能靠它</t>
+          <t>断言这个选择器一个都命中不到（例如首页上不该出现 .activity-quiz-page）。它等的是「消失」，本来就不在时会立刻通过</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5437,7 +5505,7 @@
     <row r="36" ht="27" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>检查元素不在视口里</t>
+          <t>检查元素在视口里</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5458,7 +5526,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>断言这个元素已经被滚出屏幕（或只露一角）。和上一条配对用：先证明「确实滚下去了」，再证明「切完 tab 回到顶部了」</t>
+          <t>断言这个元素完整显示在屏幕里（上下左右都在视口内、且有尺寸）。「检查元素存在」只能说明「在 DOM 里」——滚出屏幕的元素依然存在，所以「切了 tab 有没有回到顶部」这类问题只能靠它</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5470,7 +5538,7 @@
     <row r="37" ht="27" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>检查元素数量</t>
+          <t>检查元素不在视口里</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5478,14 +5546,10 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>期望数量</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>.hot-topics .inline-flex / 5</t>
+          <t>.flow-item</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5495,7 +5559,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
+          <t>断言这个元素已经被滚出屏幕（或只露一角）。和上一条配对用：先证明「确实滚下去了」，再证明「切完 tab 回到顶部了」</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5507,7 +5571,7 @@
     <row r="38" ht="27" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>检查输入框的值</t>
+          <t>检查元素数量</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5517,12 +5581,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>期望值</t>
+          <t>期望数量</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>wx-input.search-input / test</t>
+          <t>.hot-topics .inline-flex / 5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5532,7 +5596,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
+          <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5544,14 +5608,22 @@
     <row r="39" ht="40.5" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>记住积分余额</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
+          <t>检查输入框的值</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>选择器</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>期望值</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>（不用填参数；之后配一步「检查积分增加」）</t>
+          <t>wx-input.search-input / test</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5561,7 +5633,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>记住用户现在看到的积分余额（自己先回首页再进积分商城、强制重新取数，读页面上的「当前积分」）。和「检查积分增加」配成一对用：写数据前后各来一次，就能验证「发多少到账多少」。⚠️ 读的是页面上的数（用户看到的），不是库里那个 user.points —— 两者会差一批「还没从中台同步进来的流水」（见 docs/踩坑记录.md 坑 42）。只读</t>
+          <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5573,18 +5645,14 @@
     <row r="40" ht="27" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>检查积分增加</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>期望增加（分）</t>
-        </is>
-      </c>
+          <t>记住积分余额</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1021（配合上一步「记住积分余额」；少发/多发/没发都会红）</t>
+          <t>（不用填参数；之后配一步「检查积分增加」）</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5594,7 +5662,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>读一次当前积分余额，断言它比上一步「记住积分余额」记下的多正好这么多分。例：提交答卷后写 1021 —— 少发、多发、没发都能抓出来。只读（但要先有「记住积分余额」）</t>
+          <t>记住用户现在看到的积分余额（自己先回首页再进积分商城、强制重新取数，读页面上的「当前积分」）。和「检查积分增加」配成一对用：写数据前后各来一次，就能验证「发多少到账多少」。⚠️ 读的是页面上的数（用户看到的），不是库里那个 user.points —— 两者会差一批「还没从中台同步进来的流水」（见 docs/踩坑记录.md 坑 42）。只读</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5606,14 +5674,18 @@
     <row r="41" ht="27" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>检查活动入口</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>检查积分增加</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>期望增加（分）</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>1021（配合上一步「记住积分余额」；少发/多发/没发都会红）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5623,19 +5695,19 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
+          <t>读一次当前积分余额，断言它比上一步「记住积分余额」记下的多正好这么多分。例：提交答卷后写 1021 —— 少发、多发、没发都能抓出来。只读（但要先有「记住积分余额」）</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>⑤ 需求专项检查</t>
+          <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="27" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>检查首页筛选栏顺序</t>
+          <t>检查活动入口</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -5652,7 +5724,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
+          <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5664,7 +5736,7 @@
     <row r="43" ht="40.5" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>检查回到顶部按钮</t>
+          <t>检查首页筛选栏顺序</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -5681,7 +5753,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
+          <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5693,7 +5765,7 @@
     <row r="44" ht="27" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>检查答题页</t>
+          <t>检查回到顶部按钮</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -5710,7 +5782,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于一道题的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
+          <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5722,7 +5794,7 @@
     <row r="45" ht="40.5" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>检查案例库列表</t>
+          <t>检查答题页</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -5739,7 +5811,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验案例库列表页：① 分类上方有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「复制图标 + 复制数」，且整页找不到评论图标。只读</t>
+          <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于一道题的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5751,7 +5823,7 @@
     <row r="46" ht="27" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>检查案例详情页</t>
+          <t>检查案例库列表</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -5768,7 +5840,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部没有复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
+          <t>按需求 713381608 校验案例库列表页：① 分类上方有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「复制图标 + 复制数」，且整页找不到评论图标。只读</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5780,7 +5852,7 @@
     <row r="47" ht="40.5" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>检查案例库介绍长图</t>
+          <t>检查案例详情页</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -5797,7 +5869,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验介绍长图页：整页是单张图片，而且是长图（图高远大于屏高）。只读</t>
+          <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部没有复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5809,18 +5881,14 @@
     <row r="48" ht="27" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>检查课程详情页</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
-        </is>
-      </c>
+          <t>检查案例库介绍长图</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>课程介绍</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5830,7 +5898,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、默认选中填的那个（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
+          <t>按需求 713381608 校验介绍长图页：整页是单张图片，而且是长图（图高远大于屏高）。只读</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5842,14 +5910,18 @@
     <row r="49" ht="54" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>检查0课时课程不显示</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>检查课程详情页</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>课程介绍</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5859,7 +5931,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字一个都没出现在小程序的课程列表里（会自己滚到列表底部）。只读</t>
+          <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、默认选中填的那个（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5871,18 +5943,14 @@
     <row r="50" ht="40.5" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>检查未购买点课时</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>课程名</t>
-        </is>
-      </c>
+          <t>检查0课时课程不显示</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>7.8课程new</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5892,7 +5960,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>按需求 713367615 第 2 条校验：未购买的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号没买过的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
+          <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字一个都没出现在小程序的课程列表里（会自己滚到列表底部）。只读</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5904,14 +5972,18 @@
     <row r="51" ht="67.5" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>打开答题活动</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>检查未购买点课时</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>课程名</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>7.8课程new</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5921,19 +5993,19 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
+          <t>按需求 713367615 第 2 条校验：未购买的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号没买过的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+          <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
     <row r="52" ht="54" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>逐题作答</t>
+          <t>打开答题活动</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -5945,12 +6017,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>只改前端选中态（不写库、不需要开关）</t>
+          <t>不会</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、不写库，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
+          <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5962,7 +6034,7 @@
     <row r="53" ht="27" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>提交答卷</t>
+          <t>逐题作答</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -5974,12 +6046,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>会写库（必须开开关）</t>
+          <t>只改前端选中态（不写库、不需要开关）</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>点答题页的提交按钮 —— 会真的写数据。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
+          <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、不写库，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5991,28 +6063,24 @@
     <row r="54" ht="67.5" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>复位答题记录</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>活动名</t>
-        </is>
-      </c>
+          <t>提交答卷</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Z-B4-答题角标</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>会删库（默认只预览；真删要开开关）</t>
+          <t>会写库（必须开开关）</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：默认只预览、不删，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+          <t>点答题页的提交按钮 —— 会真的写数据。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -6024,7 +6092,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>检查答题记录数</t>
+          <t>复位答题记录</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6032,24 +6100,20 @@
           <t>活动名</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>期望条数</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Z-B4-答题角标 / 1</t>
+          <t>Z-B4-答题角标</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>不会</t>
+          <t>会删库（默认只预览；真删要开开关）</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>读数据库，断言这个活动的提交记录正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+          <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：默认只预览、不删，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6061,24 +6125,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>复制当前案例</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
+          <t>检查答题记录数</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>活动名</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>期望条数</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>Z-B4-答题角标 / 1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>会写库（要开开关；没开时记跳过）</t>
+          <t>不会</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>在案例详情页点「复制案例」—— 一条龙：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → 自动复位（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
+          <t>读数据库，断言这个活动的提交记录正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -6090,28 +6162,24 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>屏蔽礼品分类</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>分类名</t>
-        </is>
-      </c>
+          <t>复制当前案例</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>实物商品（跟后台一字不差；跑完记得用「还原礼品分类」改回去）</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>会写库（要开开关）</t>
+          <t>会写库（要开开关；没开时记跳过）</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>把某个礼品分类改成未启用/屏蔽（只改 gift_category.status），造出「屏蔽分类后礼品不该显示」这个夹具。分类名要跟后台一字不差（重名会被拒绝，那时改用工具 --id）。⚠️ 会写测试库：必须开开关 UITEST_ALLOW_SUBMIT=1；这条用例末尾必须跟一步「还原礼品分类」（owner 2026/10/14：数据改完记得还原）</t>
+          <t>在案例详情页点「复制案例」—— 一条龙：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → 自动复位（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6123,7 +6191,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>还原礼品分类</t>
+          <t>屏蔽礼品分类</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6134,20 +6202,53 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
+          <t>实物商品（跟后台一字不差；跑完记得用「还原礼品分类」改回去）</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>会写库（要开开关）</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>把某个礼品分类改成未启用/屏蔽（只改 gift_category.status），造出「屏蔽分类后礼品不该显示」这个夹具。分类名要跟后台一字不差（重名会被拒绝，那时改用工具 --id）。⚠️ 会写测试库：必须开开关 UITEST_ALLOW_SUBMIT=1；这条用例末尾必须跟一步「还原礼品分类」（owner 2026/10/14：数据改完记得还原）</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>还原礼品分类</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>分类名</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
           <t>实物商品（跟「屏蔽礼品分类」里填的那个名字一样）</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>会写库（要开开关）</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>把「屏蔽礼品分类」改回去（status 还原成启用）—— 写链路的收尾步，跟着屏蔽那步成对使用</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1073,7 +1073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H176"/>
+  <dimension ref="A1:H183"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4230,8 +4230,123 @@
         </is>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ZW_034</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>案例详情页显示「案例标签 / 案例简介」（缺陷 713587133）</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；不用登录（只读）。案例库首屏往后能翻到案例「亲亲」</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>缺陷 713587133（原文：案例详情中缺少显示案例描述信息）。
+源码锚点 src/packageA/pages/case-detail/index.tsx：.meta-block-tags-intro 里两块 ——
+  · 「案例标签：{tags}」·「案例简介：{introduction}」；
+  · **条件渲染**：tags 和 introduction 都为空时整块不显示 —— 所以挑了「有简介」的案例当样本。
+样本（2026/10/16 只读查库）：案例 id=90「亲亲」，introduction='去'、tags='电子与通信'，status=1（上架）。
+第 4 步先证明那块在；第 5-6 步对内容（**文案口径来自库里那两列**；样例数据改了就把这两格一起改）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="D178" t="n">
+        <v>2</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="D179" t="n">
+        <v>3</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>打开案例</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>亲亲</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="D180" t="n">
+        <v>4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>检查元素存在</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>.meta-block-tags-intro</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="D181" t="n">
+        <v>5</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>案例简介：去</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="D182" t="n">
+        <v>6</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>案例标签：电子与通信</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="D183" t="n">
+        <v>7</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="124">
+  <mergeCells count="128">
     <mergeCell ref="A48:A53"/>
     <mergeCell ref="A114:A119"/>
     <mergeCell ref="H99:H103"/>
@@ -4244,8 +4359,8 @@
     <mergeCell ref="C54:C59"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A159:A165"/>
+    <mergeCell ref="C2:C3"/>
     <mergeCell ref="C159:C165"/>
-    <mergeCell ref="C2:C3"/>
     <mergeCell ref="H110:H113"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="H30:H47"/>
@@ -4256,8 +4371,8 @@
     <mergeCell ref="A147:A152"/>
     <mergeCell ref="B95:B98"/>
     <mergeCell ref="B8:B12"/>
+    <mergeCell ref="H48:H53"/>
     <mergeCell ref="H104:H109"/>
-    <mergeCell ref="H48:H53"/>
     <mergeCell ref="A99:A103"/>
     <mergeCell ref="H64:H70"/>
     <mergeCell ref="B136:B140"/>
@@ -4268,6 +4383,7 @@
     <mergeCell ref="H131:H135"/>
     <mergeCell ref="H147:H152"/>
     <mergeCell ref="H54:H59"/>
+    <mergeCell ref="B177:B183"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="B71:B76"/>
     <mergeCell ref="C4:C7"/>
@@ -4286,8 +4402,8 @@
     <mergeCell ref="C95:C98"/>
     <mergeCell ref="A30:A47"/>
     <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C48:C53"/>
     <mergeCell ref="B110:B113"/>
-    <mergeCell ref="C48:C53"/>
     <mergeCell ref="C120:C124"/>
     <mergeCell ref="B141:B146"/>
     <mergeCell ref="H4:H7"/>
@@ -4315,14 +4431,16 @@
     <mergeCell ref="A104:A109"/>
     <mergeCell ref="B159:B165"/>
     <mergeCell ref="A166:A172"/>
-    <mergeCell ref="C13:C16"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="A4:A7"/>
+    <mergeCell ref="C13:C16"/>
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="C166:C172"/>
     <mergeCell ref="H25:H29"/>
     <mergeCell ref="B173:B176"/>
     <mergeCell ref="C125:C130"/>
+    <mergeCell ref="A177:A183"/>
+    <mergeCell ref="C177:C183"/>
     <mergeCell ref="A120:A124"/>
     <mergeCell ref="H141:H146"/>
     <mergeCell ref="A80:A88"/>
@@ -4348,6 +4466,7 @@
     <mergeCell ref="C110:C113"/>
     <mergeCell ref="B120:B124"/>
     <mergeCell ref="A141:A146"/>
+    <mergeCell ref="H177:H183"/>
     <mergeCell ref="B89:B94"/>
     <mergeCell ref="A25:A29"/>
     <mergeCell ref="C25:C29"/>
@@ -4430,8 +4549,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4459,8 +4576,6 @@
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4488,8 +4603,6 @@
           <t>打开积分商城</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4517,8 +4630,6 @@
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4551,7 +4662,6 @@
           <t>顶部栏名称（只能填：课程 / 专栏 / 压铸百科）</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>专栏</t>
@@ -4579,8 +4689,6 @@
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4608,8 +4716,6 @@
           <t>点主页按钮</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4637,8 +4743,6 @@
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4666,8 +4770,6 @@
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4700,7 +4802,6 @@
           <t>课程名</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>717</t>
@@ -4733,7 +4834,6 @@
           <t>关键词</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -4766,7 +4866,6 @@
           <t>关键词</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -4794,8 +4893,6 @@
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4828,7 +4925,6 @@
           <t>词</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>压铸测试</t>
@@ -4856,8 +4952,6 @@
           <t>打开第一个热门话题</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4885,8 +4979,6 @@
           <t>打开第一个帖子</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4914,8 +5006,6 @@
           <t>打开第一张专栏</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4943,8 +5033,6 @@
           <t>打开第一个案例</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4972,8 +5060,6 @@
           <t>打开案例库介绍长图</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5006,7 +5092,6 @@
           <t>案例名</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>填充任务1</t>
@@ -5187,7 +5272,6 @@
           <t>筛选栏名称（只能填：最新提问 / 推荐 / 精选问答 / 我的关注）</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>推荐</t>
@@ -5215,8 +5299,6 @@
           <t>下拉刷新</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5249,7 +5331,6 @@
           <t>毫秒</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>2000（= 等 2 秒）</t>
@@ -5277,8 +5358,6 @@
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5311,7 +5390,6 @@
           <t>范围（只能填：全量 / 只看有文字）</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>只看有文字</t>
@@ -5344,7 +5422,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>答对最多可赢积分</t>
@@ -5377,7 +5454,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>最新提问（搜索页上不该有）</t>
@@ -5447,7 +5523,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>.search-container</t>
@@ -5480,7 +5555,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>.activity-quiz-page</t>
@@ -5513,7 +5587,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>.flow-item</t>
@@ -5546,7 +5619,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>.flow-item</t>
@@ -5648,8 +5720,6 @@
           <t>记住积分余额</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>（不用填参数；之后配一步「检查积分增加」）</t>
@@ -5682,7 +5752,6 @@
           <t>期望增加（分）</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>1021（配合上一步「记住积分余额」；少发/多发/没发都会红）</t>
@@ -5710,8 +5779,6 @@
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5739,8 +5806,6 @@
           <t>检查首页筛选栏顺序</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5768,8 +5833,6 @@
           <t>检查回到顶部按钮</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5797,8 +5860,6 @@
           <t>检查答题页</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5826,8 +5887,6 @@
           <t>检查案例库列表</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5855,8 +5914,6 @@
           <t>检查案例详情页</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5884,8 +5941,6 @@
           <t>检查案例库介绍长图</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5918,7 +5973,6 @@
           <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>课程介绍</t>
@@ -5946,8 +6000,6 @@
           <t>检查0课时课程不显示</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5980,7 +6032,6 @@
           <t>课程名</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>7.8课程new</t>
@@ -6008,8 +6059,6 @@
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6037,8 +6086,6 @@
           <t>逐题作答</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6066,8 +6113,6 @@
           <t>提交答卷</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6100,7 +6145,6 @@
           <t>活动名</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>Z-B4-答题角标</t>
@@ -6165,8 +6209,6 @@
           <t>复制当前案例</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6199,7 +6241,6 @@
           <t>分类名</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>实物商品（跟后台一字不差；跑完记得用「还原礼品分类」改回去）</t>
@@ -6232,7 +6273,6 @@
           <t>分类名</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>实物商品（跟「屏蔽礼品分类」里填的那个名字一样）</t>
@@ -8288,7 +8328,6 @@
           <t>方案一变形</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8301,7 +8340,6 @@
           <t>仅凝固</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8314,7 +8352,6 @@
           <t>仅充填2</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8327,7 +8364,6 @@
           <t>充填凝固应力</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8340,7 +8376,6 @@
           <t>充填凝固应力1</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8353,7 +8388,6 @@
           <t>7201744-孙</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8366,7 +8400,6 @@
           <t>带组织性能结果</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8379,7 +8412,6 @@
           <t>充填-排气</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8392,7 +8424,6 @@
           <t>1月 20250115</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8405,7 +8436,6 @@
           <t>紫色1</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8418,7 +8448,6 @@
           <t>内部数据6</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8431,7 +8460,6 @@
           <t>1QQ区qqqqq</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8444,7 +8472,6 @@
           <t>重力铸造-重力砂型-0602-163625-仅充填仅浏览-重力铸造-重力砂型-0602-163625</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8457,7 +8484,6 @@
           <t>重力铸造-重力砂型-0602-163625-充填凝固0602_165141-仅浏览</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8470,7 +8496,6 @@
           <t>COPY3</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8483,7 +8508,6 @@
           <t>3月26测试 私有材料分享(copy)</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8496,7 +8520,6 @@
           <t>内部数据-虚拟模具</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8509,7 +8532,6 @@
           <t>内部数据</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8522,7 +8544,6 @@
           <t>鹅鹅鹅</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8535,7 +8556,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8548,7 +8568,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8561,7 +8580,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8574,7 +8592,6 @@
           <t>仅凝固+应力-选择点2</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8587,7 +8604,6 @@
           <t>仅凝固1</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8600,7 +8616,6 @@
           <t>循环凝固</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8613,7 +8628,6 @@
           <t>131231</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8626,7 +8640,6 @@
           <t>131231</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8639,7 +8652,6 @@
           <t>循环凝固-热循环</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8652,7 +8664,6 @@
           <t>6668</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8665,7 +8676,6 @@
           <t>6668</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8678,7 +8688,6 @@
           <t>填充任务1</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8691,7 +8700,6 @@
           <t>0605测试</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8704,7 +8712,6 @@
           <t>循环凝固+应力+选点1</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8717,7 +8724,6 @@
           <t>料筒(copy)</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8730,7 +8736,6 @@
           <t>仅凝固</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8743,7 +8748,6 @@
           <t>#713392277</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8756,7 +8760,6 @@
           <t>？？？？</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8769,7 +8772,6 @@
           <t>复制任务失败问题测试-分享</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8782,7 +8784,6 @@
           <t>浇口充填-高级模式</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8795,7 +8796,6 @@
           <t>4.17</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8808,7 +8808,6 @@
           <t>热热热热</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8821,7 +8820,6 @@
           <t>eeee</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8834,7 +8832,6 @@
           <t>亲亲</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8847,7 +8844,6 @@
           <t>3333 私有曲线</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8860,7 +8856,6 @@
           <t>v2</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8873,7 +8868,6 @@
           <t>111111</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8886,7 +8880,6 @@
           <t>测试二级页面案例111111111111111111111111111</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8899,7 +8892,6 @@
           <t>分享高压 2</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8912,7 +8904,6 @@
           <t>料筒充填</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8925,7 +8916,6 @@
           <t>料筒充填1</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8938,7 +8928,6 @@
           <t>料筒分享</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8951,7 +8940,6 @@
           <t>1WWWW</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8964,7 +8952,6 @@
           <t>凝固应力</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8977,7 +8964,6 @@
           <t>模拟汽车</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8990,7 +8976,6 @@
           <t>模拟汽车减震</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9003,7 +8988,6 @@
           <t>多浇口充填(粒子数量10)</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9011,7 +8995,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
           <t>课程那张表里的「我们账号买没买」按 user_id=1966910（config/env.yaml）判断</t>
@@ -9024,7 +9007,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
           <t>注意：这些课程名在库里有多门同名，按名字打开只会命中第一门 —— 012345678901234567890123456789、付费课程1、免费课程、免费课程1、无敌贵的课程、测试封面图、测试封面图-修改、测试验证课时bug</t>
@@ -9037,7 +9019,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
           <t>案例共 56 条，已全部列出</t>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1073,7 +1073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4345,8 +4345,88 @@
         </is>
       </c>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>ZW_035</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>案例库列表的复制数与库里对得上（缺陷 713453275）</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；不用登录（只读）。**需要能连上测试库**（连不上记跳过，不算失败）</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>第 3 步先下拉刷新：**列表可能是旧的**（打开案例库是幂等的，已经在那一页就不会重新取数，坑 43/49/53），拿旧列表跟库对账等于白对。刷新完再比，比的是「这一屏真实显示的数」。
+第 3 步先下拉刷新：**列表可能是旧的**（打开案例库是幂等的，已经在那一页就不会重新取数，坑 43/49/53），拿旧列表跟库对账等于白对。刷新完再比，比的是「这一屏真实显示的数」。
+缺陷 713453275（原文：复制数的查看无数据返回）。
+为什么要跟库对账：源码 src/components/case-list/index.tsx 里写的是 `copyCount ?? 0` ——**永远有个数字**，所以「卡片上有没有数字」这种断言是**假绿**（缺陷回归清单里提醒过）。
+第 4 步拿库里（上架未删）每条案例的 copy_count 跟卡片上显示的数逐张比；库里重名的案例自动跳过（无法确定卡片对的是哪一条），一张都比不了就报错、不当通过。
+工具：tools/case_copy_counts.py（只读，SELECT）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="D185" t="n">
+        <v>2</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="D186" t="n">
+        <v>3</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>下拉刷新</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="D187" t="n">
+        <v>4</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>检查案例库复制数对账</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="D188" t="n">
+        <v>5</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="128">
+  <mergeCells count="132">
     <mergeCell ref="A48:A53"/>
     <mergeCell ref="A114:A119"/>
     <mergeCell ref="H99:H103"/>
@@ -4396,6 +4476,7 @@
     <mergeCell ref="H8:H12"/>
     <mergeCell ref="B60:B63"/>
     <mergeCell ref="B25:B29"/>
+    <mergeCell ref="C184:C188"/>
     <mergeCell ref="A64:A70"/>
     <mergeCell ref="C153:C158"/>
     <mergeCell ref="H95:H98"/>
@@ -4421,6 +4502,7 @@
     <mergeCell ref="H80:H88"/>
     <mergeCell ref="B48:B53"/>
     <mergeCell ref="B64:B70"/>
+    <mergeCell ref="H184:H188"/>
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="B80:B88"/>
     <mergeCell ref="B131:B135"/>
@@ -4447,6 +4529,7 @@
     <mergeCell ref="C80:C88"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="C8:C12"/>
+    <mergeCell ref="A184:A188"/>
     <mergeCell ref="B21:B24"/>
     <mergeCell ref="H125:H130"/>
     <mergeCell ref="B99:B103"/>
@@ -4463,6 +4546,7 @@
     <mergeCell ref="C17:C20"/>
     <mergeCell ref="H13:H16"/>
     <mergeCell ref="H153:H158"/>
+    <mergeCell ref="B184:B188"/>
     <mergeCell ref="C110:C113"/>
     <mergeCell ref="B120:B124"/>
     <mergeCell ref="A141:A146"/>
@@ -4478,7 +4562,7 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>='动作清单'!$A$2:$A$59</formula1>
+      <formula1>='动作清单'!$A$2:$A$60</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -4494,7 +4578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5911,12 +5995,17 @@
     <row r="47" ht="40.5" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>检查案例详情页</t>
+          <t>检查案例库复制数对账</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>最多比几张（可不填）</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5926,7 +6015,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部没有复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
+          <t>缺陷 713453275「复制数的查看无数据返回」的回归断言：卡片上显示的复制数，必须等于库里那条案例的 copy_count（参数1 填最多比几张，留空 = 3）。为什么要这么较真：源码里是 copyCount ?? 0，永远有个数字 ——所以「卡片上有数字」这种断言是假绿。库里重名的案例会自动跳过（无法确定对哪一条）。连不上库时记「跳过」并说明原因，不会硬判通过。只读</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5938,7 +6027,7 @@
     <row r="48" ht="27" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>检查案例库介绍长图</t>
+          <t>检查案例详情页</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5953,7 +6042,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验介绍长图页：整页是单张图片，而且是长图（图高远大于屏高）。只读</t>
+          <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部没有复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5965,17 +6054,12 @@
     <row r="49" ht="54" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>检查课程详情页</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
+          <t>检查案例库介绍长图</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>课程介绍</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5985,7 +6069,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、默认选中填的那个（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
+          <t>按需求 713381608 校验介绍长图页：整页是单张图片，而且是长图（图高远大于屏高）。只读</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5997,12 +6081,17 @@
     <row r="50" ht="40.5" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>检查0课时课程不显示</t>
+          <t>检查课程详情页</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>课程介绍</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6012,7 +6101,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字一个都没出现在小程序的课程列表里（会自己滚到列表底部）。只读</t>
+          <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、默认选中填的那个（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -6024,17 +6113,12 @@
     <row r="51" ht="67.5" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>检查未购买点课时</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>课程名</t>
+          <t>检查0课时课程不显示</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7.8课程new</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6044,7 +6128,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>按需求 713367615 第 2 条校验：未购买的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号没买过的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
+          <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字一个都没出现在小程序的课程列表里（会自己滚到列表底部）。只读</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -6056,12 +6140,17 @@
     <row r="52" ht="54" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>打开答题活动</t>
+          <t>检查未购买点课时</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>课程名</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>7.8课程new</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6071,19 +6160,19 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
+          <t>按需求 713367615 第 2 条校验：未购买的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号没买过的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+          <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
     <row r="53" ht="27" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>逐题作答</t>
+          <t>打开答题活动</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6093,12 +6182,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>只改前端选中态（不写库、不需要开关）</t>
+          <t>不会</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、不写库，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
+          <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -6110,7 +6199,7 @@
     <row r="54" ht="67.5" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>提交答卷</t>
+          <t>逐题作答</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6120,12 +6209,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>会写库（必须开开关）</t>
+          <t>只改前端选中态（不写库、不需要开关）</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>点答题页的提交按钮 —— 会真的写数据。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
+          <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、不写库，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -6137,27 +6226,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>复位答题记录</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>活动名</t>
+          <t>提交答卷</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Z-B4-答题角标</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>会删库（默认只预览；真删要开开关）</t>
+          <t>会写库（必须开开关）</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：默认只预览、不删，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+          <t>点答题页的提交按钮 —— 会真的写数据。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6169,7 +6253,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>检查答题记录数</t>
+          <t>复位答题记录</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6177,24 +6261,19 @@
           <t>活动名</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>期望条数</t>
-        </is>
-      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Z-B4-答题角标 / 1</t>
+          <t>Z-B4-答题角标</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>不会</t>
+          <t>会删库（默认只预览；真删要开开关）</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>读数据库，断言这个活动的提交记录正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+          <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：默认只预览、不删，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -6206,22 +6285,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>复制当前案例</t>
+          <t>检查答题记录数</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>活动名</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>期望条数</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>Z-B4-答题角标 / 1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>会写库（要开开关；没开时记跳过）</t>
+          <t>不会</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>在案例详情页点「复制案例」—— 一条龙：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → 自动复位（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
+          <t>读数据库，断言这个活动的提交记录正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6233,27 +6322,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>屏蔽礼品分类</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>分类名</t>
+          <t>复制当前案例</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>实物商品（跟后台一字不差；跑完记得用「还原礼品分类」改回去）</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>会写库（要开开关）</t>
+          <t>会写库（要开开关；没开时记跳过）</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>把某个礼品分类改成未启用/屏蔽（只改 gift_category.status），造出「屏蔽分类后礼品不该显示」这个夹具。分类名要跟后台一字不差（重名会被拒绝，那时改用工具 --id）。⚠️ 会写测试库：必须开开关 UITEST_ALLOW_SUBMIT=1；这条用例末尾必须跟一步「还原礼品分类」（owner 2026/10/14：数据改完记得还原）</t>
+          <t>在案例详情页点「复制案例」—— 一条龙：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → 自动复位（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6265,30 +6349,62 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>屏蔽礼品分类</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>分类名</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>实物商品（跟后台一字不差；跑完记得用「还原礼品分类」改回去）</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>会写库（要开开关）</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>把某个礼品分类改成未启用/屏蔽（只改 gift_category.status），造出「屏蔽分类后礼品不该显示」这个夹具。分类名要跟后台一字不差（重名会被拒绝，那时改用工具 --id）。⚠️ 会写测试库：必须开开关 UITEST_ALLOW_SUBMIT=1；这条用例末尾必须跟一步「还原礼品分类」（owner 2026/10/14：数据改完记得还原）</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>还原礼品分类</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>分类名</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>实物商品（跟「屏蔽礼品分类」里填的那个名字一样）</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>会写库（要开开关）</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>把「屏蔽礼品分类」改回去（status 还原成启用）—— 写链路的收尾步，跟着屏蔽那步成对使用</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1073,7 +1073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H192"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4425,8 +4425,81 @@
         </is>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>ZW_036</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>案例库卡片标题最多两行（新动作「检查元素行数」的回归）</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；不用登录（只读）</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>为什么有这条：缺陷 713587136「案例介绍卡片中案例描述显示的行数错误（应该 1 行、实际两行）」要的判据就是「这个文字元素渲染了几行」—— 2026/10/16 把能力补上了（动作「检查元素行数」）。
+样本与口径：案例库卡片标题 .case-list-card-title，源码 components/case-list/index.tsx 里写着`numberOfLines={2}` —— **最多两行**；实测一屏 10 张标题都是 1 行（高 16 / 行高 16），拿它验证「没超过 2 行」是稳的，也能挡住「标题失控换行到三行」这种版面回归。
+量法：把元素内容包进 Range，按「行的顶边」去重后数矩形个数（不依赖 line-height —— 真机上很多元素的 line-height 是 normal，除法会崩；直接数矩形又会被「元素框+文本节点」数成双份）。
+护航那片（.escort-case-desc）是这条缺陷的原始元素，但测试环境没配内容，等数据到位再补。</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="D190" t="n">
+        <v>2</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="D191" t="n">
+        <v>3</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>检查元素行数</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>.case-list-card-title</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="D192" t="n">
+        <v>4</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="132">
+  <mergeCells count="136">
     <mergeCell ref="A48:A53"/>
     <mergeCell ref="A114:A119"/>
     <mergeCell ref="H99:H103"/>
@@ -4439,9 +4512,10 @@
     <mergeCell ref="C54:C59"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A159:A165"/>
+    <mergeCell ref="C159:C165"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C159:C165"/>
     <mergeCell ref="H110:H113"/>
+    <mergeCell ref="A189:A192"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="H30:H47"/>
     <mergeCell ref="A17:A20"/>
@@ -4451,8 +4525,8 @@
     <mergeCell ref="A147:A152"/>
     <mergeCell ref="B95:B98"/>
     <mergeCell ref="B8:B12"/>
+    <mergeCell ref="H104:H109"/>
     <mergeCell ref="H48:H53"/>
-    <mergeCell ref="H104:H109"/>
     <mergeCell ref="A99:A103"/>
     <mergeCell ref="H64:H70"/>
     <mergeCell ref="B136:B140"/>
@@ -4483,8 +4557,9 @@
     <mergeCell ref="C95:C98"/>
     <mergeCell ref="A30:A47"/>
     <mergeCell ref="B4:B7"/>
+    <mergeCell ref="B110:B113"/>
     <mergeCell ref="C48:C53"/>
-    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="C189:C192"/>
     <mergeCell ref="C120:C124"/>
     <mergeCell ref="B141:B146"/>
     <mergeCell ref="H4:H7"/>
@@ -4512,12 +4587,14 @@
     <mergeCell ref="C30:C47"/>
     <mergeCell ref="A104:A109"/>
     <mergeCell ref="B159:B165"/>
+    <mergeCell ref="H189:H192"/>
     <mergeCell ref="A166:A172"/>
+    <mergeCell ref="C13:C16"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="C13:C16"/>
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="C166:C172"/>
+    <mergeCell ref="B189:B192"/>
     <mergeCell ref="H25:H29"/>
     <mergeCell ref="B173:B176"/>
     <mergeCell ref="C125:C130"/>
@@ -4528,8 +4605,8 @@
     <mergeCell ref="A80:A88"/>
     <mergeCell ref="C80:C88"/>
     <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A184:A188"/>
     <mergeCell ref="C8:C12"/>
-    <mergeCell ref="A184:A188"/>
     <mergeCell ref="B21:B24"/>
     <mergeCell ref="H125:H130"/>
     <mergeCell ref="B99:B103"/>
@@ -4562,7 +4639,7 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
-      <formula1>='动作清单'!$A$2:$A$60</formula1>
+      <formula1>='动作清单'!$A$2:$A$61</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -4578,7 +4655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4633,6 +4710,8 @@
           <t>回到首页</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4660,6 +4739,8 @@
           <t>切到用户中心</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4687,6 +4768,8 @@
           <t>打开积分商城</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4714,6 +4797,8 @@
           <t>打开学习中心专栏</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4746,6 +4831,7 @@
           <t>顶部栏名称（只能填：课程 / 专栏 / 压铸百科）</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>专栏</t>
@@ -4773,6 +4859,8 @@
           <t>返回上一页</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4800,6 +4888,8 @@
           <t>点主页按钮</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4827,6 +4917,8 @@
           <t>打开搜索页</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4854,6 +4946,8 @@
           <t>打开案例库</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4886,6 +4980,7 @@
           <t>课程名</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>717</t>
@@ -4918,6 +5013,7 @@
           <t>关键词</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -4950,6 +5046,7 @@
           <t>关键词</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -4977,6 +5074,8 @@
           <t>执行搜索</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5009,6 +5108,7 @@
           <t>词</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>压铸测试</t>
@@ -5036,6 +5136,8 @@
           <t>打开第一个热门话题</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5063,6 +5165,8 @@
           <t>打开第一个帖子</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5090,6 +5194,8 @@
           <t>打开第一张专栏</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5117,6 +5223,8 @@
           <t>打开第一个案例</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5144,6 +5252,8 @@
           <t>打开案例库介绍长图</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5176,6 +5286,7 @@
           <t>案例名</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>填充任务1</t>
@@ -5356,6 +5467,7 @@
           <t>筛选栏名称（只能填：最新提问 / 推荐 / 精选问答 / 我的关注）</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>推荐</t>
@@ -5383,6 +5495,8 @@
           <t>下拉刷新</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5415,6 +5529,7 @@
           <t>毫秒</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>2000（= 等 2 秒）</t>
@@ -5442,6 +5557,8 @@
           <t>打印页面文字</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5474,6 +5591,7 @@
           <t>范围（只能填：全量 / 只看有文字）</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>只看有文字</t>
@@ -5506,6 +5624,7 @@
           <t>文字</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>答对最多可赢积分</t>
@@ -5538,6 +5657,7 @@
           <t>文字</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>最新提问（搜索页上不该有）</t>
@@ -5607,6 +5727,7 @@
           <t>选择器</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>.search-container</t>
@@ -5639,6 +5760,7 @@
           <t>选择器</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>.activity-quiz-page</t>
@@ -5671,6 +5793,7 @@
           <t>选择器</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>.flow-item</t>
@@ -5703,6 +5826,7 @@
           <t>选择器</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>.flow-item</t>
@@ -5727,7 +5851,7 @@
     <row r="38" ht="27" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>检查元素数量</t>
+          <t>检查元素行数</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5737,12 +5861,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>期望数量</t>
+          <t>期望最多几行</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>.hot-topics .inline-flex / 5</t>
+          <t>.case-list-card-title / 2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5752,7 +5876,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
+          <t>断言这个放文字的元素渲染出来不超过 N 行（缺陷 713587136「应该显示 1 行、实际显示了两行」要的就是这个判据）：参数1 填选择器（例如 .escort-case-desc、.case-list-card-title），参数2 填最多几行（例如 1、2）。命中几个就查几个（一屏卡片会全量一遍），有一个超了就算失败并把它打出来。想只查某一个就把选择器写具体（:has-text("…") 这类 Playwright 写法也能用）。量法是「把文字包进 Range，数它占了几个矩形」，不依赖 line-height。只读</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5764,7 +5888,7 @@
     <row r="39" ht="40.5" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>检查输入框的值</t>
+          <t>检查元素数量</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5774,12 +5898,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>期望值</t>
+          <t>期望数量</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>wx-input.search-input / test</t>
+          <t>.hot-topics .inline-flex / 5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5789,7 +5913,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
+          <t>断言选择器命中的元素个数正好是期望值，例如 .search-container / 1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5801,12 +5925,22 @@
     <row r="40" ht="27" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>记住积分余额</t>
+          <t>检查输入框的值</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>选择器</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>期望值</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>（不用填参数；之后配一步「检查积分增加」）</t>
+          <t>wx-input.search-input / test</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5816,7 +5950,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>记住用户现在看到的积分余额（自己先回首页再进积分商城、强制重新取数，读页面上的「当前积分」）。和「检查积分增加」配成一对用：写数据前后各来一次，就能验证「发多少到账多少」。⚠️ 读的是页面上的数（用户看到的），不是库里那个 user.points —— 两者会差一批「还没从中台同步进来的流水」（见 docs/踩坑记录.md 坑 42）。只读</t>
+          <t>读出输入框里真实的值再比较。这是表格里唯一能「读出来再比较」的检查，例如 wx-input.search-input / test</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5828,17 +5962,14 @@
     <row r="41" ht="27" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>检查积分增加</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>期望增加（分）</t>
-        </is>
-      </c>
+          <t>记住积分余额</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1021（配合上一步「记住积分余额」；少发/多发/没发都会红）</t>
+          <t>（不用填参数；之后配一步「检查积分增加」）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5848,7 +5979,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>读一次当前积分余额，断言它比上一步「记住积分余额」记下的多正好这么多分。例：提交答卷后写 1021 —— 少发、多发、没发都能抓出来。只读（但要先有「记住积分余额」）</t>
+          <t>记住用户现在看到的积分余额（自己先回首页再进积分商城、强制重新取数，读页面上的「当前积分」）。和「检查积分增加」配成一对用：写数据前后各来一次，就能验证「发多少到账多少」。⚠️ 读的是页面上的数（用户看到的），不是库里那个 user.points —— 两者会差一批「还没从中台同步进来的流水」（见 docs/踩坑记录.md 坑 42）。只读</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5860,12 +5991,18 @@
     <row r="42" ht="27" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>检查活动入口</t>
-        </is>
-      </c>
+          <t>检查积分增加</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>期望增加（分）</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>1021（配合上一步「记住积分余额」；少发/多发/没发都会红）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5875,21 +6012,23 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
+          <t>读一次当前积分余额，断言它比上一步「记住积分余额」记下的多正好这么多分。例：提交答卷后写 1021 —— 少发、多发、没发都能抓出来。只读（但要先有「记住积分余额」）</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>⑤ 需求专项检查</t>
+          <t>④ 通用断言（检查「看得见没有」）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40.5" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>检查首页筛选栏顺序</t>
-        </is>
-      </c>
+          <t>检查活动入口</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5902,7 +6041,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
+          <t>按需求 713594979 校验首页活动入口在 最新提问/推荐/精选问答/我的关注 4 个 tab 下都显示</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5914,9 +6053,11 @@
     <row r="44" ht="27" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>检查回到顶部按钮</t>
-        </is>
-      </c>
+          <t>检查首页筛选栏顺序</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5929,7 +6070,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
+          <t>按需求 713341876 校验：筛选 tab 顺序是 最新提问→推荐→精选问答→我的关注，且默认选中「最新提问」</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5941,9 +6082,11 @@
     <row r="45" ht="40.5" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>检查答题页</t>
-        </is>
-      </c>
+          <t>检查回到顶部按钮</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5956,7 +6099,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于一道题的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
+          <t>按需求 713582097 校验积分商城的「回到顶部」按钮：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5968,9 +6111,11 @@
     <row r="46" ht="27" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>检查案例库列表</t>
-        </is>
-      </c>
+          <t>检查答题页</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5983,7 +6128,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验案例库列表页：① 分类上方有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「复制图标 + 复制数」，且整页找不到评论图标。只读</t>
+          <t>按需求 713594985 校验答题页：吸顶进度、选项 2~6 个、提交按钮状态与「是否选完」一致。只适用于一道题的活动；多选题库活动会记成「跳过」并说明原因（见 docs/踩坑记录.md）</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5995,17 +6140,14 @@
     <row r="47" ht="40.5" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>检查案例库复制数对账</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>最多比几张（可不填）</t>
-        </is>
-      </c>
+          <t>检查案例库列表</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6015,7 +6157,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>缺陷 713453275「复制数的查看无数据返回」的回归断言：卡片上显示的复制数，必须等于库里那条案例的 copy_count（参数1 填最多比几张，留空 = 3）。为什么要这么较真：源码里是 copyCount ?? 0，永远有个数字 ——所以「卡片上有数字」这种断言是假绿。库里重名的案例会自动跳过（无法确定对哪一条）。连不上库时记「跳过」并说明原因，不会硬判通过。只读</t>
+          <t>按需求 713381608 校验案例库列表页：① 分类上方有介绍 banner（按坐标判「在上方」）；② 每张卡片右下角是「复制图标 + 复制数」，且整页找不到评论图标。只读</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6027,12 +6169,18 @@
     <row r="48" ht="27" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>检查案例详情页</t>
-        </is>
-      </c>
+          <t>检查案例库复制数对账</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>最多比几张（可不填）</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6042,7 +6190,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部没有复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
+          <t>缺陷 713453275「复制数的查看无数据返回」的回归断言：卡片上显示的复制数，必须等于库里那条案例的 copy_count（参数1 填最多比几张，留空 = 3）。为什么要这么较真：源码里是 copyCount ?? 0，永远有个数字 ——所以「卡片上有数字」这种断言是假绿。库里重名的案例会自动跳过（无法确定对哪一条）。连不上库时记「跳过」并说明原因，不会硬判通过。只读</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6054,9 +6202,11 @@
     <row r="49" ht="54" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>检查案例库介绍长图</t>
-        </is>
-      </c>
+          <t>检查案例详情页</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6069,7 +6219,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>按需求 713381608 校验介绍长图页：整页是单张图片，而且是长图（图高远大于屏高）。只读</t>
+          <t>按需求 713381608 校验案例详情页：① 评论区标题是「全部评论」（页面上不能再有「全部回答」）；② 详情页底部没有复制数/评论数图标（实测只有点赞/收藏/分享）。只读</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6081,17 +6231,14 @@
     <row r="50" ht="40.5" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>检查课程详情页</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
-        </is>
-      </c>
+          <t>检查案例库介绍长图</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>课程介绍</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6101,7 +6248,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、默认选中填的那个（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
+          <t>按需求 713381608 校验介绍长图页：整页是单张图片，而且是长图（图高远大于屏高）。只读</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -6113,12 +6260,18 @@
     <row r="51" ht="67.5" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>检查0课时课程不显示</t>
-        </is>
-      </c>
+          <t>检查课程详情页</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>课程介绍</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6128,7 +6281,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字一个都没出现在小程序的课程列表里（会自己滚到列表底部）。只读</t>
+          <t>按需求 713367615 校验课程详情页：有「课程介绍 / 课程目录」两个 tab、默认选中填的那个（未开始学习填 课程介绍；已开始学习填 课程目录）、展示课程标题、展示第一课时封面和视频。只读</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -6140,17 +6293,14 @@
     <row r="52" ht="54" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>检查未购买点课时</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>课程名</t>
-        </is>
-      </c>
+          <t>检查0课时课程不显示</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>7.8课程new</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6160,7 +6310,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>按需求 713367615 第 2 条校验：未购买的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号没买过的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
+          <t>按需求 713367615 第 1 条校验：先去数据库拿「0 课时的公开课程」名单，再确认这些名字一个都没出现在小程序的课程列表里（会自己滚到列表底部）。只读</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -6172,12 +6322,18 @@
     <row r="53" ht="27" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>打开答题活动</t>
-        </is>
-      </c>
+          <t>检查未购买点课时</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>课程名</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>7.8课程new</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6187,21 +6343,23 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
+          <t>按需求 713367615 第 2 条校验：未购买的课程上点课时，封面图和标题都不变、始终显示课程名称。参数1 填一门我们账号没买过的课（例如 7.8课程new）；页面不是未购买态会明确报错，不会假装通过。只读</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+          <t>⑤ 需求专项检查</t>
         </is>
       </c>
     </row>
     <row r="54" ht="67.5" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>逐题作答</t>
-        </is>
-      </c>
+          <t>打开答题活动</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6209,12 +6367,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>只改前端选中态（不写库、不需要开关）</t>
+          <t>不会</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、不写库，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
+          <t>打开「答题赢积分」活动页（只读：不选选项、不提交）</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -6226,9 +6384,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>提交答卷</t>
-        </is>
-      </c>
+          <t>逐题作答</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6236,12 +6396,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>会写库（必须开开关）</t>
+          <t>只改前端选中态（不写库、不需要开关）</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>点答题页的提交按钮 —— 会真的写数据。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
+          <t>把答题页上每道题都选上第一个选项（多题活动会一题一题点过去，屏幕外的题会自动滚进可视区）。只改前端选中态、不写库，所以不需要开关；但选完不提交的话，离开页面就没了（需求原文：未提交已选的选项不会保存）</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6253,27 +6413,24 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>复位答题记录</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>活动名</t>
-        </is>
-      </c>
+          <t>提交答卷</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Z-B4-答题角标</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>会删库（默认只预览；真删要开开关）</t>
+          <t>会写库（必须开开关）</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：默认只预览、不删，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+          <t>点答题页的提交按钮 —— 会真的写数据。必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步直接报错（不跳过、不静默）。跑完记得用「复位答题记录」把数据清掉</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -6285,7 +6442,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>检查答题记录数</t>
+          <t>复位答题记录</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6293,24 +6450,20 @@
           <t>活动名</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>期望条数</t>
-        </is>
-      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Z-B4-答题角标 / 1</t>
+          <t>Z-B4-答题角标</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>不会</t>
+          <t>会删库（默认只预览；真删要开开关）</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>读数据库，断言这个活动的提交记录正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
+          <t>删掉这个活动在测试库里留下的答题记录（提交 + 明细），让「答题机会」回到能用状态。⚠️ 这是护栏动作：默认只预览、不删，真删要打开开关 UITEST_ALLOW_SUBMIT=1；活动名要跟页面上的标题一字不差（例如 Z-B4-答题角标）；名字找不到或有重名会被拒绝执行（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6322,22 +6475,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>复制当前案例</t>
+          <t>检查答题记录数</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>活动名</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>期望条数</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>（不用填参数）</t>
+          <t>Z-B4-答题角标 / 1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>会写库（要开开关；没开时记跳过）</t>
+          <t>不会</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>在案例详情页点「复制案例」—— 一条龙：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → 自动复位（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
+          <t>读数据库，断言这个活动的提交记录正好是 N 条（例如提交前填 0、提交后填 1）。用来把「界面上说提交成功」和「库里真有这条」对上 —— 只读，不需要开关（「活动名」填数据里的名字：候选值见「名称候选」工作表，可直接复制）</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6349,27 +6512,24 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>屏蔽礼品分类</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>分类名</t>
-        </is>
-      </c>
+          <t>复制当前案例</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>实物商品（跟后台一字不差；跑完记得用「还原礼品分类」改回去）</t>
+          <t>（不用填参数）</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>会写库（要开开关）</t>
+          <t>会写库（要开开关；没开时记跳过）</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>把某个礼品分类改成未启用/屏蔽（只改 gift_category.status），造出「屏蔽分类后礼品不该显示」这个夹具。分类名要跟后台一字不差（重名会被拒绝，那时改用工具 --id）。⚠️ 会写测试库：必须开开关 UITEST_ALLOW_SUBMIT=1；这条用例末尾必须跟一步「还原礼品分类」（owner 2026/10/14：数据改完记得还原）</t>
+          <t>在案例详情页点「复制案例」—— 一条龙：记下水位 → 点复制 → 断言提示「复制成功 / 使用手机号登录智铸超云，即可查看案例详情」逐字出现 → 读数据库确认复制记录 +1、复制数 +1 → 自动复位（删掉这次那条记录、把复制数改回去）。⚠️ 会写测试库数据：必须打开开关 UITEST_ALLOW_SUBMIT=1，否则这一步记「跳过」（并说明原因）。先用「打开案例库」+「打开第一个案例」走到详情页再用它</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6381,30 +6541,64 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>屏蔽礼品分类</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>分类名</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>实物商品（跟后台一字不差；跑完记得用「还原礼品分类」改回去）</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>会写库（要开开关）</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>把某个礼品分类改成未启用/屏蔽（只改 gift_category.status），造出「屏蔽分类后礼品不该显示」这个夹具。分类名要跟后台一字不差（重名会被拒绝，那时改用工具 --id）。⚠️ 会写测试库：必须开开关 UITEST_ALLOW_SUBMIT=1；这条用例末尾必须跟一步「还原礼品分类」（owner 2026/10/14：数据改完记得还原）</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>还原礼品分类</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>分类名</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
         <is>
           <t>实物商品（跟「屏蔽礼品分类」里填的那个名字一样）</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>会写库（要开开关）</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>把「屏蔽礼品分类」改回去（status 还原成启用）—— 写链路的收尾步，跟着屏蔽那步成对使用</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>⑥ 答题 / 写链路（要开开关，跑完必须复位）</t>
         </is>
@@ -8444,6 +8638,7 @@
           <t>方案一变形</t>
         </is>
       </c>
+      <c r="C96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8456,6 +8651,7 @@
           <t>仅凝固</t>
         </is>
       </c>
+      <c r="C97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8468,6 +8664,7 @@
           <t>仅充填2</t>
         </is>
       </c>
+      <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8480,6 +8677,7 @@
           <t>充填凝固应力</t>
         </is>
       </c>
+      <c r="C99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8492,6 +8690,7 @@
           <t>充填凝固应力1</t>
         </is>
       </c>
+      <c r="C100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8504,6 +8703,7 @@
           <t>7201744-孙</t>
         </is>
       </c>
+      <c r="C101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8516,6 +8716,7 @@
           <t>带组织性能结果</t>
         </is>
       </c>
+      <c r="C102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8528,6 +8729,7 @@
           <t>充填-排气</t>
         </is>
       </c>
+      <c r="C103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8540,6 +8742,7 @@
           <t>1月 20250115</t>
         </is>
       </c>
+      <c r="C104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8552,6 +8755,7 @@
           <t>紫色1</t>
         </is>
       </c>
+      <c r="C105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8564,6 +8768,7 @@
           <t>内部数据6</t>
         </is>
       </c>
+      <c r="C106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8576,6 +8781,7 @@
           <t>1QQ区qqqqq</t>
         </is>
       </c>
+      <c r="C107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8588,6 +8794,7 @@
           <t>重力铸造-重力砂型-0602-163625-仅充填仅浏览-重力铸造-重力砂型-0602-163625</t>
         </is>
       </c>
+      <c r="C108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8600,6 +8807,7 @@
           <t>重力铸造-重力砂型-0602-163625-充填凝固0602_165141-仅浏览</t>
         </is>
       </c>
+      <c r="C109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8612,6 +8820,7 @@
           <t>COPY3</t>
         </is>
       </c>
+      <c r="C110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8624,6 +8833,7 @@
           <t>3月26测试 私有材料分享(copy)</t>
         </is>
       </c>
+      <c r="C111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8636,6 +8846,7 @@
           <t>内部数据-虚拟模具</t>
         </is>
       </c>
+      <c r="C112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8648,6 +8859,7 @@
           <t>内部数据</t>
         </is>
       </c>
+      <c r="C113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8660,6 +8872,7 @@
           <t>鹅鹅鹅</t>
         </is>
       </c>
+      <c r="C114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8672,6 +8885,7 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8684,6 +8898,7 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8696,6 +8911,7 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8708,6 +8924,7 @@
           <t>仅凝固+应力-选择点2</t>
         </is>
       </c>
+      <c r="C118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8720,6 +8937,7 @@
           <t>仅凝固1</t>
         </is>
       </c>
+      <c r="C119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8732,6 +8950,7 @@
           <t>循环凝固</t>
         </is>
       </c>
+      <c r="C120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8744,6 +8963,7 @@
           <t>131231</t>
         </is>
       </c>
+      <c r="C121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8756,6 +8976,7 @@
           <t>131231</t>
         </is>
       </c>
+      <c r="C122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8768,6 +8989,7 @@
           <t>循环凝固-热循环</t>
         </is>
       </c>
+      <c r="C123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8780,6 +9002,7 @@
           <t>6668</t>
         </is>
       </c>
+      <c r="C124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8792,6 +9015,7 @@
           <t>6668</t>
         </is>
       </c>
+      <c r="C125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8804,6 +9028,7 @@
           <t>填充任务1</t>
         </is>
       </c>
+      <c r="C126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8816,6 +9041,7 @@
           <t>0605测试</t>
         </is>
       </c>
+      <c r="C127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8828,6 +9054,7 @@
           <t>循环凝固+应力+选点1</t>
         </is>
       </c>
+      <c r="C128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8840,6 +9067,7 @@
           <t>料筒(copy)</t>
         </is>
       </c>
+      <c r="C129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8852,6 +9080,7 @@
           <t>仅凝固</t>
         </is>
       </c>
+      <c r="C130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8864,6 +9093,7 @@
           <t>#713392277</t>
         </is>
       </c>
+      <c r="C131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8876,6 +9106,7 @@
           <t>？？？？</t>
         </is>
       </c>
+      <c r="C132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8888,6 +9119,7 @@
           <t>复制任务失败问题测试-分享</t>
         </is>
       </c>
+      <c r="C133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8900,6 +9132,7 @@
           <t>浇口充填-高级模式</t>
         </is>
       </c>
+      <c r="C134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8912,6 +9145,7 @@
           <t>4.17</t>
         </is>
       </c>
+      <c r="C135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8924,6 +9158,7 @@
           <t>热热热热</t>
         </is>
       </c>
+      <c r="C136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8936,6 +9171,7 @@
           <t>eeee</t>
         </is>
       </c>
+      <c r="C137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8948,6 +9184,7 @@
           <t>亲亲</t>
         </is>
       </c>
+      <c r="C138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8960,6 +9197,7 @@
           <t>3333 私有曲线</t>
         </is>
       </c>
+      <c r="C139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8972,6 +9210,7 @@
           <t>v2</t>
         </is>
       </c>
+      <c r="C140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8984,6 +9223,7 @@
           <t>111111</t>
         </is>
       </c>
+      <c r="C141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8996,6 +9236,7 @@
           <t>测试二级页面案例111111111111111111111111111</t>
         </is>
       </c>
+      <c r="C142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9008,6 +9249,7 @@
           <t>分享高压 2</t>
         </is>
       </c>
+      <c r="C143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9020,6 +9262,7 @@
           <t>料筒充填</t>
         </is>
       </c>
+      <c r="C144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9032,6 +9275,7 @@
           <t>料筒充填1</t>
         </is>
       </c>
+      <c r="C145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9044,6 +9288,7 @@
           <t>料筒分享</t>
         </is>
       </c>
+      <c r="C146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9056,6 +9301,7 @@
           <t>1WWWW</t>
         </is>
       </c>
+      <c r="C147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9068,6 +9314,7 @@
           <t>凝固应力</t>
         </is>
       </c>
+      <c r="C148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9080,6 +9327,7 @@
           <t>模拟汽车</t>
         </is>
       </c>
+      <c r="C149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9092,6 +9340,7 @@
           <t>模拟汽车减震</t>
         </is>
       </c>
+      <c r="C150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9104,6 +9353,7 @@
           <t>多浇口充填(粒子数量10)</t>
         </is>
       </c>
+      <c r="C151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9111,6 +9361,7 @@
           <t>（说明）</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
           <t>课程那张表里的「我们账号买没买」按 user_id=1966910（config/env.yaml）判断</t>
@@ -9123,6 +9374,7 @@
           <t>（说明）</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
           <t>注意：这些课程名在库里有多门同名，按名字打开只会命中第一门 —— 012345678901234567890123456789、付费课程1、免费课程、免费课程1、无敌贵的课程、测试封面图、测试封面图-修改、测试验证课时bug</t>
@@ -9135,6 +9387,7 @@
           <t>（说明）</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
           <t>案例共 56 条，已全部列出</t>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1073,7 +1073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H198"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4498,8 +4498,113 @@
         </is>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ZW_037</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>护航案例介绍卡片的描述只显示 1 行（缺陷 713587136）</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；不用登录（只读）。护航服务要配了「行业案例」（测试环境里有 3 条）</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>1</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>缺陷 713587136（原文：案例介绍卡片中案例描述显示的行数错误 —— 应该按照 UI 显示 1 行，实际显示了两行）。
+路径：案例库 → 顶部 tab「压铸护航服务」→ 子 tab「案例介绍」→ 卡片描述 .escort-case-desc。
+**2026/10/16 真机实测：这条缺陷在当前版本仍然复现** —— 3 张卡片里，「打撒大」「三四十」两条是 1 行 ✓，而 192 字那条（管理后台案例 id=12「压铸电机壳体」）实测 **2 行**（高 36 / 行高 18）。
+原因（已定位到 DOM）：数据库里那条描述带换行，小程序把它渲染成了 &lt;br&gt; —— 外层 CSS 是 white-space: nowrap，但 **&lt;br&gt; 不受 nowrap 管**，所以照样断成两行。
+→ 所以这条用例**今天应该是红的**：它盯的就是这个真实缺陷，不是框架问题。前端修好（例如给 Text 加 numberOfLines={1}，或把描述里的换行去掉）它自然转绿。
+量法见动作「检查元素行数」（Range 矩形按行的顶边归并，已用 1 行/7 行两种样本校准过）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="D194" t="n">
+        <v>2</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="D195" t="n">
+        <v>3</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>压铸护航服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="D196" t="n">
+        <v>4</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>案例介绍</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="D197" t="n">
+        <v>5</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>检查元素行数</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>.escort-case-desc</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="D198" t="n">
+        <v>6</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="136">
+  <mergeCells count="140">
     <mergeCell ref="A48:A53"/>
     <mergeCell ref="A114:A119"/>
     <mergeCell ref="H99:H103"/>
@@ -4512,8 +4617,8 @@
     <mergeCell ref="C54:C59"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A159:A165"/>
+    <mergeCell ref="C2:C3"/>
     <mergeCell ref="C159:C165"/>
-    <mergeCell ref="C2:C3"/>
     <mergeCell ref="H110:H113"/>
     <mergeCell ref="A189:A192"/>
     <mergeCell ref="B13:B16"/>
@@ -4525,8 +4630,8 @@
     <mergeCell ref="A147:A152"/>
     <mergeCell ref="B95:B98"/>
     <mergeCell ref="B8:B12"/>
+    <mergeCell ref="H48:H53"/>
     <mergeCell ref="H104:H109"/>
-    <mergeCell ref="H48:H53"/>
     <mergeCell ref="A99:A103"/>
     <mergeCell ref="H64:H70"/>
     <mergeCell ref="B136:B140"/>
@@ -4546,6 +4651,8 @@
     <mergeCell ref="A21:A24"/>
     <mergeCell ref="H173:H176"/>
     <mergeCell ref="C21:C24"/>
+    <mergeCell ref="A193:A198"/>
+    <mergeCell ref="C193:C198"/>
     <mergeCell ref="A89:A94"/>
     <mergeCell ref="H8:H12"/>
     <mergeCell ref="B60:B63"/>
@@ -4557,12 +4664,13 @@
     <mergeCell ref="C95:C98"/>
     <mergeCell ref="A30:A47"/>
     <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C48:C53"/>
     <mergeCell ref="B110:B113"/>
-    <mergeCell ref="C48:C53"/>
     <mergeCell ref="C189:C192"/>
     <mergeCell ref="C120:C124"/>
     <mergeCell ref="B141:B146"/>
     <mergeCell ref="H4:H7"/>
+    <mergeCell ref="B193:B198"/>
     <mergeCell ref="A110:A113"/>
     <mergeCell ref="H159:H165"/>
     <mergeCell ref="A173:A176"/>
@@ -4571,6 +4679,7 @@
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="H77:H79"/>
     <mergeCell ref="C141:C146"/>
+    <mergeCell ref="H193:H198"/>
     <mergeCell ref="H120:H124"/>
     <mergeCell ref="H114:H119"/>
     <mergeCell ref="H89:H94"/>
@@ -4589,9 +4698,9 @@
     <mergeCell ref="B159:B165"/>
     <mergeCell ref="H189:H192"/>
     <mergeCell ref="A166:A172"/>
-    <mergeCell ref="C13:C16"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="A4:A7"/>
+    <mergeCell ref="C13:C16"/>
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="C166:C172"/>
     <mergeCell ref="B189:B192"/>
@@ -4710,8 +4819,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4739,8 +4846,6 @@
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4768,8 +4873,6 @@
           <t>打开积分商城</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4797,8 +4900,6 @@
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4831,7 +4932,6 @@
           <t>顶部栏名称（只能填：课程 / 专栏 / 压铸百科）</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>专栏</t>
@@ -4859,8 +4959,6 @@
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4888,8 +4986,6 @@
           <t>点主页按钮</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4917,8 +5013,6 @@
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4946,8 +5040,6 @@
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -4980,7 +5072,6 @@
           <t>课程名</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>717</t>
@@ -5013,7 +5104,6 @@
           <t>关键词</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -5046,7 +5136,6 @@
           <t>关键词</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -5074,8 +5163,6 @@
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5108,7 +5195,6 @@
           <t>词</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>压铸测试</t>
@@ -5136,8 +5222,6 @@
           <t>打开第一个热门话题</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5165,8 +5249,6 @@
           <t>打开第一个帖子</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5194,8 +5276,6 @@
           <t>打开第一张专栏</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5223,8 +5303,6 @@
           <t>打开第一个案例</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5252,8 +5330,6 @@
           <t>打开案例库介绍长图</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5286,7 +5362,6 @@
           <t>案例名</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>填充任务1</t>
@@ -5467,7 +5542,6 @@
           <t>筛选栏名称（只能填：最新提问 / 推荐 / 精选问答 / 我的关注）</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>推荐</t>
@@ -5495,8 +5569,6 @@
           <t>下拉刷新</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5529,7 +5601,6 @@
           <t>毫秒</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>2000（= 等 2 秒）</t>
@@ -5557,8 +5628,6 @@
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5591,7 +5660,6 @@
           <t>范围（只能填：全量 / 只看有文字）</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>只看有文字</t>
@@ -5624,7 +5692,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>答对最多可赢积分</t>
@@ -5657,7 +5724,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>最新提问（搜索页上不该有）</t>
@@ -5727,7 +5793,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>.search-container</t>
@@ -5760,7 +5825,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>.activity-quiz-page</t>
@@ -5793,7 +5857,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>.flow-item</t>
@@ -5826,7 +5889,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>.flow-item</t>
@@ -5965,8 +6027,6 @@
           <t>记住积分余额</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>（不用填参数；之后配一步「检查积分增加」）</t>
@@ -5999,7 +6059,6 @@
           <t>期望增加（分）</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>1021（配合上一步「记住积分余额」；少发/多发/没发都会红）</t>
@@ -6027,8 +6086,6 @@
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6056,8 +6113,6 @@
           <t>检查首页筛选栏顺序</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6085,8 +6140,6 @@
           <t>检查回到顶部按钮</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6114,8 +6167,6 @@
           <t>检查答题页</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6143,8 +6194,6 @@
           <t>检查案例库列表</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6177,7 +6226,6 @@
           <t>最多比几张（可不填）</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>3</t>
@@ -6205,8 +6253,6 @@
           <t>检查案例详情页</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6234,8 +6280,6 @@
           <t>检查案例库介绍长图</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6268,7 +6312,6 @@
           <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>课程介绍</t>
@@ -6296,8 +6339,6 @@
           <t>检查0课时课程不显示</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6330,7 +6371,6 @@
           <t>课程名</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>7.8课程new</t>
@@ -6358,8 +6398,6 @@
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6387,8 +6425,6 @@
           <t>逐题作答</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6416,8 +6452,6 @@
           <t>提交答卷</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6450,7 +6484,6 @@
           <t>活动名</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>Z-B4-答题角标</t>
@@ -6515,8 +6548,6 @@
           <t>复制当前案例</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6549,7 +6580,6 @@
           <t>分类名</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>实物商品（跟后台一字不差；跑完记得用「还原礼品分类」改回去）</t>
@@ -6582,7 +6612,6 @@
           <t>分类名</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>实物商品（跟「屏蔽礼品分类」里填的那个名字一样）</t>
@@ -8638,7 +8667,6 @@
           <t>方案一变形</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8651,7 +8679,6 @@
           <t>仅凝固</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8664,7 +8691,6 @@
           <t>仅充填2</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8677,7 +8703,6 @@
           <t>充填凝固应力</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8690,7 +8715,6 @@
           <t>充填凝固应力1</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8703,7 +8727,6 @@
           <t>7201744-孙</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8716,7 +8739,6 @@
           <t>带组织性能结果</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8729,7 +8751,6 @@
           <t>充填-排气</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8742,7 +8763,6 @@
           <t>1月 20250115</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8755,7 +8775,6 @@
           <t>紫色1</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8768,7 +8787,6 @@
           <t>内部数据6</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8781,7 +8799,6 @@
           <t>1QQ区qqqqq</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8794,7 +8811,6 @@
           <t>重力铸造-重力砂型-0602-163625-仅充填仅浏览-重力铸造-重力砂型-0602-163625</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8807,7 +8823,6 @@
           <t>重力铸造-重力砂型-0602-163625-充填凝固0602_165141-仅浏览</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8820,7 +8835,6 @@
           <t>COPY3</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8833,7 +8847,6 @@
           <t>3月26测试 私有材料分享(copy)</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8846,7 +8859,6 @@
           <t>内部数据-虚拟模具</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8859,7 +8871,6 @@
           <t>内部数据</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8872,7 +8883,6 @@
           <t>鹅鹅鹅</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8885,7 +8895,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8898,7 +8907,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8911,7 +8919,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8924,7 +8931,6 @@
           <t>仅凝固+应力-选择点2</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8937,7 +8943,6 @@
           <t>仅凝固1</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8950,7 +8955,6 @@
           <t>循环凝固</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8963,7 +8967,6 @@
           <t>131231</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8976,7 +8979,6 @@
           <t>131231</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8989,7 +8991,6 @@
           <t>循环凝固-热循环</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9002,7 +9003,6 @@
           <t>6668</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9015,7 +9015,6 @@
           <t>6668</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9028,7 +9027,6 @@
           <t>填充任务1</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9041,7 +9039,6 @@
           <t>0605测试</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9054,7 +9051,6 @@
           <t>循环凝固+应力+选点1</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9067,7 +9063,6 @@
           <t>料筒(copy)</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9080,7 +9075,6 @@
           <t>仅凝固</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9093,7 +9087,6 @@
           <t>#713392277</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9106,7 +9099,6 @@
           <t>？？？？</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9119,7 +9111,6 @@
           <t>复制任务失败问题测试-分享</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9132,7 +9123,6 @@
           <t>浇口充填-高级模式</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9145,7 +9135,6 @@
           <t>4.17</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9158,7 +9147,6 @@
           <t>热热热热</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9171,7 +9159,6 @@
           <t>eeee</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9184,7 +9171,6 @@
           <t>亲亲</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9197,7 +9183,6 @@
           <t>3333 私有曲线</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9210,7 +9195,6 @@
           <t>v2</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9223,7 +9207,6 @@
           <t>111111</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9236,7 +9219,6 @@
           <t>测试二级页面案例111111111111111111111111111</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9249,7 +9231,6 @@
           <t>分享高压 2</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9262,7 +9243,6 @@
           <t>料筒充填</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9275,7 +9255,6 @@
           <t>料筒充填1</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9288,7 +9267,6 @@
           <t>料筒分享</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9301,7 +9279,6 @@
           <t>1WWWW</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9314,7 +9291,6 @@
           <t>凝固应力</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9327,7 +9303,6 @@
           <t>模拟汽车</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9340,7 +9315,6 @@
           <t>模拟汽车减震</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9353,7 +9327,6 @@
           <t>多浇口充填(粒子数量10)</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9361,7 +9334,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
           <t>课程那张表里的「我们账号买没买」按 user_id=1966910（config/env.yaml）判断</t>
@@ -9374,7 +9346,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
           <t>注意：这些课程名在库里有多门同名，按名字打开只会命中第一门 —— 012345678901234567890123456789、付费课程1、免费课程、免费课程1、无敌贵的课程、测试封面图、测试封面图-修改、测试验证课时bug</t>
@@ -9387,7 +9358,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
           <t>案例共 56 条，已全部列出</t>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1073,7 +1073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H198"/>
+  <dimension ref="A1:H219"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4603,8 +4603,352 @@
         </is>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ZW_038</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>护航服务：三个视图入口、默认视图、切换高亮联动、切完回到页面顶部（需求 713555327 第 1 条）</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；不用登录（只读）</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>需求 713555327（Sprint20，已关闭）第 1 条原文：「页面采用单页多视图结构，顶部设有三个标签页：服务介绍、案例介绍、套餐介绍。默认进入服务介绍视图。切换标签时，页面内容整体替换，同时顶部标签高亮随当前视图联动，并自动回到页面顶部。」
+真机实测（2026/10/16）：三个 tab 的 class 是 escort-view-tab，选中那个多一个 active（颜色 rgb(212,20,20)、字重 500）；默认确实是「服务介绍」；切到「套餐介绍」后选中态跟着走。
+第 6-7 步先滚下去、证明第一块模块标题被滚出视口；第 9 步切完视图它又回到视口里 —— 这就是需求说的「自动回到页面顶部」（源码 EscortSection.tsx 的 switchView 里确实会把 scrollTop 归零）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="D200" t="n">
+        <v>2</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="D201" t="n">
+        <v>3</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>压铸护航服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="D202" t="n">
+        <v>4</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>检查元素数量</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>.escort-view-tab</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="D203" t="n">
+        <v>5</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>检查元素数量</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>.escort-view-tab.active:has-text("服务介绍")</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="D204" t="n">
+        <v>6</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>滑动</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="D205" t="n">
+        <v>7</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>检查元素不在视口里</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>.escort-module-title</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="D206" t="n">
+        <v>8</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>套餐介绍</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="D207" t="n">
+        <v>9</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>检查元素在视口里</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>.escort-module-title</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="D208" t="n">
+        <v>10</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>检查元素数量</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>.escort-view-tab.active:has-text("套餐介绍")</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="D209" t="n">
+        <v>11</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>套餐方案</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="D210" t="n">
+        <v>12</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>ZW_039</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>护航案例卡片整卡可点，详情页底部有「我也要做」（需求 713555327 第 4、5 条）</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；不用登录（只读）。护航开了「行业案例」且至少 1 条启用</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>1</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>需求 713555327 第 4 条：「案例以竖向列表排布，每一个案例是一张可点击卡片，整个卡片都是可点击区域…点击后跳转案例详情页」；第 5 条：「详情页底部固定悬浮按钮『我也要做』」。
+真机实测（2026/10/16）：列表项 .escort-case-card（3 张，整卡 333×247）；详情页根容器 .escort-case-detail，封面 .ecd-cover-title、描述 .ecd-description、分段内容 .ecd-segments，底部固定条 .ecd-reserve-bar 里写着「我也要做」。
+第 5 步点的是卡片本身（不是卡里的某个小元素）—— 需求要的就是「整卡可点」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="D212" t="n">
+        <v>2</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="D213" t="n">
+        <v>3</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>压铸护航服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="D214" t="n">
+        <v>4</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>案例介绍</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="D215" t="n">
+        <v>5</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>点选择器</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>.escort-case-card</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="D216" t="n">
+        <v>6</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>检查元素存在</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>.escort-case-detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="D217" t="n">
+        <v>7</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>我也要做</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="D218" t="n">
+        <v>8</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>返回上一页</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="D219" t="n">
+        <v>9</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="140">
+  <mergeCells count="148">
     <mergeCell ref="A48:A53"/>
     <mergeCell ref="A114:A119"/>
     <mergeCell ref="H99:H103"/>
@@ -4636,6 +4980,7 @@
     <mergeCell ref="H64:H70"/>
     <mergeCell ref="B136:B140"/>
     <mergeCell ref="B104:B109"/>
+    <mergeCell ref="H199:H210"/>
     <mergeCell ref="B166:B172"/>
     <mergeCell ref="A136:A140"/>
     <mergeCell ref="B153:B158"/>
@@ -4646,6 +4991,7 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="B71:B76"/>
     <mergeCell ref="C4:C7"/>
+    <mergeCell ref="B211:B219"/>
     <mergeCell ref="B17:B20"/>
     <mergeCell ref="C136:C140"/>
     <mergeCell ref="A21:A24"/>
@@ -4657,6 +5003,7 @@
     <mergeCell ref="H8:H12"/>
     <mergeCell ref="B60:B63"/>
     <mergeCell ref="B25:B29"/>
+    <mergeCell ref="B199:B210"/>
     <mergeCell ref="C184:C188"/>
     <mergeCell ref="A64:A70"/>
     <mergeCell ref="C153:C158"/>
@@ -4669,6 +5016,7 @@
     <mergeCell ref="C189:C192"/>
     <mergeCell ref="C120:C124"/>
     <mergeCell ref="B141:B146"/>
+    <mergeCell ref="C211:C219"/>
     <mergeCell ref="H4:H7"/>
     <mergeCell ref="B193:B198"/>
     <mergeCell ref="A110:A113"/>
@@ -4677,6 +5025,7 @@
     <mergeCell ref="A60:A63"/>
     <mergeCell ref="B125:B130"/>
     <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A199:A210"/>
     <mergeCell ref="H77:H79"/>
     <mergeCell ref="C141:C146"/>
     <mergeCell ref="H193:H198"/>
@@ -4704,6 +5053,7 @@
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="C166:C172"/>
     <mergeCell ref="B189:B192"/>
+    <mergeCell ref="H211:H219"/>
     <mergeCell ref="H25:H29"/>
     <mergeCell ref="B173:B176"/>
     <mergeCell ref="C125:C130"/>
@@ -4713,6 +5063,7 @@
     <mergeCell ref="H141:H146"/>
     <mergeCell ref="A80:A88"/>
     <mergeCell ref="C80:C88"/>
+    <mergeCell ref="C199:C210"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="A184:A188"/>
     <mergeCell ref="C8:C12"/>
@@ -4728,6 +5079,7 @@
     <mergeCell ref="A77:A79"/>
     <mergeCell ref="A71:A76"/>
     <mergeCell ref="C71:C76"/>
+    <mergeCell ref="A211:A219"/>
     <mergeCell ref="H166:H172"/>
     <mergeCell ref="C17:C20"/>
     <mergeCell ref="H13:H16"/>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1073,7 +1073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H219"/>
+  <dimension ref="A1:H236"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4947,12 +4947,291 @@
         </is>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ZW_040</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>护航套餐：推荐横幅、整卡可点进详情、常见问题可同时展开多项（需求 713555327 第 6 条）</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；不用登录（只读）。护航配了套餐与常见问题（测试环境里套餐 4 条、常见问题 3 条）</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>需求 713555327 第 6 条原文：「套餐介绍：套餐以竖向卡片列表展示，推荐套餐卡片顶部以通栏横幅标识『推荐』，整个卡片都是可点击区域…套餐下方显示常见问题，手风琴样式，**可同时展开多项查看**」。
+真机实测（2026/10/16）：套餐卡 .escort-package-card（4 张，都带 recommend、顶部横幅文案是「热门推荐」——含需求的『推荐』二字，这是实际文案，写在断言里的是实测值）；点卡片进 .escort-package-detail（标题「套餐详情」）。
+常见问题（.escort-faq-item / .escort-faq-q-text / .escort-faq-a）：源码里答案是**条件渲染**（`{open ? &lt;Text className="escort-faq-a"&gt;…&lt;/Text&gt; : null}`），所以折叠时 .escort-faq-a **根本不在 DOM 里** ——这条正好用「元素数量 0 / 1 / 2」精确验「可同时展开多项」，不会出现「看不见但数得到」的假绿。
+第 12、14 步点的问题文案来自后台配置（是是是是是是的 / DSUIOF JUSPFIP）—— 后台改了这几句，就把这两格一起改（报告里会明确说找不到哪句）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="D221" t="n">
+        <v>2</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="D222" t="n">
+        <v>3</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>压铸护航服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="D223" t="n">
+        <v>4</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>套餐介绍</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="D224" t="n">
+        <v>5</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>热门推荐</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="D225" t="n">
+        <v>6</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>查看详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="D226" t="n">
+        <v>7</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>点选择器</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>.escort-package-card</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="D227" t="n">
+        <v>8</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>检查元素存在</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>.escort-package-detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="D228" t="n">
+        <v>9</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>返回上一页</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="D229" t="n">
+        <v>10</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>滑动</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="D230" t="n">
+        <v>11</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>检查元素数量</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>.escort-faq-a</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="D231" t="n">
+        <v>12</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>是是是是是是的</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="D232" t="n">
+        <v>13</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>检查元素数量</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>.escort-faq-a</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="D233" t="n">
+        <v>14</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>DSUIOF JUSPFIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="D234" t="n">
+        <v>15</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>检查元素数量</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>.escort-faq-a</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="D235" t="n">
+        <v>16</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>JKLDSJF KJIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="D236" t="n">
+        <v>17</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="148">
+  <mergeCells count="152">
     <mergeCell ref="A48:A53"/>
     <mergeCell ref="A114:A119"/>
     <mergeCell ref="H99:H103"/>
     <mergeCell ref="A131:A135"/>
+    <mergeCell ref="B220:B236"/>
     <mergeCell ref="C131:C135"/>
     <mergeCell ref="A153:A158"/>
     <mergeCell ref="B30:B47"/>
@@ -4993,6 +5272,7 @@
     <mergeCell ref="C4:C7"/>
     <mergeCell ref="B211:B219"/>
     <mergeCell ref="B17:B20"/>
+    <mergeCell ref="H220:H236"/>
     <mergeCell ref="C136:C140"/>
     <mergeCell ref="A21:A24"/>
     <mergeCell ref="H173:H176"/>
@@ -5015,11 +5295,13 @@
     <mergeCell ref="B110:B113"/>
     <mergeCell ref="C189:C192"/>
     <mergeCell ref="C120:C124"/>
+    <mergeCell ref="A220:A236"/>
     <mergeCell ref="B141:B146"/>
     <mergeCell ref="C211:C219"/>
     <mergeCell ref="H4:H7"/>
     <mergeCell ref="B193:B198"/>
     <mergeCell ref="A110:A113"/>
+    <mergeCell ref="C220:C236"/>
     <mergeCell ref="H159:H165"/>
     <mergeCell ref="A173:A176"/>
     <mergeCell ref="A60:A63"/>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动作清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名称候选" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="用例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="动作清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="名称候选" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="填写说明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -182,7 +182,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="42">
     <fill>
       <patternFill/>
     </fill>
@@ -379,6 +379,54 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+        <bgColor rgb="FFEDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CBAD"/>
+        <bgColor rgb="FFF8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+        <bgColor rgb="FFC6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -636,7 +684,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -661,6 +709,14 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -713,6 +769,72 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDDEBF7"/>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2EFDA"/>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEDEDED"/>
+          <bgColor rgb="FFEDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBDD7EE"/>
+          <bgColor rgb="FFBDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6E0B4"/>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1073,7 +1195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H236"/>
+  <dimension ref="A1:I249"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1084,6 +1206,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="78.125" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1127,6 +1250,11 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>类型分类</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -1158,6 +1286,11 @@
         <is>
           <t>第1步：需求 713594979；只读
 第2步：只切 tab + 数活动卡，不改数据</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>业务规则与数据型</t>
         </is>
       </c>
     </row>
@@ -1205,6 +1338,11 @@
 第2步：关键词只能字母/数字/下划线/点/连字符（adb 不支持中文输入）
 第3步：搜索页的真实输入框
 第4步：把手机交还给下一条用例</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>操作型</t>
         </is>
       </c>
     </row>
@@ -1287,6 +1425,11 @@
 第5步：把手机交还给下一条用例</t>
         </is>
       </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>展示文案型</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="D9" s="7" t="n">
@@ -1379,6 +1522,11 @@
 「热门专栏 / 往期专栏 任一 + 有卡片」（见 learn_center_page.js 的注释）。</t>
         </is>
       </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>操作型</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="D14" s="7" t="n">
@@ -1447,6 +1595,11 @@
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>操作型</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="D18" s="7" t="n">
@@ -1515,6 +1668,11 @@
       <c r="F21" s="7" t="inlineStr"/>
       <c r="G21" s="7" t="inlineStr"/>
       <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>展示文案型</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="D22" s="7" t="n">
@@ -1583,6 +1741,11 @@
       <c r="F25" s="7" t="inlineStr"/>
       <c r="G25" s="7" t="inlineStr"/>
       <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>业务规则与数据型</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="D26" s="7" t="n">
@@ -1684,6 +1847,11 @@
 第16步：进详情页</t>
         </is>
       </c>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>框架自检型</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="D31" s="7" t="n">
@@ -1973,6 +2141,11 @@
 第6步：把手机交还给下一条</t>
         </is>
       </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>业务规则与数据型</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="D49" s="7" t="n">
@@ -2081,6 +2254,11 @@
 第6步：把手机交还给下一条</t>
         </is>
       </c>
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>业务规则与数据型</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="D55" s="7" t="n">
@@ -2186,6 +2364,11 @@
 第2步：用户中心 -&gt; 积分商城（二级页，没有底部 tab 栏）
 第3步：需求口径：未滚动隐藏 / 滚过阈值出现 / 点击后回顶部并隐藏
 第4步：把手机交还给下一条</t>
+        </is>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
+          <t>业务规则与数据型</t>
         </is>
       </c>
     </row>
@@ -2262,6 +2445,11 @@
 第7步：把手机交还给下一条。注：「结果是否真的按该话题筛过」要读页面标题才能验，留给以后的代码用例</t>
         </is>
       </c>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>展示文案型</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="D65" s="7" t="n">
@@ -2387,6 +2575,11 @@
 第6步：把手机交还给下一条</t>
         </is>
       </c>
+      <c r="I71" s="15" t="inlineStr">
+        <is>
+          <t>操作型</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="D72" s="7" t="n">
@@ -2487,6 +2680,11 @@
           <t>第1步：先摆正起点
 第2步：需求：最新提问和推荐互换顺序 + 最新提问为默认展示（置顶帖那半句依赖数据，暂不覆盖）
 第3步：把手机交还给下一条</t>
+        </is>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>展示文案型</t>
         </is>
       </c>
     </row>
@@ -2553,6 +2751,11 @@
 第9步：把手机交还给下一条用例</t>
         </is>
       </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>操作型</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="D81" s="7" t="n">
@@ -2686,6 +2889,11 @@
 第6步：把手机交还给下一条用例</t>
         </is>
       </c>
+      <c r="I89" s="14" t="inlineStr">
+        <is>
+          <t>业务规则与数据型</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="D90" s="7" t="n">
@@ -2783,6 +2991,11 @@
 第2步：我们账号对这门课是已购买 + 学习进度 0%（库里 user_course_relation 有、course_record 没有）
 第3步：需求原文：已购买用户-未开始学习 -&gt; 默认课程介绍，展示课程标题和第一课时封面/视频
 第4步：把手机交还给下一条用例</t>
+        </is>
+      </c>
+      <c r="I95" s="15" t="inlineStr">
+        <is>
+          <t>操作型</t>
         </is>
       </c>
     </row>
@@ -2863,6 +3076,11 @@
 第3步：切到课程列表
 第4步：库里 28 门 0 课时的公开课程，一个都不该出现在列表里（会让列表滚到底再对账）
 第5步：把手机交还给下一条用例</t>
+        </is>
+      </c>
+      <c r="I99" s="14" t="inlineStr">
+        <is>
+          <t>业务规则与数据型</t>
         </is>
       </c>
     </row>
@@ -2954,6 +3172,11 @@
 第6步：把手机交还给下一条用例</t>
         </is>
       </c>
+      <c r="I104" s="14" t="inlineStr">
+        <is>
+          <t>业务规则与数据型</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="D105" s="7" t="n">
@@ -3057,6 +3280,11 @@
 第4步：把手机交还给下一条用例</t>
         </is>
       </c>
+      <c r="I110" s="14" t="inlineStr">
+        <is>
+          <t>业务规则与数据型</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="D111" s="7" t="n">
@@ -3129,6 +3357,11 @@
       <c r="F114" s="7" t="inlineStr"/>
       <c r="G114" s="7" t="inlineStr"/>
       <c r="H114" s="7" t="inlineStr"/>
+      <c r="I114" s="16" t="inlineStr">
+        <is>
+          <t>展示文案型</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="D115" s="7" t="n">
@@ -3239,6 +3472,11 @@
 第3步：中文搜索的关键一步：框架自己敲不了中文，靠点历史词条触发。这个词用工具造过：python tools/search_history_tool.py --user 1966910 --keyword 压铸测试 --add --yes
 第4步：结果页的搜索栏里应当是这个词（= 真的照它搜了）
 第5步：把手机交还给下一条用例</t>
+        </is>
+      </c>
+      <c r="I120" s="15" t="inlineStr">
+        <is>
+          <t>操作型</t>
         </is>
       </c>
     </row>
@@ -3334,6 +3572,11 @@
 第6步：把手机交还给下一条用例</t>
         </is>
       </c>
+      <c r="I125" s="14" t="inlineStr">
+        <is>
+          <t>业务规则与数据型</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="D126" s="7" t="n">
@@ -3439,6 +3682,11 @@
 第2步顺带验证四个 tab 的文案、顺序与默认选中（需求 713341876）—— 单独写"不显示"容易变成一句空断言。</t>
         </is>
       </c>
+      <c r="I131" s="16" t="inlineStr">
+        <is>
+          <t>展示文案型</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="D132" s="5" t="n">
@@ -3527,6 +3775,11 @@
           <t>缺陷 713073541（原文：当用户为普通用户时，搜索结果、个人中心应该不显示普通用户的标签）+ 713295623（普通用户不显示身份标签）；只读。
 第3步是"证明个人中心真的到了"的前置断言 —— 少了它，页面没到也会绿（假绿）。
 没覆盖的半句：搜索结果里也不显示身份标签（关键词结果随线上数据变，容易假红，留给以后）。</t>
+        </is>
+      </c>
+      <c r="I136" s="14" t="inlineStr">
+        <is>
+          <t>业务规则与数据型</t>
         </is>
       </c>
     </row>
@@ -3620,6 +3873,11 @@
 第5步点遮罩是收尾必须：面板 + 键盘会把整页盖住（overlay-mask），不关掉后面「回到首页」点不到任何东西。</t>
         </is>
       </c>
+      <c r="I141" s="15" t="inlineStr">
+        <is>
+          <t>操作型</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="D142" s="5" t="n">
@@ -3725,6 +3983,11 @@
 第4步点的是话题结果页的排序筛选项；第5步的断言不是"验证排序结果"，而是**页面还在** ——
 点一下筛选项就报错的话，那排 tab 会直接不见，这正是那个 bug 的样子。
 排序结果对不对要读数据，框架暂时验不了（记在《缺陷回归候选清单》里）。</t>
+        </is>
+      </c>
+      <c r="I147" s="15" t="inlineStr">
+        <is>
+          <t>操作型</t>
         </is>
       </c>
     </row>
@@ -3830,6 +4093,11 @@
 但「热门推荐」那一栏里该分类的礼品还会显示（另一个模块的问题，已单独记在缺陷回归清单里）。</t>
         </is>
       </c>
+      <c r="I153" s="14" t="inlineStr">
+        <is>
+          <t>业务规则与数据型</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="D154" t="n">
@@ -3928,6 +4196,11 @@
 2026/10/15 真机实测：滚下去后第一张卡 top=-632，切完 tab 回到 top=313（视口高 738）—— 会回顶部。</t>
         </is>
       </c>
+      <c r="I159" s="15" t="inlineStr">
+        <is>
+          <t>操作型</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="D160" t="n">
@@ -4051,6 +4324,11 @@
 第 5-6 步：反向走一遍，回到「最新提问」。第 7 步收尾归位。</t>
         </is>
       </c>
+      <c r="I166" s="15" t="inlineStr">
+        <is>
+          <t>操作型</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="D167" t="n">
@@ -4192,6 +4470,11 @@
 实测（2026/10/16）：后台置顶一条帖子 → 只靠一次「下拉刷新」→ 第一条立刻变「置顶 兄弟」（约 1 秒）；取消置顶后再下拉一次 → 立刻摘掉。
 对照（不刷新就是看不到）：置顶之后**不做任何刷新**去读，列表还是旧的 —— 所以这条测试是灵敏的。
 第 2 步的动作自己会验证刷新真的发生了（转圈的点出现又停、容器位置回原位），没触发会重试两次并报错，不会假装成功。</t>
+        </is>
+      </c>
+      <c r="I173" s="15" t="inlineStr">
+        <is>
+          <t>操作型</t>
         </is>
       </c>
     </row>
@@ -4264,6 +4547,11 @@
 第 4 步先证明那块在；第 5-6 步对内容（**文案口径来自库里那两列**；样例数据改了就把这两格一起改）。</t>
         </is>
       </c>
+      <c r="I177" s="16" t="inlineStr">
+        <is>
+          <t>展示文案型</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="D178" t="n">
@@ -4379,6 +4667,11 @@
 工具：tools/case_copy_counts.py（只读，SELECT）。</t>
         </is>
       </c>
+      <c r="I184" s="14" t="inlineStr">
+        <is>
+          <t>业务规则与数据型</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="D185" t="n">
@@ -4455,6 +4748,11 @@
 样本与口径：案例库卡片标题 .case-list-card-title，源码 components/case-list/index.tsx 里写着`numberOfLines={2}` —— **最多两行**；实测一屏 10 张标题都是 1 行（高 16 / 行高 16），拿它验证「没超过 2 行」是稳的，也能挡住「标题失控换行到三行」这种版面回归。
 量法：把元素内容包进 Range，按「行的顶边」去重后数矩形个数（不依赖 line-height —— 真机上很多元素的 line-height 是 normal，除法会崩；直接数矩形又会被「元素框+文本节点」数成双份）。
 护航那片（.escort-case-desc）是这条缺陷的原始元素，但测试环境没配内容，等数据到位再补。</t>
+        </is>
+      </c>
+      <c r="I189" s="16" t="inlineStr">
+        <is>
+          <t>展示文案型</t>
         </is>
       </c>
     </row>
@@ -4532,6 +4830,11 @@
 量法见动作「检查元素行数」（Range 矩形按行的顶边归并，已用 1 行/7 行两种样本校准过）。</t>
         </is>
       </c>
+      <c r="I193" s="16" t="inlineStr">
+        <is>
+          <t>展示文案型</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="D194" t="n">
@@ -4634,6 +4937,11 @@
 第 6-7 步先滚下去、证明第一块模块标题被滚出视口；第 9 步切完视图它又回到视口里 —— 这就是需求说的「自动回到页面顶部」（源码 EscortSection.tsx 的 switchView 里确实会把 scrollTop 归零）。</t>
         </is>
       </c>
+      <c r="I199" s="15" t="inlineStr">
+        <is>
+          <t>操作型</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="D200" t="n">
@@ -4834,6 +5142,11 @@
           <t>需求 713555327 第 4 条：「案例以竖向列表排布，每一个案例是一张可点击卡片，整个卡片都是可点击区域…点击后跳转案例详情页」；第 5 条：「详情页底部固定悬浮按钮『我也要做』」。
 真机实测（2026/10/16）：列表项 .escort-case-card（3 张，整卡 333×247）；详情页根容器 .escort-case-detail，封面 .ecd-cover-title、描述 .ecd-description、分段内容 .ecd-segments，底部固定条 .ecd-reserve-bar 里写着「我也要做」。
 第 5 步点的是卡片本身（不是卡里的某个小元素）—— 需求要的就是「整卡可点」。</t>
+        </is>
+      </c>
+      <c r="I211" s="15" t="inlineStr">
+        <is>
+          <t>操作型</t>
         </is>
       </c>
     </row>
@@ -4979,6 +5292,11 @@
 第 12、14 步点的问题文案来自后台配置（是是是是是是的 / DSUIOF JUSPFIP）—— 后台改了这几句，就把这两格一起改（报告里会明确说找不到哪句）。</t>
         </is>
       </c>
+      <c r="I220" s="15" t="inlineStr">
+        <is>
+          <t>操作型</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="D221" t="n">
@@ -5225,14 +5543,232 @@
         </is>
       </c>
     </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>ZW_041</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>护航服务介绍：四个区块齐全 + 悬浮件固定可见（需求 713555327 第 1、2 条）</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；不用登录（只读）。护航开了服务内容/服务优势/适用场景各至少 1 条</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>需求 713555327 第 2 条：「服务介绍：包含基础信息、服务内容、服务优势、适用场景」；第 1 条还有半句：「底部悬浮条始终固定在视口底部…包含『立即预约』按钮…客服按钮悬浮固定在屏幕右侧…随页面滚动保持可见」。
+真机实测（2026/10/16，服务介绍视图）：基础信息块 .escort-base-info；三个模块标题 .escort-module-title（正好 3 个：服务内容/服务优势/适用场景）；底部悬浮条 .escort-reserve-bar 里是「立即预约」；右侧悬浮客服按钮 .escort-service-btn（固定定位，图标没文字）。
+第 10-12 步先滚下去，再断言这两个悬浮件**仍然在视口里** —— 这就是需求说的「随页面滚动保持可见」（只断言「存在」抓不到固定定位坏掉的情况）。
+基础信息那块只断言「存在」：它的主标题/副标题在后台是空的（目前只配了背景图），断言具体文案会变成对后台配置的断言。</t>
+        </is>
+      </c>
+      <c r="I237" s="16" t="inlineStr">
+        <is>
+          <t>展示文案型</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="D238" t="n">
+        <v>2</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="D239" t="n">
+        <v>3</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>压铸护航服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="D240" t="n">
+        <v>4</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>检查元素数量</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>.escort-module-title</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="D241" t="n">
+        <v>5</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>服务内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="D242" t="n">
+        <v>6</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>服务优势</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="D243" t="n">
+        <v>7</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>适用场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="D244" t="n">
+        <v>8</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>检查元素存在</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>.escort-base-info</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="D245" t="n">
+        <v>9</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>立即预约</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="D246" t="n">
+        <v>10</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>滑动</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="D247" t="n">
+        <v>11</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>检查元素在视口里</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>.escort-reserve-bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="D248" t="n">
+        <v>12</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>检查元素在视口里</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>.escort-service-btn</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="D249" t="n">
+        <v>13</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="152">
+  <mergeCells count="195">
+    <mergeCell ref="I193:I198"/>
     <mergeCell ref="A48:A53"/>
+    <mergeCell ref="I237:I249"/>
     <mergeCell ref="A114:A119"/>
+    <mergeCell ref="A237:A249"/>
+    <mergeCell ref="I8:I12"/>
     <mergeCell ref="H99:H103"/>
     <mergeCell ref="A131:A135"/>
     <mergeCell ref="B220:B236"/>
     <mergeCell ref="C131:C135"/>
+    <mergeCell ref="I166:I172"/>
     <mergeCell ref="A153:A158"/>
     <mergeCell ref="B30:B47"/>
     <mergeCell ref="H17:H20"/>
@@ -5240,68 +5776,86 @@
     <mergeCell ref="C54:C59"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A159:A165"/>
+    <mergeCell ref="C159:C165"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C159:C165"/>
     <mergeCell ref="H110:H113"/>
     <mergeCell ref="A189:A192"/>
     <mergeCell ref="B13:B16"/>
+    <mergeCell ref="I71:I76"/>
+    <mergeCell ref="I120:I124"/>
     <mergeCell ref="H30:H47"/>
+    <mergeCell ref="I17:I20"/>
     <mergeCell ref="A17:A20"/>
     <mergeCell ref="C173:C176"/>
     <mergeCell ref="C60:C63"/>
     <mergeCell ref="C64:C70"/>
     <mergeCell ref="A147:A152"/>
     <mergeCell ref="B95:B98"/>
+    <mergeCell ref="I220:I236"/>
+    <mergeCell ref="I48:I53"/>
+    <mergeCell ref="I114:I119"/>
+    <mergeCell ref="I60:I63"/>
     <mergeCell ref="B8:B12"/>
-    <mergeCell ref="H48:H53"/>
     <mergeCell ref="H104:H109"/>
     <mergeCell ref="A99:A103"/>
+    <mergeCell ref="H48:H53"/>
+    <mergeCell ref="I25:I29"/>
     <mergeCell ref="H64:H70"/>
     <mergeCell ref="B136:B140"/>
     <mergeCell ref="B104:B109"/>
+    <mergeCell ref="I131:I135"/>
     <mergeCell ref="H199:H210"/>
+    <mergeCell ref="I189:I192"/>
     <mergeCell ref="B166:B172"/>
     <mergeCell ref="A136:A140"/>
     <mergeCell ref="B153:B158"/>
     <mergeCell ref="H131:H135"/>
     <mergeCell ref="H147:H152"/>
+    <mergeCell ref="I95:I98"/>
     <mergeCell ref="H54:H59"/>
     <mergeCell ref="B177:B183"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="B71:B76"/>
     <mergeCell ref="C4:C7"/>
+    <mergeCell ref="H220:H236"/>
     <mergeCell ref="B211:B219"/>
     <mergeCell ref="B17:B20"/>
-    <mergeCell ref="H220:H236"/>
     <mergeCell ref="C136:C140"/>
     <mergeCell ref="A21:A24"/>
     <mergeCell ref="H173:H176"/>
     <mergeCell ref="C21:C24"/>
+    <mergeCell ref="I125:I130"/>
     <mergeCell ref="A193:A198"/>
     <mergeCell ref="C193:C198"/>
     <mergeCell ref="A89:A94"/>
     <mergeCell ref="H8:H12"/>
     <mergeCell ref="B60:B63"/>
+    <mergeCell ref="I136:I140"/>
+    <mergeCell ref="B199:B210"/>
     <mergeCell ref="B25:B29"/>
-    <mergeCell ref="B199:B210"/>
     <mergeCell ref="C184:C188"/>
     <mergeCell ref="A64:A70"/>
     <mergeCell ref="C153:C158"/>
+    <mergeCell ref="C237:C249"/>
     <mergeCell ref="H95:H98"/>
     <mergeCell ref="C95:C98"/>
+    <mergeCell ref="I80:I88"/>
     <mergeCell ref="A30:A47"/>
     <mergeCell ref="B4:B7"/>
+    <mergeCell ref="B237:B249"/>
+    <mergeCell ref="I153:I158"/>
+    <mergeCell ref="B110:B113"/>
     <mergeCell ref="C48:C53"/>
-    <mergeCell ref="B110:B113"/>
     <mergeCell ref="C189:C192"/>
+    <mergeCell ref="I159:I165"/>
     <mergeCell ref="C120:C124"/>
     <mergeCell ref="A220:A236"/>
+    <mergeCell ref="C220:C236"/>
+    <mergeCell ref="C211:C219"/>
     <mergeCell ref="B141:B146"/>
-    <mergeCell ref="C211:C219"/>
+    <mergeCell ref="A110:A113"/>
     <mergeCell ref="H4:H7"/>
     <mergeCell ref="B193:B198"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="C220:C236"/>
     <mergeCell ref="H159:H165"/>
     <mergeCell ref="A173:A176"/>
     <mergeCell ref="A60:A63"/>
@@ -5310,82 +5864,119 @@
     <mergeCell ref="A199:A210"/>
     <mergeCell ref="H77:H79"/>
     <mergeCell ref="C141:C146"/>
+    <mergeCell ref="H120:H124"/>
     <mergeCell ref="H193:H198"/>
-    <mergeCell ref="H120:H124"/>
     <mergeCell ref="H114:H119"/>
     <mergeCell ref="H89:H94"/>
     <mergeCell ref="H80:H88"/>
     <mergeCell ref="B48:B53"/>
     <mergeCell ref="B64:B70"/>
     <mergeCell ref="H184:H188"/>
+    <mergeCell ref="I211:I219"/>
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="B80:B88"/>
+    <mergeCell ref="I21:I24"/>
+    <mergeCell ref="I141:I146"/>
+    <mergeCell ref="H237:H249"/>
+    <mergeCell ref="H60:H63"/>
+    <mergeCell ref="B21:B24"/>
     <mergeCell ref="B131:B135"/>
-    <mergeCell ref="H60:H63"/>
     <mergeCell ref="C114:C119"/>
     <mergeCell ref="B147:B152"/>
     <mergeCell ref="C30:C47"/>
     <mergeCell ref="A104:A109"/>
     <mergeCell ref="B159:B165"/>
     <mergeCell ref="H189:H192"/>
+    <mergeCell ref="B189:B192"/>
     <mergeCell ref="A166:A172"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="I30:I47"/>
+    <mergeCell ref="C13:C16"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="C13:C16"/>
-    <mergeCell ref="B77:B79"/>
     <mergeCell ref="C166:C172"/>
-    <mergeCell ref="B189:B192"/>
     <mergeCell ref="H211:H219"/>
     <mergeCell ref="H25:H29"/>
+    <mergeCell ref="I184:I188"/>
     <mergeCell ref="B173:B176"/>
     <mergeCell ref="C125:C130"/>
     <mergeCell ref="A177:A183"/>
     <mergeCell ref="C177:C183"/>
     <mergeCell ref="A120:A124"/>
+    <mergeCell ref="I2:I3"/>
     <mergeCell ref="H141:H146"/>
     <mergeCell ref="A80:A88"/>
+    <mergeCell ref="I89:I94"/>
     <mergeCell ref="C80:C88"/>
     <mergeCell ref="C199:C210"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="A184:A188"/>
     <mergeCell ref="C8:C12"/>
-    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="I177:I183"/>
     <mergeCell ref="H125:H130"/>
+    <mergeCell ref="I104:I109"/>
     <mergeCell ref="B99:B103"/>
+    <mergeCell ref="C89:C94"/>
+    <mergeCell ref="I64:I70"/>
+    <mergeCell ref="I54:I59"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="C104:C109"/>
     <mergeCell ref="C147:C152"/>
-    <mergeCell ref="C104:C109"/>
-    <mergeCell ref="C89:C94"/>
-    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="I199:I210"/>
     <mergeCell ref="H136:H140"/>
     <mergeCell ref="H21:H24"/>
     <mergeCell ref="A77:A79"/>
+    <mergeCell ref="I147:I152"/>
     <mergeCell ref="A71:A76"/>
     <mergeCell ref="C71:C76"/>
     <mergeCell ref="A211:A219"/>
     <mergeCell ref="H166:H172"/>
+    <mergeCell ref="I99:I103"/>
+    <mergeCell ref="I77:I79"/>
     <mergeCell ref="C17:C20"/>
     <mergeCell ref="H13:H16"/>
     <mergeCell ref="H153:H158"/>
     <mergeCell ref="B184:B188"/>
+    <mergeCell ref="I173:I176"/>
     <mergeCell ref="C110:C113"/>
     <mergeCell ref="B120:B124"/>
     <mergeCell ref="A141:A146"/>
     <mergeCell ref="H177:H183"/>
     <mergeCell ref="B89:B94"/>
+    <mergeCell ref="I13:I16"/>
+    <mergeCell ref="I4:I7"/>
     <mergeCell ref="A25:A29"/>
     <mergeCell ref="C25:C29"/>
     <mergeCell ref="A125:A130"/>
+    <mergeCell ref="I110:I113"/>
     <mergeCell ref="C99:C103"/>
     <mergeCell ref="H71:H76"/>
     <mergeCell ref="B54:B59"/>
     <mergeCell ref="B114:B119"/>
   </mergeCells>
-  <dataValidations count="2">
+  <conditionalFormatting sqref="I2:I1000">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+      <formula>"操作型"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
+      <formula>"展示文案型"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
+      <formula>"业务规则与数据型"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
+      <formula>"框架自检型"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
     <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个动作" error="只能从列表里选。全部可选项见「动作清单」工作表；确实需要新动作时找 AI 加。" promptTitle="动作" prompt="点右边的小箭头选一个动作（可选项见「动作清单」工作表）" type="list">
       <formula1>='动作清单'!$A$2:$A$61</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="序号不合法" error="只能填 1、2、3… 这样的正整数。" promptTitle="步骤序号" prompt="同一用例内的顺序号：1、2、3…（要么全写，要么全不写，都不写就按表格先后顺序跑）" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="没有这个类型" error="只能从这四个里选：操作型 / 展示文案型 / 业务规则与数据型 / 框架自检型。口径见「填写说明」工作表。" promptTitle="类型分类" prompt="这条用例主要在验什么：操作型 / 展示文案型 / 业务规则与数据型 / 框架自检型（可不填，但建议填 —— 挑着跑时按它筛）" type="list">
+      <formula1>"操作型,展示文案型,业务规则与数据型,框架自检型"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5453,6 +6044,8 @@
           <t>回到首页</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5480,6 +6073,8 @@
           <t>切到用户中心</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5507,6 +6102,8 @@
           <t>打开积分商城</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5534,6 +6131,8 @@
           <t>打开学习中心专栏</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5566,6 +6165,7 @@
           <t>顶部栏名称（只能填：课程 / 专栏 / 压铸百科）</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>专栏</t>
@@ -5593,6 +6193,8 @@
           <t>返回上一页</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5620,6 +6222,8 @@
           <t>点主页按钮</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5647,6 +6251,8 @@
           <t>打开搜索页</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5674,6 +6280,8 @@
           <t>打开案例库</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5706,6 +6314,7 @@
           <t>课程名</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>717</t>
@@ -5738,6 +6347,7 @@
           <t>关键词</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -5770,6 +6380,7 @@
           <t>关键词</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -5797,6 +6408,8 @@
           <t>执行搜索</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5829,6 +6442,7 @@
           <t>词</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>压铸测试</t>
@@ -5856,6 +6470,8 @@
           <t>打开第一个热门话题</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5883,6 +6499,8 @@
           <t>打开第一个帖子</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5910,6 +6528,8 @@
           <t>打开第一张专栏</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5937,6 +6557,8 @@
           <t>打开第一个案例</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5964,6 +6586,8 @@
           <t>打开案例库介绍长图</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -5996,6 +6620,7 @@
           <t>案例名</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>填充任务1</t>
@@ -6176,6 +6801,7 @@
           <t>筛选栏名称（只能填：最新提问 / 推荐 / 精选问答 / 我的关注）</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>推荐</t>
@@ -6203,6 +6829,8 @@
           <t>下拉刷新</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6235,6 +6863,7 @@
           <t>毫秒</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>2000（= 等 2 秒）</t>
@@ -6262,6 +6891,8 @@
           <t>打印页面文字</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6294,6 +6925,7 @@
           <t>范围（只能填：全量 / 只看有文字）</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>只看有文字</t>
@@ -6326,6 +6958,7 @@
           <t>文字</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>答对最多可赢积分</t>
@@ -6358,6 +6991,7 @@
           <t>文字</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>最新提问（搜索页上不该有）</t>
@@ -6427,6 +7061,7 @@
           <t>选择器</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>.search-container</t>
@@ -6459,6 +7094,7 @@
           <t>选择器</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>.activity-quiz-page</t>
@@ -6491,6 +7127,7 @@
           <t>选择器</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>.flow-item</t>
@@ -6523,6 +7160,7 @@
           <t>选择器</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>.flow-item</t>
@@ -6661,6 +7299,8 @@
           <t>记住积分余额</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>（不用填参数；之后配一步「检查积分增加」）</t>
@@ -6693,6 +7333,7 @@
           <t>期望增加（分）</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>1021（配合上一步「记住积分余额」；少发/多发/没发都会红）</t>
@@ -6720,6 +7361,8 @@
           <t>检查活动入口</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6747,6 +7390,8 @@
           <t>检查首页筛选栏顺序</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6774,6 +7419,8 @@
           <t>检查回到顶部按钮</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6801,6 +7448,8 @@
           <t>检查答题页</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6828,6 +7477,8 @@
           <t>检查案例库列表</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6860,6 +7511,7 @@
           <t>最多比几张（可不填）</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>3</t>
@@ -6887,6 +7539,8 @@
           <t>检查案例详情页</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6914,6 +7568,8 @@
           <t>检查案例库介绍长图</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6946,6 +7602,7 @@
           <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>课程介绍</t>
@@ -6973,6 +7630,8 @@
           <t>检查0课时课程不显示</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7005,6 +7664,7 @@
           <t>课程名</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>7.8课程new</t>
@@ -7032,6 +7692,8 @@
           <t>打开答题活动</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7059,6 +7721,8 @@
           <t>逐题作答</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7086,6 +7750,8 @@
           <t>提交答卷</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7118,6 +7784,7 @@
           <t>活动名</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>Z-B4-答题角标</t>
@@ -7182,6 +7849,8 @@
           <t>复制当前案例</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7214,6 +7883,7 @@
           <t>分类名</t>
         </is>
       </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>实物商品（跟后台一字不差；跑完记得用「还原礼品分类」改回去）</t>
@@ -7246,6 +7916,7 @@
           <t>分类名</t>
         </is>
       </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>实物商品（跟「屏蔽礼品分类」里填的那个名字一样）</t>
@@ -7273,395 +7944,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A58"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <cols>
-    <col width="99.875" customWidth="1" style="5" min="1" max="1"/>
-    <col width="9" customWidth="1" style="5" min="2" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>怎么用这张表（零基础版）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>【表长什么样】8 列，分两种：</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  按用例的 4 列（表里并成一格，只有第一步那行有值）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     用例编号 | 用例标题 | 前置条件 | 备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  按步骤的 4 列（每一行都要填）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     步骤序号 | 动作 | 参数1 | 参数2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  编号格式：ZW_001、ZW_002…（前缀 + 三位数字，唯一就行；填错的编号会让这条用例对不上号）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>1. 一行 = 一个步骤。同一个「用例编号」的若干行，按「步骤序号」顺序执行；它们一起算一条用例。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2. 一条用例怎么摆：第一行写「用例编号 + 用例标题 + 前置条件 + 备注」，</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   下面几行的这四列并成一格、空着就行 —— 表上看起来就是「一案一块」，</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   一眼数得出有几条用例、每条几步、每条要怎么准备。每行都要填的是「步骤序号」和「动作」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   （按这个排版，导出时编号空着的行会自动并到上一条用例；但第一行数据必须写编号，否则整表报错。）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>2b.「前置条件」写「跑这条之前手机得在什么状态」（要不要先登录、首页得有什么卡），</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   它不是动作、不会被自动执行 —— 是给人看的，也是「这条挂了先查什么」的线索。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>2c.「备注」是整条用例的备注（也并成一格）。某一步自己的说明写在同一格里，</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   用「第2步：…」开头即可。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>3. 「动作」只能填「动作清单」工作表里列出的名字 —— 填别的会在导出时报错，不会静默跳过。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>3b. 有几类参数要填数据里的名字（课程名 / 案例名 / 活动名），一字不差才行；</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    候选值在「名称候选」工作表里，直接复制粘贴即可（刷新它：python tools/export_cases.py --dropdown）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>4. 「参数1 / 参数2」按动作需要填，不用就留空。填多了（该动作用不到）也会报错，防手滑；</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   参数名后面写着「（可不填）」的，留空就走默认值（例如「第几个」留空 = 第 1 个）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>5. 「备注」随便写，只出现在日志和报告里，不影响执行（但它会显示在报告里，写清需求号很有用）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>6. 填完执行：python run.py      （它会先自动把本表导出成 json，再跑用例）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   只想跑表格里的某一条：python run.py -k 活动入口_001</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>7. 每条用例开头都先用「回到首页」把起点摆正；会把手机停在二级页（搜索页/详情页/答题页）的用例，</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   最后再补一步「回到首页」把手机交还。原因：表里的用例共用同一部手机，</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   上一条停在二级页上，下一条可能报「找不到底部 tab」—— 开头摆正 + 结尾交还就不受影响。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>8. 「动作」列是下拉框（点单元格右边的小箭头选），可选项来自「动作清单」工作表；</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   「步骤序号」列只接受 1、2、3… 这样的正整数。填错的动作名根本选不出来，省一轮报错。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>8b. 自己新加的行不会自动并格。改完想让它并回去、顺便刷新下拉框，跑一次：</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    python tools/export_cases.py --dropdown    （只动排版，不动你填的内容；Excel 开着这份表时先关掉）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>9. 不知道「检查文字显示」该填哪段字？先加一行「打印页面文字」跑一次 ——</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   当前屏幕上看得见的文字会打进日志，照着抄就行（挑完把它删掉即可）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>默认禁止（安全阀，避免手滑把真实数据改了）</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="27" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 「点文字」不能点这些字：提交、兑换、签到、下单、支付、购买、领取、抽奖、报名、删除、退出登录、退款、取消订单</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="27" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     原因：这些操作会改真实数据/消耗真实积分。真要测它们，得单独写用例并显式打开开关，不能靠表格里写一行就触发。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 「打开答题活动」只打开页面，不选选项、不提交（选选项会消耗答题机会）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>要测「会改数据」的操作？开着开关跑（owner 2026/10/12 同意）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 开关就是一句环境变量：跑之前先执行  $env:UITEST_ALLOW_SUBMIT="1"  （PowerShell）</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     不设这个开关时，下面这两个动作会直接报错，不会偷偷执行，也不会假装跳过。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 「复位答题记录」（参数1=活动名）：删掉该活动在测试库里留下的答题记录。</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     默认只预览不删；开了开关才真删。跑完写数据的用例，务必用它把记录清干净。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 「提交答卷」：真的提交一次，用来测「提交后按钮变成已提交已参加」这条需求。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 「逐题作答」「检查答题记录数」不需要开关：前者只改前端选中态（不写库），后者是只读。</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 写链路的标准写法（照抄即可）：回到首页 → 打开答题活动 → 复位答题记录(活动名) →</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     逐题作答 → 检查文字显示(已答) → 提交答卷 → 检查文字显示(已参加) →</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     检查答题记录数(活动名 / 1) → 复位答题记录(活动名) → 回到首页</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="27" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 现成模板：test_case/suprecast_app/test_quiz_submit.js（跑法：$env:UITEST_ALLOW_SUBMIT="1"; python run.py -k 答题写链路）</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>已知限制（诚实标注，别误读成框架不行）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 搜索关键词只能是字母/数字/下划线/点/连字符：关键词是通过 adb 发过去的，adb 发中文不报错但不生效。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 「点文字」点的是屏幕上看得见的文字；同名文字有多个时点第 1 个。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 断言的等待时间写死在框架里（文字类 8 秒、元素类 8 秒），表格里暂时改不了。</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 「复位答题记录」只能删答题相关的两张表；别的写操作（积分兑换、签到）还没做复位手段。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9301,6 +9583,7 @@
           <t>方案一变形</t>
         </is>
       </c>
+      <c r="C96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9313,6 +9596,7 @@
           <t>仅凝固</t>
         </is>
       </c>
+      <c r="C97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9325,6 +9609,7 @@
           <t>仅充填2</t>
         </is>
       </c>
+      <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9337,6 +9622,7 @@
           <t>充填凝固应力</t>
         </is>
       </c>
+      <c r="C99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9349,6 +9635,7 @@
           <t>充填凝固应力1</t>
         </is>
       </c>
+      <c r="C100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9361,6 +9648,7 @@
           <t>7201744-孙</t>
         </is>
       </c>
+      <c r="C101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9373,6 +9661,7 @@
           <t>带组织性能结果</t>
         </is>
       </c>
+      <c r="C102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9385,6 +9674,7 @@
           <t>充填-排气</t>
         </is>
       </c>
+      <c r="C103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9397,6 +9687,7 @@
           <t>1月 20250115</t>
         </is>
       </c>
+      <c r="C104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9409,6 +9700,7 @@
           <t>紫色1</t>
         </is>
       </c>
+      <c r="C105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9421,6 +9713,7 @@
           <t>内部数据6</t>
         </is>
       </c>
+      <c r="C106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9433,6 +9726,7 @@
           <t>1QQ区qqqqq</t>
         </is>
       </c>
+      <c r="C107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9445,6 +9739,7 @@
           <t>重力铸造-重力砂型-0602-163625-仅充填仅浏览-重力铸造-重力砂型-0602-163625</t>
         </is>
       </c>
+      <c r="C108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9457,6 +9752,7 @@
           <t>重力铸造-重力砂型-0602-163625-充填凝固0602_165141-仅浏览</t>
         </is>
       </c>
+      <c r="C109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9469,6 +9765,7 @@
           <t>COPY3</t>
         </is>
       </c>
+      <c r="C110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9481,6 +9778,7 @@
           <t>3月26测试 私有材料分享(copy)</t>
         </is>
       </c>
+      <c r="C111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9493,6 +9791,7 @@
           <t>内部数据-虚拟模具</t>
         </is>
       </c>
+      <c r="C112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9505,6 +9804,7 @@
           <t>内部数据</t>
         </is>
       </c>
+      <c r="C113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9517,6 +9817,7 @@
           <t>鹅鹅鹅</t>
         </is>
       </c>
+      <c r="C114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9529,6 +9830,7 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9541,6 +9843,7 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9553,6 +9856,7 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9565,6 +9869,7 @@
           <t>仅凝固+应力-选择点2</t>
         </is>
       </c>
+      <c r="C118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9577,6 +9882,7 @@
           <t>仅凝固1</t>
         </is>
       </c>
+      <c r="C119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -9589,6 +9895,7 @@
           <t>循环凝固</t>
         </is>
       </c>
+      <c r="C120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -9601,6 +9908,7 @@
           <t>131231</t>
         </is>
       </c>
+      <c r="C121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9613,6 +9921,7 @@
           <t>131231</t>
         </is>
       </c>
+      <c r="C122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9625,6 +9934,7 @@
           <t>循环凝固-热循环</t>
         </is>
       </c>
+      <c r="C123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9637,6 +9947,7 @@
           <t>6668</t>
         </is>
       </c>
+      <c r="C124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9649,6 +9960,7 @@
           <t>6668</t>
         </is>
       </c>
+      <c r="C125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9661,6 +9973,7 @@
           <t>填充任务1</t>
         </is>
       </c>
+      <c r="C126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9673,6 +9986,7 @@
           <t>0605测试</t>
         </is>
       </c>
+      <c r="C127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9685,6 +9999,7 @@
           <t>循环凝固+应力+选点1</t>
         </is>
       </c>
+      <c r="C128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9697,6 +10012,7 @@
           <t>料筒(copy)</t>
         </is>
       </c>
+      <c r="C129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9709,6 +10025,7 @@
           <t>仅凝固</t>
         </is>
       </c>
+      <c r="C130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9721,6 +10038,7 @@
           <t>#713392277</t>
         </is>
       </c>
+      <c r="C131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9733,6 +10051,7 @@
           <t>？？？？</t>
         </is>
       </c>
+      <c r="C132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9745,6 +10064,7 @@
           <t>复制任务失败问题测试-分享</t>
         </is>
       </c>
+      <c r="C133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9757,6 +10077,7 @@
           <t>浇口充填-高级模式</t>
         </is>
       </c>
+      <c r="C134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9769,6 +10090,7 @@
           <t>4.17</t>
         </is>
       </c>
+      <c r="C135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9781,6 +10103,7 @@
           <t>热热热热</t>
         </is>
       </c>
+      <c r="C136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9793,6 +10116,7 @@
           <t>eeee</t>
         </is>
       </c>
+      <c r="C137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9805,6 +10129,7 @@
           <t>亲亲</t>
         </is>
       </c>
+      <c r="C138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9817,6 +10142,7 @@
           <t>3333 私有曲线</t>
         </is>
       </c>
+      <c r="C139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9829,6 +10155,7 @@
           <t>v2</t>
         </is>
       </c>
+      <c r="C140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9841,6 +10168,7 @@
           <t>111111</t>
         </is>
       </c>
+      <c r="C141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9853,6 +10181,7 @@
           <t>测试二级页面案例111111111111111111111111111</t>
         </is>
       </c>
+      <c r="C142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9865,6 +10194,7 @@
           <t>分享高压 2</t>
         </is>
       </c>
+      <c r="C143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9877,6 +10207,7 @@
           <t>料筒充填</t>
         </is>
       </c>
+      <c r="C144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9889,6 +10220,7 @@
           <t>料筒充填1</t>
         </is>
       </c>
+      <c r="C145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9901,6 +10233,7 @@
           <t>料筒分享</t>
         </is>
       </c>
+      <c r="C146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9913,6 +10246,7 @@
           <t>1WWWW</t>
         </is>
       </c>
+      <c r="C147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9925,6 +10259,7 @@
           <t>凝固应力</t>
         </is>
       </c>
+      <c r="C148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9937,6 +10272,7 @@
           <t>模拟汽车</t>
         </is>
       </c>
+      <c r="C149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9949,6 +10285,7 @@
           <t>模拟汽车减震</t>
         </is>
       </c>
+      <c r="C150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9961,6 +10298,7 @@
           <t>多浇口充填(粒子数量10)</t>
         </is>
       </c>
+      <c r="C151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9968,6 +10306,7 @@
           <t>（说明）</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
           <t>课程那张表里的「我们账号买没买」按 user_id=1966910（config/env.yaml）判断</t>
@@ -9980,6 +10319,7 @@
           <t>（说明）</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
           <t>注意：这些课程名在库里有多门同名，按名字打开只会命中第一门 —— 012345678901234567890123456789、付费课程1、免费课程、免费课程1、无敌贵的课程、测试封面图、测试封面图-修改、测试验证课时bug</t>
@@ -9992,9 +10332,473 @@
           <t>（说明）</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
           <t>案例共 56 条，已全部列出</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>怎么用这张表（零基础版）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【表长什么样】9 列，分两种：</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  按用例的 5 列（表里并成一格，只有第一步那行有值）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     用例编号 | 用例标题 | 前置条件 | 备注 | 类型分类</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  按步骤的 4 列（每一行都要填）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     步骤序号 | 动作 | 参数1 | 参数2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  编号格式：ZW_001、ZW_002…（前缀 + 三位数字，唯一就行；填错的编号会让这条用例对不上号）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1. 一行 = 一个步骤。同一个「用例编号」的若干行，按「步骤序号」顺序执行；它们一起算一条用例。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2. 一条用例怎么摆：第一行写「用例编号 + 用例标题 + 前置条件 + 备注」，</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   下面几行的这四列并成一格、空着就行 —— 表上看起来就是「一案一块」，</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   一眼数得出有几条用例、每条几步、每条要怎么准备。每行都要填的是「步骤序号」和「动作」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   （按这个排版，导出时编号空着的行会自动并到上一条用例；但第一行数据必须写编号，否则整表报错。）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2b.「前置条件」写「跑这条之前手机得在什么状态」（要不要先登录、首页得有什么卡），</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   它不是动作、不会被自动执行 —— 是给人看的，也是「这条挂了先查什么」的线索。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2c.「备注」是整条用例的备注（也并成一格）。某一步自己的说明写在同一格里，</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   用「第2步：…」开头即可。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2d.「类型分类」是可选的（也并成一格，下拉框里只有四个值）—— 说的是「这条用例主要在验什么」：</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     操作型          走得通、点得动、切得过来（页面到没到、点了有没有反应、滚动/选中态对不对）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     展示文案型      需求规定的字、字段、顺序、条数出现在页面上没有</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     业务规则与数据型 条件、权限、状态机、配置联动、跟数据库对账（会写数据的写链路也算这类）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     框架自检型      把表格能填的动作挨个跑一遍，验「这张表 + 这些动作」本身还使不使得</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     （表里照这个值上了底色，一眼能看出哪条是哪类：淡蓝 = 操作型、淡绿 = 展示文案型、</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       淡橙 = 业务规则与数据型、淡灰 = 框架自检型。改了类型，底色自动跟着变）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   它只影响怎么挑着跑和统计，不影响执行：改版/换设备后先跑「操作型」当冒烟；</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   发版回归跑「展示文案型 + 业务规则与数据型」。不填也能跑，导出时会给一句建议。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3. 「动作」只能填「动作清单」工作表里列出的名字 —— 填别的会在导出时报错，不会静默跳过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3b. 有几类参数要填数据里的名字（课程名 / 案例名 / 活动名），一字不差才行；</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    候选值在「名称候选」工作表里，直接复制粘贴即可（刷新它：python tools/export_cases.py --dropdown）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4. 「参数1 / 参数2」按动作需要填，不用就留空。填多了（该动作用不到）也会报错，防手滑；</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   参数名后面写着「（可不填）」的，留空就走默认值（例如「第几个」留空 = 第 1 个）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>5. 「备注」随便写，只出现在日志和报告里，不影响执行（但它会显示在报告里，写清需求号很有用）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>6. 填完执行：python run.py      （它会先自动把本表导出成 json，再跑用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   只想跑表格里的某一条：python run.py -k ZW_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>7. 每条用例开头都先用「回到首页」把起点摆正；会把手机停在二级页（搜索页/详情页/答题页）的用例，</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   最后再补一步「回到首页」把手机交还。原因：表里的用例共用同一部手机，</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   上一条停在二级页上，下一条可能报「找不到底部 tab」—— 开头摆正 + 结尾交还就不受影响。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>8. 「动作」列和「类型分类」列都是下拉框（点单元格右边的小箭头选）：动作的可选项来自</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   「动作清单」工作表，类型的可选项就是上面那四个；「步骤序号」列只接受 1、2、3… 这样的正整数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   填错的动作名根本选不出来，省一轮报错。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>8b. 自己新加的行不会自动并格。改完想让它并回去、顺便刷新下拉框，跑一次：</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    python tools/export_cases.py --dropdown    （只动排版，不动你填的内容；Excel 开着这份表时先关掉）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>9. 不知道「检查文字显示」该填哪段字？先加一行「打印页面文字」跑一次 ——</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   当前屏幕上看得见的文字会打进日志，照着抄就行（挑完把它删掉即可）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>默认禁止（安全阀，避免手滑把真实数据改了）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 「点文字」不能点这些字：提交、兑换、签到、下单、支付、购买、领取、抽奖、报名、删除、退出登录、退款、取消订单</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     原因：这些操作会改真实数据/消耗真实积分。真要测它们，得单独写用例并显式打开开关，不能靠表格里写一行就触发。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 「打开答题活动」只打开页面，不选选项、不提交（选选项会消耗答题机会）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>要测「会改数据」的操作？开着开关跑（owner 2026/10/12 同意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 开关就是一句环境变量：跑之前先执行  $env:UITEST_ALLOW_SUBMIT="1"  （PowerShell）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     不设这个开关时，下面这两个动作会直接报错，不会偷偷执行，也不会假装跳过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 「复位答题记录」（参数1=活动名）：删掉该活动在测试库里留下的答题记录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     默认只预览不删；开了开关才真删。跑完写数据的用例，务必用它把记录清干净。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 「提交答卷」：真的提交一次，用来测「提交后按钮变成已提交已参加」这条需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 「逐题作答」「检查答题记录数」不需要开关：前者只改前端选中态（不写库），后者是只读。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 写链路的标准写法（照抄即可）：回到首页 → 打开答题活动 → 复位答题记录(活动名) →</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     逐题作答 → 检查文字显示(已答) → 提交答卷 → 检查文字显示(已参加) →</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     检查答题记录数(活动名 / 1) → 复位答题记录(活动名) → 回到首页</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 现成模板：test_case/suprecast_app/test_quiz_submit.js（跑法：$env:UITEST_ALLOW_SUBMIT="1"; python run.py -k 答题写链路）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>已知限制（诚实标注，别误读成框架不行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 搜索关键词只能是字母/数字/下划线/点/连字符：关键词是通过 adb 发过去的，adb 发中文不报错但不生效。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 「点文字」点的是屏幕上看得见的文字；同名文字有多个时点第 1 个。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 断言的等待时间写死在框架里（文字类 8 秒、元素类 8 秒），表格里暂时改不了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 「复位答题记录」只能删答题相关的两张表；别的写操作（积分兑换、签到）还没做复位手段。</t>
         </is>
       </c>
     </row>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="动作清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="名称候选" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="填写说明" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动作清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名称候选" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1195,7 +1195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I249"/>
+  <dimension ref="A1:I264"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5756,8 +5756,262 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>ZW_042</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>护航预约弹窗：四个字段齐全、空表单提交被拦下（需求 713555353）</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；不用登录（只读：**空表单点提交不会发请求**，源码里校验没过就直接 return）</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>1</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>需求 713555353（已关闭）：「2、表单内容：姓名、联系方式、期望交付时间、产品和需求描述（选填）…7、提交预约：全部字段校验通过后，方可点击，否则 toast 提示『请先正确填写信息』」。
+真机实测（2026/10/16）：弹窗 .reserve-popup，四行字段文案是「姓名 / 手机号 / 期望交付时间 / 产品和需求描述（选填）」，描述框右下角有「0/300」计数；空表单时提交按钮带 `reserve-popup-submit-disabled` 类。
+**为什么只测「填错/没填」这一半**：在测试环境提交一次会**真的产生预约记录并给管理员发短信**（需求 1195 那张通知表里写着「用户提交护航服务预约」要发短信）—— 那是外部副作用，不该由一条表格用例随手触发。所以成功态（成功弹窗/回显/「我知道了」）这条用例**不覆盖**，留给你手动验一次或将来配测试收件人。
+第 12 步点提交时表单是**空的**（源码：`validate()` 没过就 `return`，不发请求）；第 13 步断言没切成「预约提交成功」—— 这就是「被拦下了」的可观测证据。（那句 toast 是**原生**提示、不在网页 DOM 里，所以只能靠截图看，没写成断言。）
+第 14 步用弹窗自带的关闭按钮 .reserve-popup-close 收起弹窗 —— **不是**点蒙层：实测蒙层中心被弹窗面板压着，框架会如实报「点不到：被 … 盖住了」（那是正确行为，不是 bug）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="D251" t="n">
+        <v>2</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="D252" t="n">
+        <v>3</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>压铸护航服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="D253" t="n">
+        <v>4</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>立即预约</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="D254" t="n">
+        <v>5</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>检查元素数量</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>.reserve-popup</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="D255" t="n">
+        <v>6</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="D256" t="n">
+        <v>7</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>手机号</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="D257" t="n">
+        <v>8</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>期望交付时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="D258" t="n">
+        <v>9</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>产品和需求描述（选填）</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="D259" t="n">
+        <v>10</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>0/300</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="D260" t="n">
+        <v>11</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>检查元素数量</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>.reserve-popup-submit-disabled</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="D261" t="n">
+        <v>12</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>点选择器</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>.reserve-popup-submit</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="D262" t="n">
+        <v>13</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>检查文字不显示</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>预约提交成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="D263" t="n">
+        <v>14</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>点选择器</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>.reserve-popup-close</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="D264" t="n">
+        <v>15</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="195">
+  <mergeCells count="200">
     <mergeCell ref="I193:I198"/>
     <mergeCell ref="A48:A53"/>
     <mergeCell ref="I237:I249"/>
@@ -5765,6 +6019,8 @@
     <mergeCell ref="A237:A249"/>
     <mergeCell ref="I8:I12"/>
     <mergeCell ref="H99:H103"/>
+    <mergeCell ref="A250:A264"/>
+    <mergeCell ref="C250:C264"/>
     <mergeCell ref="A131:A135"/>
     <mergeCell ref="B220:B236"/>
     <mergeCell ref="C131:C135"/>
@@ -5790,15 +6046,15 @@
     <mergeCell ref="C60:C63"/>
     <mergeCell ref="C64:C70"/>
     <mergeCell ref="A147:A152"/>
+    <mergeCell ref="I220:I236"/>
     <mergeCell ref="B95:B98"/>
-    <mergeCell ref="I220:I236"/>
     <mergeCell ref="I48:I53"/>
     <mergeCell ref="I114:I119"/>
     <mergeCell ref="I60:I63"/>
     <mergeCell ref="B8:B12"/>
+    <mergeCell ref="H48:H53"/>
     <mergeCell ref="H104:H109"/>
     <mergeCell ref="A99:A103"/>
-    <mergeCell ref="H48:H53"/>
     <mergeCell ref="I25:I29"/>
     <mergeCell ref="H64:H70"/>
     <mergeCell ref="B136:B140"/>
@@ -5841,6 +6097,7 @@
     <mergeCell ref="C95:C98"/>
     <mergeCell ref="I80:I88"/>
     <mergeCell ref="A30:A47"/>
+    <mergeCell ref="I250:I264"/>
     <mergeCell ref="B4:B7"/>
     <mergeCell ref="B237:B249"/>
     <mergeCell ref="I153:I158"/>
@@ -5850,11 +6107,11 @@
     <mergeCell ref="I159:I165"/>
     <mergeCell ref="C120:C124"/>
     <mergeCell ref="A220:A236"/>
+    <mergeCell ref="B141:B146"/>
     <mergeCell ref="C220:C236"/>
     <mergeCell ref="C211:C219"/>
-    <mergeCell ref="B141:B146"/>
+    <mergeCell ref="H4:H7"/>
     <mergeCell ref="A110:A113"/>
-    <mergeCell ref="H4:H7"/>
     <mergeCell ref="B193:B198"/>
     <mergeCell ref="H159:H165"/>
     <mergeCell ref="A173:A176"/>
@@ -5864,8 +6121,8 @@
     <mergeCell ref="A199:A210"/>
     <mergeCell ref="H77:H79"/>
     <mergeCell ref="C141:C146"/>
+    <mergeCell ref="H193:H198"/>
     <mergeCell ref="H120:H124"/>
-    <mergeCell ref="H193:H198"/>
     <mergeCell ref="H114:H119"/>
     <mergeCell ref="H89:H94"/>
     <mergeCell ref="H80:H88"/>
@@ -5873,13 +6130,13 @@
     <mergeCell ref="B64:B70"/>
     <mergeCell ref="H184:H188"/>
     <mergeCell ref="I211:I219"/>
+    <mergeCell ref="I21:I24"/>
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="B80:B88"/>
-    <mergeCell ref="I21:I24"/>
     <mergeCell ref="I141:I146"/>
+    <mergeCell ref="B250:B264"/>
     <mergeCell ref="H237:H249"/>
     <mergeCell ref="H60:H63"/>
-    <mergeCell ref="B21:B24"/>
     <mergeCell ref="B131:B135"/>
     <mergeCell ref="C114:C119"/>
     <mergeCell ref="B147:B152"/>
@@ -5887,11 +6144,11 @@
     <mergeCell ref="A104:A109"/>
     <mergeCell ref="B159:B165"/>
     <mergeCell ref="H189:H192"/>
+    <mergeCell ref="A166:A172"/>
+    <mergeCell ref="I30:I47"/>
     <mergeCell ref="B189:B192"/>
-    <mergeCell ref="A166:A172"/>
+    <mergeCell ref="C13:C16"/>
     <mergeCell ref="B77:B79"/>
-    <mergeCell ref="I30:I47"/>
-    <mergeCell ref="C13:C16"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C166:C172"/>
@@ -5912,29 +6169,31 @@
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="A184:A188"/>
     <mergeCell ref="C8:C12"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="I104:I109"/>
+    <mergeCell ref="H125:H130"/>
+    <mergeCell ref="B99:B103"/>
     <mergeCell ref="I177:I183"/>
-    <mergeCell ref="H125:H130"/>
-    <mergeCell ref="I104:I109"/>
-    <mergeCell ref="B99:B103"/>
+    <mergeCell ref="I64:I70"/>
     <mergeCell ref="C89:C94"/>
-    <mergeCell ref="I64:I70"/>
-    <mergeCell ref="I54:I59"/>
-    <mergeCell ref="C77:C79"/>
     <mergeCell ref="C104:C109"/>
     <mergeCell ref="C147:C152"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="I54:I59"/>
     <mergeCell ref="I199:I210"/>
     <mergeCell ref="H136:H140"/>
     <mergeCell ref="H21:H24"/>
     <mergeCell ref="A77:A79"/>
     <mergeCell ref="I147:I152"/>
     <mergeCell ref="A71:A76"/>
+    <mergeCell ref="H250:H264"/>
     <mergeCell ref="C71:C76"/>
     <mergeCell ref="A211:A219"/>
     <mergeCell ref="H166:H172"/>
     <mergeCell ref="I99:I103"/>
-    <mergeCell ref="I77:I79"/>
     <mergeCell ref="C17:C20"/>
     <mergeCell ref="H13:H16"/>
+    <mergeCell ref="I77:I79"/>
     <mergeCell ref="H153:H158"/>
     <mergeCell ref="B184:B188"/>
     <mergeCell ref="I173:I176"/>
@@ -6044,8 +6303,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6073,8 +6330,6 @@
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6102,8 +6357,6 @@
           <t>打开积分商城</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6131,8 +6384,6 @@
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6165,7 +6416,6 @@
           <t>顶部栏名称（只能填：课程 / 专栏 / 压铸百科）</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>专栏</t>
@@ -6193,8 +6443,6 @@
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6222,8 +6470,6 @@
           <t>点主页按钮</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6251,8 +6497,6 @@
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6280,8 +6524,6 @@
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6314,7 +6556,6 @@
           <t>课程名</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>717</t>
@@ -6347,7 +6588,6 @@
           <t>关键词</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -6380,7 +6620,6 @@
           <t>关键词</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -6408,8 +6647,6 @@
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6442,7 +6679,6 @@
           <t>词</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>压铸测试</t>
@@ -6470,8 +6706,6 @@
           <t>打开第一个热门话题</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6499,8 +6733,6 @@
           <t>打开第一个帖子</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6528,8 +6760,6 @@
           <t>打开第一张专栏</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6557,8 +6787,6 @@
           <t>打开第一个案例</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6586,8 +6814,6 @@
           <t>打开案例库介绍长图</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6620,7 +6846,6 @@
           <t>案例名</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>填充任务1</t>
@@ -6801,7 +7026,6 @@
           <t>筛选栏名称（只能填：最新提问 / 推荐 / 精选问答 / 我的关注）</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>推荐</t>
@@ -6829,8 +7053,6 @@
           <t>下拉刷新</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6863,7 +7085,6 @@
           <t>毫秒</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>2000（= 等 2 秒）</t>
@@ -6891,8 +7112,6 @@
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6925,7 +7144,6 @@
           <t>范围（只能填：全量 / 只看有文字）</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>只看有文字</t>
@@ -6958,7 +7176,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>答对最多可赢积分</t>
@@ -6991,7 +7208,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>最新提问（搜索页上不该有）</t>
@@ -7061,7 +7277,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>.search-container</t>
@@ -7094,7 +7309,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>.activity-quiz-page</t>
@@ -7127,7 +7341,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>.flow-item</t>
@@ -7160,7 +7373,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>.flow-item</t>
@@ -7299,8 +7511,6 @@
           <t>记住积分余额</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>（不用填参数；之后配一步「检查积分增加」）</t>
@@ -7333,7 +7543,6 @@
           <t>期望增加（分）</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>1021（配合上一步「记住积分余额」；少发/多发/没发都会红）</t>
@@ -7361,8 +7570,6 @@
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7390,8 +7597,6 @@
           <t>检查首页筛选栏顺序</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7419,8 +7624,6 @@
           <t>检查回到顶部按钮</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7448,8 +7651,6 @@
           <t>检查答题页</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7477,8 +7678,6 @@
           <t>检查案例库列表</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7511,7 +7710,6 @@
           <t>最多比几张（可不填）</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>3</t>
@@ -7539,8 +7737,6 @@
           <t>检查案例详情页</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7568,8 +7764,6 @@
           <t>检查案例库介绍长图</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7602,7 +7796,6 @@
           <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>课程介绍</t>
@@ -7630,8 +7823,6 @@
           <t>检查0课时课程不显示</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7664,7 +7855,6 @@
           <t>课程名</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>7.8课程new</t>
@@ -7692,8 +7882,6 @@
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7721,8 +7909,6 @@
           <t>逐题作答</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7750,8 +7936,6 @@
           <t>提交答卷</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7784,7 +7968,6 @@
           <t>活动名</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>Z-B4-答题角标</t>
@@ -7849,8 +8032,6 @@
           <t>复制当前案例</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7883,7 +8064,6 @@
           <t>分类名</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>实物商品（跟后台一字不差；跑完记得用「还原礼品分类」改回去）</t>
@@ -7916,7 +8096,6 @@
           <t>分类名</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>实物商品（跟「屏蔽礼品分类」里填的那个名字一样）</t>
@@ -9583,7 +9762,6 @@
           <t>方案一变形</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9596,7 +9774,6 @@
           <t>仅凝固</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9609,7 +9786,6 @@
           <t>仅充填2</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9622,7 +9798,6 @@
           <t>充填凝固应力</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9635,7 +9810,6 @@
           <t>充填凝固应力1</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9648,7 +9822,6 @@
           <t>7201744-孙</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9661,7 +9834,6 @@
           <t>带组织性能结果</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9674,7 +9846,6 @@
           <t>充填-排气</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9687,7 +9858,6 @@
           <t>1月 20250115</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9700,7 +9870,6 @@
           <t>紫色1</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9713,7 +9882,6 @@
           <t>内部数据6</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9726,7 +9894,6 @@
           <t>1QQ区qqqqq</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9739,7 +9906,6 @@
           <t>重力铸造-重力砂型-0602-163625-仅充填仅浏览-重力铸造-重力砂型-0602-163625</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9752,7 +9918,6 @@
           <t>重力铸造-重力砂型-0602-163625-充填凝固0602_165141-仅浏览</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9765,7 +9930,6 @@
           <t>COPY3</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9778,7 +9942,6 @@
           <t>3月26测试 私有材料分享(copy)</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9791,7 +9954,6 @@
           <t>内部数据-虚拟模具</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9804,7 +9966,6 @@
           <t>内部数据</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9817,7 +9978,6 @@
           <t>鹅鹅鹅</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9830,7 +9990,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9843,7 +10002,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9856,7 +10014,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9869,7 +10026,6 @@
           <t>仅凝固+应力-选择点2</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9882,7 +10038,6 @@
           <t>仅凝固1</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -9895,7 +10050,6 @@
           <t>循环凝固</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -9908,7 +10062,6 @@
           <t>131231</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9921,7 +10074,6 @@
           <t>131231</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9934,7 +10086,6 @@
           <t>循环凝固-热循环</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9947,7 +10098,6 @@
           <t>6668</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9960,7 +10110,6 @@
           <t>6668</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9973,7 +10122,6 @@
           <t>填充任务1</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9986,7 +10134,6 @@
           <t>0605测试</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9999,7 +10146,6 @@
           <t>循环凝固+应力+选点1</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10012,7 +10158,6 @@
           <t>料筒(copy)</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10025,7 +10170,6 @@
           <t>仅凝固</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10038,7 +10182,6 @@
           <t>#713392277</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10051,7 +10194,6 @@
           <t>？？？？</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10064,7 +10206,6 @@
           <t>复制任务失败问题测试-分享</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -10077,7 +10218,6 @@
           <t>浇口充填-高级模式</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -10090,7 +10230,6 @@
           <t>4.17</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -10103,7 +10242,6 @@
           <t>热热热热</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -10116,7 +10254,6 @@
           <t>eeee</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10129,7 +10266,6 @@
           <t>亲亲</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -10142,7 +10278,6 @@
           <t>3333 私有曲线</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10155,7 +10290,6 @@
           <t>v2</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -10168,7 +10302,6 @@
           <t>111111</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10181,7 +10314,6 @@
           <t>测试二级页面案例111111111111111111111111111</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -10194,7 +10326,6 @@
           <t>分享高压 2</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10207,7 +10338,6 @@
           <t>料筒充填</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10220,7 +10350,6 @@
           <t>料筒充填1</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10233,7 +10362,6 @@
           <t>料筒分享</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10246,7 +10374,6 @@
           <t>1WWWW</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10259,7 +10386,6 @@
           <t>凝固应力</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10272,7 +10398,6 @@
           <t>模拟汽车</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10285,7 +10410,6 @@
           <t>模拟汽车减震</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10298,7 +10422,6 @@
           <t>多浇口充填(粒子数量10)</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10306,7 +10429,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
           <t>课程那张表里的「我们账号买没买」按 user_id=1966910（config/env.yaml）判断</t>
@@ -10319,7 +10441,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
           <t>注意：这些课程名在库里有多门同名，按名字打开只会命中第一门 —— 012345678901234567890123456789、付费课程1、免费课程、免费课程1、无敌贵的课程、测试封面图、测试封面图-修改、测试验证课时bug</t>
@@ -10332,7 +10453,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
           <t>案例共 56 条，已全部列出</t>
@@ -10363,7 +10483,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -10406,7 +10525,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -10659,7 +10777,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
@@ -10688,7 +10805,6 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -10766,7 +10882,6 @@
         </is>
       </c>
     </row>
-    <row r="63"/>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1195,7 +1195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I264"/>
+  <dimension ref="A1:I269"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6010,8 +6010,102 @@
         </is>
       </c>
     </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>ZW_043</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>底部 tab 由「仿真案例库」改名为「设计专区」（需求 713556982 第 1 条）</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>手机在小程序首页；不用登录（只读）</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>1</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>需求 713556982「压铸护航和案例库整合」第 1 条：「原底部的仿真案例库名称和图案改为设计专区」。
+真机实测（2026/10/16）：底部 tab 栏（[class*="custom-tab-bar"]）的文字是「有问必答 学习中心 设计专区 我的」—— **有「设计专区」、没有「仿真案例库」**。
+第 3-4 步把这两件事分开断言：**底部 tab 栏里**要有「设计专区」、且**不能**有「仿真案例库」。
+⚠️ 注意范围：页面里**仍然有**「仿真案例库」这四个字 —— 它是案例库页**顶部**的 tab（跟「压铸护航服务」并列，见 `ZW_015` 的检查）；所以第 4 步特意把范围圈在底部 tab 栏里，整页断言「找不到仿真案例库」会是**假失败**。
+需求第 2 条（顶部两个 tab + 默认仿真案例库 + 搜索框下移成单独一行）已经并进动作「检查案例库列表」的结构检查里（`ZW_015` 第 3 步跑的就是它）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="D266" t="n">
+        <v>2</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="D267" t="n">
+        <v>3</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>检查元素数量</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>[class*="custom-tab-bar"]:has-text("设计专区")</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="D268" t="n">
+        <v>4</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>检查元素数量</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>[class*="custom-tab-bar"]:has-text("仿真案例库")</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="D269" t="n">
+        <v>5</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="200">
+  <mergeCells count="205">
     <mergeCell ref="I193:I198"/>
     <mergeCell ref="A48:A53"/>
     <mergeCell ref="I237:I249"/>
@@ -6027,6 +6121,7 @@
     <mergeCell ref="I166:I172"/>
     <mergeCell ref="A153:A158"/>
     <mergeCell ref="B30:B47"/>
+    <mergeCell ref="A265:A269"/>
     <mergeCell ref="H17:H20"/>
     <mergeCell ref="A54:A59"/>
     <mergeCell ref="C54:C59"/>
@@ -6046,15 +6141,15 @@
     <mergeCell ref="C60:C63"/>
     <mergeCell ref="C64:C70"/>
     <mergeCell ref="A147:A152"/>
+    <mergeCell ref="B95:B98"/>
     <mergeCell ref="I220:I236"/>
-    <mergeCell ref="B95:B98"/>
     <mergeCell ref="I48:I53"/>
     <mergeCell ref="I114:I119"/>
     <mergeCell ref="I60:I63"/>
     <mergeCell ref="B8:B12"/>
-    <mergeCell ref="H48:H53"/>
     <mergeCell ref="H104:H109"/>
     <mergeCell ref="A99:A103"/>
+    <mergeCell ref="H48:H53"/>
     <mergeCell ref="I25:I29"/>
     <mergeCell ref="H64:H70"/>
     <mergeCell ref="B136:B140"/>
@@ -6077,9 +6172,10 @@
     <mergeCell ref="B211:B219"/>
     <mergeCell ref="B17:B20"/>
     <mergeCell ref="C136:C140"/>
+    <mergeCell ref="I265:I269"/>
     <mergeCell ref="A21:A24"/>
+    <mergeCell ref="C21:C24"/>
     <mergeCell ref="H173:H176"/>
-    <mergeCell ref="C21:C24"/>
     <mergeCell ref="I125:I130"/>
     <mergeCell ref="A193:A198"/>
     <mergeCell ref="C193:C198"/>
@@ -6107,11 +6203,11 @@
     <mergeCell ref="I159:I165"/>
     <mergeCell ref="C120:C124"/>
     <mergeCell ref="A220:A236"/>
-    <mergeCell ref="B141:B146"/>
     <mergeCell ref="C220:C236"/>
     <mergeCell ref="C211:C219"/>
+    <mergeCell ref="B141:B146"/>
+    <mergeCell ref="A110:A113"/>
     <mergeCell ref="H4:H7"/>
-    <mergeCell ref="A110:A113"/>
     <mergeCell ref="B193:B198"/>
     <mergeCell ref="H159:H165"/>
     <mergeCell ref="A173:A176"/>
@@ -6121,8 +6217,8 @@
     <mergeCell ref="A199:A210"/>
     <mergeCell ref="H77:H79"/>
     <mergeCell ref="C141:C146"/>
+    <mergeCell ref="H120:H124"/>
     <mergeCell ref="H193:H198"/>
-    <mergeCell ref="H120:H124"/>
     <mergeCell ref="H114:H119"/>
     <mergeCell ref="H89:H94"/>
     <mergeCell ref="H80:H88"/>
@@ -6130,13 +6226,14 @@
     <mergeCell ref="B64:B70"/>
     <mergeCell ref="H184:H188"/>
     <mergeCell ref="I211:I219"/>
-    <mergeCell ref="I21:I24"/>
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="B80:B88"/>
+    <mergeCell ref="I21:I24"/>
     <mergeCell ref="I141:I146"/>
     <mergeCell ref="B250:B264"/>
     <mergeCell ref="H237:H249"/>
     <mergeCell ref="H60:H63"/>
+    <mergeCell ref="B21:B24"/>
     <mergeCell ref="B131:B135"/>
     <mergeCell ref="C114:C119"/>
     <mergeCell ref="B147:B152"/>
@@ -6144,16 +6241,17 @@
     <mergeCell ref="A104:A109"/>
     <mergeCell ref="B159:B165"/>
     <mergeCell ref="H189:H192"/>
+    <mergeCell ref="B189:B192"/>
     <mergeCell ref="A166:A172"/>
+    <mergeCell ref="B77:B79"/>
     <mergeCell ref="I30:I47"/>
-    <mergeCell ref="B189:B192"/>
     <mergeCell ref="C13:C16"/>
-    <mergeCell ref="B77:B79"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C166:C172"/>
     <mergeCell ref="H211:H219"/>
     <mergeCell ref="H25:H29"/>
+    <mergeCell ref="C265:C269"/>
     <mergeCell ref="I184:I188"/>
     <mergeCell ref="B173:B176"/>
     <mergeCell ref="C125:C130"/>
@@ -6169,33 +6267,34 @@
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="A184:A188"/>
     <mergeCell ref="C8:C12"/>
-    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="I177:I183"/>
+    <mergeCell ref="H125:H130"/>
     <mergeCell ref="I104:I109"/>
-    <mergeCell ref="H125:H130"/>
     <mergeCell ref="B99:B103"/>
-    <mergeCell ref="I177:I183"/>
+    <mergeCell ref="C89:C94"/>
     <mergeCell ref="I64:I70"/>
-    <mergeCell ref="C89:C94"/>
+    <mergeCell ref="I54:I59"/>
+    <mergeCell ref="C77:C79"/>
     <mergeCell ref="C104:C109"/>
     <mergeCell ref="C147:C152"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="I54:I59"/>
     <mergeCell ref="I199:I210"/>
     <mergeCell ref="H136:H140"/>
     <mergeCell ref="H21:H24"/>
     <mergeCell ref="A77:A79"/>
     <mergeCell ref="I147:I152"/>
+    <mergeCell ref="B265:B269"/>
     <mergeCell ref="A71:A76"/>
     <mergeCell ref="H250:H264"/>
     <mergeCell ref="C71:C76"/>
     <mergeCell ref="A211:A219"/>
     <mergeCell ref="H166:H172"/>
     <mergeCell ref="I99:I103"/>
+    <mergeCell ref="I77:I79"/>
     <mergeCell ref="C17:C20"/>
     <mergeCell ref="H13:H16"/>
-    <mergeCell ref="I77:I79"/>
     <mergeCell ref="H153:H158"/>
     <mergeCell ref="B184:B188"/>
+    <mergeCell ref="H265:H269"/>
     <mergeCell ref="I173:I176"/>
     <mergeCell ref="C110:C113"/>
     <mergeCell ref="B120:B124"/>
@@ -6303,6 +6402,8 @@
           <t>回到首页</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6330,6 +6431,8 @@
           <t>切到用户中心</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6357,6 +6460,8 @@
           <t>打开积分商城</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6384,6 +6489,8 @@
           <t>打开学习中心专栏</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6416,6 +6523,7 @@
           <t>顶部栏名称（只能填：课程 / 专栏 / 压铸百科）</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>专栏</t>
@@ -6443,6 +6551,8 @@
           <t>返回上一页</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6470,6 +6580,8 @@
           <t>点主页按钮</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6497,6 +6609,8 @@
           <t>打开搜索页</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6524,6 +6638,8 @@
           <t>打开案例库</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6556,6 +6672,7 @@
           <t>课程名</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>717</t>
@@ -6588,6 +6705,7 @@
           <t>关键词</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -6620,6 +6738,7 @@
           <t>关键词</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -6647,6 +6766,8 @@
           <t>执行搜索</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6679,6 +6800,7 @@
           <t>词</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>压铸测试</t>
@@ -6706,6 +6828,8 @@
           <t>打开第一个热门话题</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6733,6 +6857,8 @@
           <t>打开第一个帖子</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6760,6 +6886,8 @@
           <t>打开第一张专栏</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6787,6 +6915,8 @@
           <t>打开第一个案例</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6814,6 +6944,8 @@
           <t>打开案例库介绍长图</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6846,6 +6978,7 @@
           <t>案例名</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>填充任务1</t>
@@ -7026,6 +7159,7 @@
           <t>筛选栏名称（只能填：最新提问 / 推荐 / 精选问答 / 我的关注）</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>推荐</t>
@@ -7053,6 +7187,8 @@
           <t>下拉刷新</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7085,6 +7221,7 @@
           <t>毫秒</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>2000（= 等 2 秒）</t>
@@ -7112,6 +7249,8 @@
           <t>打印页面文字</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7144,6 +7283,7 @@
           <t>范围（只能填：全量 / 只看有文字）</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>只看有文字</t>
@@ -7176,6 +7316,7 @@
           <t>文字</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>答对最多可赢积分</t>
@@ -7208,6 +7349,7 @@
           <t>文字</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>最新提问（搜索页上不该有）</t>
@@ -7277,6 +7419,7 @@
           <t>选择器</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>.search-container</t>
@@ -7309,6 +7452,7 @@
           <t>选择器</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>.activity-quiz-page</t>
@@ -7341,6 +7485,7 @@
           <t>选择器</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>.flow-item</t>
@@ -7373,6 +7518,7 @@
           <t>选择器</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>.flow-item</t>
@@ -7511,6 +7657,8 @@
           <t>记住积分余额</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>（不用填参数；之后配一步「检查积分增加」）</t>
@@ -7543,6 +7691,7 @@
           <t>期望增加（分）</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>1021（配合上一步「记住积分余额」；少发/多发/没发都会红）</t>
@@ -7570,6 +7719,8 @@
           <t>检查活动入口</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7597,6 +7748,8 @@
           <t>检查首页筛选栏顺序</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7624,6 +7777,8 @@
           <t>检查回到顶部按钮</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7651,6 +7806,8 @@
           <t>检查答题页</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7678,6 +7835,8 @@
           <t>检查案例库列表</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7710,6 +7869,7 @@
           <t>最多比几张（可不填）</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>3</t>
@@ -7737,6 +7897,8 @@
           <t>检查案例详情页</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7764,6 +7926,8 @@
           <t>检查案例库介绍长图</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7796,6 +7960,7 @@
           <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>课程介绍</t>
@@ -7823,6 +7988,8 @@
           <t>检查0课时课程不显示</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7855,6 +8022,7 @@
           <t>课程名</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>7.8课程new</t>
@@ -7882,6 +8050,8 @@
           <t>打开答题活动</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7909,6 +8079,8 @@
           <t>逐题作答</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7936,6 +8108,8 @@
           <t>提交答卷</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7968,6 +8142,7 @@
           <t>活动名</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>Z-B4-答题角标</t>
@@ -8032,6 +8207,8 @@
           <t>复制当前案例</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -8064,6 +8241,7 @@
           <t>分类名</t>
         </is>
       </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>实物商品（跟后台一字不差；跑完记得用「还原礼品分类」改回去）</t>
@@ -8096,6 +8274,7 @@
           <t>分类名</t>
         </is>
       </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>实物商品（跟「屏蔽礼品分类」里填的那个名字一样）</t>
@@ -8128,7 +8307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C154"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9249,12 +9428,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>一二三四五六七八九十</t>
+          <t>Z-B6-答题角标</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>id=352</t>
+          <t>id=482</t>
         </is>
       </c>
     </row>
@@ -9266,490 +9445,378 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Z-题干图验证</t>
+          <t>Z-B5-题干四图</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>id=349</t>
+          <t>id=481</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Z-导入床</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>id=348</t>
-        </is>
-      </c>
+          <t>方案一变形</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Z-B4-答题角标</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>id=347</t>
-        </is>
-      </c>
+          <t>仅凝固</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>答题</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>id=343</t>
-        </is>
-      </c>
+          <t>仅充填2</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>M1-六选项六图</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>id=340</t>
-        </is>
-      </c>
+          <t>充填凝固应力</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>L5-待开始14题</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>id=339</t>
-        </is>
-      </c>
+          <t>充填凝固应力1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>L4-排序3题</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>id=338</t>
-        </is>
-      </c>
+          <t>7201744-孙</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>L3-导入床</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>id=337</t>
-        </is>
-      </c>
+          <t>带组织性能结果</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>L2-六选项多选</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>id=336</t>
-        </is>
-      </c>
+          <t>充填-排气</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>L1-规则200字</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>id=335</t>
-        </is>
-      </c>
+          <t>1月 20250115</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>G1-三题型带答案</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>id=316</t>
-        </is>
-      </c>
+          <t>紫色1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>F4-1000分</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>id=315</t>
-        </is>
-      </c>
+          <t>内部数据6</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>F3-十分答题</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>id=314</t>
-        </is>
-      </c>
+          <t>1QQ区qqqqq</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>F2-十分答题</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>id=313</t>
-        </is>
-      </c>
+          <t>重力铸造-重力砂型-0602-163625-仅充填仅浏览-重力铸造-重力砂型-0602-163625</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>F1-十分答题</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>id=312</t>
-        </is>
-      </c>
+          <t>重力铸造-重力砂型-0602-163625-充填凝固0602_165141-仅浏览</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>id=311</t>
-        </is>
-      </c>
+          <t>COPY3</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>000</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>id=310</t>
-        </is>
-      </c>
+          <t>3月26测试 私有材料分享(copy)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>积分上限</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>id=309</t>
-        </is>
-      </c>
+          <t>内部数据-虚拟模具</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>答题</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>id=304</t>
-        </is>
-      </c>
+          <t>内部数据</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>B6-字段全覆盖</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>id=287</t>
-        </is>
-      </c>
+          <t>鹅鹅鹅</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>B5-导入床</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>id=269</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B4-每日限开</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>id=268</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B3-15题</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>id=267</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B2-14题</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>id=266</t>
-        </is>
-      </c>
+          <t>仅凝固+应力-选择点2</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>B1-1题</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>id=265</t>
-        </is>
-      </c>
+          <t>仅凝固1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>A5-特殊字符</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>id=264</t>
-        </is>
-      </c>
+          <t>循环凝固</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>A4-不轮播</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>id=263</t>
-        </is>
-      </c>
+          <t>131231</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>A1-答题</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>id=260</t>
-        </is>
-      </c>
+          <t>131231</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>答题活动</t>
+          <t>案例</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>轮播-答题</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>id=255</t>
-        </is>
-      </c>
+          <t>循环凝固-热循环</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9759,9 +9826,10 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>方案一变形</t>
-        </is>
-      </c>
+          <t>6668</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9771,9 +9839,10 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>仅凝固</t>
-        </is>
-      </c>
+          <t>6668</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9783,9 +9852,10 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>仅充填2</t>
-        </is>
-      </c>
+          <t>填充任务1</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9795,9 +9865,10 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>充填凝固应力</t>
-        </is>
-      </c>
+          <t>0605测试</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9807,9 +9878,10 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>充填凝固应力1</t>
-        </is>
-      </c>
+          <t>循环凝固+应力+选点1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9819,9 +9891,10 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>7201744-孙</t>
-        </is>
-      </c>
+          <t>料筒(copy)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9831,9 +9904,10 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>带组织性能结果</t>
-        </is>
-      </c>
+          <t>仅凝固</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9843,9 +9917,10 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>充填-排气</t>
-        </is>
-      </c>
+          <t>#713392277</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9855,9 +9930,10 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1月 20250115</t>
-        </is>
-      </c>
+          <t>？？？？</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9867,9 +9943,10 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>紫色1</t>
-        </is>
-      </c>
+          <t>复制任务失败问题测试-分享</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9879,9 +9956,10 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>内部数据6</t>
-        </is>
-      </c>
+          <t>浇口充填-高级模式</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9891,9 +9969,10 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1QQ区qqqqq</t>
-        </is>
-      </c>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9903,9 +9982,10 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>重力铸造-重力砂型-0602-163625-仅充填仅浏览-重力铸造-重力砂型-0602-163625</t>
-        </is>
-      </c>
+          <t>热热热热</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9915,9 +9995,10 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>重力铸造-重力砂型-0602-163625-充填凝固0602_165141-仅浏览</t>
-        </is>
-      </c>
+          <t>eeee</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9927,9 +10008,10 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>COPY3</t>
-        </is>
-      </c>
+          <t>亲亲</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9939,9 +10021,10 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3月26测试 私有材料分享(copy)</t>
-        </is>
-      </c>
+          <t>3333 私有曲线</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9951,9 +10034,10 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>内部数据-虚拟模具</t>
-        </is>
-      </c>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9963,9 +10047,10 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>内部数据</t>
-        </is>
-      </c>
+          <t>111111</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9975,9 +10060,10 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>鹅鹅鹅</t>
-        </is>
-      </c>
+          <t>测试二级页面案例111111111111111111111111111</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9987,9 +10073,10 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>分享高压 2</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9999,9 +10086,10 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>料筒充填</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10011,9 +10099,10 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>料筒充填1</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10023,9 +10112,10 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>仅凝固+应力-选择点2</t>
-        </is>
-      </c>
+          <t>料筒分享</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10035,9 +10125,10 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>仅凝固1</t>
-        </is>
-      </c>
+          <t>1WWWW</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10047,9 +10138,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>循环凝固</t>
-        </is>
-      </c>
+          <t>凝固应力</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10059,9 +10151,10 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>131231</t>
-        </is>
-      </c>
+          <t>模拟汽车</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10071,9 +10164,10 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>131231</t>
-        </is>
-      </c>
+          <t>模拟汽车减震</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10083,377 +10177,45 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>循环凝固-热循环</t>
-        </is>
-      </c>
+          <t>多浇口充填(粒子数量10)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>6668</t>
+          <t>（说明）</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>课程那张表里的「我们账号买没买」按 user_id=1966910（config/env.yaml）判断</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>6668</t>
+          <t>（说明）</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>注意：这些课程名在库里有多门同名，按名字打开只会命中第一门 —— 012345678901234567890123456789、付费课程1、免费课程、免费课程1、无敌贵的课程、测试封面图、测试封面图-修改、测试验证课时bug</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>填充任务1</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>0605测试</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>循环凝固+应力+选点1</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>料筒(copy)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>仅凝固</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>#713392277</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>？？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>复制任务失败问题测试-分享</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>浇口充填-高级模式</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>热热热热</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>eeee</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>亲亲</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>3333 私有曲线</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>111111</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>测试二级页面案例111111111111111111111111111</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>分享高压 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>料筒充填</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>料筒充填1</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>料筒分享</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>1WWWW</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>凝固应力</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>模拟汽车</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>模拟汽车减震</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>案例</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>多浇口充填(粒子数量10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
           <t>（说明）</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>课程那张表里的「我们账号买没买」按 user_id=1966910（config/env.yaml）判断</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>（说明）</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>注意：这些课程名在库里有多门同名，按名字打开只会命中第一门 —— 012345678901234567890123456789、付费课程1、免费课程、免费课程1、无敌贵的课程、测试封面图、测试封面图-修改、测试验证课时bug</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>（说明）</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr">
         <is>
           <t>案例共 56 条，已全部列出</t>
         </is>
@@ -10483,6 +10245,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -10525,6 +10288,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -10777,6 +10541,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
@@ -10805,6 +10570,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -10882,6 +10648,7 @@
         </is>
       </c>
     </row>
+    <row r="63"/>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动作清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名称候选" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="用例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="动作清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="名称候选" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="填写说明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1195,7 +1195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I269"/>
+  <dimension ref="A1:I289"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5789,6 +5789,11 @@
 第 14 步用弹窗自带的关闭按钮 .reserve-popup-close 收起弹窗 —— **不是**点蒙层：实测蒙层中心被弹窗面板压着，框架会如实报「点不到：被 … 盖住了」（那是正确行为，不是 bug）。</t>
         </is>
       </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>展示文案型</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="D251" t="n">
@@ -6043,6 +6048,11 @@
 需求第 2 条（顶部两个 tab + 默认仿真案例库 + 搜索框下移成单独一行）已经并进动作「检查案例库列表」的结构检查里（`ZW_015` 第 3 步跑的就是它）。</t>
         </is>
       </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>展示文案型</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="D266" t="n">
@@ -6104,8 +6114,297 @@
         </is>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>ZW_044</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>评论为 0 时评论文案显示「参与评论获取积分」（需求 713495189）</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>手机在小程序上；不用登录（只读）。样本：首页第一条帖子、案例「亲亲」、专栏「O1-预热专栏」、课程「test2」当前评论数都是 0（2026/10/16 只读查过库）</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>1</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>需求 713495189 原文：「登录状态下，评论数为 0 时，评论区文案由『期待你的评论』改为『参与评论获取积分』；相关页面：有问必答帖子、仿真案例详情页、课程（已购用户）、专栏详情页。未购买课程用户看 0 评论课程时，文案与原状态保持一致不修改。」
+步骤分组：第 2-4 步 = 帖子详情；第 6-9 步 = 案例详情；第 11-14 步 = 专栏详情；第 16-19 步 = **未购买**课程（要求「保持不变」，所以要的是「暂无评论」、且**不能**出现新文案）。
+为什么课程挑「test2」：课程 tab「课程上新」里直接看得见它，库里 course_comment 对它 0 条、我们账号也没买过（2026/10/16 只读查过）。
+⚠️ 样本会漂：第 2 步进的是**首页第一条帖子**，第 3 步要它当前 0 评论（2026/10/16 实测是 0）。哪天第一条帖子有评论了，这一步会红 —— 那是样本变了，换一条 0 评论的帖子（或删掉这一步），不是功能坏了。
+「已购 + 0 评价」那一格（课程 717）也已经实测过，但要改数据（临时隐藏它唯一那条评论、验完还原），没法做成只读用例 —— 证据与夹具过程写在 docs/交接文档.md。源码里课程这一路的判据是 `src/packageA/pages/course/detail/index.tsx:592`：`isPurchase ? "参与评论获取积分" : "暂无评论"`；帖子/案例/专栏走的是共用组件 `src/components/comment-list/index.tsx:572`。</t>
+        </is>
+      </c>
+      <c r="I270" s="16" t="inlineStr">
+        <is>
+          <t>展示文案型</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="D271" t="n">
+        <v>2</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>打开第一个帖子</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="D272" t="n">
+        <v>3</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>参与评论获取积分</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="D273" t="n">
+        <v>4</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>检查文字不显示</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>期待你的评论</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="D274" t="n">
+        <v>5</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>点主页按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="D275" t="n">
+        <v>6</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>打开案例库</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="D276" t="n">
+        <v>7</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>打开案例</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>亲亲</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="D277" t="n">
+        <v>8</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>参与评论获取积分</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="D278" t="n">
+        <v>9</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>检查文字不显示</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>期待你的评论</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="D279" t="n">
+        <v>10</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="D280" t="n">
+        <v>11</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>打开学习中心专栏</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="D281" t="n">
+        <v>12</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>O1-预热专栏</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="D282" t="n">
+        <v>13</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>参与评论获取积分</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="D283" t="n">
+        <v>14</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>检查文字不显示</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>期待你的评论</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="D284" t="n">
+        <v>15</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="D285" t="n">
+        <v>16</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>打开课程详情</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>test2</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="D286" t="n">
+        <v>17</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>点文字</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>评价</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="D287" t="n">
+        <v>18</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>检查文字显示</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>暂无评论</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="D288" t="n">
+        <v>19</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>检查文字不显示</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>参与评论获取积分</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="D289" t="n">
+        <v>20</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>回到首页</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="205">
+  <mergeCells count="210">
     <mergeCell ref="I193:I198"/>
     <mergeCell ref="A48:A53"/>
     <mergeCell ref="I237:I249"/>
@@ -6123,6 +6422,7 @@
     <mergeCell ref="B30:B47"/>
     <mergeCell ref="A265:A269"/>
     <mergeCell ref="H17:H20"/>
+    <mergeCell ref="B270:B289"/>
     <mergeCell ref="A54:A59"/>
     <mergeCell ref="C54:C59"/>
     <mergeCell ref="A2:A3"/>
@@ -6141,15 +6441,15 @@
     <mergeCell ref="C60:C63"/>
     <mergeCell ref="C64:C70"/>
     <mergeCell ref="A147:A152"/>
+    <mergeCell ref="I220:I236"/>
     <mergeCell ref="B95:B98"/>
-    <mergeCell ref="I220:I236"/>
     <mergeCell ref="I48:I53"/>
     <mergeCell ref="I114:I119"/>
     <mergeCell ref="I60:I63"/>
     <mergeCell ref="B8:B12"/>
+    <mergeCell ref="H48:H53"/>
     <mergeCell ref="H104:H109"/>
     <mergeCell ref="A99:A103"/>
-    <mergeCell ref="H48:H53"/>
     <mergeCell ref="I25:I29"/>
     <mergeCell ref="H64:H70"/>
     <mergeCell ref="B136:B140"/>
@@ -6162,6 +6462,7 @@
     <mergeCell ref="B153:B158"/>
     <mergeCell ref="H131:H135"/>
     <mergeCell ref="H147:H152"/>
+    <mergeCell ref="C270:C289"/>
     <mergeCell ref="I95:I98"/>
     <mergeCell ref="H54:H59"/>
     <mergeCell ref="B177:B183"/>
@@ -6174,8 +6475,8 @@
     <mergeCell ref="C136:C140"/>
     <mergeCell ref="I265:I269"/>
     <mergeCell ref="A21:A24"/>
+    <mergeCell ref="H173:H176"/>
     <mergeCell ref="C21:C24"/>
-    <mergeCell ref="H173:H176"/>
     <mergeCell ref="I125:I130"/>
     <mergeCell ref="A193:A198"/>
     <mergeCell ref="C193:C198"/>
@@ -6197,17 +6498,18 @@
     <mergeCell ref="B4:B7"/>
     <mergeCell ref="B237:B249"/>
     <mergeCell ref="I153:I158"/>
+    <mergeCell ref="H270:H289"/>
     <mergeCell ref="B110:B113"/>
     <mergeCell ref="C48:C53"/>
     <mergeCell ref="C189:C192"/>
     <mergeCell ref="I159:I165"/>
     <mergeCell ref="C120:C124"/>
     <mergeCell ref="A220:A236"/>
+    <mergeCell ref="B141:B146"/>
     <mergeCell ref="C220:C236"/>
     <mergeCell ref="C211:C219"/>
-    <mergeCell ref="B141:B146"/>
+    <mergeCell ref="H4:H7"/>
     <mergeCell ref="A110:A113"/>
-    <mergeCell ref="H4:H7"/>
     <mergeCell ref="B193:B198"/>
     <mergeCell ref="H159:H165"/>
     <mergeCell ref="A173:A176"/>
@@ -6217,8 +6519,8 @@
     <mergeCell ref="A199:A210"/>
     <mergeCell ref="H77:H79"/>
     <mergeCell ref="C141:C146"/>
+    <mergeCell ref="H193:H198"/>
     <mergeCell ref="H120:H124"/>
-    <mergeCell ref="H193:H198"/>
     <mergeCell ref="H114:H119"/>
     <mergeCell ref="H89:H94"/>
     <mergeCell ref="H80:H88"/>
@@ -6226,26 +6528,26 @@
     <mergeCell ref="B64:B70"/>
     <mergeCell ref="H184:H188"/>
     <mergeCell ref="I211:I219"/>
+    <mergeCell ref="I21:I24"/>
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="B80:B88"/>
-    <mergeCell ref="I21:I24"/>
     <mergeCell ref="I141:I146"/>
     <mergeCell ref="B250:B264"/>
     <mergeCell ref="H237:H249"/>
     <mergeCell ref="H60:H63"/>
-    <mergeCell ref="B21:B24"/>
     <mergeCell ref="B131:B135"/>
     <mergeCell ref="C114:C119"/>
     <mergeCell ref="B147:B152"/>
     <mergeCell ref="C30:C47"/>
+    <mergeCell ref="A270:A289"/>
     <mergeCell ref="A104:A109"/>
     <mergeCell ref="B159:B165"/>
     <mergeCell ref="H189:H192"/>
+    <mergeCell ref="A166:A172"/>
+    <mergeCell ref="I30:I47"/>
     <mergeCell ref="B189:B192"/>
-    <mergeCell ref="A166:A172"/>
+    <mergeCell ref="C13:C16"/>
     <mergeCell ref="B77:B79"/>
-    <mergeCell ref="I30:I47"/>
-    <mergeCell ref="C13:C16"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C166:C172"/>
@@ -6267,16 +6569,17 @@
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="A184:A188"/>
     <mergeCell ref="C8:C12"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="I104:I109"/>
+    <mergeCell ref="H125:H130"/>
+    <mergeCell ref="B99:B103"/>
     <mergeCell ref="I177:I183"/>
-    <mergeCell ref="H125:H130"/>
-    <mergeCell ref="I104:I109"/>
-    <mergeCell ref="B99:B103"/>
+    <mergeCell ref="I64:I70"/>
     <mergeCell ref="C89:C94"/>
-    <mergeCell ref="I64:I70"/>
-    <mergeCell ref="I54:I59"/>
-    <mergeCell ref="C77:C79"/>
     <mergeCell ref="C104:C109"/>
     <mergeCell ref="C147:C152"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="I54:I59"/>
     <mergeCell ref="I199:I210"/>
     <mergeCell ref="H136:H140"/>
     <mergeCell ref="H21:H24"/>
@@ -6289,12 +6592,13 @@
     <mergeCell ref="A211:A219"/>
     <mergeCell ref="H166:H172"/>
     <mergeCell ref="I99:I103"/>
-    <mergeCell ref="I77:I79"/>
     <mergeCell ref="C17:C20"/>
     <mergeCell ref="H13:H16"/>
+    <mergeCell ref="I77:I79"/>
     <mergeCell ref="H153:H158"/>
     <mergeCell ref="B184:B188"/>
     <mergeCell ref="H265:H269"/>
+    <mergeCell ref="I270:I289"/>
     <mergeCell ref="I173:I176"/>
     <mergeCell ref="C110:C113"/>
     <mergeCell ref="B120:B124"/>
@@ -6402,8 +6706,6 @@
           <t>回到首页</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6431,8 +6733,6 @@
           <t>切到用户中心</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6460,8 +6760,6 @@
           <t>打开积分商城</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6489,8 +6787,6 @@
           <t>打开学习中心专栏</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6523,7 +6819,6 @@
           <t>顶部栏名称（只能填：课程 / 专栏 / 压铸百科）</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>专栏</t>
@@ -6551,8 +6846,6 @@
           <t>返回上一页</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6580,8 +6873,6 @@
           <t>点主页按钮</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6609,8 +6900,6 @@
           <t>打开搜索页</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6638,8 +6927,6 @@
           <t>打开案例库</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6672,7 +6959,6 @@
           <t>课程名</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>717</t>
@@ -6705,7 +6991,6 @@
           <t>关键词</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -6738,7 +7023,6 @@
           <t>关键词</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>test（中文也行，例如 压铸）</t>
@@ -6766,8 +7050,6 @@
           <t>执行搜索</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6800,7 +7082,6 @@
           <t>词</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>压铸测试</t>
@@ -6828,8 +7109,6 @@
           <t>打开第一个热门话题</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6857,8 +7136,6 @@
           <t>打开第一个帖子</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6886,8 +7163,6 @@
           <t>打开第一张专栏</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6915,8 +7190,6 @@
           <t>打开第一个案例</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6944,8 +7217,6 @@
           <t>打开案例库介绍长图</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -6978,7 +7249,6 @@
           <t>案例名</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>填充任务1</t>
@@ -7159,7 +7429,6 @@
           <t>筛选栏名称（只能填：最新提问 / 推荐 / 精选问答 / 我的关注）</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>推荐</t>
@@ -7187,8 +7456,6 @@
           <t>下拉刷新</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7221,7 +7488,6 @@
           <t>毫秒</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>2000（= 等 2 秒）</t>
@@ -7249,8 +7515,6 @@
           <t>打印页面文字</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7283,7 +7547,6 @@
           <t>范围（只能填：全量 / 只看有文字）</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>只看有文字</t>
@@ -7316,7 +7579,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>答对最多可赢积分</t>
@@ -7349,7 +7611,6 @@
           <t>文字</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>最新提问（搜索页上不该有）</t>
@@ -7419,7 +7680,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>.search-container</t>
@@ -7452,7 +7712,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>.activity-quiz-page</t>
@@ -7485,7 +7744,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>.flow-item</t>
@@ -7518,7 +7776,6 @@
           <t>选择器</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>.flow-item</t>
@@ -7657,8 +7914,6 @@
           <t>记住积分余额</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>（不用填参数；之后配一步「检查积分增加」）</t>
@@ -7691,7 +7946,6 @@
           <t>期望增加（分）</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>1021（配合上一步「记住积分余额」；少发/多发/没发都会红）</t>
@@ -7719,8 +7973,6 @@
           <t>检查活动入口</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7748,8 +8000,6 @@
           <t>检查首页筛选栏顺序</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7777,8 +8027,6 @@
           <t>检查回到顶部按钮</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7806,8 +8054,6 @@
           <t>检查答题页</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7835,8 +8081,6 @@
           <t>检查案例库列表</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7869,7 +8113,6 @@
           <t>最多比几张（可不填）</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>3</t>
@@ -7897,8 +8140,6 @@
           <t>检查案例详情页</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7926,8 +8167,6 @@
           <t>检查案例库介绍长图</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -7960,7 +8199,6 @@
           <t>期望选中的标签（只能填：课程介绍 / 课程目录）</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>课程介绍</t>
@@ -7988,8 +8226,6 @@
           <t>检查0课时课程不显示</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -8022,7 +8258,6 @@
           <t>课程名</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>7.8课程new</t>
@@ -8050,8 +8285,6 @@
           <t>打开答题活动</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -8079,8 +8312,6 @@
           <t>逐题作答</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -8108,8 +8339,6 @@
           <t>提交答卷</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -8142,7 +8371,6 @@
           <t>活动名</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>Z-B4-答题角标</t>
@@ -8207,8 +8435,6 @@
           <t>复制当前案例</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>（不用填参数）</t>
@@ -8241,7 +8467,6 @@
           <t>分类名</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>实物商品（跟后台一字不差；跑完记得用「还原礼品分类」改回去）</t>
@@ -8274,7 +8499,6 @@
           <t>分类名</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>实物商品（跟「屏蔽礼品分类」里填的那个名字一样）</t>
@@ -9465,7 +9689,6 @@
           <t>方案一变形</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9478,7 +9701,6 @@
           <t>仅凝固</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9491,7 +9713,6 @@
           <t>仅充填2</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9504,7 +9725,6 @@
           <t>充填凝固应力</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9517,7 +9737,6 @@
           <t>充填凝固应力1</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9530,7 +9749,6 @@
           <t>7201744-孙</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9543,7 +9761,6 @@
           <t>带组织性能结果</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9556,7 +9773,6 @@
           <t>充填-排气</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9569,7 +9785,6 @@
           <t>1月 20250115</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9582,7 +9797,6 @@
           <t>紫色1</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9595,7 +9809,6 @@
           <t>内部数据6</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9608,7 +9821,6 @@
           <t>1QQ区qqqqq</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9621,7 +9833,6 @@
           <t>重力铸造-重力砂型-0602-163625-仅充填仅浏览-重力铸造-重力砂型-0602-163625</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9634,7 +9845,6 @@
           <t>重力铸造-重力砂型-0602-163625-充填凝固0602_165141-仅浏览</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9647,7 +9857,6 @@
           <t>COPY3</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9660,7 +9869,6 @@
           <t>3月26测试 私有材料分享(copy)</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9673,7 +9881,6 @@
           <t>内部数据-虚拟模具</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9686,7 +9893,6 @@
           <t>内部数据</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9699,7 +9905,6 @@
           <t>鹅鹅鹅</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9712,7 +9917,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9725,7 +9929,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9738,7 +9941,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9751,7 +9953,6 @@
           <t>仅凝固+应力-选择点2</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9764,7 +9965,6 @@
           <t>仅凝固1</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9777,7 +9977,6 @@
           <t>循环凝固</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9790,7 +9989,6 @@
           <t>131231</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9803,7 +10001,6 @@
           <t>131231</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9816,7 +10013,6 @@
           <t>循环凝固-热循环</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9829,7 +10025,6 @@
           <t>6668</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9842,7 +10037,6 @@
           <t>6668</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9855,7 +10049,6 @@
           <t>填充任务1</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9868,7 +10061,6 @@
           <t>0605测试</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9881,7 +10073,6 @@
           <t>循环凝固+应力+选点1</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9894,7 +10085,6 @@
           <t>料筒(copy)</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9907,7 +10097,6 @@
           <t>仅凝固</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9920,7 +10109,6 @@
           <t>#713392277</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9933,7 +10121,6 @@
           <t>？？？？</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9946,7 +10133,6 @@
           <t>复制任务失败问题测试-分享</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9959,7 +10145,6 @@
           <t>浇口充填-高级模式</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9972,7 +10157,6 @@
           <t>4.17</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9985,7 +10169,6 @@
           <t>热热热热</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9998,7 +10181,6 @@
           <t>eeee</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10011,7 +10193,6 @@
           <t>亲亲</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10024,7 +10205,6 @@
           <t>3333 私有曲线</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10037,7 +10217,6 @@
           <t>v2</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10050,7 +10229,6 @@
           <t>111111</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10063,7 +10241,6 @@
           <t>测试二级页面案例111111111111111111111111111</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10076,7 +10253,6 @@
           <t>分享高压 2</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10089,7 +10265,6 @@
           <t>料筒充填</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10102,7 +10277,6 @@
           <t>料筒充填1</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10115,7 +10289,6 @@
           <t>料筒分享</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10128,7 +10301,6 @@
           <t>1WWWW</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10141,7 +10313,6 @@
           <t>凝固应力</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10154,7 +10325,6 @@
           <t>模拟汽车</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10167,7 +10337,6 @@
           <t>模拟汽车减震</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10180,7 +10349,6 @@
           <t>多浇口充填(粒子数量10)</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10188,7 +10356,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
           <t>课程那张表里的「我们账号买没买」按 user_id=1966910（config/env.yaml）判断</t>
@@ -10201,7 +10368,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
           <t>注意：这些课程名在库里有多门同名，按名字打开只会命中第一门 —— 012345678901234567890123456789、付费课程1、免费课程、免费课程1、无敌贵的课程、测试封面图、测试封面图-修改、测试验证课时bug</t>
@@ -10214,7 +10380,6 @@
           <t>（说明）</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
           <t>案例共 56 条，已全部列出</t>
@@ -10245,7 +10410,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -10288,7 +10452,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -10541,7 +10704,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
@@ -10570,7 +10732,6 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -10648,7 +10809,6 @@
         </is>
       </c>
     </row>
-    <row r="63"/>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>

--- a/cases/用例表.xlsx
+++ b/cases/用例表.xlsx
@@ -6144,7 +6144,8 @@
 步骤分组：第 2-4 步 = 帖子详情；第 6-9 步 = 案例详情；第 11-14 步 = 专栏详情；第 16-19 步 = **未购买**课程（要求「保持不变」，所以要的是「暂无评论」、且**不能**出现新文案）。
 为什么课程挑「test2」：课程 tab「课程上新」里直接看得见它，库里 course_comment 对它 0 条、我们账号也没买过（2026/10/16 只读查过）。
 ⚠️ 样本会漂：第 2 步进的是**首页第一条帖子**，第 3 步要它当前 0 评论（2026/10/16 实测是 0）。哪天第一条帖子有评论了，这一步会红 —— 那是样本变了，换一条 0 评论的帖子（或删掉这一步），不是功能坏了。
-「已购 + 0 评价」那一格（课程 717）也已经实测过，但要改数据（临时隐藏它唯一那条评论、验完还原），没法做成只读用例 —— 证据与夹具过程写在 docs/交接文档.md。源码里课程这一路的判据是 `src/packageA/pages/course/detail/index.tsx:592`：`isPurchase ? "参与评论获取积分" : "暂无评论"`；帖子/案例/专栏走的是共用组件 `src/components/comment-list/index.tsx:572`。</t>
+「已购 + 0 评价」那一格（课程 717）也已经实测过，但要改数据（临时隐藏它唯一那条评论、验完还原），没法做成只读用例 —— 证据与夹具过程写在 docs/交接文档.md。源码里课程这一路的判据是 `src/packageA/pages/course/detail/index.tsx:592`：`isPurchase ? "参与评论获取积分" : "暂无评论"`；帖子/案例/专栏走的是共用组件 `src/components/comment-list/index.tsx:572`。
+⚠️ 专栏那个样本会随活动**期次**漂：预热期 → 互动期 → 回顾期是后台按日期自动切的。**回顾期/结束 且评论数为 0 时，前端把整个评论区隐藏**（源码 column-detail 的 hideComments），第 13 步就会红 —— 那不是功能坏了，是样本过期：换一张「互动期 + 0 评论」的专栏（名字改第 12 步的参数1）。（2026/10/19 复核：O1-预热专栏 已是互动期 status=3、库里 0 条评论；案例「亲亲」0 条、课程 test2 0 条、首页最新一条帖子 0 条 —— 四个样本都还成立。）</t>
         </is>
       </c>
       <c r="I270" s="16" t="inlineStr">
